--- a/セリフ編集/キャラタイプ別/丁寧×内気.xlsx
+++ b/セリフ編集/キャラタイプ別/丁寧×内気.xlsx
@@ -301,7 +301,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H304"/>
+  <dimension ref="A1:H355"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -1639,7 +1639,7 @@
     <row r="42" ht="40" customHeight="1">
       <c r="A42" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_RESOLUTION_LINES.loser.shy.polite[1]</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES.ahead.shy.polite[1]</t>
         </is>
       </c>
       <c r="B42" t="inlineStr" s="2">
@@ -1649,12 +1649,12 @@
       </c>
       <c r="C42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BITTER_RESOLUTION_LINES</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES</t>
         </is>
       </c>
       <c r="D42" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.shy.polite[1]</t>
+          <t xml:space="preserve">ahead.shy.polite[1]</t>
         </is>
       </c>
       <c r="E42" t="inlineStr" s="2">
@@ -1664,14 +1664,14 @@
       </c>
       <c r="F42" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ま、負けました…悔しいです…でも、これ以上恨んだりはしません…</t>
+          <t xml:space="preserve">勝たせて…いただきました。…なのに、怖いままです…</t>
         </is>
       </c>
     </row>
     <row r="43" ht="40" customHeight="1">
       <c r="A43" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_RESOLUTION_LINES.winner.shy.polite[1]</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES.behind.shy.polite[1]</t>
         </is>
       </c>
       <c r="B43" t="inlineStr" s="2">
@@ -1681,12 +1681,12 @@
       </c>
       <c r="C43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BITTER_RESOLUTION_LINES</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES</t>
         </is>
       </c>
       <c r="D43" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.shy.polite[1]</t>
+          <t xml:space="preserve">behind.shy.polite[1]</t>
         </is>
       </c>
       <c r="E43" t="inlineStr" s="2">
@@ -1696,14 +1696,14 @@
       </c>
       <c r="F43" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝てました…でも、もう…これで終わりにしませんか…？</t>
+          <t xml:space="preserve">…もう終わったって…言われました。…言われただけです…</t>
         </is>
       </c>
     </row>
     <row r="44" ht="40" customHeight="1">
       <c r="A44" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.loser.shy.polite[1]</t>
+          <t xml:space="preserve">BITTER_RESOLUTION_LINES.loser.shy.polite[1]</t>
         </is>
       </c>
       <c r="B44" t="inlineStr" s="2">
@@ -1713,7 +1713,7 @@
       </c>
       <c r="C44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES</t>
+          <t xml:space="preserve">BITTER_RESOLUTION_LINES</t>
         </is>
       </c>
       <c r="D44" t="inlineStr" s="12">
@@ -1728,14 +1728,14 @@
       </c>
       <c r="F44" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ま、負けました…でも、あの方となら、後悔はありません…</t>
+          <t xml:space="preserve">ま、負けました…悔しいです…でも、これ以上恨んだりはしません…</t>
         </is>
       </c>
     </row>
     <row r="45" ht="40" customHeight="1">
       <c r="A45" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.winner.shy.polite[1]</t>
+          <t xml:space="preserve">BITTER_RESOLUTION_LINES.winner.shy.polite[1]</t>
         </is>
       </c>
       <c r="B45" t="inlineStr" s="2">
@@ -1745,7 +1745,7 @@
       </c>
       <c r="C45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES</t>
+          <t xml:space="preserve">BITTER_RESOLUTION_LINES</t>
         </is>
       </c>
       <c r="D45" t="inlineStr" s="12">
@@ -1760,14 +1760,14 @@
       </c>
       <c r="F45" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">か、勝たせていただきました…でも、あの方も素晴らしかったです…</t>
+          <t xml:space="preserve">勝てました…でも、もう…これで終わりにしませんか…？</t>
         </is>
       </c>
     </row>
     <row r="46" ht="40" customHeight="1">
       <c r="A46" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.attacker.shy.polite[1]</t>
+          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.loser.shy.polite[1]</t>
         </is>
       </c>
       <c r="B46" t="inlineStr" s="2">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="C46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70</t>
+          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES</t>
         </is>
       </c>
       <c r="D46" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.shy.polite[1]</t>
+          <t xml:space="preserve">loser.shy.polite[1]</t>
         </is>
       </c>
       <c r="E46" t="inlineStr" s="2">
@@ -1792,14 +1792,14 @@
       </c>
       <c r="F46" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、あの…そろそろ、決着を…</t>
+          <t xml:space="preserve">ま、負けました…でも、あの方となら、後悔はありません…</t>
         </is>
       </c>
     </row>
     <row r="47" ht="40" customHeight="1">
       <c r="A47" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.defender.shy.polite[1]</t>
+          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.winner.shy.polite[1]</t>
         </is>
       </c>
       <c r="B47" t="inlineStr" s="2">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="C47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70</t>
+          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES</t>
         </is>
       </c>
       <c r="D47" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.shy.polite[1]</t>
+          <t xml:space="preserve">winner.shy.polite[1]</t>
         </is>
       </c>
       <c r="E47" t="inlineStr" s="2">
@@ -1824,14 +1824,14 @@
       </c>
       <c r="F47" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">は、はい…お受けします…</t>
+          <t xml:space="preserve">か、勝たせていただきました…でも、あの方も素晴らしかったです…</t>
         </is>
       </c>
     </row>
     <row r="48" ht="40" customHeight="1">
       <c r="A48" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.attacker.shy.polite[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.attacker.shy.polite[1]</t>
         </is>
       </c>
       <c r="B48" t="inlineStr" s="2">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="C48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70</t>
         </is>
       </c>
       <c r="D48" t="inlineStr" s="12">
@@ -1856,14 +1856,14 @@
       </c>
       <c r="F48" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………ずっと、待っておりました…この日を…</t>
+          <t xml:space="preserve">あ、あの…そろそろ、決着を…</t>
         </is>
       </c>
     </row>
     <row r="49" ht="40" customHeight="1">
       <c r="A49" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.defender.shy.polite[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.defender.shy.polite[1]</t>
         </is>
       </c>
       <c r="B49" t="inlineStr" s="2">
@@ -1873,7 +1873,7 @@
       </c>
       <c r="C49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70</t>
         </is>
       </c>
       <c r="D49" t="inlineStr" s="12">
@@ -1888,14 +1888,14 @@
       </c>
       <c r="F49" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………はい…受けて、立ちます…</t>
+          <t xml:space="preserve">は、はい…お受けします…</t>
         </is>
       </c>
     </row>
     <row r="50" ht="40" customHeight="1">
       <c r="A50" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.attacker.shy.polite[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.attacker.shy.polite[1]</t>
         </is>
       </c>
       <c r="B50" t="inlineStr" s="2">
@@ -1905,7 +1905,7 @@
       </c>
       <c r="C50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90</t>
         </is>
       </c>
       <c r="D50" t="inlineStr" s="12">
@@ -1920,14 +1920,14 @@
       </c>
       <c r="F50" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、あの…決着を、つけさせてください…</t>
+          <t xml:space="preserve">………ずっと、待っておりました…この日を…</t>
         </is>
       </c>
     </row>
     <row r="51" ht="40" customHeight="1">
       <c r="A51" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.defender.shy.polite[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.defender.shy.polite[1]</t>
         </is>
       </c>
       <c r="B51" t="inlineStr" s="2">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="C51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90</t>
         </is>
       </c>
       <c r="D51" t="inlineStr" s="12">
@@ -1952,14 +1952,14 @@
       </c>
       <c r="F51" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">は、はい…受けて立ちます…</t>
+          <t xml:space="preserve">………はい…受けて、立ちます…</t>
         </is>
       </c>
     </row>
     <row r="52" ht="40" customHeight="1">
       <c r="A52" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateAttacker.shy.polite[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.attacker.shy.polite[1]</t>
         </is>
       </c>
       <c r="B52" t="inlineStr" s="2">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="D52" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateAttacker.shy.polite[1]</t>
+          <t xml:space="preserve">attacker.shy.polite[1]</t>
         </is>
       </c>
       <c r="E52" t="inlineStr" s="2">
@@ -1984,14 +1984,14 @@
       </c>
       <c r="F52" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、あなたは…わたしの、運命の相手です…さあ、行きましょう…</t>
+          <t xml:space="preserve">あ、あの…決着を、つけさせてください…</t>
         </is>
       </c>
     </row>
     <row r="53" ht="40" customHeight="1">
       <c r="A53" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateDefender.shy.polite[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.defender.shy.polite[1]</t>
         </is>
       </c>
       <c r="B53" t="inlineStr" s="2">
@@ -2006,7 +2006,7 @@
       </c>
       <c r="D53" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateDefender.shy.polite[1]</t>
+          <t xml:space="preserve">defender.shy.polite[1]</t>
         </is>
       </c>
       <c r="E53" t="inlineStr" s="2">
@@ -2016,14 +2016,14 @@
       </c>
       <c r="F53" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">運命なら…受けて立たないと、いけませんね…</t>
+          <t xml:space="preserve">は、はい…受けて立ちます…</t>
         </is>
       </c>
     </row>
     <row r="54" ht="40" customHeight="1">
       <c r="A54" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateLoser.shy.polite[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateAttacker.shy.polite[1]</t>
         </is>
       </c>
       <c r="B54" t="inlineStr" s="2">
@@ -2033,12 +2033,12 @@
       </c>
       <c r="C54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES</t>
         </is>
       </c>
       <c r="D54" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateLoser.shy.polite[1]</t>
+          <t xml:space="preserve">fateAttacker.shy.polite[1]</t>
         </is>
       </c>
       <c r="E54" t="inlineStr" s="2">
@@ -2048,14 +2048,14 @@
       </c>
       <c r="F54" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">運命の戦いに…ま、負けました…でも、悔いは、ないです…</t>
+          <t xml:space="preserve">あ、あなたは…わたしの、運命の相手です…さあ、行きましょう…</t>
         </is>
       </c>
     </row>
     <row r="55" ht="40" customHeight="1">
       <c r="A55" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateWinner.shy.polite[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateDefender.shy.polite[1]</t>
         </is>
       </c>
       <c r="B55" t="inlineStr" s="2">
@@ -2065,12 +2065,12 @@
       </c>
       <c r="C55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES</t>
         </is>
       </c>
       <c r="D55" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateWinner.shy.polite[1]</t>
+          <t xml:space="preserve">fateDefender.shy.polite[1]</t>
         </is>
       </c>
       <c r="E55" t="inlineStr" s="2">
@@ -2080,14 +2080,14 @@
       </c>
       <c r="F55" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">運命の戦いに…か、勝ちました…</t>
+          <t xml:space="preserve">運命なら…受けて立たないと、いけませんね…</t>
         </is>
       </c>
     </row>
     <row r="56" ht="40" customHeight="1">
       <c r="A56" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.loser.shy.polite[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateLoser.shy.polite[1]</t>
         </is>
       </c>
       <c r="B56" t="inlineStr" s="2">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="D56" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.shy.polite[1]</t>
+          <t xml:space="preserve">fateLoser.shy.polite[1]</t>
         </is>
       </c>
       <c r="E56" t="inlineStr" s="2">
@@ -2112,14 +2112,14 @@
       </c>
       <c r="F56" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ま、負けました…これで、終わりですね…</t>
+          <t xml:space="preserve">運命の戦いに…ま、負けました…でも、悔いは、ないです…</t>
         </is>
       </c>
     </row>
     <row r="57" ht="40" customHeight="1">
       <c r="A57" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.winner.shy.polite[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateWinner.shy.polite[1]</t>
         </is>
       </c>
       <c r="B57" t="inlineStr" s="2">
@@ -2134,7 +2134,7 @@
       </c>
       <c r="D57" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.shy.polite[1]</t>
+          <t xml:space="preserve">fateWinner.shy.polite[1]</t>
         </is>
       </c>
       <c r="E57" t="inlineStr" s="2">
@@ -2144,14 +2144,14 @@
       </c>
       <c r="F57" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">か、勝てました…これで、終わりにしましょう…</t>
+          <t xml:space="preserve">運命の戦いに…か、勝ちました…</t>
         </is>
       </c>
     </row>
     <row r="58" ht="40" customHeight="1">
       <c r="A58" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES.loserLines.shy.polite[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.loser.shy.polite[1]</t>
         </is>
       </c>
       <c r="B58" t="inlineStr" s="2">
@@ -2161,12 +2161,12 @@
       </c>
       <c r="C58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES</t>
         </is>
       </c>
       <c r="D58" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loserLines.shy.polite[1]</t>
+          <t xml:space="preserve">loser.shy.polite[1]</t>
         </is>
       </c>
       <c r="E58" t="inlineStr" s="2">
@@ -2176,14 +2176,14 @@
       </c>
       <c r="F58" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ま、まさか負けるなんて…く、悔しいです…</t>
+          <t xml:space="preserve">ま、負けました…これで、終わりですね…</t>
         </is>
       </c>
     </row>
     <row r="59" ht="40" customHeight="1">
       <c r="A59" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES.winnerLines.shy.polite[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.winner.shy.polite[1]</t>
         </is>
       </c>
       <c r="B59" t="inlineStr" s="2">
@@ -2193,12 +2193,12 @@
       </c>
       <c r="C59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES</t>
         </is>
       </c>
       <c r="D59" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winnerLines.shy.polite[1]</t>
+          <t xml:space="preserve">winner.shy.polite[1]</t>
         </is>
       </c>
       <c r="E59" t="inlineStr" s="2">
@@ -2208,14 +2208,14 @@
       </c>
       <c r="F59" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">か、勝てるなんて…思っていませんでした…</t>
+          <t xml:space="preserve">か、勝てました…これで、終わりにしましょう…</t>
         </is>
       </c>
     </row>
     <row r="60" ht="40" customHeight="1">
       <c r="A60" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.polite_shy.lose[1]</t>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES.loserLines.shy.polite[1]</t>
         </is>
       </c>
       <c r="B60" t="inlineStr" s="2">
@@ -2225,29 +2225,29 @@
       </c>
       <c r="C60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES</t>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES</t>
         </is>
       </c>
       <c r="D60" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite_shy.lose[1]</t>
+          <t xml:space="preserve">loserLines.shy.polite[1]</t>
         </is>
       </c>
       <c r="E60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">03 因縁・絆(Bond/Rivalry)イベント</t>
         </is>
       </c>
       <c r="F60" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの……負けて、しまいました。すみません。</t>
+          <t xml:space="preserve">ま、まさか負けるなんて…く、悔しいです…</t>
         </is>
       </c>
     </row>
     <row r="61" ht="40" customHeight="1">
       <c r="A61" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.polite_shy.lose[2]</t>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES.winnerLines.shy.polite[1]</t>
         </is>
       </c>
       <c r="B61" t="inlineStr" s="2">
@@ -2257,29 +2257,29 @@
       </c>
       <c r="C61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES</t>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES</t>
         </is>
       </c>
       <c r="D61" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite_shy.lose[2]</t>
+          <t xml:space="preserve">winnerLines.shy.polite[1]</t>
         </is>
       </c>
       <c r="E61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">03 因縁・絆(Bond/Rivalry)イベント</t>
         </is>
       </c>
       <c r="F61" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わがままを言ったのに……申し訳ありません。</t>
+          <t xml:space="preserve">か、勝てるなんて…思っていませんでした…</t>
         </is>
       </c>
     </row>
     <row r="62" ht="40" customHeight="1">
       <c r="A62" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.polite_shy.lose[3]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.polite_shy.lose[1]</t>
         </is>
       </c>
       <c r="B62" t="inlineStr" s="2">
@@ -2294,7 +2294,7 @@
       </c>
       <c r="D62" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite_shy.lose[3]</t>
+          <t xml:space="preserve">polite_shy.lose[1]</t>
         </is>
       </c>
       <c r="E62" t="inlineStr" s="2">
@@ -2304,14 +2304,14 @@
       </c>
       <c r="F62" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝てませんでした。……顔向けできないです。</t>
+          <t xml:space="preserve">あの……負けて、しまいました。すみません。</t>
         </is>
       </c>
     </row>
     <row r="63" ht="40" customHeight="1">
       <c r="A63" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.polite_shy.petition[1]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.polite_shy.lose[2]</t>
         </is>
       </c>
       <c r="B63" t="inlineStr" s="2">
@@ -2326,7 +2326,7 @@
       </c>
       <c r="D63" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite_shy.petition[1]</t>
+          <t xml:space="preserve">polite_shy.lose[2]</t>
         </is>
       </c>
       <c r="E63" t="inlineStr" s="2">
@@ -2336,14 +2336,14 @@
       </c>
       <c r="F63" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの……社長。あの方と、やらせていただけませんか。</t>
+          <t xml:space="preserve">わがままを言ったのに……申し訳ありません。</t>
         </is>
       </c>
     </row>
     <row r="64" ht="40" customHeight="1">
       <c r="A64" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.polite_shy.petition[2]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.polite_shy.lose[3]</t>
         </is>
       </c>
       <c r="B64" t="inlineStr" s="2">
@@ -2358,7 +2358,7 @@
       </c>
       <c r="D64" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite_shy.petition[2]</t>
+          <t xml:space="preserve">polite_shy.lose[3]</t>
         </is>
       </c>
       <c r="E64" t="inlineStr" s="2">
@@ -2368,14 +2368,14 @@
       </c>
       <c r="F64" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">言いにくいのですが……どうしても、あの方と。</t>
+          <t xml:space="preserve">勝てませんでした。……顔向けできないです。</t>
         </is>
       </c>
     </row>
     <row r="65" ht="40" customHeight="1">
       <c r="A65" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.polite_shy.petition[3]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.polite_shy.petition[1]</t>
         </is>
       </c>
       <c r="B65" t="inlineStr" s="2">
@@ -2390,7 +2390,7 @@
       </c>
       <c r="D65" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite_shy.petition[3]</t>
+          <t xml:space="preserve">polite_shy.petition[1]</t>
         </is>
       </c>
       <c r="E65" t="inlineStr" s="2">
@@ -2400,14 +2400,14 @@
       </c>
       <c r="F65" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">すみません、わがままです。それでも、お願いしたくて。</t>
+          <t xml:space="preserve">あの……社長。あの方と、やらせていただけませんか。</t>
         </is>
       </c>
     </row>
     <row r="66" ht="40" customHeight="1">
       <c r="A66" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.polite_shy.sendoff[1]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.polite_shy.petition[2]</t>
         </is>
       </c>
       <c r="B66" t="inlineStr" s="2">
@@ -2422,7 +2422,7 @@
       </c>
       <c r="D66" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite_shy.sendoff[1]</t>
+          <t xml:space="preserve">polite_shy.petition[2]</t>
         </is>
       </c>
       <c r="E66" t="inlineStr" s="2">
@@ -2432,14 +2432,14 @@
       </c>
       <c r="F66" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ……ありがとうございます。行って、きます。</t>
+          <t xml:space="preserve">言いにくいのですが……どうしても、あの方と。</t>
         </is>
       </c>
     </row>
     <row r="67" ht="40" customHeight="1">
       <c r="A67" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.polite_shy.sendoff[2]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.polite_shy.petition[3]</t>
         </is>
       </c>
       <c r="B67" t="inlineStr" s="2">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="D67" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite_shy.sendoff[2]</t>
+          <t xml:space="preserve">polite_shy.petition[3]</t>
         </is>
       </c>
       <c r="E67" t="inlineStr" s="2">
@@ -2464,14 +2464,14 @@
       </c>
       <c r="F67" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よろしいのですか……。ありがとうございます。</t>
+          <t xml:space="preserve">すみません、わがままです。それでも、お願いしたくて。</t>
         </is>
       </c>
     </row>
     <row r="68" ht="40" customHeight="1">
       <c r="A68" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.polite_shy.sendoff[3]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.polite_shy.sendoff[1]</t>
         </is>
       </c>
       <c r="B68" t="inlineStr" s="2">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="D68" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite_shy.sendoff[3]</t>
+          <t xml:space="preserve">polite_shy.sendoff[1]</t>
         </is>
       </c>
       <c r="E68" t="inlineStr" s="2">
@@ -2496,14 +2496,14 @@
       </c>
       <c r="F68" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">すみません、ありがとうございます。頑張ります。</t>
+          <t xml:space="preserve">あ……ありがとうございます。行って、きます。</t>
         </is>
       </c>
     </row>
     <row r="69" ht="40" customHeight="1">
       <c r="A69" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.polite_shy.win[1]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.polite_shy.sendoff[2]</t>
         </is>
       </c>
       <c r="B69" t="inlineStr" s="2">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="D69" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite_shy.win[1]</t>
+          <t xml:space="preserve">polite_shy.sendoff[2]</t>
         </is>
       </c>
       <c r="E69" t="inlineStr" s="2">
@@ -2528,14 +2528,14 @@
       </c>
       <c r="F69" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの……勝てました。ありがとうございました。</t>
+          <t xml:space="preserve">よろしいのですか……。ありがとうございます。</t>
         </is>
       </c>
     </row>
     <row r="70" ht="40" customHeight="1">
       <c r="A70" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.polite_shy.win[2]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.polite_shy.sendoff[3]</t>
         </is>
       </c>
       <c r="B70" t="inlineStr" s="2">
@@ -2550,7 +2550,7 @@
       </c>
       <c r="D70" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite_shy.win[2]</t>
+          <t xml:space="preserve">polite_shy.sendoff[3]</t>
         </is>
       </c>
       <c r="E70" t="inlineStr" s="2">
@@ -2560,14 +2560,14 @@
       </c>
       <c r="F70" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝ちました。……信じてくださって、嬉しかったです。</t>
+          <t xml:space="preserve">すみません、ありがとうございます。頑張ります。</t>
         </is>
       </c>
     </row>
     <row r="71" ht="40" customHeight="1">
       <c r="A71" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.polite_shy.win[3]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.polite_shy.win[1]</t>
         </is>
       </c>
       <c r="B71" t="inlineStr" s="2">
@@ -2582,7 +2582,7 @@
       </c>
       <c r="D71" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite_shy.win[3]</t>
+          <t xml:space="preserve">polite_shy.win[1]</t>
         </is>
       </c>
       <c r="E71" t="inlineStr" s="2">
@@ -2592,14 +2592,14 @@
       </c>
       <c r="F71" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたし、勝てたんですね……。ありがとうございます。</t>
+          <t xml:space="preserve">あの……勝てました。ありがとうございました。</t>
         </is>
       </c>
     </row>
     <row r="72" ht="40" customHeight="1">
       <c r="A72" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.polite_shy._accept[1]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.polite_shy.win[2]</t>
         </is>
       </c>
       <c r="B72" t="inlineStr" s="2">
@@ -2609,12 +2609,12 @@
       </c>
       <c r="C72" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+          <t xml:space="preserve">CHALLENGE_LINES</t>
         </is>
       </c>
       <c r="D72" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite_shy._accept[1]</t>
+          <t xml:space="preserve">polite_shy.win[2]</t>
         </is>
       </c>
       <c r="E72" t="inlineStr" s="2">
@@ -2624,14 +2624,14 @@
       </c>
       <c r="F72" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">え……わたしで、いいんですか。</t>
+          <t xml:space="preserve">勝ちました。……信じてくださって、嬉しかったです。</t>
         </is>
       </c>
     </row>
     <row r="73" ht="40" customHeight="1">
       <c r="A73" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.polite_shy._accept[2]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.polite_shy.win[3]</t>
         </is>
       </c>
       <c r="B73" t="inlineStr" s="2">
@@ -2641,12 +2641,12 @@
       </c>
       <c r="C73" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+          <t xml:space="preserve">CHALLENGE_LINES</t>
         </is>
       </c>
       <c r="D73" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite_shy._accept[2]</t>
+          <t xml:space="preserve">polite_shy.win[3]</t>
         </is>
       </c>
       <c r="E73" t="inlineStr" s="2">
@@ -2656,14 +2656,14 @@
       </c>
       <c r="F73" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの……お受けします。自信は、ないですけど。</t>
+          <t xml:space="preserve">わたし、勝てたんですね……。ありがとうございます。</t>
         </is>
       </c>
     </row>
     <row r="74" ht="40" customHeight="1">
       <c r="A74" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.polite_shy._accept[3]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.polite_shy._accept[1]</t>
         </is>
       </c>
       <c r="B74" t="inlineStr" s="2">
@@ -2678,7 +2678,7 @@
       </c>
       <c r="D74" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite_shy._accept[3]</t>
+          <t xml:space="preserve">polite_shy._accept[1]</t>
         </is>
       </c>
       <c r="E74" t="inlineStr" s="2">
@@ -2688,14 +2688,14 @@
       </c>
       <c r="F74" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">名指し、されるとは思わなくて……。でも、逃げません。</t>
+          <t xml:space="preserve">え……わたしで、いいんですか。</t>
         </is>
       </c>
     </row>
     <row r="75" ht="40" customHeight="1">
       <c r="A75" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.polite_shy.draw[1]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.polite_shy._accept[2]</t>
         </is>
       </c>
       <c r="B75" t="inlineStr" s="2">
@@ -2710,7 +2710,7 @@
       </c>
       <c r="D75" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite_shy.draw[1]</t>
+          <t xml:space="preserve">polite_shy._accept[2]</t>
         </is>
       </c>
       <c r="E75" t="inlineStr" s="2">
@@ -2720,14 +2720,14 @@
       </c>
       <c r="F75" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">引き分け……。よかったのか、悪かったのか。</t>
+          <t xml:space="preserve">あの……お受けします。自信は、ないですけど。</t>
         </is>
       </c>
     </row>
     <row r="76" ht="40" customHeight="1">
       <c r="A76" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.polite_shy.draw[2]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.polite_shy._accept[3]</t>
         </is>
       </c>
       <c r="B76" t="inlineStr" s="2">
@@ -2742,7 +2742,7 @@
       </c>
       <c r="D76" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite_shy.draw[2]</t>
+          <t xml:space="preserve">polite_shy._accept[3]</t>
         </is>
       </c>
       <c r="E76" t="inlineStr" s="2">
@@ -2752,14 +2752,14 @@
       </c>
       <c r="F76" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">決着、つかなかったですね……。少し、ほっとしてます。</t>
+          <t xml:space="preserve">名指し、されるとは思わなくて……。でも、逃げません。</t>
         </is>
       </c>
     </row>
     <row r="77" ht="40" customHeight="1">
       <c r="A77" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.polite_shy.draw[3]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.polite_shy.draw[1]</t>
         </is>
       </c>
       <c r="B77" t="inlineStr" s="2">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="D77" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite_shy.draw[3]</t>
+          <t xml:space="preserve">polite_shy.draw[1]</t>
         </is>
       </c>
       <c r="E77" t="inlineStr" s="2">
@@ -2784,14 +2784,14 @@
       </c>
       <c r="F77" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの……もう一度、やりますか。今度は、ちゃんと。</t>
+          <t xml:space="preserve">決着つかず……。よかったのか、悪かったのか。</t>
         </is>
       </c>
     </row>
     <row r="78" ht="40" customHeight="1">
       <c r="A78" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.polite_shy.lose[1]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.polite_shy.draw[2]</t>
         </is>
       </c>
       <c r="B78" t="inlineStr" s="2">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="D78" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite_shy.lose[1]</t>
+          <t xml:space="preserve">polite_shy.draw[2]</t>
         </is>
       </c>
       <c r="E78" t="inlineStr" s="2">
@@ -2816,14 +2816,14 @@
       </c>
       <c r="F78" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やっぱり……わたしじゃ、だめでしたね。</t>
+          <t xml:space="preserve">決着、つかなかったですね……。少し、ほっとしてます。</t>
         </is>
       </c>
     </row>
     <row r="79" ht="40" customHeight="1">
       <c r="A79" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.polite_shy.lose[2]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.polite_shy.draw[3]</t>
         </is>
       </c>
       <c r="B79" t="inlineStr" s="2">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="D79" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite_shy.lose[2]</t>
+          <t xml:space="preserve">polite_shy.draw[3]</t>
         </is>
       </c>
       <c r="E79" t="inlineStr" s="2">
@@ -2848,14 +2848,14 @@
       </c>
       <c r="F79" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……強かったです。何も、できませんでした。</t>
+          <t xml:space="preserve">あの……もう一度、やりますか。今度は、ちゃんと。</t>
         </is>
       </c>
     </row>
     <row r="80" ht="40" customHeight="1">
       <c r="A80" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.polite_shy.lose[3]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.polite_shy.lose[1]</t>
         </is>
       </c>
       <c r="B80" t="inlineStr" s="2">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="D80" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite_shy.lose[3]</t>
+          <t xml:space="preserve">polite_shy.lose[1]</t>
         </is>
       </c>
       <c r="E80" t="inlineStr" s="2">
@@ -2880,14 +2880,14 @@
       </c>
       <c r="F80" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ごめんなさい……。がっかり、させてしまいましたよね。</t>
+          <t xml:space="preserve">やっぱり……わたしじゃ、だめでしたね。</t>
         </is>
       </c>
     </row>
     <row r="81" ht="40" customHeight="1">
       <c r="A81" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.polite_shy.win[1]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.polite_shy.lose[2]</t>
         </is>
       </c>
       <c r="B81" t="inlineStr" s="2">
@@ -2902,7 +2902,7 @@
       </c>
       <c r="D81" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite_shy.win[1]</t>
+          <t xml:space="preserve">polite_shy.lose[2]</t>
         </is>
       </c>
       <c r="E81" t="inlineStr" s="2">
@@ -2912,14 +2912,14 @@
       </c>
       <c r="F81" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの……勝てちゃいました。すみません。</t>
+          <t xml:space="preserve">……強かったです。何も、できませんでした。</t>
         </is>
       </c>
     </row>
     <row r="82" ht="40" customHeight="1">
       <c r="A82" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.polite_shy.win[2]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.polite_shy.lose[3]</t>
         </is>
       </c>
       <c r="B82" t="inlineStr" s="2">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="D82" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite_shy.win[2]</t>
+          <t xml:space="preserve">polite_shy.lose[3]</t>
         </is>
       </c>
       <c r="E82" t="inlineStr" s="2">
@@ -2944,14 +2944,14 @@
       </c>
       <c r="F82" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝ったんですよね、わたし……。実感がなくて。</t>
+          <t xml:space="preserve">ごめんなさい……。がっかり、させてしまいましたよね。</t>
         </is>
       </c>
     </row>
     <row r="83" ht="40" customHeight="1">
       <c r="A83" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.polite_shy.win[3]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.polite_shy.win[1]</t>
         </is>
       </c>
       <c r="B83" t="inlineStr" s="2">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="D83" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite_shy.win[3]</t>
+          <t xml:space="preserve">polite_shy.win[1]</t>
         </is>
       </c>
       <c r="E83" t="inlineStr" s="2">
@@ -2976,14 +2976,14 @@
       </c>
       <c r="F83" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたしを選んで、後悔してませんか……。</t>
+          <t xml:space="preserve">あの……勝てちゃいました。すみません。</t>
         </is>
       </c>
     </row>
     <row r="84" ht="40" customHeight="1">
       <c r="A84" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.shy.polite[1]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.polite_shy.win[2]</t>
         </is>
       </c>
       <c r="B84" t="inlineStr" s="2">
@@ -2993,29 +2993,29 @@
       </c>
       <c r="C84" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
         </is>
       </c>
       <c r="D84" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accepted.shy.polite[1]</t>
+          <t xml:space="preserve">polite_shy.win[2]</t>
         </is>
       </c>
       <c r="E84" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
         </is>
       </c>
       <c r="F84" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ご、ごめんなさい…っ。お世話になりました…</t>
+          <t xml:space="preserve">勝ったんですよね、わたし……。実感がなくて。</t>
         </is>
       </c>
     </row>
     <row r="85" ht="40" customHeight="1">
       <c r="A85" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.shy.polite[1]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.polite_shy.win[3]</t>
         </is>
       </c>
       <c r="B85" t="inlineStr" s="2">
@@ -3025,29 +3025,29 @@
       </c>
       <c r="C85" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
         </is>
       </c>
       <c r="D85" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defended.shy.polite[1]</t>
+          <t xml:space="preserve">polite_shy.win[3]</t>
         </is>
       </c>
       <c r="E85" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
         </is>
       </c>
       <c r="F85" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ほ、本当に…いいんですか…？ ありがとうございます…!</t>
+          <t xml:space="preserve">わたしを選んで、後悔してませんか……。</t>
         </is>
       </c>
     </row>
     <row r="86" ht="40" customHeight="1">
       <c r="A86" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.shy.polite[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.shy.polite[1]</t>
         </is>
       </c>
       <c r="B86" t="inlineStr" s="2">
@@ -3062,7 +3062,7 @@
       </c>
       <c r="D86" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defense_failed.shy.polite[1]</t>
+          <t xml:space="preserve">accepted.shy.polite[1]</t>
         </is>
       </c>
       <c r="E86" t="inlineStr" s="2">
@@ -3072,14 +3072,14 @@
       </c>
       <c r="F86" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ごめんなさい…どうしても、行かなきゃいけないんです…</t>
+          <t xml:space="preserve">ご、ごめんなさい…っ。お世話になりました…</t>
         </is>
       </c>
     </row>
     <row r="87" ht="40" customHeight="1">
       <c r="A87" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.default.shy.polite[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.shy.polite[1]</t>
         </is>
       </c>
       <c r="B87" t="inlineStr" s="2">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="C87" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETAIN_LINES</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D87" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">default.shy.polite[1]</t>
+          <t xml:space="preserve">defended.shy.polite[1]</t>
         </is>
       </c>
       <c r="E87" t="inlineStr" s="2">
@@ -3104,14 +3104,14 @@
       </c>
       <c r="F87" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こ、ここに残ってもよろしいですか…？</t>
+          <t xml:space="preserve">ほ、本当に…いいんですか…？ ありがとうございます…!</t>
         </is>
       </c>
     </row>
     <row r="88" ht="40" customHeight="1">
       <c r="A88" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.former_champ.shy.polite[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.shy.polite[1]</t>
         </is>
       </c>
       <c r="B88" t="inlineStr" s="2">
@@ -3121,12 +3121,12 @@
       </c>
       <c r="C88" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETAIN_LINES</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D88" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">former_champ.shy.polite[1]</t>
+          <t xml:space="preserve">defense_failed.shy.polite[1]</t>
         </is>
       </c>
       <c r="E88" t="inlineStr" s="2">
@@ -3136,14 +3136,14 @@
       </c>
       <c r="F88" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">チャ、チャンピオンだったわたしが…ここに残っても、いいんでしょうか…</t>
+          <t xml:space="preserve">…ごめんなさい…どうしても、行かなきゃいけないんです…</t>
         </is>
       </c>
     </row>
     <row r="89" ht="40" customHeight="1">
       <c r="A89" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.heel.shy.polite[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.default.shy.polite[1]</t>
         </is>
       </c>
       <c r="B89" t="inlineStr" s="2">
@@ -3158,7 +3158,7 @@
       </c>
       <c r="D89" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heel.shy.polite[1]</t>
+          <t xml:space="preserve">default.shy.polite[1]</t>
         </is>
       </c>
       <c r="E89" t="inlineStr" s="2">
@@ -3168,14 +3168,14 @@
       </c>
       <c r="F89" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こ、こんなわたしでも…置いていただけるんですか…？</t>
+          <t xml:space="preserve">こ、ここに残ってもよろしいですか…？</t>
         </is>
       </c>
     </row>
     <row r="90" ht="40" customHeight="1">
       <c r="A90" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.high_trust.shy.polite[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.former_champ.shy.polite[1]</t>
         </is>
       </c>
       <c r="B90" t="inlineStr" s="2">
@@ -3190,7 +3190,7 @@
       </c>
       <c r="D90" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">high_trust.shy.polite[1]</t>
+          <t xml:space="preserve">former_champ.shy.polite[1]</t>
         </is>
       </c>
       <c r="E90" t="inlineStr" s="2">
@@ -3200,14 +3200,14 @@
       </c>
       <c r="F90" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、あの…ずっと、ここにいたいんです…お願いします…</t>
+          <t xml:space="preserve">チャ、チャンピオンだったわたしが…ここに残っても、いいんでしょうか…</t>
         </is>
       </c>
     </row>
     <row r="91" ht="40" customHeight="1">
       <c r="A91" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_former_champ.shy.polite[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.heel.shy.polite[1]</t>
         </is>
       </c>
       <c r="B91" t="inlineStr" s="2">
@@ -3217,12 +3217,12 @@
       </c>
       <c r="C91" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
+          <t xml:space="preserve">RETAIN_LINES</t>
         </is>
       </c>
       <c r="D91" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_former_champ.shy.polite[1]</t>
+          <t xml:space="preserve">heel.shy.polite[1]</t>
         </is>
       </c>
       <c r="E91" t="inlineStr" s="2">
@@ -3232,14 +3232,14 @@
       </c>
       <c r="F91" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">は、はい…チャンピオンになれただけで…幸せでした…</t>
+          <t xml:space="preserve">こ、こんなわたしでも…置いていただけるんですか…？</t>
         </is>
       </c>
     </row>
     <row r="92" ht="40" customHeight="1">
       <c r="A92" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_heel.shy.polite[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.high_trust.shy.polite[1]</t>
         </is>
       </c>
       <c r="B92" t="inlineStr" s="2">
@@ -3249,12 +3249,12 @@
       </c>
       <c r="C92" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
+          <t xml:space="preserve">RETAIN_LINES</t>
         </is>
       </c>
       <c r="D92" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_heel.shy.polite[1]</t>
+          <t xml:space="preserve">high_trust.shy.polite[1]</t>
         </is>
       </c>
       <c r="E92" t="inlineStr" s="2">
@@ -3264,14 +3264,14 @@
       </c>
       <c r="F92" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こ、こんなわたしでも…受け入れてくださって、ありがとうございました…</t>
+          <t xml:space="preserve">あ、あの…ずっと、ここにいたいんです…お願いします…</t>
         </is>
       </c>
     </row>
     <row r="93" ht="40" customHeight="1">
       <c r="A93" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_no_title.shy.polite[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_former_champ.shy.polite[1]</t>
         </is>
       </c>
       <c r="B93" t="inlineStr" s="2">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="D93" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_no_title.shy.polite[1]</t>
+          <t xml:space="preserve">accept_former_champ.shy.polite[1]</t>
         </is>
       </c>
       <c r="E93" t="inlineStr" s="2">
@@ -3296,14 +3296,14 @@
       </c>
       <c r="F93" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">は、はい…ベルトには届きませんでしたが…ここまでで、十分です…</t>
+          <t xml:space="preserve">は、はい…チャンピオンになれただけで…幸せでした…</t>
         </is>
       </c>
     </row>
     <row r="94" ht="40" customHeight="1">
       <c r="A94" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_terminal.shy.polite[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_heel.shy.polite[1]</t>
         </is>
       </c>
       <c r="B94" t="inlineStr" s="2">
@@ -3318,7 +3318,7 @@
       </c>
       <c r="D94" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_terminal.shy.polite[1]</t>
+          <t xml:space="preserve">accept_heel.shy.polite[1]</t>
         </is>
       </c>
       <c r="E94" t="inlineStr" s="2">
@@ -3328,14 +3328,14 @@
       </c>
       <c r="F94" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こ、これ以上は…続けられません…ご、ごめんなさい…</t>
+          <t xml:space="preserve">こ、こんなわたしでも…受け入れてくださって、ありがとうございました…</t>
         </is>
       </c>
     </row>
     <row r="95" ht="40" customHeight="1">
       <c r="A95" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_winless.shy.polite[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_no_title.shy.polite[1]</t>
         </is>
       </c>
       <c r="B95" t="inlineStr" s="2">
@@ -3350,7 +3350,7 @@
       </c>
       <c r="D95" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_winless.shy.polite[1]</t>
+          <t xml:space="preserve">accept_no_title.shy.polite[1]</t>
         </is>
       </c>
       <c r="E95" t="inlineStr" s="2">
@@ -3360,14 +3360,14 @@
       </c>
       <c r="F95" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ほ、ほとんど勝てませんでした…でも、戦えた日々が宝物です…</t>
+          <t xml:space="preserve">は、はい…ベルトには届きませんでしたが…ここまでで、十分です…</t>
         </is>
       </c>
     </row>
     <row r="96" ht="40" customHeight="1">
       <c r="A96" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_champ.shy.polite[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_terminal.shy.polite[1]</t>
         </is>
       </c>
       <c r="B96" t="inlineStr" s="2">
@@ -3377,12 +3377,12 @@
       </c>
       <c r="C96" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
         </is>
       </c>
       <c r="D96" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_champ.shy.polite[1]</t>
+          <t xml:space="preserve">accept_terminal.shy.polite[1]</t>
         </is>
       </c>
       <c r="E96" t="inlineStr" s="2">
@@ -3392,14 +3392,14 @@
       </c>
       <c r="F96" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">い、いえ…まだ、チャンピオンですから…続けさせてください…</t>
+          <t xml:space="preserve">こ、これ以上は…続けられません…ご、ごめんなさい…</t>
         </is>
       </c>
     </row>
     <row r="97" ht="40" customHeight="1">
       <c r="A97" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_distrust.shy.polite[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_winless.shy.polite[1]</t>
         </is>
       </c>
       <c r="B97" t="inlineStr" s="2">
@@ -3409,12 +3409,12 @@
       </c>
       <c r="C97" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
         </is>
       </c>
       <c r="D97" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_distrust.shy.polite[1]</t>
+          <t xml:space="preserve">accept_winless.shy.polite[1]</t>
         </is>
       </c>
       <c r="E97" t="inlineStr" s="2">
@@ -3424,14 +3424,14 @@
       </c>
       <c r="F97" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、あの…どうして、そんなことを言うんですか…悲しいです…</t>
+          <t xml:space="preserve">ほ、ほとんど勝てませんでした…でも、戦えた日々が宝物です…</t>
         </is>
       </c>
     </row>
     <row r="98" ht="40" customHeight="1">
       <c r="A98" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_fighting.shy.polite[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_champ.shy.polite[1]</t>
         </is>
       </c>
       <c r="B98" t="inlineStr" s="2">
@@ -3446,7 +3446,7 @@
       </c>
       <c r="D98" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_fighting.shy.polite[1]</t>
+          <t xml:space="preserve">refuse_champ.shy.polite[1]</t>
         </is>
       </c>
       <c r="E98" t="inlineStr" s="2">
@@ -3456,14 +3456,14 @@
       </c>
       <c r="F98" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ま、まだ、戦えます…もう少しだけ、お願いします…</t>
+          <t xml:space="preserve">い、いえ…まだ、チャンピオンですから…続けさせてください…</t>
         </is>
       </c>
     </row>
     <row r="99" ht="40" customHeight="1">
       <c r="A99" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_heel.shy.polite[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_distrust.shy.polite[1]</t>
         </is>
       </c>
       <c r="B99" t="inlineStr" s="2">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="D99" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_heel.shy.polite[1]</t>
+          <t xml:space="preserve">refuse_distrust.shy.polite[1]</t>
         </is>
       </c>
       <c r="E99" t="inlineStr" s="2">
@@ -3488,14 +3488,14 @@
       </c>
       <c r="F99" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こ、こんなわたしですけど…まだ、リングにいたいんです…</t>
+          <t xml:space="preserve">あ、あの…どうして、そんなことを言うんですか…悲しいです…</t>
         </is>
       </c>
     </row>
     <row r="100" ht="40" customHeight="1">
       <c r="A100" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A1_champion.shy.polite[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_fighting.shy.polite[1]</t>
         </is>
       </c>
       <c r="B100" t="inlineStr" s="2">
@@ -3505,12 +3505,12 @@
       </c>
       <c r="C100" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES</t>
         </is>
       </c>
       <c r="D100" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A1_champion.shy.polite[1]</t>
+          <t xml:space="preserve">refuse_fighting.shy.polite[1]</t>
         </is>
       </c>
       <c r="E100" t="inlineStr" s="2">
@@ -3520,14 +3520,14 @@
       </c>
       <c r="F100" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">チ、チャンピオンとして…リングを去る決断をしました…あ、ありがとうございました…</t>
+          <t xml:space="preserve">ま、まだ、戦えます…もう少しだけ、お願いします…</t>
         </is>
       </c>
     </row>
     <row r="101" ht="40" customHeight="1">
       <c r="A101" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A2_uncrowned.shy.polite[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_heel.shy.polite[1]</t>
         </is>
       </c>
       <c r="B101" t="inlineStr" s="2">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="C101" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES</t>
         </is>
       </c>
       <c r="D101" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A2_uncrowned.shy.polite[1]</t>
+          <t xml:space="preserve">refuse_heel.shy.polite[1]</t>
         </is>
       </c>
       <c r="E101" t="inlineStr" s="2">
@@ -3552,14 +3552,14 @@
       </c>
       <c r="F101" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ベルトには…手が届きませんでした…でも、悔いは、ないんです…</t>
+          <t xml:space="preserve">こ、こんなわたしですけど…まだ、リングにいたいんです…</t>
         </is>
       </c>
     </row>
     <row r="102" ht="40" customHeight="1">
       <c r="A102" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A3_heel.shy.polite[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A1_champion.shy.polite[1]</t>
         </is>
       </c>
       <c r="B102" t="inlineStr" s="2">
@@ -3574,7 +3574,7 @@
       </c>
       <c r="D102" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A3_heel.shy.polite[1]</t>
+          <t xml:space="preserve">A1_champion.shy.polite[1]</t>
         </is>
       </c>
       <c r="E102" t="inlineStr" s="2">
@@ -3584,14 +3584,14 @@
       </c>
       <c r="F102" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こ、こんなわたしでしたが…リングを、去ります…</t>
+          <t xml:space="preserve">チ、チャンピオンとして…リングを去る決断をしました…あ、ありがとうございました…</t>
         </is>
       </c>
     </row>
     <row r="103" ht="40" customHeight="1">
       <c r="A103" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A4_veteran.shy.polite[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A2_uncrowned.shy.polite[1]</t>
         </is>
       </c>
       <c r="B103" t="inlineStr" s="2">
@@ -3606,7 +3606,7 @@
       </c>
       <c r="D103" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A4_veteran.shy.polite[1]</t>
+          <t xml:space="preserve">A2_uncrowned.shy.polite[1]</t>
         </is>
       </c>
       <c r="E103" t="inlineStr" s="2">
@@ -3616,14 +3616,14 @@
       </c>
       <c r="F103" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">な、長い間…ありがとうございました…これで、引退させていただきます…</t>
+          <t xml:space="preserve">ベルトには…手が届きませんでした…でも、悔いは、ないんです…</t>
         </is>
       </c>
     </row>
     <row r="104" ht="40" customHeight="1">
       <c r="A104" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B1_young.shy.polite[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A3_heel.shy.polite[1]</t>
         </is>
       </c>
       <c r="B104" t="inlineStr" s="2">
@@ -3638,7 +3638,7 @@
       </c>
       <c r="D104" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1_young.shy.polite[1]</t>
+          <t xml:space="preserve">A3_heel.shy.polite[1]</t>
         </is>
       </c>
       <c r="E104" t="inlineStr" s="2">
@@ -3648,14 +3648,14 @@
       </c>
       <c r="F104" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ま、まだ若いのに…ご、ごめんなさい…続けられないんです…</t>
+          <t xml:space="preserve">こ、こんなわたしでしたが…リングを、去ります…</t>
         </is>
       </c>
     </row>
     <row r="105" ht="40" customHeight="1">
       <c r="A105" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B2_prime.shy.polite[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A4_veteran.shy.polite[1]</t>
         </is>
       </c>
       <c r="B105" t="inlineStr" s="2">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="D105" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_prime.shy.polite[1]</t>
+          <t xml:space="preserve">A4_veteran.shy.polite[1]</t>
         </is>
       </c>
       <c r="E105" t="inlineStr" s="2">
@@ -3680,14 +3680,14 @@
       </c>
       <c r="F105" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今が、一番の時期かもしれませんが…決めたんです…</t>
+          <t xml:space="preserve">な、長い間…ありがとうございました…これで、引退させていただきます…</t>
         </is>
       </c>
     </row>
     <row r="106" ht="40" customHeight="1">
       <c r="A106" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B3_older.shy.polite[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B1_young.shy.polite[1]</t>
         </is>
       </c>
       <c r="B106" t="inlineStr" s="2">
@@ -3702,7 +3702,7 @@
       </c>
       <c r="D106" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B3_older.shy.polite[1]</t>
+          <t xml:space="preserve">B1_young.shy.polite[1]</t>
         </is>
       </c>
       <c r="E106" t="inlineStr" s="2">
@@ -3712,14 +3712,14 @@
       </c>
       <c r="F106" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">も、もう…体が、ついていきません…ごめんなさい…</t>
+          <t xml:space="preserve">ま、まだ若いのに…ご、ごめんなさい…続けられないんです…</t>
         </is>
       </c>
     </row>
     <row r="107" ht="40" customHeight="1">
       <c r="A107" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B4_champion_injury.shy.polite[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B2_prime.shy.polite[1]</t>
         </is>
       </c>
       <c r="B107" t="inlineStr" s="2">
@@ -3734,7 +3734,7 @@
       </c>
       <c r="D107" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_champion_injury.shy.polite[1]</t>
+          <t xml:space="preserve">B2_prime.shy.polite[1]</t>
         </is>
       </c>
       <c r="E107" t="inlineStr" s="2">
@@ -3744,14 +3744,14 @@
       </c>
       <c r="F107" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">チャンピオンなのに…け、怪我で…ご、ごめんなさい…</t>
+          <t xml:space="preserve">今が、一番の時期かもしれませんが…決めたんです…</t>
         </is>
       </c>
     </row>
     <row r="108" ht="40" customHeight="1">
       <c r="A108" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VOLUNTARY_STAY_LINES.shy.polite[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B3_older.shy.polite[1]</t>
         </is>
       </c>
       <c r="B108" t="inlineStr" s="2">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="C108" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">VOLUNTARY_STAY_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D108" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">shy.polite[1]</t>
+          <t xml:space="preserve">B3_older.shy.polite[1]</t>
         </is>
       </c>
       <c r="E108" t="inlineStr" s="2">
@@ -3776,14 +3776,14 @@
       </c>
       <c r="F108" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、あの…残らせていただけますか…ここが、好きで…</t>
+          <t xml:space="preserve">も、もう…体が、ついていきません…ごめんなさい…</t>
         </is>
       </c>
     </row>
     <row r="109" ht="40" customHeight="1">
       <c r="A109" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.shy.polite[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B4_champion_injury.shy.polite[1]</t>
         </is>
       </c>
       <c r="B109" t="inlineStr" s="2">
@@ -3793,29 +3793,29 @@
       </c>
       <c r="C109" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D109" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_accept.shy.polite[1]</t>
+          <t xml:space="preserve">B4_champion_injury.shy.polite[1]</t>
         </is>
       </c>
       <c r="E109" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">06 契約交渉</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F109" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こ、こんな良いお話…あ、ありがとうございます…精一杯頑張ります…</t>
+          <t xml:space="preserve">チャンピオンなのに…け、怪我で…ご、ごめんなさい…</t>
         </is>
       </c>
     </row>
     <row r="110" ht="40" customHeight="1">
       <c r="A110" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.shy.polite[1]</t>
+          <t xml:space="preserve">VOLUNTARY_STAY_LINES.shy.polite[1]</t>
         </is>
       </c>
       <c r="B110" t="inlineStr" s="2">
@@ -3825,29 +3825,29 @@
       </c>
       <c r="C110" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+          <t xml:space="preserve">VOLUNTARY_STAY_LINES</t>
         </is>
       </c>
       <c r="D110" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_accept.shy.polite[1]</t>
+          <t xml:space="preserve">shy.polite[1]</t>
         </is>
       </c>
       <c r="E110" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">06 契約交渉</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F110" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">は、はい…その条件で…お受けします…</t>
+          <t xml:space="preserve">あ、あの…残らせていただけますか…ここが、好きで…</t>
         </is>
       </c>
     </row>
     <row r="111" ht="40" customHeight="1">
       <c r="A111" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.shy.polite[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.shy.polite[1]</t>
         </is>
       </c>
       <c r="B111" t="inlineStr" s="2">
@@ -3862,7 +3862,7 @@
       </c>
       <c r="D111" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_refuse.shy.polite[1]</t>
+          <t xml:space="preserve">raise_accept.shy.polite[1]</t>
         </is>
       </c>
       <c r="E111" t="inlineStr" s="2">
@@ -3872,14 +3872,14 @@
       </c>
       <c r="F111" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">考えさせていただいたんですが…やっぱり、難しいです…</t>
+          <t xml:space="preserve">こ、こんな良いお話…あ、ありがとうございます…精一杯頑張ります…</t>
         </is>
       </c>
     </row>
     <row r="112" ht="40" customHeight="1">
       <c r="A112" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.shy.polite[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.shy.polite[1]</t>
         </is>
       </c>
       <c r="B112" t="inlineStr" s="2">
@@ -3894,7 +3894,7 @@
       </c>
       <c r="D112" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_open.shy.polite[1]</t>
+          <t xml:space="preserve">raise_negotiate_accept.shy.polite[1]</t>
         </is>
       </c>
       <c r="E112" t="inlineStr" s="2">
@@ -3904,14 +3904,14 @@
       </c>
       <c r="F112" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、あの…契約のことで、お話があるんです…</t>
+          <t xml:space="preserve">は、はい…その条件で…お受けします…</t>
         </is>
       </c>
     </row>
     <row r="113" ht="40" customHeight="1">
       <c r="A113" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.shy.polite[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.shy.polite[1]</t>
         </is>
       </c>
       <c r="B113" t="inlineStr" s="2">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="D113" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_refuse.shy.polite[1]</t>
+          <t xml:space="preserve">raise_negotiate_refuse.shy.polite[1]</t>
         </is>
       </c>
       <c r="E113" t="inlineStr" s="2">
@@ -3936,14 +3936,14 @@
       </c>
       <c r="F113" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">すみません…この条件では、ちょっと…</t>
+          <t xml:space="preserve">考えさせていただいたんですが…やっぱり、難しいです…</t>
         </is>
       </c>
     </row>
     <row r="114" ht="40" customHeight="1">
       <c r="A114" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.shy.polite[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.shy.polite[1]</t>
         </is>
       </c>
       <c r="B114" t="inlineStr" s="2">
@@ -3958,7 +3958,7 @@
       </c>
       <c r="D114" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_listen.shy.polite[1]</t>
+          <t xml:space="preserve">raise_open.shy.polite[1]</t>
         </is>
       </c>
       <c r="E114" t="inlineStr" s="2">
@@ -3968,14 +3968,14 @@
       </c>
       <c r="F114" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お、お話だけは…聞かせていただきます…</t>
+          <t xml:space="preserve">あ、あの…契約のことで、お話があるんです…</t>
         </is>
       </c>
     </row>
     <row r="115" ht="40" customHeight="1">
       <c r="A115" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.shy.polite[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.shy.polite[1]</t>
         </is>
       </c>
       <c r="B115" t="inlineStr" s="2">
@@ -3990,7 +3990,7 @@
       </c>
       <c r="D115" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_open.shy.polite[1]</t>
+          <t xml:space="preserve">raise_refuse.shy.polite[1]</t>
         </is>
       </c>
       <c r="E115" t="inlineStr" s="2">
@@ -4000,14 +4000,14 @@
       </c>
       <c r="F115" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、あの…他の団体からも、お話をいただいていて…</t>
+          <t xml:space="preserve">すみません…この条件では、ちょっと…</t>
         </is>
       </c>
     </row>
     <row r="116" ht="40" customHeight="1">
       <c r="A116" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.shy.polite[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.shy.polite[1]</t>
         </is>
       </c>
       <c r="B116" t="inlineStr" s="2">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="D116" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_release.shy.polite[1]</t>
+          <t xml:space="preserve">sudden_departure.shy.polite[1]</t>
         </is>
       </c>
       <c r="E116" t="inlineStr" s="2">
@@ -4032,14 +4032,14 @@
       </c>
       <c r="F116" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、あの…移籍させてください…お、お世話になりました…</t>
+          <t xml:space="preserve">……あの、辞め……辞めさせていただけますか……。もう、無理なんです……。</t>
         </is>
       </c>
     </row>
     <row r="117" ht="40" customHeight="1">
       <c r="A117" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.shy.polite[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.shy.polite[2]</t>
         </is>
       </c>
       <c r="B117" t="inlineStr" s="2">
@@ -4054,7 +4054,7 @@
       </c>
       <c r="D117" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_fail.shy.polite[1]</t>
+          <t xml:space="preserve">sudden_departure.shy.polite[2]</t>
         </is>
       </c>
       <c r="E117" t="inlineStr" s="2">
@@ -4064,14 +4064,14 @@
       </c>
       <c r="F117" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ご、ごめんなさい…やっぱり、行かせてください…</t>
+          <t xml:space="preserve">……申し訳ありません。もう、ここには居られません……。</t>
         </is>
       </c>
     </row>
     <row r="118" ht="40" customHeight="1">
       <c r="A118" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.shy.polite[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.shy.polite[1]</t>
         </is>
       </c>
       <c r="B118" t="inlineStr" s="2">
@@ -4086,7 +4086,7 @@
       </c>
       <c r="D118" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_success.shy.polite[1]</t>
+          <t xml:space="preserve">transfer_listen.shy.polite[1]</t>
         </is>
       </c>
       <c r="E118" t="inlineStr" s="2">
@@ -4096,14 +4096,14 @@
       </c>
       <c r="F118" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こ、ここに残ります…引き止めてくださって、ありがとうございます…</t>
+          <t xml:space="preserve">お、お話だけは…聞かせていただきます…</t>
         </is>
       </c>
     </row>
     <row r="119" ht="40" customHeight="1">
       <c r="A119" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.blocked.shy.polite[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.shy.polite[1]</t>
         </is>
       </c>
       <c r="B119" t="inlineStr" s="2">
@@ -4113,12 +4113,12 @@
       </c>
       <c r="C119" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D119" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">blocked.shy.polite[1]</t>
+          <t xml:space="preserve">transfer_open.shy.polite[1]</t>
         </is>
       </c>
       <c r="E119" t="inlineStr" s="2">
@@ -4128,14 +4128,14 @@
       </c>
       <c r="F119" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、あの…この件は、お話できません…</t>
+          <t xml:space="preserve">あ、あの…他の団体からも、お話をいただいていて…</t>
         </is>
       </c>
     </row>
     <row r="120" ht="40" customHeight="1">
       <c r="A120" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.fail.shy.polite[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.shy.polite[1]</t>
         </is>
       </c>
       <c r="B120" t="inlineStr" s="2">
@@ -4145,12 +4145,12 @@
       </c>
       <c r="C120" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D120" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fail.shy.polite[1]</t>
+          <t xml:space="preserve">transfer_release.shy.polite[1]</t>
         </is>
       </c>
       <c r="E120" t="inlineStr" s="2">
@@ -4160,14 +4160,14 @@
       </c>
       <c r="F120" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">す、すみません…今回は、難しいです…</t>
+          <t xml:space="preserve">あ、あの…移籍させてください…お、お世話になりました…</t>
         </is>
       </c>
     </row>
     <row r="121" ht="40" customHeight="1">
       <c r="A121" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.start.shy.polite[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.shy.polite[1]</t>
         </is>
       </c>
       <c r="B121" t="inlineStr" s="2">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="C121" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D121" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">start.shy.polite[1]</t>
+          <t xml:space="preserve">transfer_retain_fail.shy.polite[1]</t>
         </is>
       </c>
       <c r="E121" t="inlineStr" s="2">
@@ -4192,14 +4192,14 @@
       </c>
       <c r="F121" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、あの…交渉、始めさせていただきます…</t>
+          <t xml:space="preserve">ご、ごめんなさい…やっぱり、行かせてください…</t>
         </is>
       </c>
     </row>
     <row r="122" ht="40" customHeight="1">
       <c r="A122" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.success.shy.polite[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.shy.polite[1]</t>
         </is>
       </c>
       <c r="B122" t="inlineStr" s="2">
@@ -4209,12 +4209,12 @@
       </c>
       <c r="C122" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D122" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">success.shy.polite[1]</t>
+          <t xml:space="preserve">transfer_retain_success.shy.polite[1]</t>
         </is>
       </c>
       <c r="E122" t="inlineStr" s="2">
@@ -4224,14 +4224,14 @@
       </c>
       <c r="F122" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こ、こちらでお願いします…ありがとうございます…</t>
+          <t xml:space="preserve">こ、ここに残ります…引き止めてくださって、ありがとうございます…</t>
         </is>
       </c>
     </row>
     <row r="123" ht="40" customHeight="1">
       <c r="A123" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_ABSTRACT.polite.shy[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.blocked.shy.polite[1]</t>
         </is>
       </c>
       <c r="B123" t="inlineStr" s="2">
@@ -4241,29 +4241,29 @@
       </c>
       <c r="C123" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">F07_LINES</t>
+          <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
       <c r="D123" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">leaderDemand.DEMAND_ABSTRACT.polite.shy[1]</t>
+          <t xml:space="preserve">blocked.shy.polite[1]</t>
         </is>
       </c>
       <c r="E123" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F123" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…社長、あの…私たちのメンバーのこと、気にかけていただけると…嬉しいです。</t>
+          <t xml:space="preserve">あ、あの…この件は、お話できません…</t>
         </is>
       </c>
     </row>
     <row r="124" ht="40" customHeight="1">
       <c r="A124" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MAIN.polite.shy[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.fail.shy.polite[1]</t>
         </is>
       </c>
       <c r="B124" t="inlineStr" s="2">
@@ -4273,29 +4273,29 @@
       </c>
       <c r="C124" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">F07_LINES</t>
+          <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
       <c r="D124" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">leaderDemand.DEMAND_MAIN.polite.shy[1]</t>
+          <t xml:space="preserve">fail.shy.polite[1]</t>
         </is>
       </c>
       <c r="E124" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F124" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…社長、あの…次のメイン、私たちに…お任せいただけたら、嬉しいです。</t>
+          <t xml:space="preserve">す、すみません…今回は、難しいです…</t>
         </is>
       </c>
     </row>
     <row r="125" ht="40" customHeight="1">
       <c r="A125" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MONEY.polite.shy[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.start.shy.polite[1]</t>
         </is>
       </c>
       <c r="B125" t="inlineStr" s="2">
@@ -4305,29 +4305,29 @@
       </c>
       <c r="C125" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">F07_LINES</t>
+          <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
       <c r="D125" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">leaderDemand.DEMAND_MONEY.polite.shy[1]</t>
+          <t xml:space="preserve">start.shy.polite[1]</t>
         </is>
       </c>
       <c r="E125" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F125" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…社長、あの…待遇のこと、少しだけお話、させていただけませんか。</t>
+          <t xml:space="preserve">あ、あの…交渉、始めさせていただきます…</t>
         </is>
       </c>
     </row>
     <row r="126" ht="40" customHeight="1">
       <c r="A126" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_RECOGNITION.polite.shy[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.success.shy.polite[1]</t>
         </is>
       </c>
       <c r="B126" t="inlineStr" s="2">
@@ -4337,29 +4337,29 @@
       </c>
       <c r="C126" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">F07_LINES</t>
+          <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
       <c r="D126" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">leaderDemand.DEMAND_RECOGNITION.polite.shy[1]</t>
+          <t xml:space="preserve">success.shy.polite[1]</t>
         </is>
       </c>
       <c r="E126" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F126" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…社長、あの…私たちのこと、見ていてくださると…うれしいです。</t>
+          <t xml:space="preserve">こ、こちらでお願いします…ありがとうございます…</t>
         </is>
       </c>
     </row>
     <row r="127" ht="40" customHeight="1">
       <c r="A127" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.A.polite.shy[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_ABSTRACT.polite.shy[1]</t>
         </is>
       </c>
       <c r="B127" t="inlineStr" s="2">
@@ -4374,7 +4374,7 @@
       </c>
       <c r="D127" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.A.polite.shy[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_ABSTRACT.polite.shy[1]</t>
         </is>
       </c>
       <c r="E127" t="inlineStr" s="2">
@@ -4384,14 +4384,14 @@
       </c>
       <c r="F127" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…あの、ありがとうございます。…嬉しい、です。</t>
+          <t xml:space="preserve">…社長、あの…私たちのメンバーのこと、気にかけていただけると…嬉しいです。</t>
         </is>
       </c>
     </row>
     <row r="128" ht="40" customHeight="1">
       <c r="A128" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.B.polite.shy[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MAIN.polite.shy[1]</t>
         </is>
       </c>
       <c r="B128" t="inlineStr" s="2">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="D128" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.B.polite.shy[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_MAIN.polite.shy[1]</t>
         </is>
       </c>
       <c r="E128" t="inlineStr" s="2">
@@ -4416,14 +4416,14 @@
       </c>
       <c r="F128" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…はい…ごめんなさい。</t>
+          <t xml:space="preserve">…社長、あの…次のメイン、私たちに…お任せいただけたら、嬉しいです。</t>
         </is>
       </c>
     </row>
     <row r="129" ht="40" customHeight="1">
       <c r="A129" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.C.polite.shy[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MONEY.polite.shy[1]</t>
         </is>
       </c>
       <c r="B129" t="inlineStr" s="2">
@@ -4438,7 +4438,7 @@
       </c>
       <c r="D129" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.C.polite.shy[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_MONEY.polite.shy[1]</t>
         </is>
       </c>
       <c r="E129" t="inlineStr" s="2">
@@ -4448,14 +4448,14 @@
       </c>
       <c r="F129" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…あの、ありがとうございます。…嬉しいです。</t>
+          <t xml:space="preserve">…社長、あの…待遇のこと、少しだけお話、させていただけませんか。</t>
         </is>
       </c>
     </row>
     <row r="130" ht="40" customHeight="1">
       <c r="A130" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.A.polite.shy[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_RECOGNITION.polite.shy[1]</t>
         </is>
       </c>
       <c r="B130" t="inlineStr" s="2">
@@ -4470,7 +4470,7 @@
       </c>
       <c r="D130" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MAIN.A.polite.shy[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_RECOGNITION.polite.shy[1]</t>
         </is>
       </c>
       <c r="E130" t="inlineStr" s="2">
@@ -4480,14 +4480,14 @@
       </c>
       <c r="F130" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…あの、ありがとうございます。…精一杯、がんばります。</t>
+          <t xml:space="preserve">…社長、あの…私たちのこと、見ていてくださると…うれしいです。</t>
         </is>
       </c>
     </row>
     <row r="131" ht="40" customHeight="1">
       <c r="A131" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.B.polite.shy[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.A.polite.shy[1]</t>
         </is>
       </c>
       <c r="B131" t="inlineStr" s="2">
@@ -4502,7 +4502,7 @@
       </c>
       <c r="D131" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MAIN.B.polite.shy[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.A.polite.shy[1]</t>
         </is>
       </c>
       <c r="E131" t="inlineStr" s="2">
@@ -4512,14 +4512,14 @@
       </c>
       <c r="F131" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…はい…承知しました。失礼いたしました。</t>
+          <t xml:space="preserve">…あの、ありがとうございます。…嬉しい、です。</t>
         </is>
       </c>
     </row>
     <row r="132" ht="40" customHeight="1">
       <c r="A132" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.C.polite.shy[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.B.polite.shy[1]</t>
         </is>
       </c>
       <c r="B132" t="inlineStr" s="2">
@@ -4534,7 +4534,7 @@
       </c>
       <c r="D132" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MAIN.C.polite.shy[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.B.polite.shy[1]</t>
         </is>
       </c>
       <c r="E132" t="inlineStr" s="2">
@@ -4544,14 +4544,14 @@
       </c>
       <c r="F132" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…あの、ありがとうございます。</t>
+          <t xml:space="preserve">…はい…ごめんなさい。</t>
         </is>
       </c>
     </row>
     <row r="133" ht="40" customHeight="1">
       <c r="A133" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.A.polite.shy[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.C.polite.shy[1]</t>
         </is>
       </c>
       <c r="B133" t="inlineStr" s="2">
@@ -4566,7 +4566,7 @@
       </c>
       <c r="D133" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MONEY.A.polite.shy[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.C.polite.shy[1]</t>
         </is>
       </c>
       <c r="E133" t="inlineStr" s="2">
@@ -4576,14 +4576,14 @@
       </c>
       <c r="F133" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…あの、ありがとう、ございます。…みんなに、伝えます。</t>
+          <t xml:space="preserve">…あの、ありがとうございます。…嬉しいです。</t>
         </is>
       </c>
     </row>
     <row r="134" ht="40" customHeight="1">
       <c r="A134" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.B.polite.shy[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.A.polite.shy[1]</t>
         </is>
       </c>
       <c r="B134" t="inlineStr" s="2">
@@ -4598,7 +4598,7 @@
       </c>
       <c r="D134" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MONEY.B.polite.shy[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.A.polite.shy[1]</t>
         </is>
       </c>
       <c r="E134" t="inlineStr" s="2">
@@ -4608,14 +4608,14 @@
       </c>
       <c r="F134" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…はい…承知しました。失礼いたしました。</t>
+          <t xml:space="preserve">…あの、ありがとうございます。…精一杯、がんばります。</t>
         </is>
       </c>
     </row>
     <row r="135" ht="40" customHeight="1">
       <c r="A135" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.C.polite.shy[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.B.polite.shy[1]</t>
         </is>
       </c>
       <c r="B135" t="inlineStr" s="2">
@@ -4630,7 +4630,7 @@
       </c>
       <c r="D135" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MONEY.C.polite.shy[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.B.polite.shy[1]</t>
         </is>
       </c>
       <c r="E135" t="inlineStr" s="2">
@@ -4640,14 +4640,14 @@
       </c>
       <c r="F135" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…あの、ありがとうございます。…嬉しいです。</t>
+          <t xml:space="preserve">…はい…承知しました。失礼いたしました。</t>
         </is>
       </c>
     </row>
     <row r="136" ht="40" customHeight="1">
       <c r="A136" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.A.polite.shy[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.C.polite.shy[1]</t>
         </is>
       </c>
       <c r="B136" t="inlineStr" s="2">
@@ -4662,7 +4662,7 @@
       </c>
       <c r="D136" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.A.polite.shy[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.C.polite.shy[1]</t>
         </is>
       </c>
       <c r="E136" t="inlineStr" s="2">
@@ -4672,14 +4672,14 @@
       </c>
       <c r="F136" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…あの、ありがとうございます。…がんばります。</t>
+          <t xml:space="preserve">…あの、ありがとうございます。</t>
         </is>
       </c>
     </row>
     <row r="137" ht="40" customHeight="1">
       <c r="A137" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.B.polite.shy[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.A.polite.shy[1]</t>
         </is>
       </c>
       <c r="B137" t="inlineStr" s="2">
@@ -4694,7 +4694,7 @@
       </c>
       <c r="D137" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.B.polite.shy[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.A.polite.shy[1]</t>
         </is>
       </c>
       <c r="E137" t="inlineStr" s="2">
@@ -4704,14 +4704,14 @@
       </c>
       <c r="F137" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…はい…ごめんなさい。</t>
+          <t xml:space="preserve">…あの、ありがとう、ございます。…みんなに、伝えます。</t>
         </is>
       </c>
     </row>
     <row r="138" ht="40" customHeight="1">
       <c r="A138" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.C.polite.shy[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.B.polite.shy[1]</t>
         </is>
       </c>
       <c r="B138" t="inlineStr" s="2">
@@ -4726,7 +4726,7 @@
       </c>
       <c r="D138" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.C.polite.shy[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.B.polite.shy[1]</t>
         </is>
       </c>
       <c r="E138" t="inlineStr" s="2">
@@ -4736,14 +4736,14 @@
       </c>
       <c r="F138" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…あの、ありがとうございます。…嬉しいです。</t>
+          <t xml:space="preserve">…はい…承知しました。失礼いたしました。</t>
         </is>
       </c>
     </row>
     <row r="139" ht="40" customHeight="1">
       <c r="A139" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.A.polite.shy[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.C.polite.shy[1]</t>
         </is>
       </c>
       <c r="B139" t="inlineStr" s="2">
@@ -4758,7 +4758,7 @@
       </c>
       <c r="D139" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.A.polite.shy[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.C.polite.shy[1]</t>
         </is>
       </c>
       <c r="E139" t="inlineStr" s="2">
@@ -4768,14 +4768,14 @@
       </c>
       <c r="F139" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ごめんなさい…次は、声、かけます。</t>
+          <t xml:space="preserve">…あの、ありがとうございます。…嬉しいです。</t>
         </is>
       </c>
     </row>
     <row r="140" ht="40" customHeight="1">
       <c r="A140" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.B.polite.shy[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.A.polite.shy[1]</t>
         </is>
       </c>
       <c r="B140" t="inlineStr" s="2">
@@ -4790,7 +4790,7 @@
       </c>
       <c r="D140" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.B.polite.shy[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.A.polite.shy[1]</t>
         </is>
       </c>
       <c r="E140" t="inlineStr" s="2">
@@ -4800,14 +4800,14 @@
       </c>
       <c r="F140" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…はい…ありがとうございます。…でも、少し、考えます。</t>
+          <t xml:space="preserve">…あの、ありがとうございます。…がんばります。</t>
         </is>
       </c>
     </row>
     <row r="141" ht="40" customHeight="1">
       <c r="A141" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.A.polite.shy[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.B.polite.shy[1]</t>
         </is>
       </c>
       <c r="B141" t="inlineStr" s="2">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="D141" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.A.polite.shy[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.B.polite.shy[1]</t>
         </is>
       </c>
       <c r="E141" t="inlineStr" s="2">
@@ -4839,7 +4839,7 @@
     <row r="142" ht="40" customHeight="1">
       <c r="A142" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.B.polite.shy[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.C.polite.shy[1]</t>
         </is>
       </c>
       <c r="B142" t="inlineStr" s="2">
@@ -4854,7 +4854,7 @@
       </c>
       <c r="D142" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.B.polite.shy[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.C.polite.shy[1]</t>
         </is>
       </c>
       <c r="E142" t="inlineStr" s="2">
@@ -4864,14 +4864,14 @@
       </c>
       <c r="F142" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…はい…ありがとうございます。</t>
+          <t xml:space="preserve">…あの、ありがとうございます。…嬉しいです。</t>
         </is>
       </c>
     </row>
     <row r="143" ht="40" customHeight="1">
       <c r="A143" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.A.polite.shy[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.A.polite.shy[1]</t>
         </is>
       </c>
       <c r="B143" t="inlineStr" s="2">
@@ -4886,7 +4886,7 @@
       </c>
       <c r="D143" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.A.polite.shy[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.A.polite.shy[1]</t>
         </is>
       </c>
       <c r="E143" t="inlineStr" s="2">
@@ -4896,14 +4896,14 @@
       </c>
       <c r="F143" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…はい…ごめんなさい、控えます。</t>
+          <t xml:space="preserve">…ごめんなさい…次は、声、かけます。</t>
         </is>
       </c>
     </row>
     <row r="144" ht="40" customHeight="1">
       <c r="A144" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.B.polite.shy[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.B.polite.shy[1]</t>
         </is>
       </c>
       <c r="B144" t="inlineStr" s="2">
@@ -4918,7 +4918,7 @@
       </c>
       <c r="D144" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.B.polite.shy[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.B.polite.shy[1]</t>
         </is>
       </c>
       <c r="E144" t="inlineStr" s="2">
@@ -4928,14 +4928,14 @@
       </c>
       <c r="F144" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…はい…ありがとうございます。…続けます。</t>
+          <t xml:space="preserve">…はい…ありがとうございます。…でも、少し、考えます。</t>
         </is>
       </c>
     </row>
     <row r="145" ht="40" customHeight="1">
       <c r="A145" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.A.polite.shy[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.A.polite.shy[1]</t>
         </is>
       </c>
       <c r="B145" t="inlineStr" s="2">
@@ -4950,7 +4950,7 @@
       </c>
       <c r="D145" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.A.polite.shy[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.A.polite.shy[1]</t>
         </is>
       </c>
       <c r="E145" t="inlineStr" s="2">
@@ -4960,14 +4960,14 @@
       </c>
       <c r="F145" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ごめんなさい…明日から、ちゃんと、出ます。</t>
+          <t xml:space="preserve">…はい…ごめんなさい。</t>
         </is>
       </c>
     </row>
     <row r="146" ht="40" customHeight="1">
       <c r="A146" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.B.polite.shy[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.B.polite.shy[1]</t>
         </is>
       </c>
       <c r="B146" t="inlineStr" s="2">
@@ -4982,7 +4982,7 @@
       </c>
       <c r="D146" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.B.polite.shy[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.B.polite.shy[1]</t>
         </is>
       </c>
       <c r="E146" t="inlineStr" s="2">
@@ -4992,14 +4992,14 @@
       </c>
       <c r="F146" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…はい…ありがとうございます。…嬉しい、です。</t>
+          <t xml:space="preserve">…はい…ありがとうございます。</t>
         </is>
       </c>
     </row>
     <row r="147" ht="40" customHeight="1">
       <c r="A147" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.C.polite.shy[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.A.polite.shy[1]</t>
         </is>
       </c>
       <c r="B147" t="inlineStr" s="2">
@@ -5014,7 +5014,7 @@
       </c>
       <c r="D147" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.C.polite.shy[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.A.polite.shy[1]</t>
         </is>
       </c>
       <c r="E147" t="inlineStr" s="2">
@@ -5024,14 +5024,14 @@
       </c>
       <c r="F147" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…あの、ありがとうございます。…嬉しいです。</t>
+          <t xml:space="preserve">…はい…ごめんなさい、控えます。</t>
         </is>
       </c>
     </row>
     <row r="148" ht="40" customHeight="1">
       <c r="A148" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.A.polite.shy[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.B.polite.shy[1]</t>
         </is>
       </c>
       <c r="B148" t="inlineStr" s="2">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="D148" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.A.polite.shy[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.B.polite.shy[1]</t>
         </is>
       </c>
       <c r="E148" t="inlineStr" s="2">
@@ -5056,14 +5056,14 @@
       </c>
       <c r="F148" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…はい…ありがとうございます。…休ませて、いただきます。</t>
+          <t xml:space="preserve">…はい…ありがとうございます。…続けます。</t>
         </is>
       </c>
     </row>
     <row r="149" ht="40" customHeight="1">
       <c r="A149" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.B.polite.shy[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.A.polite.shy[1]</t>
         </is>
       </c>
       <c r="B149" t="inlineStr" s="2">
@@ -5078,7 +5078,7 @@
       </c>
       <c r="D149" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.B.polite.shy[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.A.polite.shy[1]</t>
         </is>
       </c>
       <c r="E149" t="inlineStr" s="2">
@@ -5088,14 +5088,14 @@
       </c>
       <c r="F149" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…はい…大丈夫、です。</t>
+          <t xml:space="preserve">…ごめんなさい…明日から、ちゃんと、出ます。</t>
         </is>
       </c>
     </row>
     <row r="150" ht="40" customHeight="1">
       <c r="A150" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.C.polite.shy[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.B.polite.shy[1]</t>
         </is>
       </c>
       <c r="B150" t="inlineStr" s="2">
@@ -5110,7 +5110,7 @@
       </c>
       <c r="D150" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.C.polite.shy[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.B.polite.shy[1]</t>
         </is>
       </c>
       <c r="E150" t="inlineStr" s="2">
@@ -5120,14 +5120,14 @@
       </c>
       <c r="F150" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…あの、ありがとうございます。…嬉しいです。</t>
+          <t xml:space="preserve">…はい…ありがとうございます。…嬉しい、です。</t>
         </is>
       </c>
     </row>
     <row r="151" ht="40" customHeight="1">
       <c r="A151" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.A.polite.shy[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.C.polite.shy[1]</t>
         </is>
       </c>
       <c r="B151" t="inlineStr" s="2">
@@ -5142,7 +5142,7 @@
       </c>
       <c r="D151" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.A.polite.shy[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.C.polite.shy[1]</t>
         </is>
       </c>
       <c r="E151" t="inlineStr" s="2">
@@ -5152,14 +5152,14 @@
       </c>
       <c r="F151" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…はい…ごめんなさい、注意します。</t>
+          <t xml:space="preserve">…あの、ありがとうございます。…嬉しいです。</t>
         </is>
       </c>
     </row>
     <row r="152" ht="40" customHeight="1">
       <c r="A152" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.B.polite.shy[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.A.polite.shy[1]</t>
         </is>
       </c>
       <c r="B152" t="inlineStr" s="2">
@@ -5174,7 +5174,7 @@
       </c>
       <c r="D152" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.B.polite.shy[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.A.polite.shy[1]</t>
         </is>
       </c>
       <c r="E152" t="inlineStr" s="2">
@@ -5184,14 +5184,14 @@
       </c>
       <c r="F152" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…はい…ありがとうございます。</t>
+          <t xml:space="preserve">…はい…ありがとうございます。…休ませて、いただきます。</t>
         </is>
       </c>
     </row>
     <row r="153" ht="40" customHeight="1">
       <c r="A153" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.C.polite.shy[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.B.polite.shy[1]</t>
         </is>
       </c>
       <c r="B153" t="inlineStr" s="2">
@@ -5206,7 +5206,7 @@
       </c>
       <c r="D153" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.C.polite.shy[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.B.polite.shy[1]</t>
         </is>
       </c>
       <c r="E153" t="inlineStr" s="2">
@@ -5216,14 +5216,14 @@
       </c>
       <c r="F153" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…あの、ありがとうございます。…嬉しいです。</t>
+          <t xml:space="preserve">…はい…大丈夫、です。</t>
         </is>
       </c>
     </row>
     <row r="154" ht="40" customHeight="1">
       <c r="A154" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.A.polite.shy[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.C.polite.shy[1]</t>
         </is>
       </c>
       <c r="B154" t="inlineStr" s="2">
@@ -5238,7 +5238,7 @@
       </c>
       <c r="D154" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.A.polite.shy[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.C.polite.shy[1]</t>
         </is>
       </c>
       <c r="E154" t="inlineStr" s="2">
@@ -5248,14 +5248,14 @@
       </c>
       <c r="F154" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…はい…ごめんなさい。</t>
+          <t xml:space="preserve">…あの、ありがとうございます。…嬉しいです。</t>
         </is>
       </c>
     </row>
     <row r="155" ht="40" customHeight="1">
       <c r="A155" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.B.polite.shy[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.A.polite.shy[1]</t>
         </is>
       </c>
       <c r="B155" t="inlineStr" s="2">
@@ -5270,7 +5270,7 @@
       </c>
       <c r="D155" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.B.polite.shy[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.A.polite.shy[1]</t>
         </is>
       </c>
       <c r="E155" t="inlineStr" s="2">
@@ -5280,14 +5280,14 @@
       </c>
       <c r="F155" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（…俯いて、口を閉ざした）</t>
+          <t xml:space="preserve">…はい…ごめんなさい、注意します。</t>
         </is>
       </c>
     </row>
     <row r="156" ht="40" customHeight="1">
       <c r="A156" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.C.polite.shy[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.B.polite.shy[1]</t>
         </is>
       </c>
       <c r="B156" t="inlineStr" s="2">
@@ -5302,7 +5302,7 @@
       </c>
       <c r="D156" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.C.polite.shy[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.B.polite.shy[1]</t>
         </is>
       </c>
       <c r="E156" t="inlineStr" s="2">
@@ -5312,14 +5312,14 @@
       </c>
       <c r="F156" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…あの、ありがとうございます。…嬉しいです。</t>
+          <t xml:space="preserve">…はい…ありがとうございます。</t>
         </is>
       </c>
     </row>
     <row r="157" ht="40" customHeight="1">
       <c r="A157" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.A.polite.shy[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.C.polite.shy[1]</t>
         </is>
       </c>
       <c r="B157" t="inlineStr" s="2">
@@ -5334,7 +5334,7 @@
       </c>
       <c r="D157" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.A.polite.shy[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.C.polite.shy[1]</t>
         </is>
       </c>
       <c r="E157" t="inlineStr" s="2">
@@ -5344,14 +5344,14 @@
       </c>
       <c r="F157" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…はい…ごめんなさい、加減します。</t>
+          <t xml:space="preserve">…あの、ありがとうございます。…嬉しいです。</t>
         </is>
       </c>
     </row>
     <row r="158" ht="40" customHeight="1">
       <c r="A158" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.B.polite.shy[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.A.polite.shy[1]</t>
         </is>
       </c>
       <c r="B158" t="inlineStr" s="2">
@@ -5366,7 +5366,7 @@
       </c>
       <c r="D158" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.B.polite.shy[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.A.polite.shy[1]</t>
         </is>
       </c>
       <c r="E158" t="inlineStr" s="2">
@@ -5376,14 +5376,14 @@
       </c>
       <c r="F158" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…はい…ありがとうございます。…続けます。</t>
+          <t xml:space="preserve">…はい…ごめんなさい。</t>
         </is>
       </c>
     </row>
     <row r="159" ht="40" customHeight="1">
       <c r="A159" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.C.polite.shy[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.B.polite.shy[1]</t>
         </is>
       </c>
       <c r="B159" t="inlineStr" s="2">
@@ -5398,7 +5398,7 @@
       </c>
       <c r="D159" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.C.polite.shy[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.B.polite.shy[1]</t>
         </is>
       </c>
       <c r="E159" t="inlineStr" s="2">
@@ -5408,14 +5408,14 @@
       </c>
       <c r="F159" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…あの、ありがとうございます。…嬉しいです。</t>
+          <t xml:space="preserve">（…俯いて、口を閉ざした）</t>
         </is>
       </c>
     </row>
     <row r="160" ht="40" customHeight="1">
       <c r="A160" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES.shy.attack.polite</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.C.polite.shy[1]</t>
         </is>
       </c>
       <c r="B160" t="inlineStr" s="2">
@@ -5425,12 +5425,12 @@
       </c>
       <c r="C160" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D160" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">shy.attack.polite</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.C.polite.shy[1]</t>
         </is>
       </c>
       <c r="E160" t="inlineStr" s="2">
@@ -5440,14 +5440,14 @@
       </c>
       <c r="F160" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの、もう…ご一緒には、いられません…</t>
+          <t xml:space="preserve">…あの、ありがとうございます。…嬉しいです。</t>
         </is>
       </c>
     </row>
     <row r="161" ht="40" customHeight="1">
       <c r="A161" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES.shy.defend.polite</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.A.polite.shy[1]</t>
         </is>
       </c>
       <c r="B161" t="inlineStr" s="2">
@@ -5457,12 +5457,12 @@
       </c>
       <c r="C161" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D161" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">shy.defend.polite</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.A.polite.shy[1]</t>
         </is>
       </c>
       <c r="E161" t="inlineStr" s="2">
@@ -5472,14 +5472,14 @@
       </c>
       <c r="F161" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…やるしか、ないんです</t>
+          <t xml:space="preserve">…はい…ごめんなさい、加減します。</t>
         </is>
       </c>
     </row>
     <row r="162" ht="40" customHeight="1">
       <c r="A162" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES.shy.polite[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.B.polite.shy[1]</t>
         </is>
       </c>
       <c r="B162" t="inlineStr" s="2">
@@ -5489,29 +5489,29 @@
       </c>
       <c r="C162" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D162" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">shy.polite[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.B.polite.shy[1]</t>
         </is>
       </c>
       <c r="E162" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F162" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、あの…何かが、変わった気がします…壁を、越えられたかも…しれません…</t>
+          <t xml:space="preserve">…はい…ありがとうございます。…続けます。</t>
         </is>
       </c>
     </row>
     <row r="163" ht="40" customHeight="1">
       <c r="A163" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BT_HINT_LINES.shy.polite[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.C.polite.shy[1]</t>
         </is>
       </c>
       <c r="B163" t="inlineStr" s="2">
@@ -5521,29 +5521,29 @@
       </c>
       <c r="C163" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BT_HINT_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D163" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">shy.polite[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.C.polite.shy[1]</t>
         </is>
       </c>
       <c r="E163" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F163" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最近…なにかが、掴めそうな…そんな気がするんです…</t>
+          <t xml:space="preserve">…あの、ありがとうございます。…嬉しいです。</t>
         </is>
       </c>
     </row>
     <row r="164" ht="40" customHeight="1">
       <c r="A164" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES.shy.polite[1]</t>
+          <t xml:space="preserve">FACTION_F02_LINES.shy.attack.polite</t>
         </is>
       </c>
       <c r="B164" t="inlineStr" s="2">
@@ -5553,29 +5553,29 @@
       </c>
       <c r="C164" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
+          <t xml:space="preserve">FACTION_F02_LINES</t>
         </is>
       </c>
       <c r="D164" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">shy.polite[1]</t>
+          <t xml:space="preserve">shy.attack.polite</t>
         </is>
       </c>
       <c r="E164" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F164" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">な、なんだか…やる気が、出ません…ご、ごめんなさい…</t>
+          <t xml:space="preserve">あの、もう…ご一緒には、いられません…</t>
         </is>
       </c>
     </row>
     <row r="165" ht="40" customHeight="1">
       <c r="A165" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.shy.polite[1]</t>
+          <t xml:space="preserve">FACTION_F02_LINES.shy.defend.polite</t>
         </is>
       </c>
       <c r="B165" t="inlineStr" s="2">
@@ -5585,29 +5585,29 @@
       </c>
       <c r="C165" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
+          <t xml:space="preserve">FACTION_F02_LINES</t>
         </is>
       </c>
       <c r="D165" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">shy.polite[1]</t>
+          <t xml:space="preserve">shy.defend.polite</t>
         </is>
       </c>
       <c r="E165" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F165" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、あの…また、頑張ろうって思えてきました…</t>
+          <t xml:space="preserve">…やるしか、ないんです</t>
         </is>
       </c>
     </row>
     <row r="166" ht="40" customHeight="1">
       <c r="A166" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES.shy.polite[1]</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES.shy.polite[1]</t>
         </is>
       </c>
       <c r="B166" t="inlineStr" s="2">
@@ -5617,7 +5617,7 @@
       </c>
       <c r="C166" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES</t>
         </is>
       </c>
       <c r="D166" t="inlineStr" s="12">
@@ -5632,14 +5632,14 @@
       </c>
       <c r="F166" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やっと…調子が、戻ってきました…</t>
+          <t xml:space="preserve">あ、あの…何かが、変わった気がします…壁を、越えられたかも…しれません…</t>
         </is>
       </c>
     </row>
     <row r="167" ht="40" customHeight="1">
       <c r="A167" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.defeat.shy.polite[1]</t>
+          <t xml:space="preserve">BT_HINT_LINES.shy.polite[1]</t>
         </is>
       </c>
       <c r="B167" t="inlineStr" s="2">
@@ -5649,12 +5649,12 @@
       </c>
       <c r="C167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">BT_HINT_LINES</t>
         </is>
       </c>
       <c r="D167" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defeat.shy.polite[1]</t>
+          <t xml:space="preserve">shy.polite[1]</t>
         </is>
       </c>
       <c r="E167" t="inlineStr" s="2">
@@ -5664,14 +5664,14 @@
       </c>
       <c r="F167" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ま、負けが続いて…自信が、なくなりそうです…</t>
+          <t xml:space="preserve">最近…なにかが、掴めそうな…そんな気がするんです…</t>
         </is>
       </c>
     </row>
     <row r="168" ht="40" customHeight="1">
       <c r="A168" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery.shy.polite[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.fresh.shy.polite[1]</t>
         </is>
       </c>
       <c r="B168" t="inlineStr" s="2">
@@ -5681,12 +5681,12 @@
       </c>
       <c r="C168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
         </is>
       </c>
       <c r="D168" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_moderate_recovery.shy.polite[1]</t>
+          <t xml:space="preserve">fresh.shy.polite[1]</t>
         </is>
       </c>
       <c r="E168" t="inlineStr" s="2">
@@ -5696,14 +5696,14 @@
       </c>
       <c r="F168" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">け、怪我が治って…でも、まだ感覚が戻りません…</t>
+          <t xml:space="preserve">あ、あの…今日は体が軽くて…もっと、やれます…!</t>
         </is>
       </c>
     </row>
     <row r="169" ht="40" customHeight="1">
       <c r="A169" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery.shy.polite[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.heavy.shy.polite[1]</t>
         </is>
       </c>
       <c r="B169" t="inlineStr" s="2">
@@ -5713,12 +5713,12 @@
       </c>
       <c r="C169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
         </is>
       </c>
       <c r="D169" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_severe_recovery.shy.polite[1]</t>
+          <t xml:space="preserve">heavy.shy.polite[1]</t>
         </is>
       </c>
       <c r="E169" t="inlineStr" s="2">
@@ -5728,14 +5728,14 @@
       </c>
       <c r="F169" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お、大きな怪我から復帰しました…でも、不安です…</t>
+          <t xml:space="preserve">すみません…動けてはいるんですけど…空回りしてしまって</t>
         </is>
       </c>
     </row>
     <row r="170" ht="40" customHeight="1">
       <c r="A170" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.penalty_end.shy.polite[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.warm.shy.polite[1]</t>
         </is>
       </c>
       <c r="B170" t="inlineStr" s="2">
@@ -5745,12 +5745,12 @@
       </c>
       <c r="C170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
         </is>
       </c>
       <c r="D170" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">penalty_end.shy.polite[1]</t>
+          <t xml:space="preserve">warm.shy.polite[1]</t>
         </is>
       </c>
       <c r="E170" t="inlineStr" s="2">
@@ -5760,14 +5760,14 @@
       </c>
       <c r="F170" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">け、謹慎が明けました…ま、また頑張ります…</t>
+          <t xml:space="preserve">あの…できてはいるんです。ただ、残らなくて…</t>
         </is>
       </c>
     </row>
     <row r="171" ht="40" customHeight="1">
       <c r="A171" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.bestMatch.shy.polite[1]</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES.shy.polite[1]</t>
         </is>
       </c>
       <c r="B171" t="inlineStr" s="2">
@@ -5777,29 +5777,29 @@
       </c>
       <c r="C171" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
         </is>
       </c>
       <c r="D171" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bestMatch.shy.polite[1]</t>
+          <t xml:space="preserve">shy.polite[1]</t>
         </is>
       </c>
       <c r="E171" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F171" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、あの…ベストバウトに選んでいただけるなんて…相手の方のおかげです…</t>
+          <t xml:space="preserve">な、なんだか…やる気が、出ません…ご、ごめんなさい…</t>
         </is>
       </c>
     </row>
     <row r="172" ht="40" customHeight="1">
       <c r="A172" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.champion.shy.polite[1]</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.shy.polite[1]</t>
         </is>
       </c>
       <c r="B172" t="inlineStr" s="2">
@@ -5809,29 +5809,29 @@
       </c>
       <c r="C172" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
         </is>
       </c>
       <c r="D172" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.shy.polite[1]</t>
+          <t xml:space="preserve">shy.polite[1]</t>
         </is>
       </c>
       <c r="E172" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F172" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わ、わたしが…チャンピオンに…？ こ、このベルトを汚さないように頑張ります…</t>
+          <t xml:space="preserve">あ、あの…また、頑張ろうって思えてきました…</t>
         </is>
       </c>
     </row>
     <row r="173" ht="40" customHeight="1">
       <c r="A173" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.hallOfFame.shy.polite[1]</t>
+          <t xml:space="preserve">SLUMP_END_LINES.shy.polite[1]</t>
         </is>
       </c>
       <c r="B173" t="inlineStr" s="2">
@@ -5841,29 +5841,29 @@
       </c>
       <c r="C173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_END_LINES</t>
         </is>
       </c>
       <c r="D173" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hallOfFame.shy.polite[1]</t>
+          <t xml:space="preserve">shy.polite[1]</t>
         </is>
       </c>
       <c r="E173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F173" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">で、殿堂入り…ですか…？ わたしなんかが…本当に、いいんでしょうか…</t>
+          <t xml:space="preserve">やっと…調子が、戻ってきました…</t>
         </is>
       </c>
     </row>
     <row r="174" ht="40" customHeight="1">
       <c r="A174" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mediaAward.shy.polite[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.defeat.shy.polite[1]</t>
         </is>
       </c>
       <c r="B174" t="inlineStr" s="2">
@@ -5873,29 +5873,29 @@
       </c>
       <c r="C174" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D174" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mediaAward.shy.polite[1]</t>
+          <t xml:space="preserve">defeat.shy.polite[1]</t>
         </is>
       </c>
       <c r="E174" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F174" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">メディアの方々に…評価していただけて…あ、あの、本当に光栄です…</t>
+          <t xml:space="preserve">ま、負けが続いて…自信が、なくなりそうです…</t>
         </is>
       </c>
     </row>
     <row r="175" ht="40" customHeight="1">
       <c r="A175" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mvp.shy.polite[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery.shy.polite[1]</t>
         </is>
       </c>
       <c r="B175" t="inlineStr" s="2">
@@ -5905,29 +5905,29 @@
       </c>
       <c r="C175" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D175" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mvp.shy.polite[1]</t>
+          <t xml:space="preserve">injury_moderate_recovery.shy.polite[1]</t>
         </is>
       </c>
       <c r="E175" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F175" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">M、MVP…ですか…？ そ、そんな大それた賞、わたしには…</t>
+          <t xml:space="preserve">け、怪我が治って…でも、まだ感覚が戻りません…</t>
         </is>
       </c>
     </row>
     <row r="176" ht="40" customHeight="1">
       <c r="A176" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.rookie.shy.polite[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery.shy.polite[1]</t>
         </is>
       </c>
       <c r="B176" t="inlineStr" s="2">
@@ -5937,29 +5937,29 @@
       </c>
       <c r="C176" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D176" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rookie.shy.polite[1]</t>
+          <t xml:space="preserve">injury_severe_recovery.shy.polite[1]</t>
         </is>
       </c>
       <c r="E176" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F176" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">え…わたし、ですか…？ …ありがとうございます…</t>
+          <t xml:space="preserve">お、大きな怪我から復帰しました…でも、不安です…</t>
         </is>
       </c>
     </row>
     <row r="177" ht="40" customHeight="1">
       <c r="A177" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.shy.polite[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.penalty_end.shy.polite[1]</t>
         </is>
       </c>
       <c r="B177" t="inlineStr" s="2">
@@ -5969,29 +5969,29 @@
       </c>
       <c r="C177" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D177" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">shy.polite[1]</t>
+          <t xml:space="preserve">penalty_end.shy.polite[1]</t>
         </is>
       </c>
       <c r="E177" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F177" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの…ありがとうございます、ここまで連れてきてくださって</t>
+          <t xml:space="preserve">け、謹慎が明けました…ま、また頑張ります…</t>
         </is>
       </c>
     </row>
     <row r="178" ht="40" customHeight="1">
       <c r="A178" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.shy.polite[2]</t>
+          <t xml:space="preserve">AWARD_LINES.bestMatch.shy.polite[1]</t>
         </is>
       </c>
       <c r="B178" t="inlineStr" s="2">
@@ -6001,12 +6001,12 @@
       </c>
       <c r="C178" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D178" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">shy.polite[2]</t>
+          <t xml:space="preserve">bestMatch.shy.polite[1]</t>
         </is>
       </c>
       <c r="E178" t="inlineStr" s="2">
@@ -6016,14 +6016,14 @@
       </c>
       <c r="F178" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…精一杯、やります</t>
+          <t xml:space="preserve">あ、あの…ベストバウトに選んでいただけるなんて…相手の方のおかげです…</t>
         </is>
       </c>
     </row>
     <row r="179" ht="40" customHeight="1">
       <c r="A179" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.shy.polite[3]</t>
+          <t xml:space="preserve">AWARD_LINES.champion.shy.polite[1]</t>
         </is>
       </c>
       <c r="B179" t="inlineStr" s="2">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="C179" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D179" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">shy.polite[3]</t>
+          <t xml:space="preserve">champion.shy.polite[1]</t>
         </is>
       </c>
       <c r="E179" t="inlineStr" s="2">
@@ -6048,14 +6048,14 @@
       </c>
       <c r="F179" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…この恩は、一生、忘れません</t>
+          <t xml:space="preserve">わ、わたしが…チャンピオンに…？ こ、このベルトを汚さないように頑張ります…</t>
         </is>
       </c>
     </row>
     <row r="180" ht="40" customHeight="1">
       <c r="A180" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.shy.polite[1]</t>
+          <t xml:space="preserve">AWARD_LINES.hallOfFame.shy.polite[1]</t>
         </is>
       </c>
       <c r="B180" t="inlineStr" s="2">
@@ -6065,12 +6065,12 @@
       </c>
       <c r="C180" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D180" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">shy.polite[1]</t>
+          <t xml:space="preserve">hallOfFame.shy.polite[1]</t>
         </is>
       </c>
       <c r="E180" t="inlineStr" s="2">
@@ -6080,14 +6080,14 @@
       </c>
       <c r="F180" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…満員、ありがとうございます…ありがとうございます…</t>
+          <t xml:space="preserve">で、殿堂入り…ですか…？ わたしなんかが…本当に、いいんでしょうか…</t>
         </is>
       </c>
     </row>
     <row r="181" ht="40" customHeight="1">
       <c r="A181" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.shy.polite[2]</t>
+          <t xml:space="preserve">AWARD_LINES.mediaAward.shy.polite[1]</t>
         </is>
       </c>
       <c r="B181" t="inlineStr" s="2">
@@ -6097,12 +6097,12 @@
       </c>
       <c r="C181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D181" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">shy.polite[2]</t>
+          <t xml:space="preserve">mediaAward.shy.polite[1]</t>
         </is>
       </c>
       <c r="E181" t="inlineStr" s="2">
@@ -6112,14 +6112,14 @@
       </c>
       <c r="F181" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…こんな私を、応援してくださって…</t>
+          <t xml:space="preserve">メディアの方々に…評価していただけて…あ、あの、本当に光栄です…</t>
         </is>
       </c>
     </row>
     <row r="182" ht="40" customHeight="1">
       <c r="A182" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.shy.polite[3]</t>
+          <t xml:space="preserve">AWARD_LINES.mvp.shy.polite[1]</t>
         </is>
       </c>
       <c r="B182" t="inlineStr" s="2">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="C182" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D182" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">shy.polite[3]</t>
+          <t xml:space="preserve">mvp.shy.polite[1]</t>
         </is>
       </c>
       <c r="E182" t="inlineStr" s="2">
@@ -6144,14 +6144,14 @@
       </c>
       <c r="F182" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…この恩、一生忘れません…</t>
+          <t xml:space="preserve">M、MVP…ですか…？ そ、そんな大それた賞、わたしには…</t>
         </is>
       </c>
     </row>
     <row r="183" ht="40" customHeight="1">
       <c r="A183" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N1.shy.polite[1]</t>
+          <t xml:space="preserve">AWARD_LINES.rookie.shy.polite[1]</t>
         </is>
       </c>
       <c r="B183" t="inlineStr" s="2">
@@ -6161,29 +6161,29 @@
       </c>
       <c r="C183" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D183" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N1.shy.polite[1]</t>
+          <t xml:space="preserve">rookie.shy.polite[1]</t>
         </is>
       </c>
       <c r="E183" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F183" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、あの…お知らせがあります…</t>
+          <t xml:space="preserve">え…わたし、ですか…？ …ありがとうございます…</t>
         </is>
       </c>
     </row>
     <row r="184" ht="40" customHeight="1">
       <c r="A184" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N2.shy.polite[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.shy.polite[1]</t>
         </is>
       </c>
       <c r="B184" t="inlineStr" s="2">
@@ -6193,29 +6193,29 @@
       </c>
       <c r="C184" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D184" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N2.shy.polite[1]</t>
+          <t xml:space="preserve">shy.polite[1]</t>
         </is>
       </c>
       <c r="E184" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F184" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ちょ、ちょっとお伝えしたいことが…</t>
+          <t xml:space="preserve">あの…ありがとうございます、ここまで連れてきてくださって</t>
         </is>
       </c>
     </row>
     <row r="185" ht="40" customHeight="1">
       <c r="A185" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N3.shy.polite[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.shy.polite[2]</t>
         </is>
       </c>
       <c r="B185" t="inlineStr" s="2">
@@ -6225,29 +6225,29 @@
       </c>
       <c r="C185" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D185" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N3.shy.polite[1]</t>
+          <t xml:space="preserve">shy.polite[2]</t>
         </is>
       </c>
       <c r="E185" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F185" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">報告です…あ、あの…</t>
+          <t xml:space="preserve">…精一杯、やります</t>
         </is>
       </c>
     </row>
     <row r="186" ht="40" customHeight="1">
       <c r="A186" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N4.shy.polite[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.shy.polite[3]</t>
         </is>
       </c>
       <c r="B186" t="inlineStr" s="2">
@@ -6257,29 +6257,29 @@
       </c>
       <c r="C186" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D186" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N4.shy.polite[1]</t>
+          <t xml:space="preserve">shy.polite[3]</t>
         </is>
       </c>
       <c r="E186" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F186" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お、大事なお知らせです…</t>
+          <t xml:space="preserve">…この恩は、一生、忘れません</t>
         </is>
       </c>
     </row>
     <row r="187" ht="40" customHeight="1">
       <c r="A187" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.shy.polite[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.shy.polite[1]</t>
         </is>
       </c>
       <c r="B187" t="inlineStr" s="2">
@@ -6289,29 +6289,29 @@
       </c>
       <c r="C187" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D187" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_low.shy.polite[1]</t>
+          <t xml:space="preserve">shy.polite[1]</t>
         </is>
       </c>
       <c r="E187" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F187" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、あの…ちょっと、心配なことが…</t>
+          <t xml:space="preserve">…満員、ありがとうございます…ありがとうございます…</t>
         </is>
       </c>
     </row>
     <row r="188" ht="40" customHeight="1">
       <c r="A188" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.shy.polite[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.shy.polite[2]</t>
         </is>
       </c>
       <c r="B188" t="inlineStr" s="2">
@@ -6321,29 +6321,29 @@
       </c>
       <c r="C188" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D188" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_warning.shy.polite[1]</t>
+          <t xml:space="preserve">shy.polite[2]</t>
         </is>
       </c>
       <c r="E188" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F188" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">き、緊急のお知らせです…!</t>
+          <t xml:space="preserve">…こんな私を、応援してくださって…</t>
         </is>
       </c>
     </row>
     <row r="189" ht="40" customHeight="1">
       <c r="A189" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.breakthrough.voice.shy.polite[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.shy.polite[3]</t>
         </is>
       </c>
       <c r="B189" t="inlineStr" s="2">
@@ -6353,29 +6353,29 @@
       </c>
       <c r="C189" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D189" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">breakthrough.voice.shy.polite[1]</t>
+          <t xml:space="preserve">shy.polite[3]</t>
         </is>
       </c>
       <c r="E189" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F189" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…な、何かが、変わった気がします…</t>
+          <t xml:space="preserve">…この恩、一生忘れません…</t>
         </is>
       </c>
     </row>
     <row r="190" ht="40" customHeight="1">
       <c r="A190" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G1.voice.shy.polite[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N1.shy.polite[1]</t>
         </is>
       </c>
       <c r="B190" t="inlineStr" s="2">
@@ -6385,12 +6385,12 @@
       </c>
       <c r="C190" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D190" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G1.voice.shy.polite[1]</t>
+          <t xml:space="preserve">N1.shy.polite[1]</t>
         </is>
       </c>
       <c r="E190" t="inlineStr" s="2">
@@ -6400,14 +6400,14 @@
       </c>
       <c r="F190" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…もう少し、お給料が、上がったらいいな…</t>
+          <t xml:space="preserve">あ、あの…お知らせがあります…</t>
         </is>
       </c>
     </row>
     <row r="191" ht="40" customHeight="1">
       <c r="A191" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G2.voice.shy.polite[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N2.shy.polite[1]</t>
         </is>
       </c>
       <c r="B191" t="inlineStr" s="2">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="C191" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D191" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G2.voice.shy.polite[1]</t>
+          <t xml:space="preserve">N2.shy.polite[1]</t>
         </is>
       </c>
       <c r="E191" t="inlineStr" s="2">
@@ -6432,14 +6432,14 @@
       </c>
       <c r="F191" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ひ、ひとりだと、寂しいです…</t>
+          <t xml:space="preserve">ちょ、ちょっとお伝えしたいことが…</t>
         </is>
       </c>
     </row>
     <row r="192" ht="40" customHeight="1">
       <c r="A192" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G3.voice.shy.polite[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N3.shy.polite[1]</t>
         </is>
       </c>
       <c r="B192" t="inlineStr" s="2">
@@ -6449,12 +6449,12 @@
       </c>
       <c r="C192" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D192" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G3.voice.shy.polite[1]</t>
+          <t xml:space="preserve">N3.shy.polite[1]</t>
         </is>
       </c>
       <c r="E192" t="inlineStr" s="2">
@@ -6464,14 +6464,14 @@
       </c>
       <c r="F192" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…も、もっと注目されないと、ダメですよね…</t>
+          <t xml:space="preserve">報告です…あ、あの…</t>
         </is>
       </c>
     </row>
     <row r="193" ht="40" customHeight="1">
       <c r="A193" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G4.voice.shy.polite[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N4.shy.polite[1]</t>
         </is>
       </c>
       <c r="B193" t="inlineStr" s="2">
@@ -6481,12 +6481,12 @@
       </c>
       <c r="C193" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D193" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G4.voice.shy.polite[1]</t>
+          <t xml:space="preserve">N4.shy.polite[1]</t>
         </is>
       </c>
       <c r="E193" t="inlineStr" s="2">
@@ -6496,14 +6496,14 @@
       </c>
       <c r="F193" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…つ、強くなりたい、です…</t>
+          <t xml:space="preserve">お、大事なお知らせです…</t>
         </is>
       </c>
     </row>
     <row r="194" ht="40" customHeight="1">
       <c r="A194" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R2.voice.shy.polite[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.shy.polite[1]</t>
         </is>
       </c>
       <c r="B194" t="inlineStr" s="2">
@@ -6513,12 +6513,12 @@
       </c>
       <c r="C194" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D194" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R2.voice.shy.polite[1]</t>
+          <t xml:space="preserve">N5_low.shy.polite[1]</t>
         </is>
       </c>
       <c r="E194" t="inlineStr" s="2">
@@ -6528,14 +6528,14 @@
       </c>
       <c r="F194" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…あ、あの人と、また話せたらいいな…</t>
+          <t xml:space="preserve">あ、あの…ちょっと、心配なことが…</t>
         </is>
       </c>
     </row>
     <row r="195" ht="40" customHeight="1">
       <c r="A195" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R3.modal.shy.polite[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.shy.polite[1]</t>
         </is>
       </c>
       <c r="B195" t="inlineStr" s="2">
@@ -6545,12 +6545,12 @@
       </c>
       <c r="C195" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D195" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R3.modal.shy.polite[1]</t>
+          <t xml:space="preserve">N5_warning.shy.polite[1]</t>
         </is>
       </c>
       <c r="E195" t="inlineStr" s="2">
@@ -6560,14 +6560,14 @@
       </c>
       <c r="F195" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、あの…少し、お話できますか…</t>
+          <t xml:space="preserve">き、緊急のお知らせです…!</t>
         </is>
       </c>
     </row>
     <row r="196" ht="40" customHeight="1">
       <c r="A196" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R4.voice.shy.polite[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.breakthrough.voice.shy.polite[1]</t>
         </is>
       </c>
       <c r="B196" t="inlineStr" s="2">
@@ -6582,7 +6582,7 @@
       </c>
       <c r="D196" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R4.voice.shy.polite[1]</t>
+          <t xml:space="preserve">breakthrough.voice.shy.polite[1]</t>
         </is>
       </c>
       <c r="E196" t="inlineStr" s="2">
@@ -6592,14 +6592,14 @@
       </c>
       <c r="F196" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…あ、あの人とは、距離を置きたい、かも…</t>
+          <t xml:space="preserve">…な、何かが、変わった気がします…</t>
         </is>
       </c>
     </row>
     <row r="197" ht="40" customHeight="1">
       <c r="A197" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R5.voice.shy.polite[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G1.voice.shy.polite[1]</t>
         </is>
       </c>
       <c r="B197" t="inlineStr" s="2">
@@ -6614,7 +6614,7 @@
       </c>
       <c r="D197" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R5.voice.shy.polite[1]</t>
+          <t xml:space="preserve">G1.voice.shy.polite[1]</t>
         </is>
       </c>
       <c r="E197" t="inlineStr" s="2">
@@ -6624,14 +6624,14 @@
       </c>
       <c r="F197" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ま、負けたく、ないです…</t>
+          <t xml:space="preserve">…もう少し、お給料が、上がったらいいな…</t>
         </is>
       </c>
     </row>
     <row r="198" ht="40" customHeight="1">
       <c r="A198" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.warVictory.voice.shy.polite[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G2.voice.shy.polite[1]</t>
         </is>
       </c>
       <c r="B198" t="inlineStr" s="2">
@@ -6646,7 +6646,7 @@
       </c>
       <c r="D198" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">warVictory.voice.shy.polite[1]</t>
+          <t xml:space="preserve">G2.voice.shy.polite[1]</t>
         </is>
       </c>
       <c r="E198" t="inlineStr" s="2">
@@ -6656,14 +6656,14 @@
       </c>
       <c r="F198" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…か、勝てて、よかったです…</t>
+          <t xml:space="preserve">…ひ、ひとりだと、寂しいです…</t>
         </is>
       </c>
     </row>
     <row r="199" ht="40" customHeight="1">
       <c r="A199" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus_repeat.shy.polite[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G3.voice.shy.polite[1]</t>
         </is>
       </c>
       <c r="B199" t="inlineStr" s="2">
@@ -6673,29 +6673,29 @@
       </c>
       <c r="C199" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D199" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus_repeat.shy.polite[1]</t>
+          <t xml:space="preserve">G3.voice.shy.polite[1]</t>
         </is>
       </c>
       <c r="E199" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F199" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ま、また…？ そんな、毎回いただいては…申し訳ないです…</t>
+          <t xml:space="preserve">…も、もっと注目されないと、ダメですよね…</t>
         </is>
       </c>
     </row>
     <row r="200" ht="40" customHeight="1">
       <c r="A200" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.shy.polite[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G4.voice.shy.polite[1]</t>
         </is>
       </c>
       <c r="B200" t="inlineStr" s="2">
@@ -6705,29 +6705,29 @@
       </c>
       <c r="C200" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D200" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus.shy.polite[1]</t>
+          <t xml:space="preserve">G4.voice.shy.polite[1]</t>
         </is>
       </c>
       <c r="E200" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F200" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ぼ、ボーナスを…？ あ、ありがとうございます…大切に使わせていただきます…</t>
+          <t xml:space="preserve">…つ、強くなりたい、です…</t>
         </is>
       </c>
     </row>
     <row r="201" ht="40" customHeight="1">
       <c r="A201" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.shy.polite[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R2.voice.shy.polite[1]</t>
         </is>
       </c>
       <c r="B201" t="inlineStr" s="2">
@@ -6737,29 +6737,29 @@
       </c>
       <c r="C201" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D201" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">camp.shy.polite[1]</t>
+          <t xml:space="preserve">R2.voice.shy.polite[1]</t>
         </is>
       </c>
       <c r="E201" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F201" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">が、合宿…ですか…緊張しますけど…頑張ります…!</t>
+          <t xml:space="preserve">…あ、あの人と、また話せたらいいな…</t>
         </is>
       </c>
     </row>
     <row r="202" ht="40" customHeight="1">
       <c r="A202" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.shy.polite[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R3.modal.shy.polite[1]</t>
         </is>
       </c>
       <c r="B202" t="inlineStr" s="2">
@@ -6769,29 +6769,29 @@
       </c>
       <c r="C202" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D202" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage_high_trust.shy.polite[1]</t>
+          <t xml:space="preserve">R3.modal.shy.polite[1]</t>
         </is>
       </c>
       <c r="E202" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F202" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いつも気にかけてくださって…あ、あの、本当に感謝しています…</t>
+          <t xml:space="preserve">あ、あの…少し、お話できますか…</t>
         </is>
       </c>
     </row>
     <row r="203" ht="40" customHeight="1">
       <c r="A203" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.shy.polite[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R4.voice.shy.polite[1]</t>
         </is>
       </c>
       <c r="B203" t="inlineStr" s="2">
@@ -6801,29 +6801,29 @@
       </c>
       <c r="C203" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D203" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage.shy.polite[1]</t>
+          <t xml:space="preserve">R4.voice.shy.polite[1]</t>
         </is>
       </c>
       <c r="E203" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F203" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、ありがとうございます…そう言っていただけると、頑張れます…</t>
+          <t xml:space="preserve">…あ、あの人とは、距離を置きたい、かも…</t>
         </is>
       </c>
     </row>
     <row r="204" ht="40" customHeight="1">
       <c r="A204" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.shy.polite[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R5.voice.shy.polite[1]</t>
         </is>
       </c>
       <c r="B204" t="inlineStr" s="2">
@@ -6833,29 +6833,29 @@
       </c>
       <c r="C204" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D204" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">media.shy.polite[1]</t>
+          <t xml:space="preserve">R5.voice.shy.polite[1]</t>
         </is>
       </c>
       <c r="E204" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F204" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">メ、メディア出演…ですか…き、緊張しますけど…や、やってみます…</t>
+          <t xml:space="preserve">…ま、負けたく、ないです…</t>
         </is>
       </c>
     </row>
     <row r="205" ht="40" customHeight="1">
       <c r="A205" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.shy.polite[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.warVictory.voice.shy.polite[1]</t>
         </is>
       </c>
       <c r="B205" t="inlineStr" s="2">
@@ -6865,29 +6865,29 @@
       </c>
       <c r="C205" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D205" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">party.shy.polite[1]</t>
+          <t xml:space="preserve">warVictory.voice.shy.polite[1]</t>
         </is>
       </c>
       <c r="E205" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F205" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">パ、パーティー…人が多いところは少し苦手ですけど…頑張って参加します…</t>
+          <t xml:space="preserve">…か、勝てて、よかったです…</t>
         </is>
       </c>
     </row>
     <row r="206" ht="40" customHeight="1">
       <c r="A206" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.shy.polite[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus_repeat.shy.polite[1]</t>
         </is>
       </c>
       <c r="B206" t="inlineStr" s="2">
@@ -6902,7 +6902,7 @@
       </c>
       <c r="D206" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refresh_leave.shy.polite[1]</t>
+          <t xml:space="preserve">bonus_repeat.shy.polite[1]</t>
         </is>
       </c>
       <c r="E206" t="inlineStr" s="2">
@@ -6912,14 +6912,14 @@
       </c>
       <c r="F206" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お休みを…？ あ、あの…ありがとうございます、ゆっくり休ませていただきます…</t>
+          <t xml:space="preserve">ま、また…？ そんな、毎回いただいては…申し訳ないです…</t>
         </is>
       </c>
     </row>
     <row r="207" ht="40" customHeight="1">
       <c r="A207" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.shy.polite[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.shy.polite[1]</t>
         </is>
       </c>
       <c r="B207" t="inlineStr" s="2">
@@ -6934,7 +6934,7 @@
       </c>
       <c r="D207" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trainer.shy.polite[1]</t>
+          <t xml:space="preserve">bonus.shy.polite[1]</t>
         </is>
       </c>
       <c r="E207" t="inlineStr" s="2">
@@ -6944,14 +6944,14 @@
       </c>
       <c r="F207" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">専属トレーナー…ですか…あ、あの、よろしくお願いいたします…</t>
+          <t xml:space="preserve">ぼ、ボーナスを…？ あ、ありがとうございます…大切に使わせていただきます…</t>
         </is>
       </c>
     </row>
     <row r="208" ht="40" customHeight="1">
       <c r="A208" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.shy.polite[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.shy.polite[1]</t>
         </is>
       </c>
       <c r="B208" t="inlineStr" s="2">
@@ -6961,12 +6961,12 @@
       </c>
       <c r="C208" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D208" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.shy.polite[1]</t>
+          <t xml:space="preserve">camp.shy.polite[1]</t>
         </is>
       </c>
       <c r="E208" t="inlineStr" s="2">
@@ -6976,14 +6976,14 @@
       </c>
       <c r="F208" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、あの…どうしたら、いいんでしょうか…</t>
+          <t xml:space="preserve">が、合宿…ですか…緊張しますけど…頑張ります…!</t>
         </is>
       </c>
     </row>
     <row r="209" ht="40" customHeight="1">
       <c r="A209" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E4.shy.polite[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.shy.polite[1]</t>
         </is>
       </c>
       <c r="B209" t="inlineStr" s="2">
@@ -6993,12 +6993,12 @@
       </c>
       <c r="C209" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D209" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E4.shy.polite[1]</t>
+          <t xml:space="preserve">encourage_high_trust.shy.polite[1]</t>
         </is>
       </c>
       <c r="E209" t="inlineStr" s="2">
@@ -7008,14 +7008,14 @@
       </c>
       <c r="F209" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">え、ええと…そ、その件は…</t>
+          <t xml:space="preserve">いつも気にかけてくださって…あ、あの、本当に感謝しています…</t>
         </is>
       </c>
     </row>
     <row r="210" ht="40" customHeight="1">
       <c r="A210" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.shy.polite[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.shy.polite[1]</t>
         </is>
       </c>
       <c r="B210" t="inlineStr" s="2">
@@ -7025,12 +7025,12 @@
       </c>
       <c r="C210" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D210" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E6.shy.polite[1]</t>
+          <t xml:space="preserve">encourage.shy.polite[1]</t>
         </is>
       </c>
       <c r="E210" t="inlineStr" s="2">
@@ -7040,14 +7040,14 @@
       </c>
       <c r="F210" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">は、はい…わかりました…やってみます…</t>
+          <t xml:space="preserve">あ、ありがとうございます…そう言っていただけると、頑張れます…</t>
         </is>
       </c>
     </row>
     <row r="211" ht="40" customHeight="1">
       <c r="A211" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.shy.polite[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.shy.polite[1]</t>
         </is>
       </c>
       <c r="B211" t="inlineStr" s="2">
@@ -7057,12 +7057,12 @@
       </c>
       <c r="C211" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D211" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_boycott.shy.polite[1]</t>
+          <t xml:space="preserve">faction_decree.shy.polite[1]</t>
         </is>
       </c>
       <c r="E211" t="inlineStr" s="2">
@@ -7072,14 +7072,14 @@
       </c>
       <c r="F211" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、あの…これは、納得できません…</t>
+          <t xml:space="preserve">……あの。皆には、わたしから……</t>
         </is>
       </c>
     </row>
     <row r="212" ht="40" customHeight="1">
       <c r="A212" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.shy.polite[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.shy.polite[1]</t>
         </is>
       </c>
       <c r="B212" t="inlineStr" s="2">
@@ -7089,12 +7089,12 @@
       </c>
       <c r="C212" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D212" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_grumble.shy.polite[1]</t>
+          <t xml:space="preserve">media.shy.polite[1]</t>
         </is>
       </c>
       <c r="E212" t="inlineStr" s="2">
@@ -7104,14 +7104,14 @@
       </c>
       <c r="F212" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">すみません…少し、不満があります…</t>
+          <t xml:space="preserve">メ、メディア出演…ですか…き、緊張しますけど…や、やってみます…</t>
         </is>
       </c>
     </row>
     <row r="213" ht="40" customHeight="1">
       <c r="A213" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.shy.polite[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.shy.polite[1]</t>
         </is>
       </c>
       <c r="B213" t="inlineStr" s="2">
@@ -7121,12 +7121,12 @@
       </c>
       <c r="C213" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D213" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_sns.shy.polite[1]</t>
+          <t xml:space="preserve">party.shy.polite[1]</t>
         </is>
       </c>
       <c r="E213" t="inlineStr" s="2">
@@ -7136,14 +7136,14 @@
       </c>
       <c r="F213" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">え、SNSで…そんな風に書かれてしまって…</t>
+          <t xml:space="preserve">パ、パーティー…人が多いところは少し苦手ですけど…頑張って参加します…</t>
         </is>
       </c>
     </row>
     <row r="214" ht="40" customHeight="1">
       <c r="A214" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.shy.polite[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.shy.polite[1]</t>
         </is>
       </c>
       <c r="B214" t="inlineStr" s="2">
@@ -7153,12 +7153,12 @@
       </c>
       <c r="C214" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D214" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S1.shy.polite[1]</t>
+          <t xml:space="preserve">refresh_leave.shy.polite[1]</t>
         </is>
       </c>
       <c r="E214" t="inlineStr" s="2">
@@ -7168,14 +7168,14 @@
       </c>
       <c r="F214" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、あの…ご相談したいことが…</t>
+          <t xml:space="preserve">お休みを…？ あ、あの…ありがとうございます、ゆっくり休ませていただきます…</t>
         </is>
       </c>
     </row>
     <row r="215" ht="40" customHeight="1">
       <c r="A215" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.shy.polite[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.shy.polite[1]</t>
         </is>
       </c>
       <c r="B215" t="inlineStr" s="2">
@@ -7185,12 +7185,12 @@
       </c>
       <c r="C215" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D215" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S2.shy.polite[1]</t>
+          <t xml:space="preserve">special_treatment.shy.polite[1]</t>
         </is>
       </c>
       <c r="E215" t="inlineStr" s="2">
@@ -7200,14 +7200,14 @@
       </c>
       <c r="F215" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">す、すみません…少しお時間いただけますか…</t>
+          <t xml:space="preserve">こ、こんな特別扱い…わたしなんかに、もったいないです…</t>
         </is>
       </c>
     </row>
     <row r="216" ht="40" customHeight="1">
       <c r="A216" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.shy.polite[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.shy.polite[1]</t>
         </is>
       </c>
       <c r="B216" t="inlineStr" s="2">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="C216" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D216" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S3.shy.polite[1]</t>
+          <t xml:space="preserve">trainer.shy.polite[1]</t>
         </is>
       </c>
       <c r="E216" t="inlineStr" s="2">
@@ -7232,14 +7232,14 @@
       </c>
       <c r="F216" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、あの…どう答えたらいいか、わからなくて…</t>
+          <t xml:space="preserve">専属トレーナー…ですか…あ、あの、よろしくお願いいたします…</t>
         </is>
       </c>
     </row>
     <row r="217" ht="40" customHeight="1">
       <c r="A217" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.shy.polite[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.shy.polite[1]</t>
         </is>
       </c>
       <c r="B217" t="inlineStr" s="2">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="D217" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_direct.shy.polite[1]</t>
+          <t xml:space="preserve">E1.shy.polite[1]</t>
         </is>
       </c>
       <c r="E217" t="inlineStr" s="2">
@@ -7264,14 +7264,14 @@
       </c>
       <c r="F217" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">は、はっきり言わせていただきます…わたしは…</t>
+          <t xml:space="preserve">あ、あの…どうしたら、いいんでしょうか…</t>
         </is>
       </c>
     </row>
     <row r="218" ht="40" customHeight="1">
       <c r="A218" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.shy.polite[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E4.shy.polite[1]</t>
         </is>
       </c>
       <c r="B218" t="inlineStr" s="2">
@@ -7286,7 +7286,7 @@
       </c>
       <c r="D218" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_silent.shy.polite[1]</t>
+          <t xml:space="preserve">E4.shy.polite[1]</t>
         </is>
       </c>
       <c r="E218" t="inlineStr" s="2">
@@ -7296,14 +7296,14 @@
       </c>
       <c r="F218" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………あの…なにも、言えません…</t>
+          <t xml:space="preserve">え、ええと…そ、その件は…</t>
         </is>
       </c>
     </row>
     <row r="219" ht="40" customHeight="1">
       <c r="A219" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.shy.polite[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.shy.polite[1]</t>
         </is>
       </c>
       <c r="B219" t="inlineStr" s="2">
@@ -7318,7 +7318,7 @@
       </c>
       <c r="D219" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S5.shy.polite[1]</t>
+          <t xml:space="preserve">E6.shy.polite[1]</t>
         </is>
       </c>
       <c r="E219" t="inlineStr" s="2">
@@ -7328,14 +7328,14 @@
       </c>
       <c r="F219" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">考えさせて…いただけますか…？</t>
+          <t xml:space="preserve">は、はい…わかりました…やってみます…</t>
         </is>
       </c>
     </row>
     <row r="220" ht="40" customHeight="1">
       <c r="A220" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.shy.polite[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.shy.polite[1]</t>
         </is>
       </c>
       <c r="B220" t="inlineStr" s="2">
@@ -7350,7 +7350,7 @@
       </c>
       <c r="D220" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S6.shy.polite[1]</t>
+          <t xml:space="preserve">S_boycott.shy.polite[1]</t>
         </is>
       </c>
       <c r="E220" t="inlineStr" s="2">
@@ -7360,14 +7360,14 @@
       </c>
       <c r="F220" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">決めました…これで、いいんですよね…？</t>
+          <t xml:space="preserve">あ、あの…これは、納得できません…</t>
         </is>
       </c>
     </row>
     <row r="221" ht="40" customHeight="1">
       <c r="A221" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.shy.polite[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.shy.polite[1]</t>
         </is>
       </c>
       <c r="B221" t="inlineStr" s="2">
@@ -7377,12 +7377,12 @@
       </c>
       <c r="C221" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D221" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1.shy.polite[1]</t>
+          <t xml:space="preserve">S_grumble.shy.polite[1]</t>
         </is>
       </c>
       <c r="E221" t="inlineStr" s="2">
@@ -7392,14 +7392,14 @@
       </c>
       <c r="F221" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、あの…これから、頑張りたいことがあります…</t>
+          <t xml:space="preserve">すみません…少し、不満があります…</t>
         </is>
       </c>
     </row>
     <row r="222" ht="40" customHeight="1">
       <c r="A222" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.shy.polite[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.shy.polite[1]</t>
         </is>
       </c>
       <c r="B222" t="inlineStr" s="2">
@@ -7409,12 +7409,12 @@
       </c>
       <c r="C222" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D222" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter1.shy.polite[1]</t>
+          <t xml:space="preserve">S_sns.shy.polite[1]</t>
         </is>
       </c>
       <c r="E222" t="inlineStr" s="2">
@@ -7424,14 +7424,14 @@
       </c>
       <c r="F222" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お、お話を聞かせていただけますか…？</t>
+          <t xml:space="preserve">え、SNSで…そんな風に書かれてしまって…</t>
         </is>
       </c>
     </row>
     <row r="223" ht="40" customHeight="1">
       <c r="A223" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.shy.polite[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.shy.polite[1]</t>
         </is>
       </c>
       <c r="B223" t="inlineStr" s="2">
@@ -7441,12 +7441,12 @@
       </c>
       <c r="C223" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D223" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter2.shy.polite[1]</t>
+          <t xml:space="preserve">S1.shy.polite[1]</t>
         </is>
       </c>
       <c r="E223" t="inlineStr" s="2">
@@ -7456,14 +7456,14 @@
       </c>
       <c r="F223" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">は、はい…お聞きします…</t>
+          <t xml:space="preserve">あ、あの…ご相談したいことが…</t>
         </is>
       </c>
     </row>
     <row r="224" ht="40" customHeight="1">
       <c r="A224" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.shy.polite[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.shy.polite[1]</t>
         </is>
       </c>
       <c r="B224" t="inlineStr" s="2">
@@ -7473,12 +7473,12 @@
       </c>
       <c r="C224" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D224" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_brand.shy.polite[1]</t>
+          <t xml:space="preserve">S2.shy.polite[1]</t>
         </is>
       </c>
       <c r="E224" t="inlineStr" s="2">
@@ -7488,14 +7488,14 @@
       </c>
       <c r="F224" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ブランドのお仕事…ですか…？ あ、あの、精一杯やらせていただきます…</t>
+          <t xml:space="preserve">す、すみません…少しお時間いただけますか…</t>
         </is>
       </c>
     </row>
     <row r="225" ht="40" customHeight="1">
       <c r="A225" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.shy.polite[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.shy.polite[1]</t>
         </is>
       </c>
       <c r="B225" t="inlineStr" s="2">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="C225" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D225" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_cm.shy.polite[1]</t>
+          <t xml:space="preserve">S3.shy.polite[1]</t>
         </is>
       </c>
       <c r="E225" t="inlineStr" s="2">
@@ -7520,14 +7520,14 @@
       </c>
       <c r="F225" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">CM…ですか…？ わ、わたしなんかで、いいんでしょうか…</t>
+          <t xml:space="preserve">あ、あの…どう答えたらいいか、わからなくて…</t>
         </is>
       </c>
     </row>
     <row r="226" ht="40" customHeight="1">
       <c r="A226" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.shy.polite[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.shy.polite[1]</t>
         </is>
       </c>
       <c r="B226" t="inlineStr" s="2">
@@ -7537,12 +7537,12 @@
       </c>
       <c r="C226" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D226" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fan.shy.polite[1]</t>
+          <t xml:space="preserve">S4_direct.shy.polite[1]</t>
         </is>
       </c>
       <c r="E226" t="inlineStr" s="2">
@@ -7552,14 +7552,14 @@
       </c>
       <c r="F226" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ファンの方に…直接、お会いできるんですか…？ う、嬉しいです…</t>
+          <t xml:space="preserve">は、はっきり言わせていただきます…わたしは…</t>
         </is>
       </c>
     </row>
     <row r="227" ht="40" customHeight="1">
       <c r="A227" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.shy.polite[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.shy.polite[1]</t>
         </is>
       </c>
       <c r="B227" t="inlineStr" s="2">
@@ -7569,12 +7569,12 @@
       </c>
       <c r="C227" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D227" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fashion.shy.polite[1]</t>
+          <t xml:space="preserve">S4_silent.shy.polite[1]</t>
         </is>
       </c>
       <c r="E227" t="inlineStr" s="2">
@@ -7584,14 +7584,14 @@
       </c>
       <c r="F227" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">フ、ファッション関連のお仕事…似合うでしょうか…</t>
+          <t xml:space="preserve">………あの…なにも、言えません…</t>
         </is>
       </c>
     </row>
     <row r="228" ht="40" customHeight="1">
       <c r="A228" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.shy.polite[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.shy.polite[1]</t>
         </is>
       </c>
       <c r="B228" t="inlineStr" s="2">
@@ -7601,12 +7601,12 @@
       </c>
       <c r="C228" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D228" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_gravure.shy.polite[1]</t>
+          <t xml:space="preserve">S5.shy.polite[1]</t>
         </is>
       </c>
       <c r="E228" t="inlineStr" s="2">
@@ -7616,14 +7616,14 @@
       </c>
       <c r="F228" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">グ、グラビア…ですか…？ は、恥ずかしいです…でも、頑張ります…</t>
+          <t xml:space="preserve">考えさせて…いただけますか…？</t>
         </is>
       </c>
     </row>
     <row r="229" ht="40" customHeight="1">
       <c r="A229" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.shy.polite[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.shy.polite[1]</t>
         </is>
       </c>
       <c r="B229" t="inlineStr" s="2">
@@ -7633,12 +7633,12 @@
       </c>
       <c r="C229" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D229" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_variety.shy.polite[1]</t>
+          <t xml:space="preserve">S6.shy.polite[1]</t>
         </is>
       </c>
       <c r="E229" t="inlineStr" s="2">
@@ -7648,14 +7648,14 @@
       </c>
       <c r="F229" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">バ、バラエティ番組…ちゃんと、お話できるか不安です…</t>
+          <t xml:space="preserve">決めました…これで、いいんですよね…？</t>
         </is>
       </c>
     </row>
     <row r="230" ht="40" customHeight="1">
       <c r="A230" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.shy.polite[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.shy.polite[1]</t>
         </is>
       </c>
       <c r="B230" t="inlineStr" s="2">
@@ -7670,7 +7670,7 @@
       </c>
       <c r="D230" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4.shy.polite[1]</t>
+          <t xml:space="preserve">B1.shy.polite[1]</t>
         </is>
       </c>
       <c r="E230" t="inlineStr" s="2">
@@ -7680,14 +7680,14 @@
       </c>
       <c r="F230" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こ、こんなお仕事、わたしに務まるでしょうか…</t>
+          <t xml:space="preserve">あ、あの…これから、頑張りたいことがあります…</t>
         </is>
       </c>
     </row>
     <row r="231" ht="40" customHeight="1">
       <c r="A231" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.shy.polite[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.shy.polite[1]</t>
         </is>
       </c>
       <c r="B231" t="inlineStr" s="2">
@@ -7697,29 +7697,29 @@
       </c>
       <c r="C231" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D231" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">shy.polite[1]</t>
+          <t xml:space="preserve">B2_fighter1.shy.polite[1]</t>
         </is>
       </c>
       <c r="E231" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F231" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、あの…よ、よろしくお願いいたします…</t>
+          <t xml:space="preserve">お、お話を聞かせていただけますか…？</t>
         </is>
       </c>
     </row>
     <row r="232" ht="40" customHeight="1">
       <c r="A232" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.shy.polite[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.shy.polite[1]</t>
         </is>
       </c>
       <c r="B232" t="inlineStr" s="2">
@@ -7729,29 +7729,29 @@
       </c>
       <c r="C232" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D232" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">shy.polite[1]</t>
+          <t xml:space="preserve">B2_fighter2.shy.polite[1]</t>
         </is>
       </c>
       <c r="E232" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F232" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">す、すみません…少しだけ休ませてください…</t>
+          <t xml:space="preserve">は、はい…お聞きします…</t>
         </is>
       </c>
     </row>
     <row r="233" ht="40" customHeight="1">
       <c r="A233" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.shy.polite[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.shy.polite[1]</t>
         </is>
       </c>
       <c r="B233" t="inlineStr" s="2">
@@ -7761,29 +7761,29 @@
       </c>
       <c r="C233" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D233" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.shy.polite[1]</t>
+          <t xml:space="preserve">B4_brand.shy.polite[1]</t>
         </is>
       </c>
       <c r="E233" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F233" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、あの…よ、よろしくお願いいたします…</t>
+          <t xml:space="preserve">ブランドのお仕事…ですか…？ あ、あの、精一杯やらせていただきます…</t>
         </is>
       </c>
     </row>
     <row r="234" ht="40" customHeight="1">
       <c r="A234" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.shy.polite[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.shy.polite[1]</t>
         </is>
       </c>
       <c r="B234" t="inlineStr" s="2">
@@ -7793,29 +7793,29 @@
       </c>
       <c r="C234" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D234" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.shy.polite[1]</t>
+          <t xml:space="preserve">B4_cm.shy.polite[1]</t>
         </is>
       </c>
       <c r="E234" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F234" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">す、すみません…少しだけ休ませてください…</t>
+          <t xml:space="preserve">CM…ですか…？ わ、わたしなんかで、いいんでしょうか…</t>
         </is>
       </c>
     </row>
     <row r="235" ht="40" customHeight="1">
       <c r="A235" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.shy.polite[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.shy.polite[1]</t>
         </is>
       </c>
       <c r="B235" t="inlineStr" s="2">
@@ -7825,29 +7825,29 @@
       </c>
       <c r="C235" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D235" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.shy.polite[1]</t>
+          <t xml:space="preserve">B4_fan.shy.polite[1]</t>
         </is>
       </c>
       <c r="E235" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F235" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ご、ごめんなさい…お、お世話になりました…</t>
+          <t xml:space="preserve">ファンの方に…直接、お会いできるんですか…？ う、嬉しいです…</t>
         </is>
       </c>
     </row>
     <row r="236" ht="40" customHeight="1">
       <c r="A236" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.shy.polite[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.shy.polite[1]</t>
         </is>
       </c>
       <c r="B236" t="inlineStr" s="2">
@@ -7857,29 +7857,29 @@
       </c>
       <c r="C236" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D236" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">shy.polite[1]</t>
+          <t xml:space="preserve">B4_fashion.shy.polite[1]</t>
         </is>
       </c>
       <c r="E236" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F236" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ご、ごめんなさい…お、お世話になりました…</t>
+          <t xml:space="preserve">フ、ファッション関連のお仕事…似合うでしょうか…</t>
         </is>
       </c>
     </row>
     <row r="237" ht="40" customHeight="1">
       <c r="A237" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.shy.polite[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.shy.polite[1]</t>
         </is>
       </c>
       <c r="B237" t="inlineStr" s="2">
@@ -7889,29 +7889,29 @@
       </c>
       <c r="C237" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D237" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_60_up.shy.polite[1]</t>
+          <t xml:space="preserve">B4_gravure.shy.polite[1]</t>
         </is>
       </c>
       <c r="E237" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F237" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一緒にいると…少しだけ自分に自信が持てるんです…</t>
+          <t xml:space="preserve">グ、グラビア…ですか…？ は、恥ずかしいです…でも、頑張ります…</t>
         </is>
       </c>
     </row>
     <row r="238" ht="40" customHeight="1">
       <c r="A238" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.goodLoss.shy.polite[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.shy.polite[1]</t>
         </is>
       </c>
       <c r="B238" t="inlineStr" s="2">
@@ -7921,29 +7921,29 @@
       </c>
       <c r="C238" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D238" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.goodLoss.shy.polite[1]</t>
+          <t xml:space="preserve">B4_variety.shy.polite[1]</t>
         </is>
       </c>
       <c r="E238" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F238" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けてしまいましたが…悔いはありません…</t>
+          <t xml:space="preserve">バ、バラエティ番組…ちゃんと、お話できるか不安です…</t>
         </is>
       </c>
     </row>
     <row r="239" ht="40" customHeight="1">
       <c r="A239" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.goodLoss.shy.polite[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.shy.polite[1]</t>
         </is>
       </c>
       <c r="B239" t="inlineStr" s="2">
@@ -7953,29 +7953,29 @@
       </c>
       <c r="C239" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D239" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.goodLoss.shy.polite[2]</t>
+          <t xml:space="preserve">B4.shy.polite[1]</t>
         </is>
       </c>
       <c r="E239" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F239" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">全力は、出せたと思います…</t>
+          <t xml:space="preserve">こ、こんなお仕事、わたしに務まるでしょうか…</t>
         </is>
       </c>
     </row>
     <row r="240" ht="40" customHeight="1">
       <c r="A240" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin.shy.polite[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.shy.polite[1]</t>
         </is>
       </c>
       <c r="B240" t="inlineStr" s="2">
@@ -7985,29 +7985,29 @@
       </c>
       <c r="C240" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
         </is>
       </c>
       <c r="D240" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.greatWin.shy.polite[1]</t>
+          <t xml:space="preserve">shy.polite[1]</t>
         </is>
       </c>
       <c r="E240" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F240" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こ、こんな大きな勝利…信じられません…ありがとうございます…</t>
+          <t xml:space="preserve">あ、あの…私などでよろしければ…せ、精一杯務めます…</t>
         </is>
       </c>
     </row>
     <row r="241" ht="40" customHeight="1">
       <c r="A241" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin.shy.polite[2]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.shy.polite[1]</t>
         </is>
       </c>
       <c r="B241" t="inlineStr" s="2">
@@ -8017,29 +8017,29 @@
       </c>
       <c r="C241" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D241" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.greatWin.shy.polite[2]</t>
+          <t xml:space="preserve">shy.polite[1]</t>
         </is>
       </c>
       <c r="E241" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F241" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こんな日が、来るなんて…夢みたいです…</t>
+          <t xml:space="preserve">あ、あの…よ、よろしくお願いいたします…</t>
         </is>
       </c>
     </row>
     <row r="242" ht="40" customHeight="1">
       <c r="A242" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.shy.polite[1]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.shy.polite[1]</t>
         </is>
       </c>
       <c r="B242" t="inlineStr" s="2">
@@ -8049,29 +8049,29 @@
       </c>
       <c r="C242" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
         </is>
       </c>
       <c r="D242" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.loss.shy.polite[1]</t>
+          <t xml:space="preserve">shy.polite[1]</t>
         </is>
       </c>
       <c r="E242" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F242" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ま、負けてしまいました…ご、ごめんなさい…</t>
+          <t xml:space="preserve">あ、あの…よろしくお願いいたします…精一杯やります…</t>
         </is>
       </c>
     </row>
     <row r="243" ht="40" customHeight="1">
       <c r="A243" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.shy.polite[2]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.shy.polite[1]</t>
         </is>
       </c>
       <c r="B243" t="inlineStr" s="2">
@@ -8081,29 +8081,29 @@
       </c>
       <c r="C243" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
         </is>
       </c>
       <c r="D243" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.loss.shy.polite[2]</t>
+          <t xml:space="preserve">shy.polite[1]</t>
         </is>
       </c>
       <c r="E243" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F243" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次こそは…勝ちたいです…</t>
+          <t xml:space="preserve">よ、よろしくお願いいたします…が、頑張ります…！</t>
         </is>
       </c>
     </row>
     <row r="244" ht="40" customHeight="1">
       <c r="A244" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.shy.polite[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.shy.polite[1]</t>
         </is>
       </c>
       <c r="B244" t="inlineStr" s="2">
@@ -8113,29 +8113,29 @@
       </c>
       <c r="C244" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D244" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.win.shy.polite[1]</t>
+          <t xml:space="preserve">shy.polite[1]</t>
         </is>
       </c>
       <c r="E244" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F244" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">か、勝てました…応援、ありがとうございます…</t>
+          <t xml:space="preserve">す、すみません…少しだけ休ませてください…</t>
         </is>
       </c>
     </row>
     <row r="245" ht="40" customHeight="1">
       <c r="A245" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.shy.polite[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.shy.polite[1]</t>
         </is>
       </c>
       <c r="B245" t="inlineStr" s="2">
@@ -8145,29 +8145,29 @@
       </c>
       <c r="C245" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D245" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.win.shy.polite[2]</t>
+          <t xml:space="preserve">bitterPrematch.ahead.shy.polite[1]</t>
         </is>
       </c>
       <c r="E245" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F245" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今日は…良い試合が、できたと思います…</t>
+          <t xml:space="preserve">勝たせて…いただきました。…なのに、怖いままです…</t>
         </is>
       </c>
     </row>
     <row r="246" ht="40" customHeight="1">
       <c r="A246" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.shy.polite[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.shy.polite[1]</t>
         </is>
       </c>
       <c r="B246" t="inlineStr" s="2">
@@ -8177,29 +8177,29 @@
       </c>
       <c r="C246" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D246" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-02.shy.polite[1]</t>
+          <t xml:space="preserve">bitterPrematch.behind.shy.polite[1]</t>
         </is>
       </c>
       <c r="E246" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F246" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、あの…今日は、よろしくお願いいたします…</t>
+          <t xml:space="preserve">…もう終わったって…言われました。…言われただけです…</t>
         </is>
       </c>
     </row>
     <row r="247" ht="40" customHeight="1">
       <c r="A247" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.shy.polite[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.shy.polite[1]</t>
         </is>
       </c>
       <c r="B247" t="inlineStr" s="2">
@@ -8209,29 +8209,29 @@
       </c>
       <c r="C247" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D247" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-02.shy.polite[2]</t>
+          <t xml:space="preserve">draftInterest.shy.polite[1]</t>
         </is>
       </c>
       <c r="E247" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F247" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">頑張ります…</t>
+          <t xml:space="preserve">あ、あの…私などでよろしければ…せ、精一杯務めます…</t>
         </is>
       </c>
     </row>
     <row r="248" ht="40" customHeight="1">
       <c r="A248" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.down.shy.polite[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.shy.polite[1]</t>
         </is>
       </c>
       <c r="B248" t="inlineStr" s="2">
@@ -8241,29 +8241,29 @@
       </c>
       <c r="C248" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D248" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-03.down.shy.polite[1]</t>
+          <t xml:space="preserve">draftJoin.shy.polite[1]</t>
         </is>
       </c>
       <c r="E248" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F248" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">う、うまくいきません…どうしたら…</t>
+          <t xml:space="preserve">あ、あの…よ、よろしくお願いいたします…</t>
         </is>
       </c>
     </row>
     <row r="249" ht="40" customHeight="1">
       <c r="A249" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.up.shy.polite[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.shy.polite[1]</t>
         </is>
       </c>
       <c r="B249" t="inlineStr" s="2">
@@ -8273,29 +8273,29 @@
       </c>
       <c r="C249" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D249" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-03.up.shy.polite[1]</t>
+          <t xml:space="preserve">faGreeting.shy.polite[1]</t>
         </is>
       </c>
       <c r="E249" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F249" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">調子が…良い気がします…</t>
+          <t xml:space="preserve">あ、あの…契約してもらえて…感謝しています…！</t>
         </is>
       </c>
     </row>
     <row r="250" ht="40" customHeight="1">
       <c r="A250" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04.shy.polite[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.shy.polite[1]</t>
         </is>
       </c>
       <c r="B250" t="inlineStr" s="2">
@@ -8305,29 +8305,29 @@
       </c>
       <c r="C250" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D250" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-04.shy.polite[1]</t>
+          <t xml:space="preserve">faSigning.shy.polite[1]</t>
         </is>
       </c>
       <c r="E250" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F250" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">練習…させていただきます…</t>
+          <t xml:space="preserve">あ、あの…よろしくお願いいたします…精一杯やります…</t>
         </is>
       </c>
     </row>
     <row r="251" ht="40" customHeight="1">
       <c r="A251" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04.shy.polite[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.shy.polite[1]</t>
         </is>
       </c>
       <c r="B251" t="inlineStr" s="2">
@@ -8337,29 +8337,29 @@
       </c>
       <c r="C251" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D251" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-04.shy.polite[2]</t>
+          <t xml:space="preserve">faWelcome.shy.polite[1]</t>
         </is>
       </c>
       <c r="E251" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F251" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もう少し…頑張ります…</t>
+          <t xml:space="preserve">よ、よろしくお願いいたします…が、頑張ります…！</t>
         </is>
       </c>
     </row>
     <row r="252" ht="40" customHeight="1">
       <c r="A252" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05.shy.polite[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.fresh.shy.polite[1]</t>
         </is>
       </c>
       <c r="B252" t="inlineStr" s="2">
@@ -8369,29 +8369,29 @@
       </c>
       <c r="C252" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D252" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-05.shy.polite[1]</t>
+          <t xml:space="preserve">heatSelf.fresh.shy.polite[1]</t>
         </is>
       </c>
       <c r="E252" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F252" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、あの…大丈夫です、心配しないでください…</t>
+          <t xml:space="preserve">あ、あの…今日は体が軽くて…もっと、やれます…!</t>
         </is>
       </c>
     </row>
     <row r="253" ht="40" customHeight="1">
       <c r="A253" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05.shy.polite[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.heavy.shy.polite[1]</t>
         </is>
       </c>
       <c r="B253" t="inlineStr" s="2">
@@ -8401,29 +8401,29 @@
       </c>
       <c r="C253" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D253" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-05.shy.polite[2]</t>
+          <t xml:space="preserve">heatSelf.heavy.shy.polite[1]</t>
         </is>
       </c>
       <c r="E253" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F253" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ご心配を、おかけして…</t>
+          <t xml:space="preserve">すみません…動けてはいるんですけど…空回りしてしまって</t>
         </is>
       </c>
     </row>
     <row r="254" ht="40" customHeight="1">
       <c r="A254" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.shy.polite[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.warm.shy.polite[1]</t>
         </is>
       </c>
       <c r="B254" t="inlineStr" s="2">
@@ -8433,29 +8433,29 @@
       </c>
       <c r="C254" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D254" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-06.shy.polite[1]</t>
+          <t xml:space="preserve">heatSelf.warm.shy.polite[1]</t>
         </is>
       </c>
       <c r="E254" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F254" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">みんなと…一緒だと、心強いです…</t>
+          <t xml:space="preserve">あの…できてはいるんです。ただ、残らなくて…</t>
         </is>
       </c>
     </row>
     <row r="255" ht="40" customHeight="1">
       <c r="A255" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.shy.polite[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.shy.polite[1]</t>
         </is>
       </c>
       <c r="B255" t="inlineStr" s="2">
@@ -8465,29 +8465,29 @@
       </c>
       <c r="C255" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D255" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-06.shy.polite[2]</t>
+          <t xml:space="preserve">injury.shy.polite[1]</t>
         </is>
       </c>
       <c r="E255" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F255" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">仲間って、いいですね…</t>
+          <t xml:space="preserve">す、すみません…少しだけ休ませてください…</t>
         </is>
       </c>
     </row>
     <row r="256" ht="40" customHeight="1">
       <c r="A256" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07.shy.polite[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.shy.polite[1]</t>
         </is>
       </c>
       <c r="B256" t="inlineStr" s="2">
@@ -8497,29 +8497,29 @@
       </c>
       <c r="C256" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D256" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-07.shy.polite[1]</t>
+          <t xml:space="preserve">release.shy.polite[1]</t>
         </is>
       </c>
       <c r="E256" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F256" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お、お客さんがいっぱいで…き、緊張します…</t>
+          <t xml:space="preserve">ご、ごめんなさい…お、お世話になりました…</t>
         </is>
       </c>
     </row>
     <row r="257" ht="40" customHeight="1">
       <c r="A257" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07.shy.polite[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.shy.polite[1]</t>
         </is>
       </c>
       <c r="B257" t="inlineStr" s="2">
@@ -8529,29 +8529,29 @@
       </c>
       <c r="C257" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D257" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-07.shy.polite[2]</t>
+          <t xml:space="preserve">rentalGreeting.shy.polite[1]</t>
         </is>
       </c>
       <c r="E257" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F257" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">がんばります…</t>
+          <t xml:space="preserve">あ、あの…短い間ではございますが…よろしくお願いいたします…</t>
         </is>
       </c>
     </row>
     <row r="258" ht="40" customHeight="1">
       <c r="A258" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.shy.polite[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.shy.polite[1]</t>
         </is>
       </c>
       <c r="B258" t="inlineStr" s="2">
@@ -8561,29 +8561,29 @@
       </c>
       <c r="C258" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D258" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-08.shy.polite[1]</t>
+          <t xml:space="preserve">scoutGreeting.shy.polite[1]</t>
         </is>
       </c>
       <c r="E258" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F258" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、あの…体調は、大丈夫です…</t>
+          <t xml:space="preserve">あ、あの…お声がけ、光栄です…！</t>
         </is>
       </c>
     </row>
     <row r="259" ht="40" customHeight="1">
       <c r="A259" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.shy.polite[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.shy.polite[1]</t>
         </is>
       </c>
       <c r="B259" t="inlineStr" s="2">
@@ -8593,29 +8593,29 @@
       </c>
       <c r="C259" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D259" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-08.shy.polite[2]</t>
+          <t xml:space="preserve">titleChallengeLoss.shy.polite[1]</t>
         </is>
       </c>
       <c r="E259" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F259" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">無理はしません…</t>
+          <t xml:space="preserve">…申し訳ありません…でも…諦めたくないんです…</t>
         </is>
       </c>
     </row>
     <row r="260" ht="40" customHeight="1">
       <c r="A260" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.shy.polite[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.shy.polite[1]</t>
         </is>
       </c>
       <c r="B260" t="inlineStr" s="2">
@@ -8625,29 +8625,29 @@
       </c>
       <c r="C260" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D260" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-09.shy.polite[1]</t>
+          <t xml:space="preserve">titleDefense.shy.polite[1]</t>
         </is>
       </c>
       <c r="E260" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F260" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次の試合…が、頑張ります…</t>
+          <t xml:space="preserve">よ、よかった…守れました…（ほっとしている）</t>
         </is>
       </c>
     </row>
     <row r="261" ht="40" customHeight="1">
       <c r="A261" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.shy.polite[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.shy.polite[1]</t>
         </is>
       </c>
       <c r="B261" t="inlineStr" s="2">
@@ -8657,29 +8657,29 @@
       </c>
       <c r="C261" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D261" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-09.shy.polite[2]</t>
+          <t xml:space="preserve">titleLoss.shy.polite[1]</t>
         </is>
       </c>
       <c r="E261" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F261" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">しっかり、準備します…</t>
+          <t xml:space="preserve">…申し訳ありません…ベルト…守れませんでした…</t>
         </is>
       </c>
     </row>
     <row r="262" ht="40" customHeight="1">
       <c r="A262" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.shy.polite[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.shy.polite[1]</t>
         </is>
       </c>
       <c r="B262" t="inlineStr" s="2">
@@ -8689,29 +8689,29 @@
       </c>
       <c r="C262" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D262" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-10.shy.polite[1]</t>
+          <t xml:space="preserve">titleWin.shy.polite[1]</t>
         </is>
       </c>
       <c r="E262" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F262" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、あの…ありがとうございます…</t>
+          <t xml:space="preserve">え…わ、私が…チャンピオン、ですか…？ 夢のようです…</t>
         </is>
       </c>
     </row>
     <row r="263" ht="40" customHeight="1">
       <c r="A263" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.shy.polite[2]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.shy.polite[1]</t>
         </is>
       </c>
       <c r="B263" t="inlineStr" s="2">
@@ -8721,29 +8721,29 @@
       </c>
       <c r="C263" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D263" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-10.shy.polite[2]</t>
+          <t xml:space="preserve">shy.polite[1]</t>
         </is>
       </c>
       <c r="E263" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F263" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">感謝、しています…</t>
+          <t xml:space="preserve">ご、ごめんなさい…お、お世話になりました…</t>
         </is>
       </c>
     </row>
     <row r="264" ht="40" customHeight="1">
       <c r="A264" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.shy.polite[1]</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.shy.polite[1]</t>
         </is>
       </c>
       <c r="B264" t="inlineStr" s="2">
@@ -8753,7 +8753,7 @@
       </c>
       <c r="C264" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
         </is>
       </c>
       <c r="D264" t="inlineStr" s="12">
@@ -8763,19 +8763,19 @@
       </c>
       <c r="E264" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F264" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">良い流れが…止まってしまいました…で、でも、また頑張ります…</t>
+          <t xml:space="preserve">あ、あの…短い間ではございますが…よろしくお願いいたします…</t>
         </is>
       </c>
     </row>
     <row r="265" ht="40" customHeight="1">
       <c r="A265" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.shy.polite[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.shy.polite[1]</t>
         </is>
       </c>
       <c r="B265" t="inlineStr" s="2">
@@ -8785,29 +8785,29 @@
       </c>
       <c r="C265" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D265" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.shy.polite[1]</t>
+          <t xml:space="preserve">shy.polite[1]</t>
         </is>
       </c>
       <c r="E265" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F265" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">け、決勝…。信じられないけど…最後まで、立たせてください…</t>
+          <t xml:space="preserve">…申し訳ありません…でも…諦めたくないんです…</t>
         </is>
       </c>
     </row>
     <row r="266" ht="40" customHeight="1">
       <c r="A266" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.shy.polite[2]</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.shy.polite[1]</t>
         </is>
       </c>
       <c r="B266" t="inlineStr" s="2">
@@ -8817,29 +8817,29 @@
       </c>
       <c r="C266" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
         </is>
       </c>
       <c r="D266" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.shy.polite[2]</t>
+          <t xml:space="preserve">shy.polite[1]</t>
         </is>
       </c>
       <c r="E266" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F266" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">身体は痛いです…でも、ここで退いたら、繋いでくれた分が…</t>
+          <t xml:space="preserve">よ、よかった…守れました…（ほっとしている）</t>
         </is>
       </c>
     </row>
     <row r="267" ht="40" customHeight="1">
       <c r="A267" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.shy.polite[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.shy.polite[1]</t>
         </is>
       </c>
       <c r="B267" t="inlineStr" s="2">
@@ -8849,29 +8849,29 @@
       </c>
       <c r="C267" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D267" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.shy.polite[1]</t>
+          <t xml:space="preserve">shy.polite[1]</t>
         </is>
       </c>
       <c r="E267" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F267" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">つ、相手の方…がんばります。仲間が待ってるので、退けません…</t>
+          <t xml:space="preserve">…申し訳ありません…ベルト…守れませんでした…</t>
         </is>
       </c>
     </row>
     <row r="268" ht="40" customHeight="1">
       <c r="A268" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.shy.polite[2]</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.shy.polite[1]</t>
         </is>
       </c>
       <c r="B268" t="inlineStr" s="2">
@@ -8881,29 +8881,29 @@
       </c>
       <c r="C268" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
         </is>
       </c>
       <c r="D268" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.shy.polite[2]</t>
+          <t xml:space="preserve">shy.polite[1]</t>
         </is>
       </c>
       <c r="E268" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F268" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こ、怖いです…でも、ここで止まったら、みんなに申し訳なくて…</t>
+          <t xml:space="preserve">え…わ、私が…チャンピオン、ですか…？ 夢のようです…</t>
         </is>
       </c>
     </row>
     <row r="269" ht="40" customHeight="1">
       <c r="A269" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.shy.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.shy.polite[1]</t>
         </is>
       </c>
       <c r="B269" t="inlineStr" s="2">
@@ -8913,29 +8913,29 @@
       </c>
       <c r="C269" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D269" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.shy.polite[1]</t>
+          <t xml:space="preserve">bond_39_down.shy.polite[1]</t>
         </is>
       </c>
       <c r="E269" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F269" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">い、一人、倒せました…! はぁ…まだ、退けません…次の方、来てください…!</t>
+          <t xml:space="preserve">…もう…同じ部屋にいるだけで…苦しいんです…</t>
         </is>
       </c>
     </row>
     <row r="270" ht="40" customHeight="1">
       <c r="A270" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.shy.polite[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.shy.polite[1]</t>
         </is>
       </c>
       <c r="B270" t="inlineStr" s="2">
@@ -8945,29 +8945,29 @@
       </c>
       <c r="C270" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D270" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.shy.polite[2]</t>
+          <t xml:space="preserve">bond_59_down.shy.polite[1]</t>
         </is>
       </c>
       <c r="E270" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F270" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">怖いです…でも、まだ立ってます。仲間に繋ぐまで、ここは…次、どうぞ…</t>
+          <t xml:space="preserve">最近…目を合わせるのが怖くて…私、何かしてしまったんでしょうか…</t>
         </is>
       </c>
     </row>
     <row r="271" ht="40" customHeight="1">
       <c r="A271" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.shy.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.shy.polite[2]</t>
         </is>
       </c>
       <c r="B271" t="inlineStr" s="2">
@@ -8977,29 +8977,29 @@
       </c>
       <c r="C271" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D271" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.shy.polite[1]</t>
+          <t xml:space="preserve">bond_59_down.shy.polite[2]</t>
         </is>
       </c>
       <c r="E271" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F271" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わ、私がMVPなんて……二人がいてくれたから、ここまで来られたんです</t>
+          <t xml:space="preserve">あの方の態度が…前と違うんです…私のせい…ですよね…</t>
         </is>
       </c>
     </row>
     <row r="272" ht="40" customHeight="1">
       <c r="A272" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.shy.polite[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.shy.polite[1]</t>
         </is>
       </c>
       <c r="B272" t="inlineStr" s="2">
@@ -9009,29 +9009,29 @@
       </c>
       <c r="C272" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D272" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.shy.polite[2]</t>
+          <t xml:space="preserve">bond_60_up.shy.polite[1]</t>
         </is>
       </c>
       <c r="E272" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F272" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">三人で勝てて、本当によかったです。私は……二人に助けられてばかりで</t>
+          <t xml:space="preserve">一緒にいると…少しだけ自分に自信が持てるんです…</t>
         </is>
       </c>
     </row>
     <row r="273" ht="40" customHeight="1">
       <c r="A273" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.shy.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.shy.polite[1]</t>
         </is>
       </c>
       <c r="B273" t="inlineStr" s="2">
@@ -9041,29 +9041,29 @@
       </c>
       <c r="C273" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D273" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.shy.polite[1]</t>
+          <t xml:space="preserve">bond_80_up.shy.polite[1]</t>
         </is>
       </c>
       <c r="E273" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F273" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">MVPは……嬉しいです。でも、みんなで勝ちたかったです。次こそは……</t>
+          <t xml:space="preserve">あの方がいなければ…私、とっくに駄目になっていたと思います…</t>
         </is>
       </c>
     </row>
     <row r="274" ht="40" customHeight="1">
       <c r="A274" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.shy.polite[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.shy.polite[2]</t>
         </is>
       </c>
       <c r="B274" t="inlineStr" s="2">
@@ -9073,29 +9073,29 @@
       </c>
       <c r="C274" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D274" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.shy.polite[2]</t>
+          <t xml:space="preserve">bond_80_up.shy.polite[2]</t>
         </is>
       </c>
       <c r="E274" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F274" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人だけ褒められても……素直に喜べなくて。次は一緒に笑いたいです</t>
+          <t xml:space="preserve">隣にいてくださるだけで…なんでも頑張れる気がするんです…</t>
         </is>
       </c>
     </row>
     <row r="275" ht="40" customHeight="1">
       <c r="A275" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.shy.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.shy.polite[1]</t>
         </is>
       </c>
       <c r="B275" t="inlineStr" s="2">
@@ -9105,29 +9105,29 @@
       </c>
       <c r="C275" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D275" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.shy.polite[1]</t>
+          <t xml:space="preserve">rivalry_29_down.shy.polite[1]</t>
         </is>
       </c>
       <c r="E275" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F275" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ず、ずっと怖かったです。でも……最後まで立っていられたのは、応援のおかげです</t>
+          <t xml:space="preserve">最近…あの方のこと、前ほど気にならなくなった…かもしれません…</t>
         </is>
       </c>
     </row>
     <row r="276" ht="40" customHeight="1">
       <c r="A276" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.shy.polite[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.shy.polite[2]</t>
         </is>
       </c>
       <c r="B276" t="inlineStr" s="2">
@@ -9137,29 +9137,29 @@
       </c>
       <c r="C276" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D276" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.shy.polite[2]</t>
+          <t xml:space="preserve">rivalry_29_down.shy.polite[2]</t>
         </is>
       </c>
       <c r="E276" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F276" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">身体が震えてます。でも……逃げなかったこと、褒めてもらえますか……</t>
+          <t xml:space="preserve">あの頃の張りつめた感じ…もうないんでしょうか…</t>
         </is>
       </c>
     </row>
     <row r="277" ht="40" customHeight="1">
       <c r="A277" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.shy.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.shy.polite[1]</t>
         </is>
       </c>
       <c r="B277" t="inlineStr" s="2">
@@ -9169,29 +9169,29 @@
       </c>
       <c r="C277" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D277" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.shy.polite[1]</t>
+          <t xml:space="preserve">rivalry_30_up.shy.polite[1]</t>
         </is>
       </c>
       <c r="E277" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F277" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ゆ、優勝…ですか…？ ほ、本当に…？ あ、ありがとうございます…!</t>
+          <t xml:space="preserve">あの方のことを考えると…胸が締めつけられて…負けたくないんです…</t>
         </is>
       </c>
     </row>
     <row r="278" ht="40" customHeight="1">
       <c r="A278" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.shy.polite[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.shy.polite[2]</t>
         </is>
       </c>
       <c r="B278" t="inlineStr" s="2">
@@ -9201,29 +9201,29 @@
       </c>
       <c r="C278" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D278" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.shy.polite[2]</t>
+          <t xml:space="preserve">rivalry_30_up.shy.polite[2]</t>
         </is>
       </c>
       <c r="E278" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F278" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">夢みたいで…まだ、信じられません…</t>
+          <t xml:space="preserve">練習しているのを見かけると…私も走り出したくなります…</t>
         </is>
       </c>
     </row>
     <row r="279" ht="40" customHeight="1">
       <c r="A279" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.shy.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.shy.polite[1]</t>
         </is>
       </c>
       <c r="B279" t="inlineStr" s="2">
@@ -9233,29 +9233,29 @@
       </c>
       <c r="C279" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D279" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.shy.polite[1]</t>
+          <t xml:space="preserve">rivalry_50_up.shy.polite[1]</t>
         </is>
       </c>
       <c r="E279" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F279" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ま、負けてしまいました…ごめんなさい…</t>
+          <t xml:space="preserve">あの方にだけは…絶対に負けたくありません…今はそれだけです…</t>
         </is>
       </c>
     </row>
     <row r="280" ht="40" customHeight="1">
       <c r="A280" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.shy.polite[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.shy.polite[2]</t>
         </is>
       </c>
       <c r="B280" t="inlineStr" s="2">
@@ -9265,29 +9265,29 @@
       </c>
       <c r="C280" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D280" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.shy.polite[2]</t>
+          <t xml:space="preserve">rivalry_50_up.shy.polite[2]</t>
         </is>
       </c>
       <c r="E280" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F280" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もっと…強くならないと…</t>
+          <t xml:space="preserve">怖いです…けれど、逃げたらもっと後悔します…だから…</t>
         </is>
       </c>
     </row>
     <row r="281" ht="40" customHeight="1">
       <c r="A281" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.shy.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.shy.polite[1]</t>
         </is>
       </c>
       <c r="B281" t="inlineStr" s="2">
@@ -9297,29 +9297,29 @@
       </c>
       <c r="C281" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D281" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.shy.polite[1]</t>
+          <t xml:space="preserve">rivalry_70_up.shy.polite[1]</t>
         </is>
       </c>
       <c r="E281" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F281" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">か、勝てました…次もがんばります…</t>
+          <t xml:space="preserve">あの方がいなければ…今の私はいません。それだけは…わかるんです…</t>
         </is>
       </c>
     </row>
     <row r="282" ht="40" customHeight="1">
       <c r="A282" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.shy.polite[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.shy.polite[2]</t>
         </is>
       </c>
       <c r="B282" t="inlineStr" s="2">
@@ -9329,29 +9329,29 @@
       </c>
       <c r="C282" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D282" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.shy.polite[2]</t>
+          <t xml:space="preserve">rivalry_70_up.shy.polite[2]</t>
         </is>
       </c>
       <c r="E282" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F282" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一勝、できました…</t>
+          <t xml:space="preserve">逃げたい…でも…あの方からだけは逃げてはいけない…</t>
         </is>
       </c>
     </row>
     <row r="283" ht="40" customHeight="1">
       <c r="A283" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.shy.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.shy.polite[1]</t>
         </is>
       </c>
       <c r="B283" t="inlineStr" s="2">
@@ -9361,29 +9361,29 @@
       </c>
       <c r="C283" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D283" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.shy.polite[1]</t>
+          <t xml:space="preserve">trust_above_75.shy.polite[1]</t>
         </is>
       </c>
       <c r="E283" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F283" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">か、勝ち上がれました…信じられません…</t>
+          <t xml:space="preserve">ここにいてもいいんだと…最近ようやく思えるようになったんです…</t>
         </is>
       </c>
     </row>
     <row r="284" ht="40" customHeight="1">
       <c r="A284" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.shy.polite[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.shy.polite[2]</t>
         </is>
       </c>
       <c r="B284" t="inlineStr" s="2">
@@ -9393,29 +9393,29 @@
       </c>
       <c r="C284" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D284" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.shy.polite[2]</t>
+          <t xml:space="preserve">trust_above_75.shy.polite[2]</t>
         </is>
       </c>
       <c r="E284" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F284" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ…続けられるんですね…</t>
+          <t xml:space="preserve">この団体に来られて…本当によかったです…心からそう思います…</t>
         </is>
       </c>
     </row>
     <row r="285" ht="40" customHeight="1">
       <c r="A285" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.shy.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.shy.polite[1]</t>
         </is>
       </c>
       <c r="B285" t="inlineStr" s="2">
@@ -9425,29 +9425,29 @@
       </c>
       <c r="C285" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D285" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.shy.polite[1]</t>
+          <t xml:space="preserve">trust_below_20.shy.polite[1]</t>
         </is>
       </c>
       <c r="E285" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F285" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">け、決勝戦…ですか…し、信じられません…</t>
+          <t xml:space="preserve">…もう…無理です…ここにいてはいけない気がするんです……</t>
         </is>
       </c>
     </row>
     <row r="286" ht="40" customHeight="1">
       <c r="A286" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.shy.polite[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.shy.polite[1]</t>
         </is>
       </c>
       <c r="B286" t="inlineStr" s="2">
@@ -9457,29 +9457,29 @@
       </c>
       <c r="C286" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D286" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.shy.polite[2]</t>
+          <t xml:space="preserve">trust_below_35.shy.polite[1]</t>
         </is>
       </c>
       <c r="E286" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F286" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">夢みたい、です…</t>
+          <t xml:space="preserve">…ここに私の居場所なんて…あるんでしょうか……</t>
         </is>
       </c>
     </row>
     <row r="287" ht="40" customHeight="1">
       <c r="A287" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.shy.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.goodLoss.shy.polite[1]</t>
         </is>
       </c>
       <c r="B287" t="inlineStr" s="2">
@@ -9489,29 +9489,29 @@
       </c>
       <c r="C287" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D287" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.shy.polite[1]</t>
+          <t xml:space="preserve">GL-01.goodLoss.shy.polite[1]</t>
         </is>
       </c>
       <c r="E287" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F287" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">き、緊張します…でも、精一杯やります…</t>
+          <t xml:space="preserve">負けてしまいましたが…悔いはありません…</t>
         </is>
       </c>
     </row>
     <row r="288" ht="40" customHeight="1">
       <c r="A288" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.shy.polite[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.goodLoss.shy.polite[2]</t>
         </is>
       </c>
       <c r="B288" t="inlineStr" s="2">
@@ -9521,29 +9521,29 @@
       </c>
       <c r="C288" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D288" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.shy.polite[2]</t>
+          <t xml:space="preserve">GL-01.goodLoss.shy.polite[2]</t>
         </is>
       </c>
       <c r="E288" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F288" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふ、深呼吸…落ち着かないと…</t>
+          <t xml:space="preserve">全力は、出せたと思います…</t>
         </is>
       </c>
     </row>
     <row r="289" ht="40" customHeight="1">
       <c r="A289" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.shy.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin.shy.polite[1]</t>
         </is>
       </c>
       <c r="B289" t="inlineStr" s="2">
@@ -9553,29 +9553,29 @@
       </c>
       <c r="C289" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D289" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.shy.polite[1]</t>
+          <t xml:space="preserve">GL-01.greatWin.shy.polite[1]</t>
         </is>
       </c>
       <c r="E289" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F289" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">え、わたしが…ジュニアトーナメントに…？ あ、あの、頑張ります…!</t>
+          <t xml:space="preserve">こ、こんな大きな勝利…信じられません…ありがとうございます…</t>
         </is>
       </c>
     </row>
     <row r="290" ht="40" customHeight="1">
       <c r="A290" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.shy.polite[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin.shy.polite[2]</t>
         </is>
       </c>
       <c r="B290" t="inlineStr" s="2">
@@ -9585,29 +9585,29 @@
       </c>
       <c r="C290" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D290" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.shy.polite[2]</t>
+          <t xml:space="preserve">GL-01.greatWin.shy.polite[2]</t>
         </is>
       </c>
       <c r="E290" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F290" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">選んでいただいて…あ、ありがとうございます…</t>
+          <t xml:space="preserve">こんな日が、来るなんて…夢みたいです…</t>
         </is>
       </c>
     </row>
     <row r="291" ht="40" customHeight="1">
       <c r="A291" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.shy.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.shy.polite[1]</t>
         </is>
       </c>
       <c r="B291" t="inlineStr" s="2">
@@ -9617,29 +9617,29 @@
       </c>
       <c r="C291" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D291" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">shy.polite[1]</t>
+          <t xml:space="preserve">GL-01.loss.shy.polite[1]</t>
         </is>
       </c>
       <c r="E291" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F291" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、あの方が…相手なんですね…せ、精一杯戦います…</t>
+          <t xml:space="preserve">ま、負けてしまいました…ご、ごめんなさい…</t>
         </is>
       </c>
     </row>
     <row r="292" ht="40" customHeight="1">
       <c r="A292" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.shy.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.shy.polite[2]</t>
         </is>
       </c>
       <c r="B292" t="inlineStr" s="2">
@@ -9649,29 +9649,29 @@
       </c>
       <c r="C292" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D292" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">shy.polite[1]</t>
+          <t xml:space="preserve">GL-01.loss.shy.polite[2]</t>
         </is>
       </c>
       <c r="E292" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F292" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">か、勝てました……本当に……ありがとうございます……</t>
+          <t xml:space="preserve">次こそは…勝ちたいです…</t>
         </is>
       </c>
     </row>
     <row r="293" ht="40" customHeight="1">
       <c r="A293" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.shy.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.shy.polite[1]</t>
         </is>
       </c>
       <c r="B293" t="inlineStr" s="2">
@@ -9681,29 +9681,29 @@
       </c>
       <c r="C293" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D293" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">shy.polite[1]</t>
+          <t xml:space="preserve">GL-01.win.shy.polite[1]</t>
         </is>
       </c>
       <c r="E293" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F293" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、あの…団体として、挑戦させてください…</t>
+          <t xml:space="preserve">か、勝てました…応援、ありがとうございます…</t>
         </is>
       </c>
     </row>
     <row r="294" ht="40" customHeight="1">
       <c r="A294" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.shy.polite[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.shy.polite[2]</t>
         </is>
       </c>
       <c r="B294" t="inlineStr" s="2">
@@ -9713,29 +9713,29 @@
       </c>
       <c r="C294" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D294" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">shy.polite[2]</t>
+          <t xml:space="preserve">GL-01.win.shy.polite[2]</t>
         </is>
       </c>
       <c r="E294" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F294" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">み、みんなで戦います…</t>
+          <t xml:space="preserve">今日は…良い試合が、できたと思います…</t>
         </is>
       </c>
     </row>
     <row r="295" ht="40" customHeight="1">
       <c r="A295" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.shy.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.shy.polite[1]</t>
         </is>
       </c>
       <c r="B295" t="inlineStr" s="2">
@@ -9745,29 +9745,29 @@
       </c>
       <c r="C295" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D295" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">shy.polite[1]</t>
+          <t xml:space="preserve">GL-02.shy.polite[1]</t>
         </is>
       </c>
       <c r="E295" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F295" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">す、すみません…今回は、お断りさせてください…</t>
+          <t xml:space="preserve">あ、あの…今日は、よろしくお願いいたします…</t>
         </is>
       </c>
     </row>
     <row r="296" ht="40" customHeight="1">
       <c r="A296" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.shy.polite[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.shy.polite[2]</t>
         </is>
       </c>
       <c r="B296" t="inlineStr" s="2">
@@ -9777,29 +9777,29 @@
       </c>
       <c r="C296" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D296" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">shy.polite[2]</t>
+          <t xml:space="preserve">GL-02.shy.polite[2]</t>
         </is>
       </c>
       <c r="E296" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F296" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ま、また機会があれば…</t>
+          <t xml:space="preserve">頑張ります…</t>
         </is>
       </c>
     </row>
     <row r="297" ht="40" customHeight="1">
       <c r="A297" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.shy.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.down.shy.polite[1]</t>
         </is>
       </c>
       <c r="B297" t="inlineStr" s="2">
@@ -9809,29 +9809,29 @@
       </c>
       <c r="C297" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D297" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.shy.polite[1]</t>
+          <t xml:space="preserve">GL-03.down.shy.polite[1]</t>
         </is>
       </c>
       <c r="E297" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F297" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ま、負けてしまいました…ご、ごめんなさい…</t>
+          <t xml:space="preserve">う、うまくいきません…どうしたら…</t>
         </is>
       </c>
     </row>
     <row r="298" ht="40" customHeight="1">
       <c r="A298" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.shy.polite[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.up.shy.polite[1]</t>
         </is>
       </c>
       <c r="B298" t="inlineStr" s="2">
@@ -9841,29 +9841,29 @@
       </c>
       <c r="C298" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D298" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.shy.polite[2]</t>
+          <t xml:space="preserve">GL-03.up.shy.polite[1]</t>
         </is>
       </c>
       <c r="E298" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F298" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次は…次こそは…</t>
+          <t xml:space="preserve">調子が…良い気がします…</t>
         </is>
       </c>
     </row>
     <row r="299" ht="40" customHeight="1">
       <c r="A299" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.shy.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04.shy.polite[1]</t>
         </is>
       </c>
       <c r="B299" t="inlineStr" s="2">
@@ -9873,29 +9873,29 @@
       </c>
       <c r="C299" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D299" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.shy.polite[1]</t>
+          <t xml:space="preserve">GL-04.shy.polite[1]</t>
         </is>
       </c>
       <c r="E299" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F299" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">か、勝てました…団体のみなさんのおかげです…</t>
+          <t xml:space="preserve">練習…させていただきます…</t>
         </is>
       </c>
     </row>
     <row r="300" ht="40" customHeight="1">
       <c r="A300" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.shy.polite[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04.shy.polite[2]</t>
         </is>
       </c>
       <c r="B300" t="inlineStr" s="2">
@@ -9905,29 +9905,29 @@
       </c>
       <c r="C300" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D300" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.shy.polite[2]</t>
+          <t xml:space="preserve">GL-04.shy.polite[2]</t>
         </is>
       </c>
       <c r="E300" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F300" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">応援、ありがとうございました…</t>
+          <t xml:space="preserve">もう少し…頑張ります…</t>
         </is>
       </c>
     </row>
     <row r="301" ht="40" customHeight="1">
       <c r="A301" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.shy.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05.shy.polite[1]</t>
         </is>
       </c>
       <c r="B301" t="inlineStr" s="2">
@@ -9937,29 +9937,29 @@
       </c>
       <c r="C301" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D301" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">shy.polite[1]</t>
+          <t xml:space="preserve">GL-05.shy.polite[1]</t>
         </is>
       </c>
       <c r="E301" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F301" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">か、勝てました…！ 団体のみなさまに恥じない試合が…できたでしょうか…</t>
+          <t xml:space="preserve">あ、あの…大丈夫です、心配しないでください…</t>
         </is>
       </c>
     </row>
     <row r="302" ht="40" customHeight="1">
       <c r="A302" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.shy.polite[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05.shy.polite[2]</t>
         </is>
       </c>
       <c r="B302" t="inlineStr" s="2">
@@ -9969,29 +9969,29 @@
       </c>
       <c r="C302" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D302" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">shy.polite[2]</t>
+          <t xml:space="preserve">GL-05.shy.polite[2]</t>
         </is>
       </c>
       <c r="E302" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F302" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">か、勝たせていただきました…。団体のみなさまに…少しは恩返しできたでしょうか…</t>
+          <t xml:space="preserve">ご心配を、おかけして…</t>
         </is>
       </c>
     </row>
     <row r="303" ht="40" customHeight="1">
       <c r="A303" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.shy.polite[3]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.shy.polite[1]</t>
         </is>
       </c>
       <c r="B303" t="inlineStr" s="2">
@@ -10001,59 +10001,1691 @@
       </c>
       <c r="C303" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D303" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">shy.polite[3]</t>
+          <t xml:space="preserve">GL-06.shy.polite[1]</t>
         </is>
       </c>
       <c r="E303" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F303" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">か、勝てました…！ 団体のみなさまに恥じない試合が…できていたら嬉しいです…</t>
+          <t xml:space="preserve">みんなと…一緒だと、心強いです…</t>
         </is>
       </c>
     </row>
     <row r="304" ht="40" customHeight="1">
       <c r="A304" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.shy.polite[2]</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">GL-06.shy.polite[2]</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">仲間って、いいですね…</t>
+        </is>
+      </c>
+    </row>
+    <row r="305" ht="40" customHeight="1">
+      <c r="A305" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07.shy.polite[1]</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">GL-07.shy.polite[1]</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">お、お客さんがいっぱいで…き、緊張します…</t>
+        </is>
+      </c>
+    </row>
+    <row r="306" ht="40" customHeight="1">
+      <c r="A306" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07.shy.polite[2]</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">GL-07.shy.polite[2]</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">がんばります…</t>
+        </is>
+      </c>
+    </row>
+    <row r="307" ht="40" customHeight="1">
+      <c r="A307" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.shy.polite[1]</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">GL-08.shy.polite[1]</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あ、あの…体調は、大丈夫です…</t>
+        </is>
+      </c>
+    </row>
+    <row r="308" ht="40" customHeight="1">
+      <c r="A308" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.shy.polite[2]</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">GL-08.shy.polite[2]</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">無理はしません…</t>
+        </is>
+      </c>
+    </row>
+    <row r="309" ht="40" customHeight="1">
+      <c r="A309" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.shy.polite[1]</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">GL-09.shy.polite[1]</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">次の試合…が、頑張ります…</t>
+        </is>
+      </c>
+    </row>
+    <row r="310" ht="40" customHeight="1">
+      <c r="A310" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.shy.polite[2]</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">GL-09.shy.polite[2]</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">しっかり、準備します…</t>
+        </is>
+      </c>
+    </row>
+    <row r="311" ht="40" customHeight="1">
+      <c r="A311" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.shy.polite[1]</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">GL-10.shy.polite[1]</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あ、あの…ありがとうございます…</t>
+        </is>
+      </c>
+    </row>
+    <row r="312" ht="40" customHeight="1">
+      <c r="A312" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.shy.polite[2]</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">GL-10.shy.polite[2]</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">感謝、しています…</t>
+        </is>
+      </c>
+    </row>
+    <row r="313" ht="40" customHeight="1">
+      <c r="A313" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.shy.polite[1]</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">shy.polite[1]</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">良い流れが…止まってしまいました…で、でも、また頑張ります…</t>
+        </is>
+      </c>
+    </row>
+    <row r="314" ht="40" customHeight="1">
+      <c r="A314" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.shy.polite[1]</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preFinal.shy.polite[1]</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">け、決勝…。信じられないけど…最後まで、立たせてください…</t>
+        </is>
+      </c>
+    </row>
+    <row r="315" ht="40" customHeight="1">
+      <c r="A315" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.shy.polite[2]</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preFinal.shy.polite[2]</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">身体は痛いです…でも、ここで退いたら、繋いでくれた分が…</t>
+        </is>
+      </c>
+    </row>
+    <row r="316" ht="40" customHeight="1">
+      <c r="A316" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.shy.polite[1]</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preMatch.shy.polite[1]</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">つ、相手の方…がんばります。仲間が待ってるので、退けません…</t>
+        </is>
+      </c>
+    </row>
+    <row r="317" ht="40" customHeight="1">
+      <c r="A317" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.shy.polite[2]</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preMatch.shy.polite[2]</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">こ、怖いです…でも、ここで止まったら、みんなに申し訳なくて…</t>
+        </is>
+      </c>
+    </row>
+    <row r="318" ht="40" customHeight="1">
+      <c r="A318" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.shy.polite[1]</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">survivor.shy.polite[1]</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">い、一人、倒せました…! はぁ…まだ、退けません…次の方、来てください…!</t>
+        </is>
+      </c>
+    </row>
+    <row r="319" ht="40" customHeight="1">
+      <c r="A319" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.shy.polite[2]</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">survivor.shy.polite[2]</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">怖いです…でも、まだ立ってます。仲間に繋ぐまで、ここは…次、どうぞ…</t>
+        </is>
+      </c>
+    </row>
+    <row r="320" ht="40" customHeight="1">
+      <c r="A320" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.shy.polite[1]</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">champion.shy.polite[1]</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">わ、私がMVPなんて……二人がいてくれたから、ここまで来られたんです</t>
+        </is>
+      </c>
+    </row>
+    <row r="321" ht="40" customHeight="1">
+      <c r="A321" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.shy.polite[2]</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">champion.shy.polite[2]</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">三人で勝てて、本当によかったです。私は……二人に助けられてばかりで</t>
+        </is>
+      </c>
+    </row>
+    <row r="322" ht="40" customHeight="1">
+      <c r="A322" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.shy.polite[1]</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">defiant.shy.polite[1]</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">MVPは……嬉しいです。でも、みんなで勝ちたかったです。次こそは……</t>
+        </is>
+      </c>
+    </row>
+    <row r="323" ht="40" customHeight="1">
+      <c r="A323" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.shy.polite[2]</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">defiant.shy.polite[2]</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">一人だけ褒められても……素直に喜べなくて。次は一緒に笑いたいです</t>
+        </is>
+      </c>
+    </row>
+    <row r="324" ht="40" customHeight="1">
+      <c r="A324" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.shy.polite[1]</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">gauntlet.shy.polite[1]</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ず、ずっと怖かったです。でも……最後まで立っていられたのは、応援のおかげです</t>
+        </is>
+      </c>
+    </row>
+    <row r="325" ht="40" customHeight="1">
+      <c r="A325" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.shy.polite[2]</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">gauntlet.shy.polite[2]</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">身体が震えてます。でも……逃げなかったこと、褒めてもらえますか……</t>
+        </is>
+      </c>
+    </row>
+    <row r="326" ht="40" customHeight="1">
+      <c r="A326" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.shy.polite[1]</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">champion.shy.polite[1]</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ゆ、優勝…ですか…？ ほ、本当に…？ あ、ありがとうございます…!</t>
+        </is>
+      </c>
+    </row>
+    <row r="327" ht="40" customHeight="1">
+      <c r="A327" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.shy.polite[2]</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">champion.shy.polite[2]</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">夢みたいで…まだ、信じられません…</t>
+        </is>
+      </c>
+    </row>
+    <row r="328" ht="40" customHeight="1">
+      <c r="A328" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.shy.polite[1]</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">postLose.shy.polite[1]</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ま、負けてしまいました…ごめんなさい…</t>
+        </is>
+      </c>
+    </row>
+    <row r="329" ht="40" customHeight="1">
+      <c r="A329" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.shy.polite[2]</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">postLose.shy.polite[2]</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">もっと…強くならないと…</t>
+        </is>
+      </c>
+    </row>
+    <row r="330" ht="40" customHeight="1">
+      <c r="A330" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.shy.polite[1]</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">postMatchWin.shy.polite[1]</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F330" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">か、勝てました…次もがんばります…</t>
+        </is>
+      </c>
+    </row>
+    <row r="331" ht="40" customHeight="1">
+      <c r="A331" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.shy.polite[2]</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">postMatchWin.shy.polite[2]</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">一勝、できました…</t>
+        </is>
+      </c>
+    </row>
+    <row r="332" ht="40" customHeight="1">
+      <c r="A332" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.shy.polite[1]</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">postWin.shy.polite[1]</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">か、勝ち上がれました…信じられません…</t>
+        </is>
+      </c>
+    </row>
+    <row r="333" ht="40" customHeight="1">
+      <c r="A333" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.shy.polite[2]</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">postWin.shy.polite[2]</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">まだ…続けられるんですね…</t>
+        </is>
+      </c>
+    </row>
+    <row r="334" ht="40" customHeight="1">
+      <c r="A334" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.shy.polite[1]</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preFinal.shy.polite[1]</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">け、決勝戦…ですか…し、信じられません…</t>
+        </is>
+      </c>
+    </row>
+    <row r="335" ht="40" customHeight="1">
+      <c r="A335" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.shy.polite[2]</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preFinal.shy.polite[2]</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F335" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">夢みたい、です…</t>
+        </is>
+      </c>
+    </row>
+    <row r="336" ht="40" customHeight="1">
+      <c r="A336" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.shy.polite[1]</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preMatch.shy.polite[1]</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F336" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">き、緊張します…でも、精一杯やります…</t>
+        </is>
+      </c>
+    </row>
+    <row r="337" ht="40" customHeight="1">
+      <c r="A337" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.shy.polite[2]</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preMatch.shy.polite[2]</t>
+        </is>
+      </c>
+      <c r="E337" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F337" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ふ、深呼吸…落ち着かないと…</t>
+        </is>
+      </c>
+    </row>
+    <row r="338" ht="40" customHeight="1">
+      <c r="A338" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.shy.polite[1]</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">summon.shy.polite[1]</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F338" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">え、わたしが…ジュニアトーナメントに…？ あ、あの、頑張ります…!</t>
+        </is>
+      </c>
+    </row>
+    <row r="339" ht="40" customHeight="1">
+      <c r="A339" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.shy.polite[2]</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">summon.shy.polite[2]</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F339" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">選んでいただいて…あ、ありがとうございます…</t>
+        </is>
+      </c>
+    </row>
+    <row r="340" ht="40" customHeight="1">
+      <c r="A340" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.shy.polite[1]</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">shy.polite[1]</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F340" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あ、あの方が…相手なんですね…せ、精一杯戦います…</t>
+        </is>
+      </c>
+    </row>
+    <row r="341" ht="40" customHeight="1">
+      <c r="A341" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.shy.polite[1]</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">shy.polite[1]</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F341" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">か、勝てました……本当に……ありがとうございます……</t>
+        </is>
+      </c>
+    </row>
+    <row r="342" ht="40" customHeight="1">
+      <c r="A342" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.shy.polite[1]</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">shy.polite[1]</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F342" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あ、あの…団体として、挑戦させてください…</t>
+        </is>
+      </c>
+    </row>
+    <row r="343" ht="40" customHeight="1">
+      <c r="A343" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.shy.polite[2]</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">shy.polite[2]</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F343" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">み、みんなで戦います…</t>
+        </is>
+      </c>
+    </row>
+    <row r="344" ht="40" customHeight="1">
+      <c r="A344" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.shy.polite[1]</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">shy.polite[1]</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F344" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">す、すみません…今回は、お断りさせてください…</t>
+        </is>
+      </c>
+    </row>
+    <row r="345" ht="40" customHeight="1">
+      <c r="A345" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.shy.polite[2]</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">shy.polite[2]</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F345" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ま、また機会があれば…</t>
+        </is>
+      </c>
+    </row>
+    <row r="346" ht="40" customHeight="1">
+      <c r="A346" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.shy.polite[1]</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">result_lose.shy.polite[1]</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F346" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ま、負けてしまいました…ご、ごめんなさい…</t>
+        </is>
+      </c>
+    </row>
+    <row r="347" ht="40" customHeight="1">
+      <c r="A347" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.shy.polite[2]</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">result_lose.shy.polite[2]</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F347" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">次は…次こそは…</t>
+        </is>
+      </c>
+    </row>
+    <row r="348" ht="40" customHeight="1">
+      <c r="A348" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.shy.polite[1]</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">result_win.shy.polite[1]</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F348" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">か、勝てました…団体のみなさんのおかげです…</t>
+        </is>
+      </c>
+    </row>
+    <row r="349" ht="40" customHeight="1">
+      <c r="A349" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.shy.polite[2]</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">result_win.shy.polite[2]</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F349" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">応援、ありがとうございました…</t>
+        </is>
+      </c>
+    </row>
+    <row r="350" ht="40" customHeight="1">
+      <c r="A350" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.shy.polite[1]</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">shy.polite[1]</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F350" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">か、勝てました…！ 団体のみなさまに恥じない試合が…できたでしょうか…</t>
+        </is>
+      </c>
+    </row>
+    <row r="351" ht="40" customHeight="1">
+      <c r="A351" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.shy.polite[2]</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">shy.polite[2]</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F351" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">か、勝たせていただきました…。団体のみなさまに…少しは恩返しできたでしょうか…</t>
+        </is>
+      </c>
+    </row>
+    <row r="352" ht="40" customHeight="1">
+      <c r="A352" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.shy.polite[3]</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">shy.polite[3]</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">か、勝てました…！ 団体のみなさまに恥じない試合が…できていたら嬉しいです…</t>
+        </is>
+      </c>
+    </row>
+    <row r="353" ht="40" customHeight="1">
+      <c r="A353" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">ENDING_LINES.fighter.shy.polite[1]</t>
         </is>
       </c>
-      <c r="B304" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C304" t="inlineStr" s="2">
+      <c r="B353" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">ENDING_LINES</t>
         </is>
       </c>
-      <c r="D304" t="inlineStr" s="12">
+      <c r="D353" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">fighter.shy.polite[1]</t>
         </is>
       </c>
-      <c r="E304" t="inlineStr" s="2">
+      <c r="E353" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">18 経営危機・エンディング</t>
         </is>
       </c>
-      <c r="F304" t="inlineStr" s="3">
+      <c r="F353" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">こ、これで…リングを降ります…あ、あの、応援してくれた皆さま…本当に、ありがとうございました…</t>
         </is>
       </c>
     </row>
+    <row r="354" ht="40" customHeight="1">
+      <c r="A354" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES.shy.polite[1]</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">shy.polite[1]</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F354" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あ、あの…契約してもらえて…感謝しています…！</t>
+        </is>
+      </c>
+    </row>
+    <row r="355" ht="40" customHeight="1">
+      <c r="A355" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">SCOUT_GREETING_LINES.shy.polite[1]</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">SCOUT_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">shy.polite[1]</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F355" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あ、あの…お声がけ、光栄です…！</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H304"/>
+  <autoFilter ref="A1:H355"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/キャラタイプ別/丁寧×内気.xlsx
+++ b/セリフ編集/キャラタイプ別/丁寧×内気.xlsx
@@ -359,7 +359,7 @@
     <row r="2" ht="40" customHeight="1">
       <c r="A2" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.atk.shy.polite[1]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.polite.shy[1]</t>
         </is>
       </c>
       <c r="B2" t="inlineStr" s="2">
@@ -374,7 +374,7 @@
       </c>
       <c r="D2" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">atk.shy.polite[1]</t>
+          <t xml:space="preserve">atk.polite.shy[1]</t>
         </is>
       </c>
       <c r="E2" t="inlineStr" s="2">
@@ -391,7 +391,7 @@
     <row r="3" ht="40" customHeight="1">
       <c r="A3" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.atk.shy.polite[2]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.polite.shy[2]</t>
         </is>
       </c>
       <c r="B3" t="inlineStr" s="2">
@@ -406,7 +406,7 @@
       </c>
       <c r="D3" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">atk.shy.polite[2]</t>
+          <t xml:space="preserve">atk.polite.shy[2]</t>
         </is>
       </c>
       <c r="E3" t="inlineStr" s="2">
@@ -423,7 +423,7 @@
     <row r="4" ht="40" customHeight="1">
       <c r="A4" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.atk.shy.polite[3]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.polite.shy[3]</t>
         </is>
       </c>
       <c r="B4" t="inlineStr" s="2">
@@ -438,7 +438,7 @@
       </c>
       <c r="D4" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">atk.shy.polite[3]</t>
+          <t xml:space="preserve">atk.polite.shy[3]</t>
         </is>
       </c>
       <c r="E4" t="inlineStr" s="2">
@@ -455,7 +455,7 @@
     <row r="5" ht="40" customHeight="1">
       <c r="A5" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.atk.shy.polite[4]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.polite.shy[4]</t>
         </is>
       </c>
       <c r="B5" t="inlineStr" s="2">
@@ -470,7 +470,7 @@
       </c>
       <c r="D5" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">atk.shy.polite[4]</t>
+          <t xml:space="preserve">atk.polite.shy[4]</t>
         </is>
       </c>
       <c r="E5" t="inlineStr" s="2">
@@ -487,7 +487,7 @@
     <row r="6" ht="40" customHeight="1">
       <c r="A6" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.bigmove.shy.polite[1]</t>
+          <t xml:space="preserve">CUTIN_LINES.bigmove.polite.shy[1]</t>
         </is>
       </c>
       <c r="B6" t="inlineStr" s="2">
@@ -502,7 +502,7 @@
       </c>
       <c r="D6" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigmove.shy.polite[1]</t>
+          <t xml:space="preserve">bigmove.polite.shy[1]</t>
         </is>
       </c>
       <c r="E6" t="inlineStr" s="2">
@@ -519,7 +519,7 @@
     <row r="7" ht="40" customHeight="1">
       <c r="A7" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.bigmove.shy.polite[2]</t>
+          <t xml:space="preserve">CUTIN_LINES.bigmove.polite.shy[2]</t>
         </is>
       </c>
       <c r="B7" t="inlineStr" s="2">
@@ -534,7 +534,7 @@
       </c>
       <c r="D7" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigmove.shy.polite[2]</t>
+          <t xml:space="preserve">bigmove.polite.shy[2]</t>
         </is>
       </c>
       <c r="E7" t="inlineStr" s="2">
@@ -551,7 +551,7 @@
     <row r="8" ht="40" customHeight="1">
       <c r="A8" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.bigmove.shy.polite[3]</t>
+          <t xml:space="preserve">CUTIN_LINES.bigmove.polite.shy[3]</t>
         </is>
       </c>
       <c r="B8" t="inlineStr" s="2">
@@ -566,7 +566,7 @@
       </c>
       <c r="D8" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigmove.shy.polite[3]</t>
+          <t xml:space="preserve">bigmove.polite.shy[3]</t>
         </is>
       </c>
       <c r="E8" t="inlineStr" s="2">
@@ -583,7 +583,7 @@
     <row r="9" ht="40" customHeight="1">
       <c r="A9" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.climax.shy.polite[1]</t>
+          <t xml:space="preserve">CUTIN_LINES.climax.polite.shy[1]</t>
         </is>
       </c>
       <c r="B9" t="inlineStr" s="2">
@@ -598,7 +598,7 @@
       </c>
       <c r="D9" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">climax.shy.polite[1]</t>
+          <t xml:space="preserve">climax.polite.shy[1]</t>
         </is>
       </c>
       <c r="E9" t="inlineStr" s="2">
@@ -615,7 +615,7 @@
     <row r="10" ht="40" customHeight="1">
       <c r="A10" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.climax.shy.polite[2]</t>
+          <t xml:space="preserve">CUTIN_LINES.climax.polite.shy[2]</t>
         </is>
       </c>
       <c r="B10" t="inlineStr" s="2">
@@ -630,7 +630,7 @@
       </c>
       <c r="D10" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">climax.shy.polite[2]</t>
+          <t xml:space="preserve">climax.polite.shy[2]</t>
         </is>
       </c>
       <c r="E10" t="inlineStr" s="2">
@@ -647,7 +647,7 @@
     <row r="11" ht="40" customHeight="1">
       <c r="A11" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_SERIF_LINES.shy.polite[1]</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES.polite.shy[1]</t>
         </is>
       </c>
       <c r="B11" t="inlineStr" s="2">
@@ -662,7 +662,7 @@
       </c>
       <c r="D11" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">shy.polite[1]</t>
+          <t xml:space="preserve">polite.shy[1]</t>
         </is>
       </c>
       <c r="E11" t="inlineStr" s="2">
@@ -679,7 +679,7 @@
     <row r="12" ht="40" customHeight="1">
       <c r="A12" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_SERIF_LINES.shy.polite[2]</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES.polite.shy[2]</t>
         </is>
       </c>
       <c r="B12" t="inlineStr" s="2">
@@ -694,7 +694,7 @@
       </c>
       <c r="D12" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">shy.polite[2]</t>
+          <t xml:space="preserve">polite.shy[2]</t>
         </is>
       </c>
       <c r="E12" t="inlineStr" s="2">
@@ -711,7 +711,7 @@
     <row r="13" ht="40" customHeight="1">
       <c r="A13" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_SERIF_LINES.shy.polite[3]</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES.polite.shy[3]</t>
         </is>
       </c>
       <c r="B13" t="inlineStr" s="2">
@@ -726,7 +726,7 @@
       </c>
       <c r="D13" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">shy.polite[3]</t>
+          <t xml:space="preserve">polite.shy[3]</t>
         </is>
       </c>
       <c r="E13" t="inlineStr" s="2">
@@ -743,7 +743,7 @@
     <row r="14" ht="40" customHeight="1">
       <c r="A14" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS.badWinner.shy.polite[1]</t>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS.badWinner.polite.shy[1]</t>
         </is>
       </c>
       <c r="B14" t="inlineStr" s="2">
@@ -758,7 +758,7 @@
       </c>
       <c r="D14" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">badWinner.shy.polite[1]</t>
+          <t xml:space="preserve">badWinner.polite.shy[1]</t>
         </is>
       </c>
       <c r="E14" t="inlineStr" s="2">
@@ -775,7 +775,7 @@
     <row r="15" ht="40" customHeight="1">
       <c r="A15" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS.goodWinner.shy.polite[1]</t>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS.goodWinner.polite.shy[1]</t>
         </is>
       </c>
       <c r="B15" t="inlineStr" s="2">
@@ -790,7 +790,7 @@
       </c>
       <c r="D15" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">goodWinner.shy.polite[1]</t>
+          <t xml:space="preserve">goodWinner.polite.shy[1]</t>
         </is>
       </c>
       <c r="E15" t="inlineStr" s="2">
@@ -807,7 +807,7 @@
     <row r="16" ht="40" customHeight="1">
       <c r="A16" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FIRST_MEET_LINES.shy.polite[1]</t>
+          <t xml:space="preserve">FIRST_MEET_LINES.polite.shy[1]</t>
         </is>
       </c>
       <c r="B16" t="inlineStr" s="2">
@@ -822,7 +822,7 @@
       </c>
       <c r="D16" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">shy.polite[1]</t>
+          <t xml:space="preserve">polite.shy[1]</t>
         </is>
       </c>
       <c r="E16" t="inlineStr" s="2">
@@ -839,7 +839,7 @@
     <row r="17" ht="40" customHeight="1">
       <c r="A17" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.loser.shy.polite[1]</t>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.loser.polite.shy[1]</t>
         </is>
       </c>
       <c r="B17" t="inlineStr" s="2">
@@ -854,7 +854,7 @@
       </c>
       <c r="D17" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.shy.polite[1]</t>
+          <t xml:space="preserve">loser.polite.shy[1]</t>
         </is>
       </c>
       <c r="E17" t="inlineStr" s="2">
@@ -871,7 +871,7 @@
     <row r="18" ht="40" customHeight="1">
       <c r="A18" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.winner.shy.polite[1]</t>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.winner.polite.shy[1]</t>
         </is>
       </c>
       <c r="B18" t="inlineStr" s="2">
@@ -886,7 +886,7 @@
       </c>
       <c r="D18" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.shy.polite[1]</t>
+          <t xml:space="preserve">winner.polite.shy[1]</t>
         </is>
       </c>
       <c r="E18" t="inlineStr" s="2">
@@ -903,7 +903,7 @@
     <row r="19" ht="40" customHeight="1">
       <c r="A19" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.competition_won.shy.polite[1]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.competition_won.polite.shy[1]</t>
         </is>
       </c>
       <c r="B19" t="inlineStr" s="2">
@@ -918,7 +918,7 @@
       </c>
       <c r="D19" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">competition_won.shy.polite[1]</t>
+          <t xml:space="preserve">competition_won.polite.shy[1]</t>
         </is>
       </c>
       <c r="E19" t="inlineStr" s="2">
@@ -935,7 +935,7 @@
     <row r="20" ht="40" customHeight="1">
       <c r="A20" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.direct.shy.polite[1]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.direct.polite.shy[1]</t>
         </is>
       </c>
       <c r="B20" t="inlineStr" s="2">
@@ -950,7 +950,7 @@
       </c>
       <c r="D20" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">direct.shy.polite[1]</t>
+          <t xml:space="preserve">direct.polite.shy[1]</t>
         </is>
       </c>
       <c r="E20" t="inlineStr" s="2">
@@ -967,7 +967,7 @@
     <row r="21" ht="40" customHeight="1">
       <c r="A21" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.fa_signing.shy.polite[1]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.fa_signing.polite.shy[1]</t>
         </is>
       </c>
       <c r="B21" t="inlineStr" s="2">
@@ -982,7 +982,7 @@
       </c>
       <c r="D21" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fa_signing.shy.polite[1]</t>
+          <t xml:space="preserve">fa_signing.polite.shy[1]</t>
         </is>
       </c>
       <c r="E21" t="inlineStr" s="2">
@@ -999,7 +999,7 @@
     <row r="22" ht="40" customHeight="1">
       <c r="A22" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.shy.polite.hit[1]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.polite.shy.hit[1]</t>
         </is>
       </c>
       <c r="B22" t="inlineStr" s="2">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="D22" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">shy.polite.hit[1]</t>
+          <t xml:space="preserve">polite.shy.hit[1]</t>
         </is>
       </c>
       <c r="E22" t="inlineStr" s="2">
@@ -1031,7 +1031,7 @@
     <row r="23" ht="40" customHeight="1">
       <c r="A23" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.shy.polite.hit[2]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.polite.shy.hit[2]</t>
         </is>
       </c>
       <c r="B23" t="inlineStr" s="2">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="D23" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">shy.polite.hit[2]</t>
+          <t xml:space="preserve">polite.shy.hit[2]</t>
         </is>
       </c>
       <c r="E23" t="inlineStr" s="2">
@@ -1063,7 +1063,7 @@
     <row r="24" ht="40" customHeight="1">
       <c r="A24" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.shy.polite.win[1]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.polite.shy.win[1]</t>
         </is>
       </c>
       <c r="B24" t="inlineStr" s="2">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="D24" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">shy.polite.win[1]</t>
+          <t xml:space="preserve">polite.shy.win[1]</t>
         </is>
       </c>
       <c r="E24" t="inlineStr" s="2">
@@ -1095,7 +1095,7 @@
     <row r="25" ht="40" customHeight="1">
       <c r="A25" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.shy.polite.win[2]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.polite.shy.win[2]</t>
         </is>
       </c>
       <c r="B25" t="inlineStr" s="2">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="D25" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">shy.polite.win[2]</t>
+          <t xml:space="preserve">polite.shy.win[2]</t>
         </is>
       </c>
       <c r="E25" t="inlineStr" s="2">
@@ -1127,7 +1127,7 @@
     <row r="26" ht="40" customHeight="1">
       <c r="A26" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BETRAYAL_LINES.shy.polite[1]</t>
+          <t xml:space="preserve">BETRAYAL_LINES.polite.shy[1]</t>
         </is>
       </c>
       <c r="B26" t="inlineStr" s="2">
@@ -1142,7 +1142,7 @@
       </c>
       <c r="D26" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">shy.polite[1]</t>
+          <t xml:space="preserve">polite.shy[1]</t>
         </is>
       </c>
       <c r="E26" t="inlineStr" s="2">
@@ -1159,7 +1159,7 @@
     <row r="27" ht="40" customHeight="1">
       <c r="A27" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BETRAYAL_LINES.shy.polite[2]</t>
+          <t xml:space="preserve">BETRAYAL_LINES.polite.shy[2]</t>
         </is>
       </c>
       <c r="B27" t="inlineStr" s="2">
@@ -1174,7 +1174,7 @@
       </c>
       <c r="D27" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">shy.polite[2]</t>
+          <t xml:space="preserve">polite.shy[2]</t>
         </is>
       </c>
       <c r="E27" t="inlineStr" s="2">
@@ -1191,7 +1191,7 @@
     <row r="28" ht="40" customHeight="1">
       <c r="A28" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BETRAYAL_LINES.shy.polite[3]</t>
+          <t xml:space="preserve">BETRAYAL_LINES.polite.shy[3]</t>
         </is>
       </c>
       <c r="B28" t="inlineStr" s="2">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="D28" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">shy.polite[3]</t>
+          <t xml:space="preserve">polite.shy[3]</t>
         </is>
       </c>
       <c r="E28" t="inlineStr" s="2">
@@ -1223,7 +1223,7 @@
     <row r="29" ht="40" customHeight="1">
       <c r="A29" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_SAVE_LINES.shy.polite[1]</t>
+          <t xml:space="preserve">CUTIN_SAVE_LINES.polite.shy[1]</t>
         </is>
       </c>
       <c r="B29" t="inlineStr" s="2">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="D29" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">shy.polite[1]</t>
+          <t xml:space="preserve">polite.shy[1]</t>
         </is>
       </c>
       <c r="E29" t="inlineStr" s="2">
@@ -1255,7 +1255,7 @@
     <row r="30" ht="40" customHeight="1">
       <c r="A30" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_SAVE_LINES.shy.polite[2]</t>
+          <t xml:space="preserve">CUTIN_SAVE_LINES.polite.shy[2]</t>
         </is>
       </c>
       <c r="B30" t="inlineStr" s="2">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="D30" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">shy.polite[2]</t>
+          <t xml:space="preserve">polite.shy[2]</t>
         </is>
       </c>
       <c r="E30" t="inlineStr" s="2">
@@ -1287,7 +1287,7 @@
     <row r="31" ht="40" customHeight="1">
       <c r="A31" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_SAVE_LINES.shy.polite[3]</t>
+          <t xml:space="preserve">CUTIN_SAVE_LINES.polite.shy[3]</t>
         </is>
       </c>
       <c r="B31" t="inlineStr" s="2">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="D31" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">shy.polite[3]</t>
+          <t xml:space="preserve">polite.shy[3]</t>
         </is>
       </c>
       <c r="E31" t="inlineStr" s="2">
@@ -1319,7 +1319,7 @@
     <row r="32" ht="40" customHeight="1">
       <c r="A32" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_LINES.shy.polite[1]</t>
+          <t xml:space="preserve">DOUBLE_TEAM_LINES.polite.shy[1]</t>
         </is>
       </c>
       <c r="B32" t="inlineStr" s="2">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="D32" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">shy.polite[1]</t>
+          <t xml:space="preserve">polite.shy[1]</t>
         </is>
       </c>
       <c r="E32" t="inlineStr" s="2">
@@ -1351,7 +1351,7 @@
     <row r="33" ht="40" customHeight="1">
       <c r="A33" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_LINES.shy.polite[2]</t>
+          <t xml:space="preserve">DOUBLE_TEAM_LINES.polite.shy[2]</t>
         </is>
       </c>
       <c r="B33" t="inlineStr" s="2">
@@ -1366,7 +1366,7 @@
       </c>
       <c r="D33" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">shy.polite[2]</t>
+          <t xml:space="preserve">polite.shy[2]</t>
         </is>
       </c>
       <c r="E33" t="inlineStr" s="2">
@@ -1383,7 +1383,7 @@
     <row r="34" ht="40" customHeight="1">
       <c r="A34" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_LINES.shy.polite[3]</t>
+          <t xml:space="preserve">DOUBLE_TEAM_LINES.polite.shy[3]</t>
         </is>
       </c>
       <c r="B34" t="inlineStr" s="2">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="D34" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">shy.polite[3]</t>
+          <t xml:space="preserve">polite.shy[3]</t>
         </is>
       </c>
       <c r="E34" t="inlineStr" s="2">
@@ -1415,7 +1415,7 @@
     <row r="35" ht="40" customHeight="1">
       <c r="A35" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HOT_TAG_LINES.shy.polite[1]</t>
+          <t xml:space="preserve">HOT_TAG_LINES.polite.shy[1]</t>
         </is>
       </c>
       <c r="B35" t="inlineStr" s="2">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="D35" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">shy.polite[1]</t>
+          <t xml:space="preserve">polite.shy[1]</t>
         </is>
       </c>
       <c r="E35" t="inlineStr" s="2">
@@ -1447,7 +1447,7 @@
     <row r="36" ht="40" customHeight="1">
       <c r="A36" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HOT_TAG_LINES.shy.polite[2]</t>
+          <t xml:space="preserve">HOT_TAG_LINES.polite.shy[2]</t>
         </is>
       </c>
       <c r="B36" t="inlineStr" s="2">
@@ -1462,7 +1462,7 @@
       </c>
       <c r="D36" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">shy.polite[2]</t>
+          <t xml:space="preserve">polite.shy[2]</t>
         </is>
       </c>
       <c r="E36" t="inlineStr" s="2">
@@ -1479,7 +1479,7 @@
     <row r="37" ht="40" customHeight="1">
       <c r="A37" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HOT_TAG_LINES.shy.polite[3]</t>
+          <t xml:space="preserve">HOT_TAG_LINES.polite.shy[3]</t>
         </is>
       </c>
       <c r="B37" t="inlineStr" s="2">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="D37" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">shy.polite[3]</t>
+          <t xml:space="preserve">polite.shy[3]</t>
         </is>
       </c>
       <c r="E37" t="inlineStr" s="2">
@@ -1511,7 +1511,7 @@
     <row r="38" ht="40" customHeight="1">
       <c r="A38" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TAG_MATCH_LOSS_LINES.shy.polite[1]</t>
+          <t xml:space="preserve">TAG_MATCH_LOSS_LINES.polite.shy[1]</t>
         </is>
       </c>
       <c r="B38" t="inlineStr" s="2">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="D38" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">shy.polite[1]</t>
+          <t xml:space="preserve">polite.shy[1]</t>
         </is>
       </c>
       <c r="E38" t="inlineStr" s="2">
@@ -1543,7 +1543,7 @@
     <row r="39" ht="40" customHeight="1">
       <c r="A39" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TAG_MATCH_LOSS_LINES.shy.polite[2]</t>
+          <t xml:space="preserve">TAG_MATCH_LOSS_LINES.polite.shy[2]</t>
         </is>
       </c>
       <c r="B39" t="inlineStr" s="2">
@@ -1558,7 +1558,7 @@
       </c>
       <c r="D39" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">shy.polite[2]</t>
+          <t xml:space="preserve">polite.shy[2]</t>
         </is>
       </c>
       <c r="E39" t="inlineStr" s="2">
@@ -1575,7 +1575,7 @@
     <row r="40" ht="40" customHeight="1">
       <c r="A40" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TAG_MATCH_WIN_LINES.shy.polite[1]</t>
+          <t xml:space="preserve">TAG_MATCH_WIN_LINES.polite.shy[1]</t>
         </is>
       </c>
       <c r="B40" t="inlineStr" s="2">
@@ -1590,7 +1590,7 @@
       </c>
       <c r="D40" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">shy.polite[1]</t>
+          <t xml:space="preserve">polite.shy[1]</t>
         </is>
       </c>
       <c r="E40" t="inlineStr" s="2">
@@ -1607,7 +1607,7 @@
     <row r="41" ht="40" customHeight="1">
       <c r="A41" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TAG_MATCH_WIN_LINES.shy.polite[2]</t>
+          <t xml:space="preserve">TAG_MATCH_WIN_LINES.polite.shy[2]</t>
         </is>
       </c>
       <c r="B41" t="inlineStr" s="2">
@@ -1622,7 +1622,7 @@
       </c>
       <c r="D41" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">shy.polite[2]</t>
+          <t xml:space="preserve">polite.shy[2]</t>
         </is>
       </c>
       <c r="E41" t="inlineStr" s="2">
@@ -1639,7 +1639,7 @@
     <row r="42" ht="40" customHeight="1">
       <c r="A42" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_PREMATCH_LINES.ahead.shy.polite[1]</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES.ahead.polite.shy[1]</t>
         </is>
       </c>
       <c r="B42" t="inlineStr" s="2">
@@ -1654,7 +1654,7 @@
       </c>
       <c r="D42" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ahead.shy.polite[1]</t>
+          <t xml:space="preserve">ahead.polite.shy[1]</t>
         </is>
       </c>
       <c r="E42" t="inlineStr" s="2">
@@ -1671,7 +1671,7 @@
     <row r="43" ht="40" customHeight="1">
       <c r="A43" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_PREMATCH_LINES.behind.shy.polite[1]</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES.behind.polite.shy[1]</t>
         </is>
       </c>
       <c r="B43" t="inlineStr" s="2">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="D43" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">behind.shy.polite[1]</t>
+          <t xml:space="preserve">behind.polite.shy[1]</t>
         </is>
       </c>
       <c r="E43" t="inlineStr" s="2">
@@ -1703,7 +1703,7 @@
     <row r="44" ht="40" customHeight="1">
       <c r="A44" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_RESOLUTION_LINES.loser.shy.polite[1]</t>
+          <t xml:space="preserve">BITTER_RESOLUTION_LINES.loser.polite.shy[1]</t>
         </is>
       </c>
       <c r="B44" t="inlineStr" s="2">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="D44" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.shy.polite[1]</t>
+          <t xml:space="preserve">loser.polite.shy[1]</t>
         </is>
       </c>
       <c r="E44" t="inlineStr" s="2">
@@ -1735,7 +1735,7 @@
     <row r="45" ht="40" customHeight="1">
       <c r="A45" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_RESOLUTION_LINES.winner.shy.polite[1]</t>
+          <t xml:space="preserve">BITTER_RESOLUTION_LINES.winner.polite.shy[1]</t>
         </is>
       </c>
       <c r="B45" t="inlineStr" s="2">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="D45" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.shy.polite[1]</t>
+          <t xml:space="preserve">winner.polite.shy[1]</t>
         </is>
       </c>
       <c r="E45" t="inlineStr" s="2">
@@ -1767,7 +1767,7 @@
     <row r="46" ht="40" customHeight="1">
       <c r="A46" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.loser.shy.polite[1]</t>
+          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.loser.polite.shy[1]</t>
         </is>
       </c>
       <c r="B46" t="inlineStr" s="2">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="D46" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.shy.polite[1]</t>
+          <t xml:space="preserve">loser.polite.shy[1]</t>
         </is>
       </c>
       <c r="E46" t="inlineStr" s="2">
@@ -1799,7 +1799,7 @@
     <row r="47" ht="40" customHeight="1">
       <c r="A47" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.winner.shy.polite[1]</t>
+          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.winner.polite.shy[1]</t>
         </is>
       </c>
       <c r="B47" t="inlineStr" s="2">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="D47" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.shy.polite[1]</t>
+          <t xml:space="preserve">winner.polite.shy[1]</t>
         </is>
       </c>
       <c r="E47" t="inlineStr" s="2">
@@ -1831,7 +1831,7 @@
     <row r="48" ht="40" customHeight="1">
       <c r="A48" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.attacker.shy.polite[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.attacker.polite.shy[1]</t>
         </is>
       </c>
       <c r="B48" t="inlineStr" s="2">
@@ -1846,7 +1846,7 @@
       </c>
       <c r="D48" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.shy.polite[1]</t>
+          <t xml:space="preserve">attacker.polite.shy[1]</t>
         </is>
       </c>
       <c r="E48" t="inlineStr" s="2">
@@ -1863,7 +1863,7 @@
     <row r="49" ht="40" customHeight="1">
       <c r="A49" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.defender.shy.polite[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.defender.polite.shy[1]</t>
         </is>
       </c>
       <c r="B49" t="inlineStr" s="2">
@@ -1878,7 +1878,7 @@
       </c>
       <c r="D49" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.shy.polite[1]</t>
+          <t xml:space="preserve">defender.polite.shy[1]</t>
         </is>
       </c>
       <c r="E49" t="inlineStr" s="2">
@@ -1895,7 +1895,7 @@
     <row r="50" ht="40" customHeight="1">
       <c r="A50" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.attacker.shy.polite[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.attacker.polite.shy[1]</t>
         </is>
       </c>
       <c r="B50" t="inlineStr" s="2">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="D50" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.shy.polite[1]</t>
+          <t xml:space="preserve">attacker.polite.shy[1]</t>
         </is>
       </c>
       <c r="E50" t="inlineStr" s="2">
@@ -1927,7 +1927,7 @@
     <row r="51" ht="40" customHeight="1">
       <c r="A51" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.defender.shy.polite[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.defender.polite.shy[1]</t>
         </is>
       </c>
       <c r="B51" t="inlineStr" s="2">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="D51" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.shy.polite[1]</t>
+          <t xml:space="preserve">defender.polite.shy[1]</t>
         </is>
       </c>
       <c r="E51" t="inlineStr" s="2">
@@ -1959,7 +1959,7 @@
     <row r="52" ht="40" customHeight="1">
       <c r="A52" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.attacker.shy.polite[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.attacker.polite.shy[1]</t>
         </is>
       </c>
       <c r="B52" t="inlineStr" s="2">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="D52" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.shy.polite[1]</t>
+          <t xml:space="preserve">attacker.polite.shy[1]</t>
         </is>
       </c>
       <c r="E52" t="inlineStr" s="2">
@@ -1991,7 +1991,7 @@
     <row r="53" ht="40" customHeight="1">
       <c r="A53" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.defender.shy.polite[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.defender.polite.shy[1]</t>
         </is>
       </c>
       <c r="B53" t="inlineStr" s="2">
@@ -2006,7 +2006,7 @@
       </c>
       <c r="D53" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.shy.polite[1]</t>
+          <t xml:space="preserve">defender.polite.shy[1]</t>
         </is>
       </c>
       <c r="E53" t="inlineStr" s="2">
@@ -2023,7 +2023,7 @@
     <row r="54" ht="40" customHeight="1">
       <c r="A54" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateAttacker.shy.polite[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateAttacker.polite.shy[1]</t>
         </is>
       </c>
       <c r="B54" t="inlineStr" s="2">
@@ -2038,7 +2038,7 @@
       </c>
       <c r="D54" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateAttacker.shy.polite[1]</t>
+          <t xml:space="preserve">fateAttacker.polite.shy[1]</t>
         </is>
       </c>
       <c r="E54" t="inlineStr" s="2">
@@ -2055,7 +2055,7 @@
     <row r="55" ht="40" customHeight="1">
       <c r="A55" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateDefender.shy.polite[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateDefender.polite.shy[1]</t>
         </is>
       </c>
       <c r="B55" t="inlineStr" s="2">
@@ -2070,7 +2070,7 @@
       </c>
       <c r="D55" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateDefender.shy.polite[1]</t>
+          <t xml:space="preserve">fateDefender.polite.shy[1]</t>
         </is>
       </c>
       <c r="E55" t="inlineStr" s="2">
@@ -2087,7 +2087,7 @@
     <row r="56" ht="40" customHeight="1">
       <c r="A56" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateLoser.shy.polite[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateLoser.polite.shy[1]</t>
         </is>
       </c>
       <c r="B56" t="inlineStr" s="2">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="D56" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateLoser.shy.polite[1]</t>
+          <t xml:space="preserve">fateLoser.polite.shy[1]</t>
         </is>
       </c>
       <c r="E56" t="inlineStr" s="2">
@@ -2119,7 +2119,7 @@
     <row r="57" ht="40" customHeight="1">
       <c r="A57" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateWinner.shy.polite[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateWinner.polite.shy[1]</t>
         </is>
       </c>
       <c r="B57" t="inlineStr" s="2">
@@ -2134,7 +2134,7 @@
       </c>
       <c r="D57" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateWinner.shy.polite[1]</t>
+          <t xml:space="preserve">fateWinner.polite.shy[1]</t>
         </is>
       </c>
       <c r="E57" t="inlineStr" s="2">
@@ -2151,7 +2151,7 @@
     <row r="58" ht="40" customHeight="1">
       <c r="A58" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.loser.shy.polite[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.loser.polite.shy[1]</t>
         </is>
       </c>
       <c r="B58" t="inlineStr" s="2">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="D58" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.shy.polite[1]</t>
+          <t xml:space="preserve">loser.polite.shy[1]</t>
         </is>
       </c>
       <c r="E58" t="inlineStr" s="2">
@@ -2183,7 +2183,7 @@
     <row r="59" ht="40" customHeight="1">
       <c r="A59" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.winner.shy.polite[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.winner.polite.shy[1]</t>
         </is>
       </c>
       <c r="B59" t="inlineStr" s="2">
@@ -2198,7 +2198,7 @@
       </c>
       <c r="D59" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.shy.polite[1]</t>
+          <t xml:space="preserve">winner.polite.shy[1]</t>
         </is>
       </c>
       <c r="E59" t="inlineStr" s="2">
@@ -2215,7 +2215,7 @@
     <row r="60" ht="40" customHeight="1">
       <c r="A60" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES.loserLines.shy.polite[1]</t>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES.loserLines.polite.shy[1]</t>
         </is>
       </c>
       <c r="B60" t="inlineStr" s="2">
@@ -2230,7 +2230,7 @@
       </c>
       <c r="D60" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loserLines.shy.polite[1]</t>
+          <t xml:space="preserve">loserLines.polite.shy[1]</t>
         </is>
       </c>
       <c r="E60" t="inlineStr" s="2">
@@ -2247,7 +2247,7 @@
     <row r="61" ht="40" customHeight="1">
       <c r="A61" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES.winnerLines.shy.polite[1]</t>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES.winnerLines.polite.shy[1]</t>
         </is>
       </c>
       <c r="B61" t="inlineStr" s="2">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="D61" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winnerLines.shy.polite[1]</t>
+          <t xml:space="preserve">winnerLines.polite.shy[1]</t>
         </is>
       </c>
       <c r="E61" t="inlineStr" s="2">
@@ -3047,7 +3047,7 @@
     <row r="86" ht="40" customHeight="1">
       <c r="A86" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.shy.polite[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.polite.shy[1]</t>
         </is>
       </c>
       <c r="B86" t="inlineStr" s="2">
@@ -3062,7 +3062,7 @@
       </c>
       <c r="D86" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accepted.shy.polite[1]</t>
+          <t xml:space="preserve">accepted.polite.shy[1]</t>
         </is>
       </c>
       <c r="E86" t="inlineStr" s="2">
@@ -3079,7 +3079,7 @@
     <row r="87" ht="40" customHeight="1">
       <c r="A87" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.shy.polite[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.polite.shy[1]</t>
         </is>
       </c>
       <c r="B87" t="inlineStr" s="2">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="D87" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defended.shy.polite[1]</t>
+          <t xml:space="preserve">defended.polite.shy[1]</t>
         </is>
       </c>
       <c r="E87" t="inlineStr" s="2">
@@ -3111,7 +3111,7 @@
     <row r="88" ht="40" customHeight="1">
       <c r="A88" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.shy.polite[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.polite.shy[1]</t>
         </is>
       </c>
       <c r="B88" t="inlineStr" s="2">
@@ -3126,7 +3126,7 @@
       </c>
       <c r="D88" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defense_failed.shy.polite[1]</t>
+          <t xml:space="preserve">defense_failed.polite.shy[1]</t>
         </is>
       </c>
       <c r="E88" t="inlineStr" s="2">
@@ -3143,7 +3143,7 @@
     <row r="89" ht="40" customHeight="1">
       <c r="A89" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.default.shy.polite[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.default.polite.shy[1]</t>
         </is>
       </c>
       <c r="B89" t="inlineStr" s="2">
@@ -3158,7 +3158,7 @@
       </c>
       <c r="D89" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">default.shy.polite[1]</t>
+          <t xml:space="preserve">default.polite.shy[1]</t>
         </is>
       </c>
       <c r="E89" t="inlineStr" s="2">
@@ -3175,7 +3175,7 @@
     <row r="90" ht="40" customHeight="1">
       <c r="A90" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.former_champ.shy.polite[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.former_champ.polite.shy[1]</t>
         </is>
       </c>
       <c r="B90" t="inlineStr" s="2">
@@ -3190,7 +3190,7 @@
       </c>
       <c r="D90" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">former_champ.shy.polite[1]</t>
+          <t xml:space="preserve">former_champ.polite.shy[1]</t>
         </is>
       </c>
       <c r="E90" t="inlineStr" s="2">
@@ -3207,7 +3207,7 @@
     <row r="91" ht="40" customHeight="1">
       <c r="A91" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.heel.shy.polite[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.heel.polite.shy[1]</t>
         </is>
       </c>
       <c r="B91" t="inlineStr" s="2">
@@ -3222,7 +3222,7 @@
       </c>
       <c r="D91" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heel.shy.polite[1]</t>
+          <t xml:space="preserve">heel.polite.shy[1]</t>
         </is>
       </c>
       <c r="E91" t="inlineStr" s="2">
@@ -3239,7 +3239,7 @@
     <row r="92" ht="40" customHeight="1">
       <c r="A92" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.high_trust.shy.polite[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.high_trust.polite.shy[1]</t>
         </is>
       </c>
       <c r="B92" t="inlineStr" s="2">
@@ -3254,7 +3254,7 @@
       </c>
       <c r="D92" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">high_trust.shy.polite[1]</t>
+          <t xml:space="preserve">high_trust.polite.shy[1]</t>
         </is>
       </c>
       <c r="E92" t="inlineStr" s="2">
@@ -3271,7 +3271,7 @@
     <row r="93" ht="40" customHeight="1">
       <c r="A93" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_former_champ.shy.polite[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_former_champ.polite.shy[1]</t>
         </is>
       </c>
       <c r="B93" t="inlineStr" s="2">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="D93" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_former_champ.shy.polite[1]</t>
+          <t xml:space="preserve">accept_former_champ.polite.shy[1]</t>
         </is>
       </c>
       <c r="E93" t="inlineStr" s="2">
@@ -3303,7 +3303,7 @@
     <row r="94" ht="40" customHeight="1">
       <c r="A94" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_heel.shy.polite[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_heel.polite.shy[1]</t>
         </is>
       </c>
       <c r="B94" t="inlineStr" s="2">
@@ -3318,7 +3318,7 @@
       </c>
       <c r="D94" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_heel.shy.polite[1]</t>
+          <t xml:space="preserve">accept_heel.polite.shy[1]</t>
         </is>
       </c>
       <c r="E94" t="inlineStr" s="2">
@@ -3335,7 +3335,7 @@
     <row r="95" ht="40" customHeight="1">
       <c r="A95" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_no_title.shy.polite[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_no_title.polite.shy[1]</t>
         </is>
       </c>
       <c r="B95" t="inlineStr" s="2">
@@ -3350,7 +3350,7 @@
       </c>
       <c r="D95" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_no_title.shy.polite[1]</t>
+          <t xml:space="preserve">accept_no_title.polite.shy[1]</t>
         </is>
       </c>
       <c r="E95" t="inlineStr" s="2">
@@ -3367,7 +3367,7 @@
     <row r="96" ht="40" customHeight="1">
       <c r="A96" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_terminal.shy.polite[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_terminal.polite.shy[1]</t>
         </is>
       </c>
       <c r="B96" t="inlineStr" s="2">
@@ -3382,7 +3382,7 @@
       </c>
       <c r="D96" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_terminal.shy.polite[1]</t>
+          <t xml:space="preserve">accept_terminal.polite.shy[1]</t>
         </is>
       </c>
       <c r="E96" t="inlineStr" s="2">
@@ -3399,7 +3399,7 @@
     <row r="97" ht="40" customHeight="1">
       <c r="A97" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_winless.shy.polite[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_winless.polite.shy[1]</t>
         </is>
       </c>
       <c r="B97" t="inlineStr" s="2">
@@ -3414,7 +3414,7 @@
       </c>
       <c r="D97" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_winless.shy.polite[1]</t>
+          <t xml:space="preserve">accept_winless.polite.shy[1]</t>
         </is>
       </c>
       <c r="E97" t="inlineStr" s="2">
@@ -3431,7 +3431,7 @@
     <row r="98" ht="40" customHeight="1">
       <c r="A98" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_champ.shy.polite[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_champ.polite.shy[1]</t>
         </is>
       </c>
       <c r="B98" t="inlineStr" s="2">
@@ -3446,7 +3446,7 @@
       </c>
       <c r="D98" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_champ.shy.polite[1]</t>
+          <t xml:space="preserve">refuse_champ.polite.shy[1]</t>
         </is>
       </c>
       <c r="E98" t="inlineStr" s="2">
@@ -3463,7 +3463,7 @@
     <row r="99" ht="40" customHeight="1">
       <c r="A99" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_distrust.shy.polite[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_distrust.polite.shy[1]</t>
         </is>
       </c>
       <c r="B99" t="inlineStr" s="2">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="D99" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_distrust.shy.polite[1]</t>
+          <t xml:space="preserve">refuse_distrust.polite.shy[1]</t>
         </is>
       </c>
       <c r="E99" t="inlineStr" s="2">
@@ -3495,7 +3495,7 @@
     <row r="100" ht="40" customHeight="1">
       <c r="A100" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_fighting.shy.polite[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_fighting.polite.shy[1]</t>
         </is>
       </c>
       <c r="B100" t="inlineStr" s="2">
@@ -3510,7 +3510,7 @@
       </c>
       <c r="D100" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_fighting.shy.polite[1]</t>
+          <t xml:space="preserve">refuse_fighting.polite.shy[1]</t>
         </is>
       </c>
       <c r="E100" t="inlineStr" s="2">
@@ -3527,7 +3527,7 @@
     <row r="101" ht="40" customHeight="1">
       <c r="A101" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_heel.shy.polite[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_heel.polite.shy[1]</t>
         </is>
       </c>
       <c r="B101" t="inlineStr" s="2">
@@ -3542,7 +3542,7 @@
       </c>
       <c r="D101" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_heel.shy.polite[1]</t>
+          <t xml:space="preserve">refuse_heel.polite.shy[1]</t>
         </is>
       </c>
       <c r="E101" t="inlineStr" s="2">
@@ -3559,7 +3559,7 @@
     <row r="102" ht="40" customHeight="1">
       <c r="A102" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A1_champion.shy.polite[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A1_champion.polite.shy[1]</t>
         </is>
       </c>
       <c r="B102" t="inlineStr" s="2">
@@ -3574,7 +3574,7 @@
       </c>
       <c r="D102" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A1_champion.shy.polite[1]</t>
+          <t xml:space="preserve">A1_champion.polite.shy[1]</t>
         </is>
       </c>
       <c r="E102" t="inlineStr" s="2">
@@ -3591,7 +3591,7 @@
     <row r="103" ht="40" customHeight="1">
       <c r="A103" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A2_uncrowned.shy.polite[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A2_uncrowned.polite.shy[1]</t>
         </is>
       </c>
       <c r="B103" t="inlineStr" s="2">
@@ -3606,7 +3606,7 @@
       </c>
       <c r="D103" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A2_uncrowned.shy.polite[1]</t>
+          <t xml:space="preserve">A2_uncrowned.polite.shy[1]</t>
         </is>
       </c>
       <c r="E103" t="inlineStr" s="2">
@@ -3623,7 +3623,7 @@
     <row r="104" ht="40" customHeight="1">
       <c r="A104" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A3_heel.shy.polite[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A3_heel.polite.shy[1]</t>
         </is>
       </c>
       <c r="B104" t="inlineStr" s="2">
@@ -3638,7 +3638,7 @@
       </c>
       <c r="D104" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A3_heel.shy.polite[1]</t>
+          <t xml:space="preserve">A3_heel.polite.shy[1]</t>
         </is>
       </c>
       <c r="E104" t="inlineStr" s="2">
@@ -3655,7 +3655,7 @@
     <row r="105" ht="40" customHeight="1">
       <c r="A105" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A4_veteran.shy.polite[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A4_veteran.polite.shy[1]</t>
         </is>
       </c>
       <c r="B105" t="inlineStr" s="2">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="D105" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A4_veteran.shy.polite[1]</t>
+          <t xml:space="preserve">A4_veteran.polite.shy[1]</t>
         </is>
       </c>
       <c r="E105" t="inlineStr" s="2">
@@ -3687,7 +3687,7 @@
     <row r="106" ht="40" customHeight="1">
       <c r="A106" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B1_young.shy.polite[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B1_young.polite.shy[1]</t>
         </is>
       </c>
       <c r="B106" t="inlineStr" s="2">
@@ -3702,7 +3702,7 @@
       </c>
       <c r="D106" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1_young.shy.polite[1]</t>
+          <t xml:space="preserve">B1_young.polite.shy[1]</t>
         </is>
       </c>
       <c r="E106" t="inlineStr" s="2">
@@ -3719,7 +3719,7 @@
     <row r="107" ht="40" customHeight="1">
       <c r="A107" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B2_prime.shy.polite[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B2_prime.polite.shy[1]</t>
         </is>
       </c>
       <c r="B107" t="inlineStr" s="2">
@@ -3734,7 +3734,7 @@
       </c>
       <c r="D107" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_prime.shy.polite[1]</t>
+          <t xml:space="preserve">B2_prime.polite.shy[1]</t>
         </is>
       </c>
       <c r="E107" t="inlineStr" s="2">
@@ -3751,7 +3751,7 @@
     <row r="108" ht="40" customHeight="1">
       <c r="A108" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B3_older.shy.polite[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B3_older.polite.shy[1]</t>
         </is>
       </c>
       <c r="B108" t="inlineStr" s="2">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="D108" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B3_older.shy.polite[1]</t>
+          <t xml:space="preserve">B3_older.polite.shy[1]</t>
         </is>
       </c>
       <c r="E108" t="inlineStr" s="2">
@@ -3783,7 +3783,7 @@
     <row r="109" ht="40" customHeight="1">
       <c r="A109" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B4_champion_injury.shy.polite[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B4_champion_injury.polite.shy[1]</t>
         </is>
       </c>
       <c r="B109" t="inlineStr" s="2">
@@ -3798,7 +3798,7 @@
       </c>
       <c r="D109" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_champion_injury.shy.polite[1]</t>
+          <t xml:space="preserve">B4_champion_injury.polite.shy[1]</t>
         </is>
       </c>
       <c r="E109" t="inlineStr" s="2">
@@ -3815,7 +3815,7 @@
     <row r="110" ht="40" customHeight="1">
       <c r="A110" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VOLUNTARY_STAY_LINES.shy.polite[1]</t>
+          <t xml:space="preserve">VOLUNTARY_STAY_LINES.polite.shy[1]</t>
         </is>
       </c>
       <c r="B110" t="inlineStr" s="2">
@@ -3830,7 +3830,7 @@
       </c>
       <c r="D110" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">shy.polite[1]</t>
+          <t xml:space="preserve">polite.shy[1]</t>
         </is>
       </c>
       <c r="E110" t="inlineStr" s="2">
@@ -3847,7 +3847,7 @@
     <row r="111" ht="40" customHeight="1">
       <c r="A111" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.shy.polite[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.polite.shy[1]</t>
         </is>
       </c>
       <c r="B111" t="inlineStr" s="2">
@@ -3862,7 +3862,7 @@
       </c>
       <c r="D111" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_accept.shy.polite[1]</t>
+          <t xml:space="preserve">raise_accept.polite.shy[1]</t>
         </is>
       </c>
       <c r="E111" t="inlineStr" s="2">
@@ -3879,7 +3879,7 @@
     <row r="112" ht="40" customHeight="1">
       <c r="A112" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.shy.polite[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.polite.shy[1]</t>
         </is>
       </c>
       <c r="B112" t="inlineStr" s="2">
@@ -3894,7 +3894,7 @@
       </c>
       <c r="D112" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_accept.shy.polite[1]</t>
+          <t xml:space="preserve">raise_negotiate_accept.polite.shy[1]</t>
         </is>
       </c>
       <c r="E112" t="inlineStr" s="2">
@@ -3911,7 +3911,7 @@
     <row r="113" ht="40" customHeight="1">
       <c r="A113" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.shy.polite[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.polite.shy[1]</t>
         </is>
       </c>
       <c r="B113" t="inlineStr" s="2">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="D113" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_refuse.shy.polite[1]</t>
+          <t xml:space="preserve">raise_negotiate_refuse.polite.shy[1]</t>
         </is>
       </c>
       <c r="E113" t="inlineStr" s="2">
@@ -3943,7 +3943,7 @@
     <row r="114" ht="40" customHeight="1">
       <c r="A114" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.shy.polite[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.polite.shy[1]</t>
         </is>
       </c>
       <c r="B114" t="inlineStr" s="2">
@@ -3958,7 +3958,7 @@
       </c>
       <c r="D114" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_open.shy.polite[1]</t>
+          <t xml:space="preserve">raise_open.polite.shy[1]</t>
         </is>
       </c>
       <c r="E114" t="inlineStr" s="2">
@@ -3975,7 +3975,7 @@
     <row r="115" ht="40" customHeight="1">
       <c r="A115" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.shy.polite[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.polite.shy[1]</t>
         </is>
       </c>
       <c r="B115" t="inlineStr" s="2">
@@ -3990,7 +3990,7 @@
       </c>
       <c r="D115" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_refuse.shy.polite[1]</t>
+          <t xml:space="preserve">raise_refuse.polite.shy[1]</t>
         </is>
       </c>
       <c r="E115" t="inlineStr" s="2">
@@ -4007,7 +4007,7 @@
     <row r="116" ht="40" customHeight="1">
       <c r="A116" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.shy.polite[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.polite.shy[1]</t>
         </is>
       </c>
       <c r="B116" t="inlineStr" s="2">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="D116" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.shy.polite[1]</t>
+          <t xml:space="preserve">sudden_departure.polite.shy[1]</t>
         </is>
       </c>
       <c r="E116" t="inlineStr" s="2">
@@ -4039,7 +4039,7 @@
     <row r="117" ht="40" customHeight="1">
       <c r="A117" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.shy.polite[2]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.polite.shy[2]</t>
         </is>
       </c>
       <c r="B117" t="inlineStr" s="2">
@@ -4054,7 +4054,7 @@
       </c>
       <c r="D117" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.shy.polite[2]</t>
+          <t xml:space="preserve">sudden_departure.polite.shy[2]</t>
         </is>
       </c>
       <c r="E117" t="inlineStr" s="2">
@@ -4071,7 +4071,7 @@
     <row r="118" ht="40" customHeight="1">
       <c r="A118" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.shy.polite[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.polite.shy[1]</t>
         </is>
       </c>
       <c r="B118" t="inlineStr" s="2">
@@ -4086,7 +4086,7 @@
       </c>
       <c r="D118" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_listen.shy.polite[1]</t>
+          <t xml:space="preserve">transfer_listen.polite.shy[1]</t>
         </is>
       </c>
       <c r="E118" t="inlineStr" s="2">
@@ -4103,7 +4103,7 @@
     <row r="119" ht="40" customHeight="1">
       <c r="A119" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.shy.polite[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.polite.shy[1]</t>
         </is>
       </c>
       <c r="B119" t="inlineStr" s="2">
@@ -4118,7 +4118,7 @@
       </c>
       <c r="D119" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_open.shy.polite[1]</t>
+          <t xml:space="preserve">transfer_open.polite.shy[1]</t>
         </is>
       </c>
       <c r="E119" t="inlineStr" s="2">
@@ -4135,7 +4135,7 @@
     <row r="120" ht="40" customHeight="1">
       <c r="A120" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.shy.polite[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.polite.shy[1]</t>
         </is>
       </c>
       <c r="B120" t="inlineStr" s="2">
@@ -4150,7 +4150,7 @@
       </c>
       <c r="D120" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_release.shy.polite[1]</t>
+          <t xml:space="preserve">transfer_release.polite.shy[1]</t>
         </is>
       </c>
       <c r="E120" t="inlineStr" s="2">
@@ -4167,7 +4167,7 @@
     <row r="121" ht="40" customHeight="1">
       <c r="A121" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.shy.polite[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.polite.shy[1]</t>
         </is>
       </c>
       <c r="B121" t="inlineStr" s="2">
@@ -4182,7 +4182,7 @@
       </c>
       <c r="D121" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_fail.shy.polite[1]</t>
+          <t xml:space="preserve">transfer_retain_fail.polite.shy[1]</t>
         </is>
       </c>
       <c r="E121" t="inlineStr" s="2">
@@ -4199,7 +4199,7 @@
     <row r="122" ht="40" customHeight="1">
       <c r="A122" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.shy.polite[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.polite.shy[1]</t>
         </is>
       </c>
       <c r="B122" t="inlineStr" s="2">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="D122" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_success.shy.polite[1]</t>
+          <t xml:space="preserve">transfer_retain_success.polite.shy[1]</t>
         </is>
       </c>
       <c r="E122" t="inlineStr" s="2">
@@ -4231,7 +4231,7 @@
     <row r="123" ht="40" customHeight="1">
       <c r="A123" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.blocked.shy.polite[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.blocked.polite.shy[1]</t>
         </is>
       </c>
       <c r="B123" t="inlineStr" s="2">
@@ -4246,7 +4246,7 @@
       </c>
       <c r="D123" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">blocked.shy.polite[1]</t>
+          <t xml:space="preserve">blocked.polite.shy[1]</t>
         </is>
       </c>
       <c r="E123" t="inlineStr" s="2">
@@ -4263,7 +4263,7 @@
     <row r="124" ht="40" customHeight="1">
       <c r="A124" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.fail.shy.polite[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.fail.polite.shy[1]</t>
         </is>
       </c>
       <c r="B124" t="inlineStr" s="2">
@@ -4278,7 +4278,7 @@
       </c>
       <c r="D124" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fail.shy.polite[1]</t>
+          <t xml:space="preserve">fail.polite.shy[1]</t>
         </is>
       </c>
       <c r="E124" t="inlineStr" s="2">
@@ -4295,7 +4295,7 @@
     <row r="125" ht="40" customHeight="1">
       <c r="A125" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.start.shy.polite[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.start.polite.shy[1]</t>
         </is>
       </c>
       <c r="B125" t="inlineStr" s="2">
@@ -4310,7 +4310,7 @@
       </c>
       <c r="D125" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">start.shy.polite[1]</t>
+          <t xml:space="preserve">start.polite.shy[1]</t>
         </is>
       </c>
       <c r="E125" t="inlineStr" s="2">
@@ -4327,7 +4327,7 @@
     <row r="126" ht="40" customHeight="1">
       <c r="A126" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.success.shy.polite[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.success.polite.shy[1]</t>
         </is>
       </c>
       <c r="B126" t="inlineStr" s="2">
@@ -4342,7 +4342,7 @@
       </c>
       <c r="D126" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">success.shy.polite[1]</t>
+          <t xml:space="preserve">success.polite.shy[1]</t>
         </is>
       </c>
       <c r="E126" t="inlineStr" s="2">
@@ -5607,7 +5607,7 @@
     <row r="166" ht="40" customHeight="1">
       <c r="A166" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES.shy.polite[1]</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES.polite.shy[1]</t>
         </is>
       </c>
       <c r="B166" t="inlineStr" s="2">
@@ -5622,7 +5622,7 @@
       </c>
       <c r="D166" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">shy.polite[1]</t>
+          <t xml:space="preserve">polite.shy[1]</t>
         </is>
       </c>
       <c r="E166" t="inlineStr" s="2">
@@ -5639,7 +5639,7 @@
     <row r="167" ht="40" customHeight="1">
       <c r="A167" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BT_HINT_LINES.shy.polite[1]</t>
+          <t xml:space="preserve">BT_HINT_LINES.polite.shy[1]</t>
         </is>
       </c>
       <c r="B167" t="inlineStr" s="2">
@@ -5654,7 +5654,7 @@
       </c>
       <c r="D167" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">shy.polite[1]</t>
+          <t xml:space="preserve">polite.shy[1]</t>
         </is>
       </c>
       <c r="E167" t="inlineStr" s="2">
@@ -5671,7 +5671,7 @@
     <row r="168" ht="40" customHeight="1">
       <c r="A168" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES.fresh.shy.polite[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.fresh.polite.shy[1]</t>
         </is>
       </c>
       <c r="B168" t="inlineStr" s="2">
@@ -5686,7 +5686,7 @@
       </c>
       <c r="D168" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fresh.shy.polite[1]</t>
+          <t xml:space="preserve">fresh.polite.shy[1]</t>
         </is>
       </c>
       <c r="E168" t="inlineStr" s="2">
@@ -5703,7 +5703,7 @@
     <row r="169" ht="40" customHeight="1">
       <c r="A169" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES.heavy.shy.polite[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.heavy.polite.shy[1]</t>
         </is>
       </c>
       <c r="B169" t="inlineStr" s="2">
@@ -5718,7 +5718,7 @@
       </c>
       <c r="D169" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heavy.shy.polite[1]</t>
+          <t xml:space="preserve">heavy.polite.shy[1]</t>
         </is>
       </c>
       <c r="E169" t="inlineStr" s="2">
@@ -5735,7 +5735,7 @@
     <row r="170" ht="40" customHeight="1">
       <c r="A170" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES.warm.shy.polite[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.warm.polite.shy[1]</t>
         </is>
       </c>
       <c r="B170" t="inlineStr" s="2">
@@ -5750,7 +5750,7 @@
       </c>
       <c r="D170" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">warm.shy.polite[1]</t>
+          <t xml:space="preserve">warm.polite.shy[1]</t>
         </is>
       </c>
       <c r="E170" t="inlineStr" s="2">
@@ -5767,7 +5767,7 @@
     <row r="171" ht="40" customHeight="1">
       <c r="A171" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES.shy.polite[1]</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES.polite.shy[1]</t>
         </is>
       </c>
       <c r="B171" t="inlineStr" s="2">
@@ -5782,7 +5782,7 @@
       </c>
       <c r="D171" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">shy.polite[1]</t>
+          <t xml:space="preserve">polite.shy[1]</t>
         </is>
       </c>
       <c r="E171" t="inlineStr" s="2">
@@ -5799,7 +5799,7 @@
     <row r="172" ht="40" customHeight="1">
       <c r="A172" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.shy.polite[1]</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.polite.shy[1]</t>
         </is>
       </c>
       <c r="B172" t="inlineStr" s="2">
@@ -5814,7 +5814,7 @@
       </c>
       <c r="D172" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">shy.polite[1]</t>
+          <t xml:space="preserve">polite.shy[1]</t>
         </is>
       </c>
       <c r="E172" t="inlineStr" s="2">
@@ -5831,7 +5831,7 @@
     <row r="173" ht="40" customHeight="1">
       <c r="A173" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES.shy.polite[1]</t>
+          <t xml:space="preserve">SLUMP_END_LINES.polite.shy[1]</t>
         </is>
       </c>
       <c r="B173" t="inlineStr" s="2">
@@ -5846,7 +5846,7 @@
       </c>
       <c r="D173" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">shy.polite[1]</t>
+          <t xml:space="preserve">polite.shy[1]</t>
         </is>
       </c>
       <c r="E173" t="inlineStr" s="2">
@@ -5863,7 +5863,7 @@
     <row r="174" ht="40" customHeight="1">
       <c r="A174" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.defeat.shy.polite[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.defeat.polite.shy[1]</t>
         </is>
       </c>
       <c r="B174" t="inlineStr" s="2">
@@ -5878,7 +5878,7 @@
       </c>
       <c r="D174" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defeat.shy.polite[1]</t>
+          <t xml:space="preserve">defeat.polite.shy[1]</t>
         </is>
       </c>
       <c r="E174" t="inlineStr" s="2">
@@ -5895,7 +5895,7 @@
     <row r="175" ht="40" customHeight="1">
       <c r="A175" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery.shy.polite[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery.polite.shy[1]</t>
         </is>
       </c>
       <c r="B175" t="inlineStr" s="2">
@@ -5910,7 +5910,7 @@
       </c>
       <c r="D175" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_moderate_recovery.shy.polite[1]</t>
+          <t xml:space="preserve">injury_moderate_recovery.polite.shy[1]</t>
         </is>
       </c>
       <c r="E175" t="inlineStr" s="2">
@@ -5927,7 +5927,7 @@
     <row r="176" ht="40" customHeight="1">
       <c r="A176" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery.shy.polite[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery.polite.shy[1]</t>
         </is>
       </c>
       <c r="B176" t="inlineStr" s="2">
@@ -5942,7 +5942,7 @@
       </c>
       <c r="D176" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_severe_recovery.shy.polite[1]</t>
+          <t xml:space="preserve">injury_severe_recovery.polite.shy[1]</t>
         </is>
       </c>
       <c r="E176" t="inlineStr" s="2">
@@ -5959,7 +5959,7 @@
     <row r="177" ht="40" customHeight="1">
       <c r="A177" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.penalty_end.shy.polite[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.penalty_end.polite.shy[1]</t>
         </is>
       </c>
       <c r="B177" t="inlineStr" s="2">
@@ -5974,7 +5974,7 @@
       </c>
       <c r="D177" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">penalty_end.shy.polite[1]</t>
+          <t xml:space="preserve">penalty_end.polite.shy[1]</t>
         </is>
       </c>
       <c r="E177" t="inlineStr" s="2">
@@ -5991,7 +5991,7 @@
     <row r="178" ht="40" customHeight="1">
       <c r="A178" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.bestMatch.shy.polite[1]</t>
+          <t xml:space="preserve">AWARD_LINES.bestMatch.polite.shy[1]</t>
         </is>
       </c>
       <c r="B178" t="inlineStr" s="2">
@@ -6006,7 +6006,7 @@
       </c>
       <c r="D178" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bestMatch.shy.polite[1]</t>
+          <t xml:space="preserve">bestMatch.polite.shy[1]</t>
         </is>
       </c>
       <c r="E178" t="inlineStr" s="2">
@@ -6023,7 +6023,7 @@
     <row r="179" ht="40" customHeight="1">
       <c r="A179" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.champion.shy.polite[1]</t>
+          <t xml:space="preserve">AWARD_LINES.champion.polite.shy[1]</t>
         </is>
       </c>
       <c r="B179" t="inlineStr" s="2">
@@ -6038,7 +6038,7 @@
       </c>
       <c r="D179" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.shy.polite[1]</t>
+          <t xml:space="preserve">champion.polite.shy[1]</t>
         </is>
       </c>
       <c r="E179" t="inlineStr" s="2">
@@ -6055,7 +6055,7 @@
     <row r="180" ht="40" customHeight="1">
       <c r="A180" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.hallOfFame.shy.polite[1]</t>
+          <t xml:space="preserve">AWARD_LINES.hallOfFame.polite.shy[1]</t>
         </is>
       </c>
       <c r="B180" t="inlineStr" s="2">
@@ -6070,7 +6070,7 @@
       </c>
       <c r="D180" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hallOfFame.shy.polite[1]</t>
+          <t xml:space="preserve">hallOfFame.polite.shy[1]</t>
         </is>
       </c>
       <c r="E180" t="inlineStr" s="2">
@@ -6087,7 +6087,7 @@
     <row r="181" ht="40" customHeight="1">
       <c r="A181" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mediaAward.shy.polite[1]</t>
+          <t xml:space="preserve">AWARD_LINES.mediaAward.polite.shy[1]</t>
         </is>
       </c>
       <c r="B181" t="inlineStr" s="2">
@@ -6102,7 +6102,7 @@
       </c>
       <c r="D181" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mediaAward.shy.polite[1]</t>
+          <t xml:space="preserve">mediaAward.polite.shy[1]</t>
         </is>
       </c>
       <c r="E181" t="inlineStr" s="2">
@@ -6119,7 +6119,7 @@
     <row r="182" ht="40" customHeight="1">
       <c r="A182" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mvp.shy.polite[1]</t>
+          <t xml:space="preserve">AWARD_LINES.mvp.polite.shy[1]</t>
         </is>
       </c>
       <c r="B182" t="inlineStr" s="2">
@@ -6134,7 +6134,7 @@
       </c>
       <c r="D182" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mvp.shy.polite[1]</t>
+          <t xml:space="preserve">mvp.polite.shy[1]</t>
         </is>
       </c>
       <c r="E182" t="inlineStr" s="2">
@@ -6151,7 +6151,7 @@
     <row r="183" ht="40" customHeight="1">
       <c r="A183" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.rookie.shy.polite[1]</t>
+          <t xml:space="preserve">AWARD_LINES.rookie.polite.shy[1]</t>
         </is>
       </c>
       <c r="B183" t="inlineStr" s="2">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="D183" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rookie.shy.polite[1]</t>
+          <t xml:space="preserve">rookie.polite.shy[1]</t>
         </is>
       </c>
       <c r="E183" t="inlineStr" s="2">
@@ -6183,7 +6183,7 @@
     <row r="184" ht="40" customHeight="1">
       <c r="A184" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.shy.polite[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.polite.shy[1]</t>
         </is>
       </c>
       <c r="B184" t="inlineStr" s="2">
@@ -6198,7 +6198,7 @@
       </c>
       <c r="D184" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">shy.polite[1]</t>
+          <t xml:space="preserve">polite.shy[1]</t>
         </is>
       </c>
       <c r="E184" t="inlineStr" s="2">
@@ -6215,7 +6215,7 @@
     <row r="185" ht="40" customHeight="1">
       <c r="A185" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.shy.polite[2]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.polite.shy[2]</t>
         </is>
       </c>
       <c r="B185" t="inlineStr" s="2">
@@ -6230,7 +6230,7 @@
       </c>
       <c r="D185" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">shy.polite[2]</t>
+          <t xml:space="preserve">polite.shy[2]</t>
         </is>
       </c>
       <c r="E185" t="inlineStr" s="2">
@@ -6247,7 +6247,7 @@
     <row r="186" ht="40" customHeight="1">
       <c r="A186" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.shy.polite[3]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.polite.shy[3]</t>
         </is>
       </c>
       <c r="B186" t="inlineStr" s="2">
@@ -6262,7 +6262,7 @@
       </c>
       <c r="D186" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">shy.polite[3]</t>
+          <t xml:space="preserve">polite.shy[3]</t>
         </is>
       </c>
       <c r="E186" t="inlineStr" s="2">
@@ -6279,7 +6279,7 @@
     <row r="187" ht="40" customHeight="1">
       <c r="A187" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.shy.polite[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.polite.shy[1]</t>
         </is>
       </c>
       <c r="B187" t="inlineStr" s="2">
@@ -6294,7 +6294,7 @@
       </c>
       <c r="D187" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">shy.polite[1]</t>
+          <t xml:space="preserve">polite.shy[1]</t>
         </is>
       </c>
       <c r="E187" t="inlineStr" s="2">
@@ -6311,7 +6311,7 @@
     <row r="188" ht="40" customHeight="1">
       <c r="A188" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.shy.polite[2]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.polite.shy[2]</t>
         </is>
       </c>
       <c r="B188" t="inlineStr" s="2">
@@ -6326,7 +6326,7 @@
       </c>
       <c r="D188" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">shy.polite[2]</t>
+          <t xml:space="preserve">polite.shy[2]</t>
         </is>
       </c>
       <c r="E188" t="inlineStr" s="2">
@@ -6343,7 +6343,7 @@
     <row r="189" ht="40" customHeight="1">
       <c r="A189" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.shy.polite[3]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.polite.shy[3]</t>
         </is>
       </c>
       <c r="B189" t="inlineStr" s="2">
@@ -6358,7 +6358,7 @@
       </c>
       <c r="D189" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">shy.polite[3]</t>
+          <t xml:space="preserve">polite.shy[3]</t>
         </is>
       </c>
       <c r="E189" t="inlineStr" s="2">
@@ -6375,7 +6375,7 @@
     <row r="190" ht="40" customHeight="1">
       <c r="A190" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N1.shy.polite[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N1.polite.shy[1]</t>
         </is>
       </c>
       <c r="B190" t="inlineStr" s="2">
@@ -6390,7 +6390,7 @@
       </c>
       <c r="D190" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N1.shy.polite[1]</t>
+          <t xml:space="preserve">N1.polite.shy[1]</t>
         </is>
       </c>
       <c r="E190" t="inlineStr" s="2">
@@ -6407,7 +6407,7 @@
     <row r="191" ht="40" customHeight="1">
       <c r="A191" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N2.shy.polite[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N2.polite.shy[1]</t>
         </is>
       </c>
       <c r="B191" t="inlineStr" s="2">
@@ -6422,7 +6422,7 @@
       </c>
       <c r="D191" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N2.shy.polite[1]</t>
+          <t xml:space="preserve">N2.polite.shy[1]</t>
         </is>
       </c>
       <c r="E191" t="inlineStr" s="2">
@@ -6439,7 +6439,7 @@
     <row r="192" ht="40" customHeight="1">
       <c r="A192" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N3.shy.polite[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N3.polite.shy[1]</t>
         </is>
       </c>
       <c r="B192" t="inlineStr" s="2">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="D192" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N3.shy.polite[1]</t>
+          <t xml:space="preserve">N3.polite.shy[1]</t>
         </is>
       </c>
       <c r="E192" t="inlineStr" s="2">
@@ -6471,7 +6471,7 @@
     <row r="193" ht="40" customHeight="1">
       <c r="A193" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N4.shy.polite[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N4.polite.shy[1]</t>
         </is>
       </c>
       <c r="B193" t="inlineStr" s="2">
@@ -6486,7 +6486,7 @@
       </c>
       <c r="D193" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N4.shy.polite[1]</t>
+          <t xml:space="preserve">N4.polite.shy[1]</t>
         </is>
       </c>
       <c r="E193" t="inlineStr" s="2">
@@ -6503,7 +6503,7 @@
     <row r="194" ht="40" customHeight="1">
       <c r="A194" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.shy.polite[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.polite.shy[1]</t>
         </is>
       </c>
       <c r="B194" t="inlineStr" s="2">
@@ -6518,7 +6518,7 @@
       </c>
       <c r="D194" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_low.shy.polite[1]</t>
+          <t xml:space="preserve">N5_low.polite.shy[1]</t>
         </is>
       </c>
       <c r="E194" t="inlineStr" s="2">
@@ -6535,7 +6535,7 @@
     <row r="195" ht="40" customHeight="1">
       <c r="A195" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.shy.polite[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.polite.shy[1]</t>
         </is>
       </c>
       <c r="B195" t="inlineStr" s="2">
@@ -6550,7 +6550,7 @@
       </c>
       <c r="D195" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_warning.shy.polite[1]</t>
+          <t xml:space="preserve">N5_warning.polite.shy[1]</t>
         </is>
       </c>
       <c r="E195" t="inlineStr" s="2">
@@ -6567,7 +6567,7 @@
     <row r="196" ht="40" customHeight="1">
       <c r="A196" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.breakthrough.voice.shy.polite[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.breakthrough.voice.polite.shy[1]</t>
         </is>
       </c>
       <c r="B196" t="inlineStr" s="2">
@@ -6582,7 +6582,7 @@
       </c>
       <c r="D196" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">breakthrough.voice.shy.polite[1]</t>
+          <t xml:space="preserve">breakthrough.voice.polite.shy[1]</t>
         </is>
       </c>
       <c r="E196" t="inlineStr" s="2">
@@ -6599,7 +6599,7 @@
     <row r="197" ht="40" customHeight="1">
       <c r="A197" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G1.voice.shy.polite[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G1.voice.polite.shy[1]</t>
         </is>
       </c>
       <c r="B197" t="inlineStr" s="2">
@@ -6614,7 +6614,7 @@
       </c>
       <c r="D197" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G1.voice.shy.polite[1]</t>
+          <t xml:space="preserve">G1.voice.polite.shy[1]</t>
         </is>
       </c>
       <c r="E197" t="inlineStr" s="2">
@@ -6631,7 +6631,7 @@
     <row r="198" ht="40" customHeight="1">
       <c r="A198" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G2.voice.shy.polite[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G2.voice.polite.shy[1]</t>
         </is>
       </c>
       <c r="B198" t="inlineStr" s="2">
@@ -6646,7 +6646,7 @@
       </c>
       <c r="D198" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G2.voice.shy.polite[1]</t>
+          <t xml:space="preserve">G2.voice.polite.shy[1]</t>
         </is>
       </c>
       <c r="E198" t="inlineStr" s="2">
@@ -6663,7 +6663,7 @@
     <row r="199" ht="40" customHeight="1">
       <c r="A199" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G3.voice.shy.polite[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G3.voice.polite.shy[1]</t>
         </is>
       </c>
       <c r="B199" t="inlineStr" s="2">
@@ -6678,7 +6678,7 @@
       </c>
       <c r="D199" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G3.voice.shy.polite[1]</t>
+          <t xml:space="preserve">G3.voice.polite.shy[1]</t>
         </is>
       </c>
       <c r="E199" t="inlineStr" s="2">
@@ -6695,7 +6695,7 @@
     <row r="200" ht="40" customHeight="1">
       <c r="A200" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G4.voice.shy.polite[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G4.voice.polite.shy[1]</t>
         </is>
       </c>
       <c r="B200" t="inlineStr" s="2">
@@ -6710,7 +6710,7 @@
       </c>
       <c r="D200" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G4.voice.shy.polite[1]</t>
+          <t xml:space="preserve">G4.voice.polite.shy[1]</t>
         </is>
       </c>
       <c r="E200" t="inlineStr" s="2">
@@ -6727,7 +6727,7 @@
     <row r="201" ht="40" customHeight="1">
       <c r="A201" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R2.voice.shy.polite[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R2.voice.polite.shy[1]</t>
         </is>
       </c>
       <c r="B201" t="inlineStr" s="2">
@@ -6742,7 +6742,7 @@
       </c>
       <c r="D201" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R2.voice.shy.polite[1]</t>
+          <t xml:space="preserve">R2.voice.polite.shy[1]</t>
         </is>
       </c>
       <c r="E201" t="inlineStr" s="2">
@@ -6759,7 +6759,7 @@
     <row r="202" ht="40" customHeight="1">
       <c r="A202" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R3.modal.shy.polite[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R3.modal.polite.shy[1]</t>
         </is>
       </c>
       <c r="B202" t="inlineStr" s="2">
@@ -6774,7 +6774,7 @@
       </c>
       <c r="D202" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R3.modal.shy.polite[1]</t>
+          <t xml:space="preserve">R3.modal.polite.shy[1]</t>
         </is>
       </c>
       <c r="E202" t="inlineStr" s="2">
@@ -6791,7 +6791,7 @@
     <row r="203" ht="40" customHeight="1">
       <c r="A203" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R4.voice.shy.polite[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R4.voice.polite.shy[1]</t>
         </is>
       </c>
       <c r="B203" t="inlineStr" s="2">
@@ -6806,7 +6806,7 @@
       </c>
       <c r="D203" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R4.voice.shy.polite[1]</t>
+          <t xml:space="preserve">R4.voice.polite.shy[1]</t>
         </is>
       </c>
       <c r="E203" t="inlineStr" s="2">
@@ -6823,7 +6823,7 @@
     <row r="204" ht="40" customHeight="1">
       <c r="A204" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R5.voice.shy.polite[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R5.voice.polite.shy[1]</t>
         </is>
       </c>
       <c r="B204" t="inlineStr" s="2">
@@ -6838,7 +6838,7 @@
       </c>
       <c r="D204" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R5.voice.shy.polite[1]</t>
+          <t xml:space="preserve">R5.voice.polite.shy[1]</t>
         </is>
       </c>
       <c r="E204" t="inlineStr" s="2">
@@ -6855,7 +6855,7 @@
     <row r="205" ht="40" customHeight="1">
       <c r="A205" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.warVictory.voice.shy.polite[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.warVictory.voice.polite.shy[1]</t>
         </is>
       </c>
       <c r="B205" t="inlineStr" s="2">
@@ -6870,7 +6870,7 @@
       </c>
       <c r="D205" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">warVictory.voice.shy.polite[1]</t>
+          <t xml:space="preserve">warVictory.voice.polite.shy[1]</t>
         </is>
       </c>
       <c r="E205" t="inlineStr" s="2">
@@ -6887,7 +6887,7 @@
     <row r="206" ht="40" customHeight="1">
       <c r="A206" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus_repeat.shy.polite[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus_repeat.polite.shy[1]</t>
         </is>
       </c>
       <c r="B206" t="inlineStr" s="2">
@@ -6902,7 +6902,7 @@
       </c>
       <c r="D206" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus_repeat.shy.polite[1]</t>
+          <t xml:space="preserve">bonus_repeat.polite.shy[1]</t>
         </is>
       </c>
       <c r="E206" t="inlineStr" s="2">
@@ -6919,7 +6919,7 @@
     <row r="207" ht="40" customHeight="1">
       <c r="A207" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.shy.polite[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.polite.shy[1]</t>
         </is>
       </c>
       <c r="B207" t="inlineStr" s="2">
@@ -6934,7 +6934,7 @@
       </c>
       <c r="D207" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus.shy.polite[1]</t>
+          <t xml:space="preserve">bonus.polite.shy[1]</t>
         </is>
       </c>
       <c r="E207" t="inlineStr" s="2">
@@ -6951,7 +6951,7 @@
     <row r="208" ht="40" customHeight="1">
       <c r="A208" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.shy.polite[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.polite.shy[1]</t>
         </is>
       </c>
       <c r="B208" t="inlineStr" s="2">
@@ -6966,7 +6966,7 @@
       </c>
       <c r="D208" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">camp.shy.polite[1]</t>
+          <t xml:space="preserve">camp.polite.shy[1]</t>
         </is>
       </c>
       <c r="E208" t="inlineStr" s="2">
@@ -6983,7 +6983,7 @@
     <row r="209" ht="40" customHeight="1">
       <c r="A209" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.shy.polite[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.polite.shy[1]</t>
         </is>
       </c>
       <c r="B209" t="inlineStr" s="2">
@@ -6998,7 +6998,7 @@
       </c>
       <c r="D209" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage_high_trust.shy.polite[1]</t>
+          <t xml:space="preserve">encourage_high_trust.polite.shy[1]</t>
         </is>
       </c>
       <c r="E209" t="inlineStr" s="2">
@@ -7015,7 +7015,7 @@
     <row r="210" ht="40" customHeight="1">
       <c r="A210" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.shy.polite[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.polite.shy[1]</t>
         </is>
       </c>
       <c r="B210" t="inlineStr" s="2">
@@ -7030,7 +7030,7 @@
       </c>
       <c r="D210" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage.shy.polite[1]</t>
+          <t xml:space="preserve">encourage.polite.shy[1]</t>
         </is>
       </c>
       <c r="E210" t="inlineStr" s="2">
@@ -7047,7 +7047,7 @@
     <row r="211" ht="40" customHeight="1">
       <c r="A211" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.shy.polite[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.polite.shy[1]</t>
         </is>
       </c>
       <c r="B211" t="inlineStr" s="2">
@@ -7062,7 +7062,7 @@
       </c>
       <c r="D211" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faction_decree.shy.polite[1]</t>
+          <t xml:space="preserve">faction_decree.polite.shy[1]</t>
         </is>
       </c>
       <c r="E211" t="inlineStr" s="2">
@@ -7079,7 +7079,7 @@
     <row r="212" ht="40" customHeight="1">
       <c r="A212" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.shy.polite[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.polite.shy[1]</t>
         </is>
       </c>
       <c r="B212" t="inlineStr" s="2">
@@ -7094,7 +7094,7 @@
       </c>
       <c r="D212" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">media.shy.polite[1]</t>
+          <t xml:space="preserve">media.polite.shy[1]</t>
         </is>
       </c>
       <c r="E212" t="inlineStr" s="2">
@@ -7111,7 +7111,7 @@
     <row r="213" ht="40" customHeight="1">
       <c r="A213" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.shy.polite[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.polite.shy[1]</t>
         </is>
       </c>
       <c r="B213" t="inlineStr" s="2">
@@ -7126,7 +7126,7 @@
       </c>
       <c r="D213" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">party.shy.polite[1]</t>
+          <t xml:space="preserve">party.polite.shy[1]</t>
         </is>
       </c>
       <c r="E213" t="inlineStr" s="2">
@@ -7143,7 +7143,7 @@
     <row r="214" ht="40" customHeight="1">
       <c r="A214" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.shy.polite[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.polite.shy[1]</t>
         </is>
       </c>
       <c r="B214" t="inlineStr" s="2">
@@ -7158,7 +7158,7 @@
       </c>
       <c r="D214" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refresh_leave.shy.polite[1]</t>
+          <t xml:space="preserve">refresh_leave.polite.shy[1]</t>
         </is>
       </c>
       <c r="E214" t="inlineStr" s="2">
@@ -7175,7 +7175,7 @@
     <row r="215" ht="40" customHeight="1">
       <c r="A215" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.shy.polite[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.polite.shy[1]</t>
         </is>
       </c>
       <c r="B215" t="inlineStr" s="2">
@@ -7190,7 +7190,7 @@
       </c>
       <c r="D215" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">special_treatment.shy.polite[1]</t>
+          <t xml:space="preserve">special_treatment.polite.shy[1]</t>
         </is>
       </c>
       <c r="E215" t="inlineStr" s="2">
@@ -7207,7 +7207,7 @@
     <row r="216" ht="40" customHeight="1">
       <c r="A216" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.shy.polite[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.polite.shy[1]</t>
         </is>
       </c>
       <c r="B216" t="inlineStr" s="2">
@@ -7222,7 +7222,7 @@
       </c>
       <c r="D216" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trainer.shy.polite[1]</t>
+          <t xml:space="preserve">trainer.polite.shy[1]</t>
         </is>
       </c>
       <c r="E216" t="inlineStr" s="2">
@@ -7239,7 +7239,7 @@
     <row r="217" ht="40" customHeight="1">
       <c r="A217" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.shy.polite[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.polite.shy[1]</t>
         </is>
       </c>
       <c r="B217" t="inlineStr" s="2">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="D217" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.shy.polite[1]</t>
+          <t xml:space="preserve">E1.polite.shy[1]</t>
         </is>
       </c>
       <c r="E217" t="inlineStr" s="2">
@@ -7271,7 +7271,7 @@
     <row r="218" ht="40" customHeight="1">
       <c r="A218" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E4.shy.polite[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E4.polite.shy[1]</t>
         </is>
       </c>
       <c r="B218" t="inlineStr" s="2">
@@ -7286,7 +7286,7 @@
       </c>
       <c r="D218" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E4.shy.polite[1]</t>
+          <t xml:space="preserve">E4.polite.shy[1]</t>
         </is>
       </c>
       <c r="E218" t="inlineStr" s="2">
@@ -7303,7 +7303,7 @@
     <row r="219" ht="40" customHeight="1">
       <c r="A219" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.shy.polite[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.polite.shy[1]</t>
         </is>
       </c>
       <c r="B219" t="inlineStr" s="2">
@@ -7318,7 +7318,7 @@
       </c>
       <c r="D219" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E6.shy.polite[1]</t>
+          <t xml:space="preserve">E6.polite.shy[1]</t>
         </is>
       </c>
       <c r="E219" t="inlineStr" s="2">
@@ -7335,7 +7335,7 @@
     <row r="220" ht="40" customHeight="1">
       <c r="A220" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.shy.polite[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.polite.shy[1]</t>
         </is>
       </c>
       <c r="B220" t="inlineStr" s="2">
@@ -7350,7 +7350,7 @@
       </c>
       <c r="D220" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_boycott.shy.polite[1]</t>
+          <t xml:space="preserve">S_boycott.polite.shy[1]</t>
         </is>
       </c>
       <c r="E220" t="inlineStr" s="2">
@@ -7367,7 +7367,7 @@
     <row r="221" ht="40" customHeight="1">
       <c r="A221" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.shy.polite[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.polite.shy[1]</t>
         </is>
       </c>
       <c r="B221" t="inlineStr" s="2">
@@ -7382,7 +7382,7 @@
       </c>
       <c r="D221" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_grumble.shy.polite[1]</t>
+          <t xml:space="preserve">S_grumble.polite.shy[1]</t>
         </is>
       </c>
       <c r="E221" t="inlineStr" s="2">
@@ -7399,7 +7399,7 @@
     <row r="222" ht="40" customHeight="1">
       <c r="A222" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.shy.polite[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.polite.shy[1]</t>
         </is>
       </c>
       <c r="B222" t="inlineStr" s="2">
@@ -7414,7 +7414,7 @@
       </c>
       <c r="D222" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_sns.shy.polite[1]</t>
+          <t xml:space="preserve">S_sns.polite.shy[1]</t>
         </is>
       </c>
       <c r="E222" t="inlineStr" s="2">
@@ -7431,7 +7431,7 @@
     <row r="223" ht="40" customHeight="1">
       <c r="A223" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.shy.polite[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.polite.shy[1]</t>
         </is>
       </c>
       <c r="B223" t="inlineStr" s="2">
@@ -7446,7 +7446,7 @@
       </c>
       <c r="D223" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S1.shy.polite[1]</t>
+          <t xml:space="preserve">S1.polite.shy[1]</t>
         </is>
       </c>
       <c r="E223" t="inlineStr" s="2">
@@ -7463,7 +7463,7 @@
     <row r="224" ht="40" customHeight="1">
       <c r="A224" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.shy.polite[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.polite.shy[1]</t>
         </is>
       </c>
       <c r="B224" t="inlineStr" s="2">
@@ -7478,7 +7478,7 @@
       </c>
       <c r="D224" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S2.shy.polite[1]</t>
+          <t xml:space="preserve">S2.polite.shy[1]</t>
         </is>
       </c>
       <c r="E224" t="inlineStr" s="2">
@@ -7495,7 +7495,7 @@
     <row r="225" ht="40" customHeight="1">
       <c r="A225" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.shy.polite[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.polite.shy[1]</t>
         </is>
       </c>
       <c r="B225" t="inlineStr" s="2">
@@ -7510,7 +7510,7 @@
       </c>
       <c r="D225" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S3.shy.polite[1]</t>
+          <t xml:space="preserve">S3.polite.shy[1]</t>
         </is>
       </c>
       <c r="E225" t="inlineStr" s="2">
@@ -7527,7 +7527,7 @@
     <row r="226" ht="40" customHeight="1">
       <c r="A226" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.shy.polite[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.polite.shy[1]</t>
         </is>
       </c>
       <c r="B226" t="inlineStr" s="2">
@@ -7542,7 +7542,7 @@
       </c>
       <c r="D226" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_direct.shy.polite[1]</t>
+          <t xml:space="preserve">S4_direct.polite.shy[1]</t>
         </is>
       </c>
       <c r="E226" t="inlineStr" s="2">
@@ -7559,7 +7559,7 @@
     <row r="227" ht="40" customHeight="1">
       <c r="A227" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.shy.polite[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.polite.shy[1]</t>
         </is>
       </c>
       <c r="B227" t="inlineStr" s="2">
@@ -7574,7 +7574,7 @@
       </c>
       <c r="D227" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_silent.shy.polite[1]</t>
+          <t xml:space="preserve">S4_silent.polite.shy[1]</t>
         </is>
       </c>
       <c r="E227" t="inlineStr" s="2">
@@ -7591,7 +7591,7 @@
     <row r="228" ht="40" customHeight="1">
       <c r="A228" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.shy.polite[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.polite.shy[1]</t>
         </is>
       </c>
       <c r="B228" t="inlineStr" s="2">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="D228" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S5.shy.polite[1]</t>
+          <t xml:space="preserve">S5.polite.shy[1]</t>
         </is>
       </c>
       <c r="E228" t="inlineStr" s="2">
@@ -7623,7 +7623,7 @@
     <row r="229" ht="40" customHeight="1">
       <c r="A229" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.shy.polite[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.polite.shy[1]</t>
         </is>
       </c>
       <c r="B229" t="inlineStr" s="2">
@@ -7638,7 +7638,7 @@
       </c>
       <c r="D229" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S6.shy.polite[1]</t>
+          <t xml:space="preserve">S6.polite.shy[1]</t>
         </is>
       </c>
       <c r="E229" t="inlineStr" s="2">
@@ -7655,7 +7655,7 @@
     <row r="230" ht="40" customHeight="1">
       <c r="A230" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.shy.polite[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.polite.shy[1]</t>
         </is>
       </c>
       <c r="B230" t="inlineStr" s="2">
@@ -7670,7 +7670,7 @@
       </c>
       <c r="D230" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1.shy.polite[1]</t>
+          <t xml:space="preserve">B1.polite.shy[1]</t>
         </is>
       </c>
       <c r="E230" t="inlineStr" s="2">
@@ -7687,7 +7687,7 @@
     <row r="231" ht="40" customHeight="1">
       <c r="A231" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.shy.polite[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.polite.shy[1]</t>
         </is>
       </c>
       <c r="B231" t="inlineStr" s="2">
@@ -7702,7 +7702,7 @@
       </c>
       <c r="D231" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter1.shy.polite[1]</t>
+          <t xml:space="preserve">B2_fighter1.polite.shy[1]</t>
         </is>
       </c>
       <c r="E231" t="inlineStr" s="2">
@@ -7719,7 +7719,7 @@
     <row r="232" ht="40" customHeight="1">
       <c r="A232" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.shy.polite[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.polite.shy[1]</t>
         </is>
       </c>
       <c r="B232" t="inlineStr" s="2">
@@ -7734,7 +7734,7 @@
       </c>
       <c r="D232" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter2.shy.polite[1]</t>
+          <t xml:space="preserve">B2_fighter2.polite.shy[1]</t>
         </is>
       </c>
       <c r="E232" t="inlineStr" s="2">
@@ -7751,7 +7751,7 @@
     <row r="233" ht="40" customHeight="1">
       <c r="A233" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.shy.polite[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.polite.shy[1]</t>
         </is>
       </c>
       <c r="B233" t="inlineStr" s="2">
@@ -7766,7 +7766,7 @@
       </c>
       <c r="D233" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_brand.shy.polite[1]</t>
+          <t xml:space="preserve">B4_brand.polite.shy[1]</t>
         </is>
       </c>
       <c r="E233" t="inlineStr" s="2">
@@ -7783,7 +7783,7 @@
     <row r="234" ht="40" customHeight="1">
       <c r="A234" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.shy.polite[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.polite.shy[1]</t>
         </is>
       </c>
       <c r="B234" t="inlineStr" s="2">
@@ -7798,7 +7798,7 @@
       </c>
       <c r="D234" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_cm.shy.polite[1]</t>
+          <t xml:space="preserve">B4_cm.polite.shy[1]</t>
         </is>
       </c>
       <c r="E234" t="inlineStr" s="2">
@@ -7815,7 +7815,7 @@
     <row r="235" ht="40" customHeight="1">
       <c r="A235" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.shy.polite[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.polite.shy[1]</t>
         </is>
       </c>
       <c r="B235" t="inlineStr" s="2">
@@ -7830,7 +7830,7 @@
       </c>
       <c r="D235" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fan.shy.polite[1]</t>
+          <t xml:space="preserve">B4_fan.polite.shy[1]</t>
         </is>
       </c>
       <c r="E235" t="inlineStr" s="2">
@@ -7847,7 +7847,7 @@
     <row r="236" ht="40" customHeight="1">
       <c r="A236" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.shy.polite[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.polite.shy[1]</t>
         </is>
       </c>
       <c r="B236" t="inlineStr" s="2">
@@ -7862,7 +7862,7 @@
       </c>
       <c r="D236" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fashion.shy.polite[1]</t>
+          <t xml:space="preserve">B4_fashion.polite.shy[1]</t>
         </is>
       </c>
       <c r="E236" t="inlineStr" s="2">
@@ -7879,7 +7879,7 @@
     <row r="237" ht="40" customHeight="1">
       <c r="A237" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.shy.polite[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.polite.shy[1]</t>
         </is>
       </c>
       <c r="B237" t="inlineStr" s="2">
@@ -7894,7 +7894,7 @@
       </c>
       <c r="D237" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_gravure.shy.polite[1]</t>
+          <t xml:space="preserve">B4_gravure.polite.shy[1]</t>
         </is>
       </c>
       <c r="E237" t="inlineStr" s="2">
@@ -7911,7 +7911,7 @@
     <row r="238" ht="40" customHeight="1">
       <c r="A238" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.shy.polite[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.polite.shy[1]</t>
         </is>
       </c>
       <c r="B238" t="inlineStr" s="2">
@@ -7926,7 +7926,7 @@
       </c>
       <c r="D238" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_variety.shy.polite[1]</t>
+          <t xml:space="preserve">B4_variety.polite.shy[1]</t>
         </is>
       </c>
       <c r="E238" t="inlineStr" s="2">
@@ -7943,7 +7943,7 @@
     <row r="239" ht="40" customHeight="1">
       <c r="A239" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.shy.polite[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.polite.shy[1]</t>
         </is>
       </c>
       <c r="B239" t="inlineStr" s="2">
@@ -7958,7 +7958,7 @@
       </c>
       <c r="D239" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4.shy.polite[1]</t>
+          <t xml:space="preserve">B4.polite.shy[1]</t>
         </is>
       </c>
       <c r="E239" t="inlineStr" s="2">
@@ -7975,7 +7975,7 @@
     <row r="240" ht="40" customHeight="1">
       <c r="A240" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.shy.polite[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.polite.shy[1]</t>
         </is>
       </c>
       <c r="B240" t="inlineStr" s="2">
@@ -7990,7 +7990,7 @@
       </c>
       <c r="D240" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">shy.polite[1]</t>
+          <t xml:space="preserve">polite.shy[1]</t>
         </is>
       </c>
       <c r="E240" t="inlineStr" s="2">
@@ -8007,7 +8007,7 @@
     <row r="241" ht="40" customHeight="1">
       <c r="A241" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.shy.polite[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.polite.shy[1]</t>
         </is>
       </c>
       <c r="B241" t="inlineStr" s="2">
@@ -8022,7 +8022,7 @@
       </c>
       <c r="D241" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">shy.polite[1]</t>
+          <t xml:space="preserve">polite.shy[1]</t>
         </is>
       </c>
       <c r="E241" t="inlineStr" s="2">
@@ -8039,7 +8039,7 @@
     <row r="242" ht="40" customHeight="1">
       <c r="A242" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.shy.polite[1]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.polite.shy[1]</t>
         </is>
       </c>
       <c r="B242" t="inlineStr" s="2">
@@ -8054,7 +8054,7 @@
       </c>
       <c r="D242" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">shy.polite[1]</t>
+          <t xml:space="preserve">polite.shy[1]</t>
         </is>
       </c>
       <c r="E242" t="inlineStr" s="2">
@@ -8071,7 +8071,7 @@
     <row r="243" ht="40" customHeight="1">
       <c r="A243" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.shy.polite[1]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.polite.shy[1]</t>
         </is>
       </c>
       <c r="B243" t="inlineStr" s="2">
@@ -8086,7 +8086,7 @@
       </c>
       <c r="D243" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">shy.polite[1]</t>
+          <t xml:space="preserve">polite.shy[1]</t>
         </is>
       </c>
       <c r="E243" t="inlineStr" s="2">
@@ -8103,7 +8103,7 @@
     <row r="244" ht="40" customHeight="1">
       <c r="A244" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.shy.polite[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.polite.shy[1]</t>
         </is>
       </c>
       <c r="B244" t="inlineStr" s="2">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="D244" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">shy.polite[1]</t>
+          <t xml:space="preserve">polite.shy[1]</t>
         </is>
       </c>
       <c r="E244" t="inlineStr" s="2">
@@ -8135,7 +8135,7 @@
     <row r="245" ht="40" customHeight="1">
       <c r="A245" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.shy.polite[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.polite.shy[1]</t>
         </is>
       </c>
       <c r="B245" t="inlineStr" s="2">
@@ -8150,7 +8150,7 @@
       </c>
       <c r="D245" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.ahead.shy.polite[1]</t>
+          <t xml:space="preserve">bitterPrematch.ahead.polite.shy[1]</t>
         </is>
       </c>
       <c r="E245" t="inlineStr" s="2">
@@ -8167,7 +8167,7 @@
     <row r="246" ht="40" customHeight="1">
       <c r="A246" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.shy.polite[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.polite.shy[1]</t>
         </is>
       </c>
       <c r="B246" t="inlineStr" s="2">
@@ -8182,7 +8182,7 @@
       </c>
       <c r="D246" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.behind.shy.polite[1]</t>
+          <t xml:space="preserve">bitterPrematch.behind.polite.shy[1]</t>
         </is>
       </c>
       <c r="E246" t="inlineStr" s="2">
@@ -8199,7 +8199,7 @@
     <row r="247" ht="40" customHeight="1">
       <c r="A247" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.shy.polite[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.polite.shy[1]</t>
         </is>
       </c>
       <c r="B247" t="inlineStr" s="2">
@@ -8214,7 +8214,7 @@
       </c>
       <c r="D247" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftInterest.shy.polite[1]</t>
+          <t xml:space="preserve">draftInterest.polite.shy[1]</t>
         </is>
       </c>
       <c r="E247" t="inlineStr" s="2">
@@ -8231,7 +8231,7 @@
     <row r="248" ht="40" customHeight="1">
       <c r="A248" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.shy.polite[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.polite.shy[1]</t>
         </is>
       </c>
       <c r="B248" t="inlineStr" s="2">
@@ -8246,7 +8246,7 @@
       </c>
       <c r="D248" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.shy.polite[1]</t>
+          <t xml:space="preserve">draftJoin.polite.shy[1]</t>
         </is>
       </c>
       <c r="E248" t="inlineStr" s="2">
@@ -8263,7 +8263,7 @@
     <row r="249" ht="40" customHeight="1">
       <c r="A249" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.shy.polite[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.polite.shy[1]</t>
         </is>
       </c>
       <c r="B249" t="inlineStr" s="2">
@@ -8278,7 +8278,7 @@
       </c>
       <c r="D249" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faGreeting.shy.polite[1]</t>
+          <t xml:space="preserve">faGreeting.polite.shy[1]</t>
         </is>
       </c>
       <c r="E249" t="inlineStr" s="2">
@@ -8295,7 +8295,7 @@
     <row r="250" ht="40" customHeight="1">
       <c r="A250" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.shy.polite[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.polite.shy[1]</t>
         </is>
       </c>
       <c r="B250" t="inlineStr" s="2">
@@ -8310,7 +8310,7 @@
       </c>
       <c r="D250" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faSigning.shy.polite[1]</t>
+          <t xml:space="preserve">faSigning.polite.shy[1]</t>
         </is>
       </c>
       <c r="E250" t="inlineStr" s="2">
@@ -8327,7 +8327,7 @@
     <row r="251" ht="40" customHeight="1">
       <c r="A251" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.shy.polite[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.polite.shy[1]</t>
         </is>
       </c>
       <c r="B251" t="inlineStr" s="2">
@@ -8342,7 +8342,7 @@
       </c>
       <c r="D251" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faWelcome.shy.polite[1]</t>
+          <t xml:space="preserve">faWelcome.polite.shy[1]</t>
         </is>
       </c>
       <c r="E251" t="inlineStr" s="2">
@@ -8359,7 +8359,7 @@
     <row r="252" ht="40" customHeight="1">
       <c r="A252" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.fresh.shy.polite[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.fresh.polite.shy[1]</t>
         </is>
       </c>
       <c r="B252" t="inlineStr" s="2">
@@ -8374,7 +8374,7 @@
       </c>
       <c r="D252" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.fresh.shy.polite[1]</t>
+          <t xml:space="preserve">heatSelf.fresh.polite.shy[1]</t>
         </is>
       </c>
       <c r="E252" t="inlineStr" s="2">
@@ -8391,7 +8391,7 @@
     <row r="253" ht="40" customHeight="1">
       <c r="A253" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.heavy.shy.polite[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.heavy.polite.shy[1]</t>
         </is>
       </c>
       <c r="B253" t="inlineStr" s="2">
@@ -8406,7 +8406,7 @@
       </c>
       <c r="D253" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.heavy.shy.polite[1]</t>
+          <t xml:space="preserve">heatSelf.heavy.polite.shy[1]</t>
         </is>
       </c>
       <c r="E253" t="inlineStr" s="2">
@@ -8423,7 +8423,7 @@
     <row r="254" ht="40" customHeight="1">
       <c r="A254" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.warm.shy.polite[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.warm.polite.shy[1]</t>
         </is>
       </c>
       <c r="B254" t="inlineStr" s="2">
@@ -8438,7 +8438,7 @@
       </c>
       <c r="D254" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.warm.shy.polite[1]</t>
+          <t xml:space="preserve">heatSelf.warm.polite.shy[1]</t>
         </is>
       </c>
       <c r="E254" t="inlineStr" s="2">
@@ -8455,7 +8455,7 @@
     <row r="255" ht="40" customHeight="1">
       <c r="A255" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.shy.polite[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.polite.shy[1]</t>
         </is>
       </c>
       <c r="B255" t="inlineStr" s="2">
@@ -8470,7 +8470,7 @@
       </c>
       <c r="D255" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.shy.polite[1]</t>
+          <t xml:space="preserve">injury.polite.shy[1]</t>
         </is>
       </c>
       <c r="E255" t="inlineStr" s="2">
@@ -8487,7 +8487,7 @@
     <row r="256" ht="40" customHeight="1">
       <c r="A256" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.shy.polite[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.polite.shy[1]</t>
         </is>
       </c>
       <c r="B256" t="inlineStr" s="2">
@@ -8502,7 +8502,7 @@
       </c>
       <c r="D256" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.shy.polite[1]</t>
+          <t xml:space="preserve">release.polite.shy[1]</t>
         </is>
       </c>
       <c r="E256" t="inlineStr" s="2">
@@ -8519,7 +8519,7 @@
     <row r="257" ht="40" customHeight="1">
       <c r="A257" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.shy.polite[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.polite.shy[1]</t>
         </is>
       </c>
       <c r="B257" t="inlineStr" s="2">
@@ -8534,7 +8534,7 @@
       </c>
       <c r="D257" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreeting.shy.polite[1]</t>
+          <t xml:space="preserve">rentalGreeting.polite.shy[1]</t>
         </is>
       </c>
       <c r="E257" t="inlineStr" s="2">
@@ -8551,7 +8551,7 @@
     <row r="258" ht="40" customHeight="1">
       <c r="A258" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.shy.polite[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.polite.shy[1]</t>
         </is>
       </c>
       <c r="B258" t="inlineStr" s="2">
@@ -8566,7 +8566,7 @@
       </c>
       <c r="D258" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">scoutGreeting.shy.polite[1]</t>
+          <t xml:space="preserve">scoutGreeting.polite.shy[1]</t>
         </is>
       </c>
       <c r="E258" t="inlineStr" s="2">
@@ -8583,7 +8583,7 @@
     <row r="259" ht="40" customHeight="1">
       <c r="A259" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.shy.polite[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.polite.shy[1]</t>
         </is>
       </c>
       <c r="B259" t="inlineStr" s="2">
@@ -8598,7 +8598,7 @@
       </c>
       <c r="D259" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleChallengeLoss.shy.polite[1]</t>
+          <t xml:space="preserve">titleChallengeLoss.polite.shy[1]</t>
         </is>
       </c>
       <c r="E259" t="inlineStr" s="2">
@@ -8615,7 +8615,7 @@
     <row r="260" ht="40" customHeight="1">
       <c r="A260" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.shy.polite[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.polite.shy[1]</t>
         </is>
       </c>
       <c r="B260" t="inlineStr" s="2">
@@ -8630,7 +8630,7 @@
       </c>
       <c r="D260" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleDefense.shy.polite[1]</t>
+          <t xml:space="preserve">titleDefense.polite.shy[1]</t>
         </is>
       </c>
       <c r="E260" t="inlineStr" s="2">
@@ -8647,7 +8647,7 @@
     <row r="261" ht="40" customHeight="1">
       <c r="A261" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.shy.polite[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.polite.shy[1]</t>
         </is>
       </c>
       <c r="B261" t="inlineStr" s="2">
@@ -8662,7 +8662,7 @@
       </c>
       <c r="D261" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleLoss.shy.polite[1]</t>
+          <t xml:space="preserve">titleLoss.polite.shy[1]</t>
         </is>
       </c>
       <c r="E261" t="inlineStr" s="2">
@@ -8679,7 +8679,7 @@
     <row r="262" ht="40" customHeight="1">
       <c r="A262" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.shy.polite[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.polite.shy[1]</t>
         </is>
       </c>
       <c r="B262" t="inlineStr" s="2">
@@ -8694,7 +8694,7 @@
       </c>
       <c r="D262" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.shy.polite[1]</t>
+          <t xml:space="preserve">titleWin.polite.shy[1]</t>
         </is>
       </c>
       <c r="E262" t="inlineStr" s="2">
@@ -8711,7 +8711,7 @@
     <row r="263" ht="40" customHeight="1">
       <c r="A263" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.shy.polite[1]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.polite.shy[1]</t>
         </is>
       </c>
       <c r="B263" t="inlineStr" s="2">
@@ -8726,7 +8726,7 @@
       </c>
       <c r="D263" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">shy.polite[1]</t>
+          <t xml:space="preserve">polite.shy[1]</t>
         </is>
       </c>
       <c r="E263" t="inlineStr" s="2">
@@ -8743,7 +8743,7 @@
     <row r="264" ht="40" customHeight="1">
       <c r="A264" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.shy.polite[1]</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.polite.shy[1]</t>
         </is>
       </c>
       <c r="B264" t="inlineStr" s="2">
@@ -8758,7 +8758,7 @@
       </c>
       <c r="D264" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">shy.polite[1]</t>
+          <t xml:space="preserve">polite.shy[1]</t>
         </is>
       </c>
       <c r="E264" t="inlineStr" s="2">
@@ -8775,7 +8775,7 @@
     <row r="265" ht="40" customHeight="1">
       <c r="A265" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.shy.polite[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.polite.shy[1]</t>
         </is>
       </c>
       <c r="B265" t="inlineStr" s="2">
@@ -8790,7 +8790,7 @@
       </c>
       <c r="D265" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">shy.polite[1]</t>
+          <t xml:space="preserve">polite.shy[1]</t>
         </is>
       </c>
       <c r="E265" t="inlineStr" s="2">
@@ -8807,7 +8807,7 @@
     <row r="266" ht="40" customHeight="1">
       <c r="A266" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.shy.polite[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.polite.shy[1]</t>
         </is>
       </c>
       <c r="B266" t="inlineStr" s="2">
@@ -8822,7 +8822,7 @@
       </c>
       <c r="D266" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">shy.polite[1]</t>
+          <t xml:space="preserve">polite.shy[1]</t>
         </is>
       </c>
       <c r="E266" t="inlineStr" s="2">
@@ -8839,7 +8839,7 @@
     <row r="267" ht="40" customHeight="1">
       <c r="A267" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.shy.polite[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.polite.shy[1]</t>
         </is>
       </c>
       <c r="B267" t="inlineStr" s="2">
@@ -8854,7 +8854,7 @@
       </c>
       <c r="D267" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">shy.polite[1]</t>
+          <t xml:space="preserve">polite.shy[1]</t>
         </is>
       </c>
       <c r="E267" t="inlineStr" s="2">
@@ -8871,7 +8871,7 @@
     <row r="268" ht="40" customHeight="1">
       <c r="A268" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.shy.polite[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.polite.shy[1]</t>
         </is>
       </c>
       <c r="B268" t="inlineStr" s="2">
@@ -8886,7 +8886,7 @@
       </c>
       <c r="D268" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">shy.polite[1]</t>
+          <t xml:space="preserve">polite.shy[1]</t>
         </is>
       </c>
       <c r="E268" t="inlineStr" s="2">
@@ -9479,7 +9479,7 @@
     <row r="287" ht="40" customHeight="1">
       <c r="A287" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.goodLoss.shy.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.goodLoss.polite.shy[1]</t>
         </is>
       </c>
       <c r="B287" t="inlineStr" s="2">
@@ -9494,7 +9494,7 @@
       </c>
       <c r="D287" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.goodLoss.shy.polite[1]</t>
+          <t xml:space="preserve">GL-01.goodLoss.polite.shy[1]</t>
         </is>
       </c>
       <c r="E287" t="inlineStr" s="2">
@@ -9511,7 +9511,7 @@
     <row r="288" ht="40" customHeight="1">
       <c r="A288" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.goodLoss.shy.polite[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.goodLoss.polite.shy[2]</t>
         </is>
       </c>
       <c r="B288" t="inlineStr" s="2">
@@ -9526,7 +9526,7 @@
       </c>
       <c r="D288" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.goodLoss.shy.polite[2]</t>
+          <t xml:space="preserve">GL-01.goodLoss.polite.shy[2]</t>
         </is>
       </c>
       <c r="E288" t="inlineStr" s="2">
@@ -9543,7 +9543,7 @@
     <row r="289" ht="40" customHeight="1">
       <c r="A289" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin.shy.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin.polite.shy[1]</t>
         </is>
       </c>
       <c r="B289" t="inlineStr" s="2">
@@ -9558,7 +9558,7 @@
       </c>
       <c r="D289" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.greatWin.shy.polite[1]</t>
+          <t xml:space="preserve">GL-01.greatWin.polite.shy[1]</t>
         </is>
       </c>
       <c r="E289" t="inlineStr" s="2">
@@ -9575,7 +9575,7 @@
     <row r="290" ht="40" customHeight="1">
       <c r="A290" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin.shy.polite[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin.polite.shy[2]</t>
         </is>
       </c>
       <c r="B290" t="inlineStr" s="2">
@@ -9590,7 +9590,7 @@
       </c>
       <c r="D290" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.greatWin.shy.polite[2]</t>
+          <t xml:space="preserve">GL-01.greatWin.polite.shy[2]</t>
         </is>
       </c>
       <c r="E290" t="inlineStr" s="2">
@@ -9607,7 +9607,7 @@
     <row r="291" ht="40" customHeight="1">
       <c r="A291" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.shy.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.polite.shy[1]</t>
         </is>
       </c>
       <c r="B291" t="inlineStr" s="2">
@@ -9622,7 +9622,7 @@
       </c>
       <c r="D291" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.loss.shy.polite[1]</t>
+          <t xml:space="preserve">GL-01.loss.polite.shy[1]</t>
         </is>
       </c>
       <c r="E291" t="inlineStr" s="2">
@@ -9639,7 +9639,7 @@
     <row r="292" ht="40" customHeight="1">
       <c r="A292" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.shy.polite[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.polite.shy[2]</t>
         </is>
       </c>
       <c r="B292" t="inlineStr" s="2">
@@ -9654,7 +9654,7 @@
       </c>
       <c r="D292" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.loss.shy.polite[2]</t>
+          <t xml:space="preserve">GL-01.loss.polite.shy[2]</t>
         </is>
       </c>
       <c r="E292" t="inlineStr" s="2">
@@ -9671,7 +9671,7 @@
     <row r="293" ht="40" customHeight="1">
       <c r="A293" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.shy.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.polite.shy[1]</t>
         </is>
       </c>
       <c r="B293" t="inlineStr" s="2">
@@ -9686,7 +9686,7 @@
       </c>
       <c r="D293" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.win.shy.polite[1]</t>
+          <t xml:space="preserve">GL-01.win.polite.shy[1]</t>
         </is>
       </c>
       <c r="E293" t="inlineStr" s="2">
@@ -9703,7 +9703,7 @@
     <row r="294" ht="40" customHeight="1">
       <c r="A294" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.shy.polite[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.polite.shy[2]</t>
         </is>
       </c>
       <c r="B294" t="inlineStr" s="2">
@@ -9718,7 +9718,7 @@
       </c>
       <c r="D294" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.win.shy.polite[2]</t>
+          <t xml:space="preserve">GL-01.win.polite.shy[2]</t>
         </is>
       </c>
       <c r="E294" t="inlineStr" s="2">
@@ -9735,7 +9735,7 @@
     <row r="295" ht="40" customHeight="1">
       <c r="A295" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.shy.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.polite.shy[1]</t>
         </is>
       </c>
       <c r="B295" t="inlineStr" s="2">
@@ -9750,7 +9750,7 @@
       </c>
       <c r="D295" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-02.shy.polite[1]</t>
+          <t xml:space="preserve">GL-02.polite.shy[1]</t>
         </is>
       </c>
       <c r="E295" t="inlineStr" s="2">
@@ -9767,7 +9767,7 @@
     <row r="296" ht="40" customHeight="1">
       <c r="A296" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.shy.polite[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.polite.shy[2]</t>
         </is>
       </c>
       <c r="B296" t="inlineStr" s="2">
@@ -9782,7 +9782,7 @@
       </c>
       <c r="D296" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-02.shy.polite[2]</t>
+          <t xml:space="preserve">GL-02.polite.shy[2]</t>
         </is>
       </c>
       <c r="E296" t="inlineStr" s="2">
@@ -9799,7 +9799,7 @@
     <row r="297" ht="40" customHeight="1">
       <c r="A297" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.down.shy.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.down.polite.shy[1]</t>
         </is>
       </c>
       <c r="B297" t="inlineStr" s="2">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="D297" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-03.down.shy.polite[1]</t>
+          <t xml:space="preserve">GL-03.down.polite.shy[1]</t>
         </is>
       </c>
       <c r="E297" t="inlineStr" s="2">
@@ -9831,7 +9831,7 @@
     <row r="298" ht="40" customHeight="1">
       <c r="A298" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.up.shy.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.up.polite.shy[1]</t>
         </is>
       </c>
       <c r="B298" t="inlineStr" s="2">
@@ -9846,7 +9846,7 @@
       </c>
       <c r="D298" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-03.up.shy.polite[1]</t>
+          <t xml:space="preserve">GL-03.up.polite.shy[1]</t>
         </is>
       </c>
       <c r="E298" t="inlineStr" s="2">
@@ -9863,7 +9863,7 @@
     <row r="299" ht="40" customHeight="1">
       <c r="A299" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04.shy.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04.polite.shy[1]</t>
         </is>
       </c>
       <c r="B299" t="inlineStr" s="2">
@@ -9878,7 +9878,7 @@
       </c>
       <c r="D299" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-04.shy.polite[1]</t>
+          <t xml:space="preserve">GL-04.polite.shy[1]</t>
         </is>
       </c>
       <c r="E299" t="inlineStr" s="2">
@@ -9895,7 +9895,7 @@
     <row r="300" ht="40" customHeight="1">
       <c r="A300" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04.shy.polite[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04.polite.shy[2]</t>
         </is>
       </c>
       <c r="B300" t="inlineStr" s="2">
@@ -9910,7 +9910,7 @@
       </c>
       <c r="D300" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-04.shy.polite[2]</t>
+          <t xml:space="preserve">GL-04.polite.shy[2]</t>
         </is>
       </c>
       <c r="E300" t="inlineStr" s="2">
@@ -9927,7 +9927,7 @@
     <row r="301" ht="40" customHeight="1">
       <c r="A301" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05.shy.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05.polite.shy[1]</t>
         </is>
       </c>
       <c r="B301" t="inlineStr" s="2">
@@ -9942,7 +9942,7 @@
       </c>
       <c r="D301" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-05.shy.polite[1]</t>
+          <t xml:space="preserve">GL-05.polite.shy[1]</t>
         </is>
       </c>
       <c r="E301" t="inlineStr" s="2">
@@ -9959,7 +9959,7 @@
     <row r="302" ht="40" customHeight="1">
       <c r="A302" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05.shy.polite[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05.polite.shy[2]</t>
         </is>
       </c>
       <c r="B302" t="inlineStr" s="2">
@@ -9974,7 +9974,7 @@
       </c>
       <c r="D302" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-05.shy.polite[2]</t>
+          <t xml:space="preserve">GL-05.polite.shy[2]</t>
         </is>
       </c>
       <c r="E302" t="inlineStr" s="2">
@@ -9991,7 +9991,7 @@
     <row r="303" ht="40" customHeight="1">
       <c r="A303" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.shy.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.polite.shy[1]</t>
         </is>
       </c>
       <c r="B303" t="inlineStr" s="2">
@@ -10006,7 +10006,7 @@
       </c>
       <c r="D303" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-06.shy.polite[1]</t>
+          <t xml:space="preserve">GL-06.polite.shy[1]</t>
         </is>
       </c>
       <c r="E303" t="inlineStr" s="2">
@@ -10023,7 +10023,7 @@
     <row r="304" ht="40" customHeight="1">
       <c r="A304" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.shy.polite[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.polite.shy[2]</t>
         </is>
       </c>
       <c r="B304" t="inlineStr" s="2">
@@ -10038,7 +10038,7 @@
       </c>
       <c r="D304" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-06.shy.polite[2]</t>
+          <t xml:space="preserve">GL-06.polite.shy[2]</t>
         </is>
       </c>
       <c r="E304" t="inlineStr" s="2">
@@ -10055,7 +10055,7 @@
     <row r="305" ht="40" customHeight="1">
       <c r="A305" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07.shy.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07.polite.shy[1]</t>
         </is>
       </c>
       <c r="B305" t="inlineStr" s="2">
@@ -10070,7 +10070,7 @@
       </c>
       <c r="D305" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-07.shy.polite[1]</t>
+          <t xml:space="preserve">GL-07.polite.shy[1]</t>
         </is>
       </c>
       <c r="E305" t="inlineStr" s="2">
@@ -10087,7 +10087,7 @@
     <row r="306" ht="40" customHeight="1">
       <c r="A306" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07.shy.polite[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07.polite.shy[2]</t>
         </is>
       </c>
       <c r="B306" t="inlineStr" s="2">
@@ -10102,7 +10102,7 @@
       </c>
       <c r="D306" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-07.shy.polite[2]</t>
+          <t xml:space="preserve">GL-07.polite.shy[2]</t>
         </is>
       </c>
       <c r="E306" t="inlineStr" s="2">
@@ -10119,7 +10119,7 @@
     <row r="307" ht="40" customHeight="1">
       <c r="A307" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.shy.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.polite.shy[1]</t>
         </is>
       </c>
       <c r="B307" t="inlineStr" s="2">
@@ -10134,7 +10134,7 @@
       </c>
       <c r="D307" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-08.shy.polite[1]</t>
+          <t xml:space="preserve">GL-08.polite.shy[1]</t>
         </is>
       </c>
       <c r="E307" t="inlineStr" s="2">
@@ -10151,7 +10151,7 @@
     <row r="308" ht="40" customHeight="1">
       <c r="A308" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.shy.polite[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.polite.shy[2]</t>
         </is>
       </c>
       <c r="B308" t="inlineStr" s="2">
@@ -10166,7 +10166,7 @@
       </c>
       <c r="D308" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-08.shy.polite[2]</t>
+          <t xml:space="preserve">GL-08.polite.shy[2]</t>
         </is>
       </c>
       <c r="E308" t="inlineStr" s="2">
@@ -10183,7 +10183,7 @@
     <row r="309" ht="40" customHeight="1">
       <c r="A309" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.shy.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.polite.shy[1]</t>
         </is>
       </c>
       <c r="B309" t="inlineStr" s="2">
@@ -10198,7 +10198,7 @@
       </c>
       <c r="D309" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-09.shy.polite[1]</t>
+          <t xml:space="preserve">GL-09.polite.shy[1]</t>
         </is>
       </c>
       <c r="E309" t="inlineStr" s="2">
@@ -10215,7 +10215,7 @@
     <row r="310" ht="40" customHeight="1">
       <c r="A310" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.shy.polite[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.polite.shy[2]</t>
         </is>
       </c>
       <c r="B310" t="inlineStr" s="2">
@@ -10230,7 +10230,7 @@
       </c>
       <c r="D310" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-09.shy.polite[2]</t>
+          <t xml:space="preserve">GL-09.polite.shy[2]</t>
         </is>
       </c>
       <c r="E310" t="inlineStr" s="2">
@@ -10247,7 +10247,7 @@
     <row r="311" ht="40" customHeight="1">
       <c r="A311" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.shy.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.polite.shy[1]</t>
         </is>
       </c>
       <c r="B311" t="inlineStr" s="2">
@@ -10262,7 +10262,7 @@
       </c>
       <c r="D311" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-10.shy.polite[1]</t>
+          <t xml:space="preserve">GL-10.polite.shy[1]</t>
         </is>
       </c>
       <c r="E311" t="inlineStr" s="2">
@@ -10279,7 +10279,7 @@
     <row r="312" ht="40" customHeight="1">
       <c r="A312" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.shy.polite[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.polite.shy[2]</t>
         </is>
       </c>
       <c r="B312" t="inlineStr" s="2">
@@ -10294,7 +10294,7 @@
       </c>
       <c r="D312" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-10.shy.polite[2]</t>
+          <t xml:space="preserve">GL-10.polite.shy[2]</t>
         </is>
       </c>
       <c r="E312" t="inlineStr" s="2">
@@ -10311,7 +10311,7 @@
     <row r="313" ht="40" customHeight="1">
       <c r="A313" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.shy.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.polite.shy[1]</t>
         </is>
       </c>
       <c r="B313" t="inlineStr" s="2">
@@ -10326,7 +10326,7 @@
       </c>
       <c r="D313" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">shy.polite[1]</t>
+          <t xml:space="preserve">polite.shy[1]</t>
         </is>
       </c>
       <c r="E313" t="inlineStr" s="2">
@@ -10343,7 +10343,7 @@
     <row r="314" ht="40" customHeight="1">
       <c r="A314" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.shy.polite[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.polite.shy[1]</t>
         </is>
       </c>
       <c r="B314" t="inlineStr" s="2">
@@ -10358,7 +10358,7 @@
       </c>
       <c r="D314" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.shy.polite[1]</t>
+          <t xml:space="preserve">preFinal.polite.shy[1]</t>
         </is>
       </c>
       <c r="E314" t="inlineStr" s="2">
@@ -10375,7 +10375,7 @@
     <row r="315" ht="40" customHeight="1">
       <c r="A315" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.shy.polite[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.polite.shy[2]</t>
         </is>
       </c>
       <c r="B315" t="inlineStr" s="2">
@@ -10390,7 +10390,7 @@
       </c>
       <c r="D315" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.shy.polite[2]</t>
+          <t xml:space="preserve">preFinal.polite.shy[2]</t>
         </is>
       </c>
       <c r="E315" t="inlineStr" s="2">
@@ -10407,7 +10407,7 @@
     <row r="316" ht="40" customHeight="1">
       <c r="A316" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.shy.polite[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.polite.shy[1]</t>
         </is>
       </c>
       <c r="B316" t="inlineStr" s="2">
@@ -10422,7 +10422,7 @@
       </c>
       <c r="D316" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.shy.polite[1]</t>
+          <t xml:space="preserve">preMatch.polite.shy[1]</t>
         </is>
       </c>
       <c r="E316" t="inlineStr" s="2">
@@ -10439,7 +10439,7 @@
     <row r="317" ht="40" customHeight="1">
       <c r="A317" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.shy.polite[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.polite.shy[2]</t>
         </is>
       </c>
       <c r="B317" t="inlineStr" s="2">
@@ -10454,7 +10454,7 @@
       </c>
       <c r="D317" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.shy.polite[2]</t>
+          <t xml:space="preserve">preMatch.polite.shy[2]</t>
         </is>
       </c>
       <c r="E317" t="inlineStr" s="2">
@@ -10471,7 +10471,7 @@
     <row r="318" ht="40" customHeight="1">
       <c r="A318" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.shy.polite[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.polite.shy[1]</t>
         </is>
       </c>
       <c r="B318" t="inlineStr" s="2">
@@ -10486,7 +10486,7 @@
       </c>
       <c r="D318" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.shy.polite[1]</t>
+          <t xml:space="preserve">survivor.polite.shy[1]</t>
         </is>
       </c>
       <c r="E318" t="inlineStr" s="2">
@@ -10503,7 +10503,7 @@
     <row r="319" ht="40" customHeight="1">
       <c r="A319" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.shy.polite[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.polite.shy[2]</t>
         </is>
       </c>
       <c r="B319" t="inlineStr" s="2">
@@ -10518,7 +10518,7 @@
       </c>
       <c r="D319" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.shy.polite[2]</t>
+          <t xml:space="preserve">survivor.polite.shy[2]</t>
         </is>
       </c>
       <c r="E319" t="inlineStr" s="2">
@@ -10535,7 +10535,7 @@
     <row r="320" ht="40" customHeight="1">
       <c r="A320" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.shy.polite[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.polite.shy[1]</t>
         </is>
       </c>
       <c r="B320" t="inlineStr" s="2">
@@ -10550,7 +10550,7 @@
       </c>
       <c r="D320" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.shy.polite[1]</t>
+          <t xml:space="preserve">champion.polite.shy[1]</t>
         </is>
       </c>
       <c r="E320" t="inlineStr" s="2">
@@ -10567,7 +10567,7 @@
     <row r="321" ht="40" customHeight="1">
       <c r="A321" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.shy.polite[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.polite.shy[2]</t>
         </is>
       </c>
       <c r="B321" t="inlineStr" s="2">
@@ -10582,7 +10582,7 @@
       </c>
       <c r="D321" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.shy.polite[2]</t>
+          <t xml:space="preserve">champion.polite.shy[2]</t>
         </is>
       </c>
       <c r="E321" t="inlineStr" s="2">
@@ -10599,7 +10599,7 @@
     <row r="322" ht="40" customHeight="1">
       <c r="A322" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.shy.polite[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.polite.shy[1]</t>
         </is>
       </c>
       <c r="B322" t="inlineStr" s="2">
@@ -10614,7 +10614,7 @@
       </c>
       <c r="D322" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.shy.polite[1]</t>
+          <t xml:space="preserve">defiant.polite.shy[1]</t>
         </is>
       </c>
       <c r="E322" t="inlineStr" s="2">
@@ -10631,7 +10631,7 @@
     <row r="323" ht="40" customHeight="1">
       <c r="A323" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.shy.polite[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.polite.shy[2]</t>
         </is>
       </c>
       <c r="B323" t="inlineStr" s="2">
@@ -10646,7 +10646,7 @@
       </c>
       <c r="D323" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.shy.polite[2]</t>
+          <t xml:space="preserve">defiant.polite.shy[2]</t>
         </is>
       </c>
       <c r="E323" t="inlineStr" s="2">
@@ -10663,7 +10663,7 @@
     <row r="324" ht="40" customHeight="1">
       <c r="A324" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.shy.polite[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.polite.shy[1]</t>
         </is>
       </c>
       <c r="B324" t="inlineStr" s="2">
@@ -10678,7 +10678,7 @@
       </c>
       <c r="D324" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.shy.polite[1]</t>
+          <t xml:space="preserve">gauntlet.polite.shy[1]</t>
         </is>
       </c>
       <c r="E324" t="inlineStr" s="2">
@@ -10695,7 +10695,7 @@
     <row r="325" ht="40" customHeight="1">
       <c r="A325" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.shy.polite[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.polite.shy[2]</t>
         </is>
       </c>
       <c r="B325" t="inlineStr" s="2">
@@ -10710,7 +10710,7 @@
       </c>
       <c r="D325" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.shy.polite[2]</t>
+          <t xml:space="preserve">gauntlet.polite.shy[2]</t>
         </is>
       </c>
       <c r="E325" t="inlineStr" s="2">
@@ -10727,7 +10727,7 @@
     <row r="326" ht="40" customHeight="1">
       <c r="A326" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.shy.polite[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.polite.shy[1]</t>
         </is>
       </c>
       <c r="B326" t="inlineStr" s="2">
@@ -10742,7 +10742,7 @@
       </c>
       <c r="D326" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.shy.polite[1]</t>
+          <t xml:space="preserve">champion.polite.shy[1]</t>
         </is>
       </c>
       <c r="E326" t="inlineStr" s="2">
@@ -10759,7 +10759,7 @@
     <row r="327" ht="40" customHeight="1">
       <c r="A327" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.shy.polite[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.polite.shy[2]</t>
         </is>
       </c>
       <c r="B327" t="inlineStr" s="2">
@@ -10774,7 +10774,7 @@
       </c>
       <c r="D327" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.shy.polite[2]</t>
+          <t xml:space="preserve">champion.polite.shy[2]</t>
         </is>
       </c>
       <c r="E327" t="inlineStr" s="2">
@@ -10791,7 +10791,7 @@
     <row r="328" ht="40" customHeight="1">
       <c r="A328" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.shy.polite[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.polite.shy[1]</t>
         </is>
       </c>
       <c r="B328" t="inlineStr" s="2">
@@ -10806,7 +10806,7 @@
       </c>
       <c r="D328" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.shy.polite[1]</t>
+          <t xml:space="preserve">postLose.polite.shy[1]</t>
         </is>
       </c>
       <c r="E328" t="inlineStr" s="2">
@@ -10823,7 +10823,7 @@
     <row r="329" ht="40" customHeight="1">
       <c r="A329" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.shy.polite[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.polite.shy[2]</t>
         </is>
       </c>
       <c r="B329" t="inlineStr" s="2">
@@ -10838,7 +10838,7 @@
       </c>
       <c r="D329" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.shy.polite[2]</t>
+          <t xml:space="preserve">postLose.polite.shy[2]</t>
         </is>
       </c>
       <c r="E329" t="inlineStr" s="2">
@@ -10855,7 +10855,7 @@
     <row r="330" ht="40" customHeight="1">
       <c r="A330" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.shy.polite[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.polite.shy[1]</t>
         </is>
       </c>
       <c r="B330" t="inlineStr" s="2">
@@ -10870,7 +10870,7 @@
       </c>
       <c r="D330" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.shy.polite[1]</t>
+          <t xml:space="preserve">postMatchWin.polite.shy[1]</t>
         </is>
       </c>
       <c r="E330" t="inlineStr" s="2">
@@ -10887,7 +10887,7 @@
     <row r="331" ht="40" customHeight="1">
       <c r="A331" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.shy.polite[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.polite.shy[2]</t>
         </is>
       </c>
       <c r="B331" t="inlineStr" s="2">
@@ -10902,7 +10902,7 @@
       </c>
       <c r="D331" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.shy.polite[2]</t>
+          <t xml:space="preserve">postMatchWin.polite.shy[2]</t>
         </is>
       </c>
       <c r="E331" t="inlineStr" s="2">
@@ -10919,7 +10919,7 @@
     <row r="332" ht="40" customHeight="1">
       <c r="A332" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.shy.polite[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.polite.shy[1]</t>
         </is>
       </c>
       <c r="B332" t="inlineStr" s="2">
@@ -10934,7 +10934,7 @@
       </c>
       <c r="D332" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.shy.polite[1]</t>
+          <t xml:space="preserve">postWin.polite.shy[1]</t>
         </is>
       </c>
       <c r="E332" t="inlineStr" s="2">
@@ -10951,7 +10951,7 @@
     <row r="333" ht="40" customHeight="1">
       <c r="A333" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.shy.polite[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.polite.shy[2]</t>
         </is>
       </c>
       <c r="B333" t="inlineStr" s="2">
@@ -10966,7 +10966,7 @@
       </c>
       <c r="D333" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.shy.polite[2]</t>
+          <t xml:space="preserve">postWin.polite.shy[2]</t>
         </is>
       </c>
       <c r="E333" t="inlineStr" s="2">
@@ -10983,7 +10983,7 @@
     <row r="334" ht="40" customHeight="1">
       <c r="A334" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.shy.polite[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.polite.shy[1]</t>
         </is>
       </c>
       <c r="B334" t="inlineStr" s="2">
@@ -10998,7 +10998,7 @@
       </c>
       <c r="D334" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.shy.polite[1]</t>
+          <t xml:space="preserve">preFinal.polite.shy[1]</t>
         </is>
       </c>
       <c r="E334" t="inlineStr" s="2">
@@ -11015,7 +11015,7 @@
     <row r="335" ht="40" customHeight="1">
       <c r="A335" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.shy.polite[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.polite.shy[2]</t>
         </is>
       </c>
       <c r="B335" t="inlineStr" s="2">
@@ -11030,7 +11030,7 @@
       </c>
       <c r="D335" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.shy.polite[2]</t>
+          <t xml:space="preserve">preFinal.polite.shy[2]</t>
         </is>
       </c>
       <c r="E335" t="inlineStr" s="2">
@@ -11047,7 +11047,7 @@
     <row r="336" ht="40" customHeight="1">
       <c r="A336" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.shy.polite[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.polite.shy[1]</t>
         </is>
       </c>
       <c r="B336" t="inlineStr" s="2">
@@ -11062,7 +11062,7 @@
       </c>
       <c r="D336" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.shy.polite[1]</t>
+          <t xml:space="preserve">preMatch.polite.shy[1]</t>
         </is>
       </c>
       <c r="E336" t="inlineStr" s="2">
@@ -11079,7 +11079,7 @@
     <row r="337" ht="40" customHeight="1">
       <c r="A337" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.shy.polite[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.polite.shy[2]</t>
         </is>
       </c>
       <c r="B337" t="inlineStr" s="2">
@@ -11094,7 +11094,7 @@
       </c>
       <c r="D337" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.shy.polite[2]</t>
+          <t xml:space="preserve">preMatch.polite.shy[2]</t>
         </is>
       </c>
       <c r="E337" t="inlineStr" s="2">
@@ -11111,7 +11111,7 @@
     <row r="338" ht="40" customHeight="1">
       <c r="A338" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.shy.polite[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.polite.shy[1]</t>
         </is>
       </c>
       <c r="B338" t="inlineStr" s="2">
@@ -11126,7 +11126,7 @@
       </c>
       <c r="D338" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.shy.polite[1]</t>
+          <t xml:space="preserve">summon.polite.shy[1]</t>
         </is>
       </c>
       <c r="E338" t="inlineStr" s="2">
@@ -11143,7 +11143,7 @@
     <row r="339" ht="40" customHeight="1">
       <c r="A339" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.shy.polite[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.polite.shy[2]</t>
         </is>
       </c>
       <c r="B339" t="inlineStr" s="2">
@@ -11158,7 +11158,7 @@
       </c>
       <c r="D339" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.shy.polite[2]</t>
+          <t xml:space="preserve">summon.polite.shy[2]</t>
         </is>
       </c>
       <c r="E339" t="inlineStr" s="2">
@@ -11175,7 +11175,7 @@
     <row r="340" ht="40" customHeight="1">
       <c r="A340" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.shy.polite[1]</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.polite.shy[1]</t>
         </is>
       </c>
       <c r="B340" t="inlineStr" s="2">
@@ -11190,7 +11190,7 @@
       </c>
       <c r="D340" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">shy.polite[1]</t>
+          <t xml:space="preserve">polite.shy[1]</t>
         </is>
       </c>
       <c r="E340" t="inlineStr" s="2">
@@ -11207,7 +11207,7 @@
     <row r="341" ht="40" customHeight="1">
       <c r="A341" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.shy.polite[1]</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.polite.shy[1]</t>
         </is>
       </c>
       <c r="B341" t="inlineStr" s="2">
@@ -11222,7 +11222,7 @@
       </c>
       <c r="D341" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">shy.polite[1]</t>
+          <t xml:space="preserve">polite.shy[1]</t>
         </is>
       </c>
       <c r="E341" t="inlineStr" s="2">
@@ -11239,7 +11239,7 @@
     <row r="342" ht="40" customHeight="1">
       <c r="A342" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.shy.polite[1]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.polite.shy[1]</t>
         </is>
       </c>
       <c r="B342" t="inlineStr" s="2">
@@ -11254,7 +11254,7 @@
       </c>
       <c r="D342" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">shy.polite[1]</t>
+          <t xml:space="preserve">polite.shy[1]</t>
         </is>
       </c>
       <c r="E342" t="inlineStr" s="2">
@@ -11271,7 +11271,7 @@
     <row r="343" ht="40" customHeight="1">
       <c r="A343" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.shy.polite[2]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.polite.shy[2]</t>
         </is>
       </c>
       <c r="B343" t="inlineStr" s="2">
@@ -11286,7 +11286,7 @@
       </c>
       <c r="D343" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">shy.polite[2]</t>
+          <t xml:space="preserve">polite.shy[2]</t>
         </is>
       </c>
       <c r="E343" t="inlineStr" s="2">
@@ -11303,7 +11303,7 @@
     <row r="344" ht="40" customHeight="1">
       <c r="A344" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.shy.polite[1]</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.polite.shy[1]</t>
         </is>
       </c>
       <c r="B344" t="inlineStr" s="2">
@@ -11318,7 +11318,7 @@
       </c>
       <c r="D344" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">shy.polite[1]</t>
+          <t xml:space="preserve">polite.shy[1]</t>
         </is>
       </c>
       <c r="E344" t="inlineStr" s="2">
@@ -11335,7 +11335,7 @@
     <row r="345" ht="40" customHeight="1">
       <c r="A345" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.shy.polite[2]</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.polite.shy[2]</t>
         </is>
       </c>
       <c r="B345" t="inlineStr" s="2">
@@ -11350,7 +11350,7 @@
       </c>
       <c r="D345" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">shy.polite[2]</t>
+          <t xml:space="preserve">polite.shy[2]</t>
         </is>
       </c>
       <c r="E345" t="inlineStr" s="2">
@@ -11367,7 +11367,7 @@
     <row r="346" ht="40" customHeight="1">
       <c r="A346" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.shy.polite[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.polite.shy[1]</t>
         </is>
       </c>
       <c r="B346" t="inlineStr" s="2">
@@ -11382,7 +11382,7 @@
       </c>
       <c r="D346" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.shy.polite[1]</t>
+          <t xml:space="preserve">result_lose.polite.shy[1]</t>
         </is>
       </c>
       <c r="E346" t="inlineStr" s="2">
@@ -11399,7 +11399,7 @@
     <row r="347" ht="40" customHeight="1">
       <c r="A347" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.shy.polite[2]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.polite.shy[2]</t>
         </is>
       </c>
       <c r="B347" t="inlineStr" s="2">
@@ -11414,7 +11414,7 @@
       </c>
       <c r="D347" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.shy.polite[2]</t>
+          <t xml:space="preserve">result_lose.polite.shy[2]</t>
         </is>
       </c>
       <c r="E347" t="inlineStr" s="2">
@@ -11431,7 +11431,7 @@
     <row r="348" ht="40" customHeight="1">
       <c r="A348" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.shy.polite[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.polite.shy[1]</t>
         </is>
       </c>
       <c r="B348" t="inlineStr" s="2">
@@ -11446,7 +11446,7 @@
       </c>
       <c r="D348" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.shy.polite[1]</t>
+          <t xml:space="preserve">result_win.polite.shy[1]</t>
         </is>
       </c>
       <c r="E348" t="inlineStr" s="2">
@@ -11463,7 +11463,7 @@
     <row r="349" ht="40" customHeight="1">
       <c r="A349" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.shy.polite[2]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.polite.shy[2]</t>
         </is>
       </c>
       <c r="B349" t="inlineStr" s="2">
@@ -11478,7 +11478,7 @@
       </c>
       <c r="D349" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.shy.polite[2]</t>
+          <t xml:space="preserve">result_win.polite.shy[2]</t>
         </is>
       </c>
       <c r="E349" t="inlineStr" s="2">
@@ -11495,7 +11495,7 @@
     <row r="350" ht="40" customHeight="1">
       <c r="A350" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.shy.polite[1]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.polite.shy[1]</t>
         </is>
       </c>
       <c r="B350" t="inlineStr" s="2">
@@ -11510,7 +11510,7 @@
       </c>
       <c r="D350" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">shy.polite[1]</t>
+          <t xml:space="preserve">polite.shy[1]</t>
         </is>
       </c>
       <c r="E350" t="inlineStr" s="2">
@@ -11527,7 +11527,7 @@
     <row r="351" ht="40" customHeight="1">
       <c r="A351" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.shy.polite[2]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.polite.shy[2]</t>
         </is>
       </c>
       <c r="B351" t="inlineStr" s="2">
@@ -11542,7 +11542,7 @@
       </c>
       <c r="D351" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">shy.polite[2]</t>
+          <t xml:space="preserve">polite.shy[2]</t>
         </is>
       </c>
       <c r="E351" t="inlineStr" s="2">
@@ -11559,7 +11559,7 @@
     <row r="352" ht="40" customHeight="1">
       <c r="A352" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.shy.polite[3]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.polite.shy[3]</t>
         </is>
       </c>
       <c r="B352" t="inlineStr" s="2">
@@ -11574,7 +11574,7 @@
       </c>
       <c r="D352" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">shy.polite[3]</t>
+          <t xml:space="preserve">polite.shy[3]</t>
         </is>
       </c>
       <c r="E352" t="inlineStr" s="2">
@@ -11591,7 +11591,7 @@
     <row r="353" ht="40" customHeight="1">
       <c r="A353" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.shy.polite[1]</t>
+          <t xml:space="preserve">ENDING_LINES.fighter.polite.shy[1]</t>
         </is>
       </c>
       <c r="B353" t="inlineStr" s="2">
@@ -11606,7 +11606,7 @@
       </c>
       <c r="D353" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.shy.polite[1]</t>
+          <t xml:space="preserve">fighter.polite.shy[1]</t>
         </is>
       </c>
       <c r="E353" t="inlineStr" s="2">
@@ -11623,7 +11623,7 @@
     <row r="354" ht="40" customHeight="1">
       <c r="A354" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.shy.polite[1]</t>
+          <t xml:space="preserve">FA_GREETING_LINES.polite.shy[1]</t>
         </is>
       </c>
       <c r="B354" t="inlineStr" s="2">
@@ -11638,7 +11638,7 @@
       </c>
       <c r="D354" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">shy.polite[1]</t>
+          <t xml:space="preserve">polite.shy[1]</t>
         </is>
       </c>
       <c r="E354" t="inlineStr" s="2">
@@ -11655,7 +11655,7 @@
     <row r="355" ht="40" customHeight="1">
       <c r="A355" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_GREETING_LINES.shy.polite[1]</t>
+          <t xml:space="preserve">SCOUT_GREETING_LINES.polite.shy[1]</t>
         </is>
       </c>
       <c r="B355" t="inlineStr" s="2">
@@ -11670,7 +11670,7 @@
       </c>
       <c r="D355" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">shy.polite[1]</t>
+          <t xml:space="preserve">polite.shy[1]</t>
         </is>
       </c>
       <c r="E355" t="inlineStr" s="2">

--- a/セリフ編集/キャラタイプ別/丁寧×内気.xlsx
+++ b/セリフ編集/キャラタイプ別/丁寧×内気.xlsx
@@ -193,7 +193,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -205,7 +205,7 @@
     <row r="1">
       <c r="A1" t="inlineStr" s="11">
         <is>
-          <t xml:space="preserve">このタイプ(丁寧×内気)に該当するキャラクター: 3名</t>
+          <t xml:space="preserve">このタイプ(丁寧×内気)に該当するキャラクター: 4名</t>
         </is>
       </c>
     </row>
@@ -290,6 +290,28 @@
       <c r="D6" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">ファンサービス、ムードメーカー</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">松岡綾乃</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Submission</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Neutral</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">引き出し上手</t>
         </is>
       </c>
     </row>
@@ -301,7 +323,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H355"/>
+  <dimension ref="A1:H357"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -384,7 +406,7 @@
       </c>
       <c r="F2" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">す、すみません…いきますっ…!</t>
+          <t xml:space="preserve">す、すみません…いきますっ…！</t>
         </is>
       </c>
     </row>
@@ -416,7 +438,7 @@
       </c>
       <c r="F3" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、あの…まだまだです…!</t>
+          <t xml:space="preserve">あ、あの…まだまだです…！</t>
         </is>
       </c>
     </row>
@@ -448,7 +470,7 @@
       </c>
       <c r="F4" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ま、負けたくないんです…!</t>
+          <t xml:space="preserve">ま、負けたくないんです…！</t>
         </is>
       </c>
     </row>
@@ -480,7 +502,7 @@
       </c>
       <c r="F5" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こ、ここから…ですっ…!</t>
+          <t xml:space="preserve">こ、ここから…ですっ…！</t>
         </is>
       </c>
     </row>
@@ -608,7 +630,7 @@
       </c>
       <c r="F9" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（…ま、まだ…いけます…!）</t>
+          <t xml:space="preserve">（…ま、まだ…いけます…！）</t>
         </is>
       </c>
     </row>
@@ -640,7 +662,7 @@
       </c>
       <c r="F10" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（こ、ここで…決めないと…!）</t>
+          <t xml:space="preserve">（こ、ここで…決めないと…！）</t>
         </is>
       </c>
     </row>
@@ -928,7 +950,7 @@
       </c>
       <c r="F19" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、あの…わたしのために争ってくださったんですか…?絶対に恩返しします…!</t>
+          <t xml:space="preserve">あ、あの…わたしのために争ってくださったんですか…？絶対に恩返しします…！</t>
         </is>
       </c>
     </row>
@@ -960,7 +982,7 @@
       </c>
       <c r="F20" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、あの…よろしくお願いいたします…頑張ります…!</t>
+          <t xml:space="preserve">あ、あの…よろしくお願いいたします…頑張ります…！</t>
         </is>
       </c>
     </row>
@@ -1088,7 +1110,7 @@
       </c>
       <c r="F24" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……勝てちゃいました……。私を切ったところに……信じられません……。</t>
+          <t xml:space="preserve">……勝てちゃいました……。わたしを切ったところに……信じられません……。</t>
         </is>
       </c>
     </row>
@@ -1120,7 +1142,7 @@
       </c>
       <c r="F25" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ちゃんと、戦えていましたか……? あそこの方に……。</t>
+          <t xml:space="preserve">……ちゃんと、戦えていましたか……？ あそこの方に……。</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1558,7 @@
       </c>
       <c r="F38" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{partner}さん…ご、ごめんなさい…私のせいで…</t>
+          <t xml:space="preserve">{partner}さん…ご、ごめんなさい…わたしのせいで…</t>
         </is>
       </c>
     </row>
@@ -1632,7 +1654,7 @@
       </c>
       <c r="F41" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わ、私…頑張れました…{partner}さんのおかげです…！</t>
+          <t xml:space="preserve">わ、わたし…頑張れました…{partner}さんのおかげです…！</t>
         </is>
       </c>
     </row>
@@ -3104,7 +3126,7 @@
       </c>
       <c r="F87" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ほ、本当に…いいんですか…？ ありがとうございます…!</t>
+          <t xml:space="preserve">ほ、本当に…いいんですか…？ ありがとうございます…！</t>
         </is>
       </c>
     </row>
@@ -4384,7 +4406,7 @@
       </c>
       <c r="F127" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…社長、あの…私たちのメンバーのこと、気にかけていただけると…嬉しいです。</t>
+          <t xml:space="preserve">…社長、あの…わたしたちのメンバーのこと、気にかけていただけると…嬉しいです。</t>
         </is>
       </c>
     </row>
@@ -4416,7 +4438,7 @@
       </c>
       <c r="F128" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…社長、あの…次のメイン、私たちに…お任せいただけたら、嬉しいです。</t>
+          <t xml:space="preserve">…社長、あの…次のメイン、わたしたちに…お任せいただけたら、嬉しいです。</t>
         </is>
       </c>
     </row>
@@ -4480,7 +4502,7 @@
       </c>
       <c r="F130" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…社長、あの…私たちのこと、見ていてくださると…うれしいです。</t>
+          <t xml:space="preserve">…社長、あの…わたしたちのこと、見ていてくださると…うれしいです。</t>
         </is>
       </c>
     </row>
@@ -5696,7 +5718,7 @@
       </c>
       <c r="F168" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、あの…今日は体が軽くて…もっと、やれます…!</t>
+          <t xml:space="preserve">あ、あの…今日は体が軽くて…もっと、やれます…！</t>
         </is>
       </c>
     </row>
@@ -5991,7 +6013,7 @@
     <row r="178" ht="40" customHeight="1">
       <c r="A178" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.bestMatch.polite.shy[1]</t>
+          <t xml:space="preserve">AWARD_LINES.autumnWarChampion.polite.shy[1]</t>
         </is>
       </c>
       <c r="B178" t="inlineStr" s="2">
@@ -6006,7 +6028,7 @@
       </c>
       <c r="D178" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bestMatch.polite.shy[1]</t>
+          <t xml:space="preserve">autumnWarChampion.polite.shy[1]</t>
         </is>
       </c>
       <c r="E178" t="inlineStr" s="2">
@@ -6016,14 +6038,14 @@
       </c>
       <c r="F178" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、あの…ベストバウトに選んでいただけるなんて…相手の方のおかげです…</t>
+          <t xml:space="preserve">仲間の声があったから、最後まで頑張れました。</t>
         </is>
       </c>
     </row>
     <row r="179" ht="40" customHeight="1">
       <c r="A179" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.champion.polite.shy[1]</t>
+          <t xml:space="preserve">AWARD_LINES.bestMatch.polite.shy[1]</t>
         </is>
       </c>
       <c r="B179" t="inlineStr" s="2">
@@ -6038,7 +6060,7 @@
       </c>
       <c r="D179" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.polite.shy[1]</t>
+          <t xml:space="preserve">bestMatch.polite.shy[1]</t>
         </is>
       </c>
       <c r="E179" t="inlineStr" s="2">
@@ -6048,14 +6070,14 @@
       </c>
       <c r="F179" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わ、わたしが…チャンピオンに…？ こ、このベルトを汚さないように頑張ります…</t>
+          <t xml:space="preserve">あ、あの…ベストバウトに選んでいただけるなんて…相手の方のおかげです…</t>
         </is>
       </c>
     </row>
     <row r="180" ht="40" customHeight="1">
       <c r="A180" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.hallOfFame.polite.shy[1]</t>
+          <t xml:space="preserve">AWARD_LINES.champion.polite.shy[1]</t>
         </is>
       </c>
       <c r="B180" t="inlineStr" s="2">
@@ -6070,7 +6092,7 @@
       </c>
       <c r="D180" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hallOfFame.polite.shy[1]</t>
+          <t xml:space="preserve">champion.polite.shy[1]</t>
         </is>
       </c>
       <c r="E180" t="inlineStr" s="2">
@@ -6080,14 +6102,14 @@
       </c>
       <c r="F180" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">で、殿堂入り…ですか…？ わたしなんかが…本当に、いいんでしょうか…</t>
+          <t xml:space="preserve">わ、わたしが…チャンピオンに…？ こ、このベルトを汚さないように頑張ります…</t>
         </is>
       </c>
     </row>
     <row r="181" ht="40" customHeight="1">
       <c r="A181" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mediaAward.polite.shy[1]</t>
+          <t xml:space="preserve">AWARD_LINES.hallOfFame.polite.shy[1]</t>
         </is>
       </c>
       <c r="B181" t="inlineStr" s="2">
@@ -6102,7 +6124,7 @@
       </c>
       <c r="D181" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mediaAward.polite.shy[1]</t>
+          <t xml:space="preserve">hallOfFame.polite.shy[1]</t>
         </is>
       </c>
       <c r="E181" t="inlineStr" s="2">
@@ -6112,14 +6134,14 @@
       </c>
       <c r="F181" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">メディアの方々に…評価していただけて…あ、あの、本当に光栄です…</t>
+          <t xml:space="preserve">で、殿堂入り…ですか…？ わたしなんかが…本当に、いいんでしょうか…</t>
         </is>
       </c>
     </row>
     <row r="182" ht="40" customHeight="1">
       <c r="A182" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mvp.polite.shy[1]</t>
+          <t xml:space="preserve">AWARD_LINES.mediaAward.polite.shy[1]</t>
         </is>
       </c>
       <c r="B182" t="inlineStr" s="2">
@@ -6134,7 +6156,7 @@
       </c>
       <c r="D182" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mvp.polite.shy[1]</t>
+          <t xml:space="preserve">mediaAward.polite.shy[1]</t>
         </is>
       </c>
       <c r="E182" t="inlineStr" s="2">
@@ -6144,14 +6166,14 @@
       </c>
       <c r="F182" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">M、MVP…ですか…？ そ、そんな大それた賞、わたしには…</t>
+          <t xml:space="preserve">メディアの方々に…評価していただけて…あ、あの、本当に光栄です…</t>
         </is>
       </c>
     </row>
     <row r="183" ht="40" customHeight="1">
       <c r="A183" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.rookie.polite.shy[1]</t>
+          <t xml:space="preserve">AWARD_LINES.mvp.polite.shy[1]</t>
         </is>
       </c>
       <c r="B183" t="inlineStr" s="2">
@@ -6166,7 +6188,7 @@
       </c>
       <c r="D183" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rookie.polite.shy[1]</t>
+          <t xml:space="preserve">mvp.polite.shy[1]</t>
         </is>
       </c>
       <c r="E183" t="inlineStr" s="2">
@@ -6176,14 +6198,14 @@
       </c>
       <c r="F183" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">え…わたし、ですか…？ …ありがとうございます…</t>
+          <t xml:space="preserve">M、MVP…ですか…？ そ、そんな大それた賞、わたしには…</t>
         </is>
       </c>
     </row>
     <row r="184" ht="40" customHeight="1">
       <c r="A184" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.polite.shy[1]</t>
+          <t xml:space="preserve">AWARD_LINES.rookie.polite.shy[1]</t>
         </is>
       </c>
       <c r="B184" t="inlineStr" s="2">
@@ -6193,12 +6215,12 @@
       </c>
       <c r="C184" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D184" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.shy[1]</t>
+          <t xml:space="preserve">rookie.polite.shy[1]</t>
         </is>
       </c>
       <c r="E184" t="inlineStr" s="2">
@@ -6208,14 +6230,14 @@
       </c>
       <c r="F184" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの…ありがとうございます、ここまで連れてきてくださって</t>
+          <t xml:space="preserve">え…わたし、ですか…？ …ありがとうございます…</t>
         </is>
       </c>
     </row>
     <row r="185" ht="40" customHeight="1">
       <c r="A185" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.polite.shy[2]</t>
+          <t xml:space="preserve">AWARD_LINES.springTagChampion.polite.shy[1]</t>
         </is>
       </c>
       <c r="B185" t="inlineStr" s="2">
@@ -6225,12 +6247,12 @@
       </c>
       <c r="C185" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D185" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.shy[2]</t>
+          <t xml:space="preserve">springTagChampion.polite.shy[1]</t>
         </is>
       </c>
       <c r="E185" t="inlineStr" s="2">
@@ -6240,14 +6262,14 @@
       </c>
       <c r="F185" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…精一杯、やります</t>
+          <t xml:space="preserve">相棒が隣にいてくれたので、落ち着いて戦えました。</t>
         </is>
       </c>
     </row>
     <row r="186" ht="40" customHeight="1">
       <c r="A186" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.polite.shy[3]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.polite.shy[1]</t>
         </is>
       </c>
       <c r="B186" t="inlineStr" s="2">
@@ -6262,7 +6284,7 @@
       </c>
       <c r="D186" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.shy[3]</t>
+          <t xml:space="preserve">polite.shy[1]</t>
         </is>
       </c>
       <c r="E186" t="inlineStr" s="2">
@@ -6272,14 +6294,14 @@
       </c>
       <c r="F186" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…この恩は、一生、忘れません</t>
+          <t xml:space="preserve">あの…ありがとうございます、ここまで連れてきてくださって</t>
         </is>
       </c>
     </row>
     <row r="187" ht="40" customHeight="1">
       <c r="A187" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.polite.shy[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.polite.shy[2]</t>
         </is>
       </c>
       <c r="B187" t="inlineStr" s="2">
@@ -6289,12 +6311,12 @@
       </c>
       <c r="C187" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D187" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.shy[1]</t>
+          <t xml:space="preserve">polite.shy[2]</t>
         </is>
       </c>
       <c r="E187" t="inlineStr" s="2">
@@ -6304,14 +6326,14 @@
       </c>
       <c r="F187" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…満員、ありがとうございます…ありがとうございます…</t>
+          <t xml:space="preserve">…精一杯、やります</t>
         </is>
       </c>
     </row>
     <row r="188" ht="40" customHeight="1">
       <c r="A188" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.polite.shy[2]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.polite.shy[3]</t>
         </is>
       </c>
       <c r="B188" t="inlineStr" s="2">
@@ -6321,12 +6343,12 @@
       </c>
       <c r="C188" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D188" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.shy[2]</t>
+          <t xml:space="preserve">polite.shy[3]</t>
         </is>
       </c>
       <c r="E188" t="inlineStr" s="2">
@@ -6336,14 +6358,14 @@
       </c>
       <c r="F188" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…こんな私を、応援してくださって…</t>
+          <t xml:space="preserve">…この恩は、一生、忘れません</t>
         </is>
       </c>
     </row>
     <row r="189" ht="40" customHeight="1">
       <c r="A189" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.polite.shy[3]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.polite.shy[1]</t>
         </is>
       </c>
       <c r="B189" t="inlineStr" s="2">
@@ -6358,7 +6380,7 @@
       </c>
       <c r="D189" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.shy[3]</t>
+          <t xml:space="preserve">polite.shy[1]</t>
         </is>
       </c>
       <c r="E189" t="inlineStr" s="2">
@@ -6368,14 +6390,14 @@
       </c>
       <c r="F189" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…この恩、一生忘れません…</t>
+          <t xml:space="preserve">…満員、ありがとうございます…ありがとうございます…</t>
         </is>
       </c>
     </row>
     <row r="190" ht="40" customHeight="1">
       <c r="A190" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N1.polite.shy[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.polite.shy[2]</t>
         </is>
       </c>
       <c r="B190" t="inlineStr" s="2">
@@ -6385,29 +6407,29 @@
       </c>
       <c r="C190" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D190" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N1.polite.shy[1]</t>
+          <t xml:space="preserve">polite.shy[2]</t>
         </is>
       </c>
       <c r="E190" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F190" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、あの…お知らせがあります…</t>
+          <t xml:space="preserve">…こんなわたしを、応援してくださって…</t>
         </is>
       </c>
     </row>
     <row r="191" ht="40" customHeight="1">
       <c r="A191" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N2.polite.shy[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.polite.shy[3]</t>
         </is>
       </c>
       <c r="B191" t="inlineStr" s="2">
@@ -6417,29 +6439,29 @@
       </c>
       <c r="C191" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D191" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N2.polite.shy[1]</t>
+          <t xml:space="preserve">polite.shy[3]</t>
         </is>
       </c>
       <c r="E191" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F191" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ちょ、ちょっとお伝えしたいことが…</t>
+          <t xml:space="preserve">…この恩、一生忘れません…</t>
         </is>
       </c>
     </row>
     <row r="192" ht="40" customHeight="1">
       <c r="A192" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N3.polite.shy[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N1.polite.shy[1]</t>
         </is>
       </c>
       <c r="B192" t="inlineStr" s="2">
@@ -6454,7 +6476,7 @@
       </c>
       <c r="D192" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N3.polite.shy[1]</t>
+          <t xml:space="preserve">N1.polite.shy[1]</t>
         </is>
       </c>
       <c r="E192" t="inlineStr" s="2">
@@ -6464,14 +6486,14 @@
       </c>
       <c r="F192" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">報告です…あ、あの…</t>
+          <t xml:space="preserve">あ、あの…お知らせがあります…</t>
         </is>
       </c>
     </row>
     <row r="193" ht="40" customHeight="1">
       <c r="A193" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N4.polite.shy[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N2.polite.shy[1]</t>
         </is>
       </c>
       <c r="B193" t="inlineStr" s="2">
@@ -6486,7 +6508,7 @@
       </c>
       <c r="D193" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N4.polite.shy[1]</t>
+          <t xml:space="preserve">N2.polite.shy[1]</t>
         </is>
       </c>
       <c r="E193" t="inlineStr" s="2">
@@ -6496,14 +6518,14 @@
       </c>
       <c r="F193" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お、大事なお知らせです…</t>
+          <t xml:space="preserve">ちょ、ちょっとお伝えしたいことが…</t>
         </is>
       </c>
     </row>
     <row r="194" ht="40" customHeight="1">
       <c r="A194" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.polite.shy[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N3.polite.shy[1]</t>
         </is>
       </c>
       <c r="B194" t="inlineStr" s="2">
@@ -6518,7 +6540,7 @@
       </c>
       <c r="D194" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_low.polite.shy[1]</t>
+          <t xml:space="preserve">N3.polite.shy[1]</t>
         </is>
       </c>
       <c r="E194" t="inlineStr" s="2">
@@ -6528,14 +6550,14 @@
       </c>
       <c r="F194" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、あの…ちょっと、心配なことが…</t>
+          <t xml:space="preserve">報告です…あ、あの…</t>
         </is>
       </c>
     </row>
     <row r="195" ht="40" customHeight="1">
       <c r="A195" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.polite.shy[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N4.polite.shy[1]</t>
         </is>
       </c>
       <c r="B195" t="inlineStr" s="2">
@@ -6550,7 +6572,7 @@
       </c>
       <c r="D195" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_warning.polite.shy[1]</t>
+          <t xml:space="preserve">N4.polite.shy[1]</t>
         </is>
       </c>
       <c r="E195" t="inlineStr" s="2">
@@ -6560,14 +6582,14 @@
       </c>
       <c r="F195" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">き、緊急のお知らせです…!</t>
+          <t xml:space="preserve">お、大事なお知らせです…</t>
         </is>
       </c>
     </row>
     <row r="196" ht="40" customHeight="1">
       <c r="A196" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.breakthrough.voice.polite.shy[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.polite.shy[1]</t>
         </is>
       </c>
       <c r="B196" t="inlineStr" s="2">
@@ -6577,12 +6599,12 @@
       </c>
       <c r="C196" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D196" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">breakthrough.voice.polite.shy[1]</t>
+          <t xml:space="preserve">N5_low.polite.shy[1]</t>
         </is>
       </c>
       <c r="E196" t="inlineStr" s="2">
@@ -6592,14 +6614,14 @@
       </c>
       <c r="F196" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…な、何かが、変わった気がします…</t>
+          <t xml:space="preserve">あ、あの…ちょっと、心配なことが…</t>
         </is>
       </c>
     </row>
     <row r="197" ht="40" customHeight="1">
       <c r="A197" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G1.voice.polite.shy[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.polite.shy[1]</t>
         </is>
       </c>
       <c r="B197" t="inlineStr" s="2">
@@ -6609,12 +6631,12 @@
       </c>
       <c r="C197" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D197" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G1.voice.polite.shy[1]</t>
+          <t xml:space="preserve">N5_warning.polite.shy[1]</t>
         </is>
       </c>
       <c r="E197" t="inlineStr" s="2">
@@ -6624,14 +6646,14 @@
       </c>
       <c r="F197" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…もう少し、お給料が、上がったらいいな…</t>
+          <t xml:space="preserve">き、緊急のお知らせです…！</t>
         </is>
       </c>
     </row>
     <row r="198" ht="40" customHeight="1">
       <c r="A198" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G2.voice.polite.shy[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.breakthrough.voice.polite.shy[1]</t>
         </is>
       </c>
       <c r="B198" t="inlineStr" s="2">
@@ -6646,7 +6668,7 @@
       </c>
       <c r="D198" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G2.voice.polite.shy[1]</t>
+          <t xml:space="preserve">breakthrough.voice.polite.shy[1]</t>
         </is>
       </c>
       <c r="E198" t="inlineStr" s="2">
@@ -6656,14 +6678,14 @@
       </c>
       <c r="F198" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ひ、ひとりだと、寂しいです…</t>
+          <t xml:space="preserve">…な、何かが、変わった気がします…</t>
         </is>
       </c>
     </row>
     <row r="199" ht="40" customHeight="1">
       <c r="A199" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G3.voice.polite.shy[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G1.voice.polite.shy[1]</t>
         </is>
       </c>
       <c r="B199" t="inlineStr" s="2">
@@ -6678,7 +6700,7 @@
       </c>
       <c r="D199" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G3.voice.polite.shy[1]</t>
+          <t xml:space="preserve">G1.voice.polite.shy[1]</t>
         </is>
       </c>
       <c r="E199" t="inlineStr" s="2">
@@ -6688,14 +6710,14 @@
       </c>
       <c r="F199" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…も、もっと注目されないと、ダメですよね…</t>
+          <t xml:space="preserve">…もう少し、お給料が、上がったらいいな…</t>
         </is>
       </c>
     </row>
     <row r="200" ht="40" customHeight="1">
       <c r="A200" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G4.voice.polite.shy[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G2.voice.polite.shy[1]</t>
         </is>
       </c>
       <c r="B200" t="inlineStr" s="2">
@@ -6710,7 +6732,7 @@
       </c>
       <c r="D200" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G4.voice.polite.shy[1]</t>
+          <t xml:space="preserve">G2.voice.polite.shy[1]</t>
         </is>
       </c>
       <c r="E200" t="inlineStr" s="2">
@@ -6720,14 +6742,14 @@
       </c>
       <c r="F200" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…つ、強くなりたい、です…</t>
+          <t xml:space="preserve">…ひ、ひとりだと、寂しいです…</t>
         </is>
       </c>
     </row>
     <row r="201" ht="40" customHeight="1">
       <c r="A201" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R2.voice.polite.shy[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G3.voice.polite.shy[1]</t>
         </is>
       </c>
       <c r="B201" t="inlineStr" s="2">
@@ -6742,7 +6764,7 @@
       </c>
       <c r="D201" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R2.voice.polite.shy[1]</t>
+          <t xml:space="preserve">G3.voice.polite.shy[1]</t>
         </is>
       </c>
       <c r="E201" t="inlineStr" s="2">
@@ -6752,14 +6774,14 @@
       </c>
       <c r="F201" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…あ、あの人と、また話せたらいいな…</t>
+          <t xml:space="preserve">…も、もっと注目されないと、ダメですよね…</t>
         </is>
       </c>
     </row>
     <row r="202" ht="40" customHeight="1">
       <c r="A202" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R3.modal.polite.shy[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G4.voice.polite.shy[1]</t>
         </is>
       </c>
       <c r="B202" t="inlineStr" s="2">
@@ -6774,7 +6796,7 @@
       </c>
       <c r="D202" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R3.modal.polite.shy[1]</t>
+          <t xml:space="preserve">G4.voice.polite.shy[1]</t>
         </is>
       </c>
       <c r="E202" t="inlineStr" s="2">
@@ -6784,14 +6806,14 @@
       </c>
       <c r="F202" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、あの…少し、お話できますか…</t>
+          <t xml:space="preserve">…つ、強くなりたい、です…</t>
         </is>
       </c>
     </row>
     <row r="203" ht="40" customHeight="1">
       <c r="A203" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R4.voice.polite.shy[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R2.voice.polite.shy[1]</t>
         </is>
       </c>
       <c r="B203" t="inlineStr" s="2">
@@ -6806,7 +6828,7 @@
       </c>
       <c r="D203" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R4.voice.polite.shy[1]</t>
+          <t xml:space="preserve">R2.voice.polite.shy[1]</t>
         </is>
       </c>
       <c r="E203" t="inlineStr" s="2">
@@ -6816,14 +6838,14 @@
       </c>
       <c r="F203" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…あ、あの人とは、距離を置きたい、かも…</t>
+          <t xml:space="preserve">…あ、あの人と、また話せたらいいな…</t>
         </is>
       </c>
     </row>
     <row r="204" ht="40" customHeight="1">
       <c r="A204" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R5.voice.polite.shy[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R3.modal.polite.shy[1]</t>
         </is>
       </c>
       <c r="B204" t="inlineStr" s="2">
@@ -6838,7 +6860,7 @@
       </c>
       <c r="D204" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R5.voice.polite.shy[1]</t>
+          <t xml:space="preserve">R3.modal.polite.shy[1]</t>
         </is>
       </c>
       <c r="E204" t="inlineStr" s="2">
@@ -6848,14 +6870,14 @@
       </c>
       <c r="F204" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ま、負けたく、ないです…</t>
+          <t xml:space="preserve">あ、あの…少し、お話できますか…</t>
         </is>
       </c>
     </row>
     <row r="205" ht="40" customHeight="1">
       <c r="A205" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.warVictory.voice.polite.shy[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R4.voice.polite.shy[1]</t>
         </is>
       </c>
       <c r="B205" t="inlineStr" s="2">
@@ -6870,7 +6892,7 @@
       </c>
       <c r="D205" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">warVictory.voice.polite.shy[1]</t>
+          <t xml:space="preserve">R4.voice.polite.shy[1]</t>
         </is>
       </c>
       <c r="E205" t="inlineStr" s="2">
@@ -6880,14 +6902,14 @@
       </c>
       <c r="F205" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…か、勝てて、よかったです…</t>
+          <t xml:space="preserve">…あ、あの人とは、距離を置きたい、かも…</t>
         </is>
       </c>
     </row>
     <row r="206" ht="40" customHeight="1">
       <c r="A206" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus_repeat.polite.shy[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R5.voice.polite.shy[1]</t>
         </is>
       </c>
       <c r="B206" t="inlineStr" s="2">
@@ -6897,29 +6919,29 @@
       </c>
       <c r="C206" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D206" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus_repeat.polite.shy[1]</t>
+          <t xml:space="preserve">R5.voice.polite.shy[1]</t>
         </is>
       </c>
       <c r="E206" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F206" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ま、また…？ そんな、毎回いただいては…申し訳ないです…</t>
+          <t xml:space="preserve">…ま、負けたく、ないです…</t>
         </is>
       </c>
     </row>
     <row r="207" ht="40" customHeight="1">
       <c r="A207" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.polite.shy[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.warVictory.voice.polite.shy[1]</t>
         </is>
       </c>
       <c r="B207" t="inlineStr" s="2">
@@ -6929,29 +6951,29 @@
       </c>
       <c r="C207" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D207" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus.polite.shy[1]</t>
+          <t xml:space="preserve">warVictory.voice.polite.shy[1]</t>
         </is>
       </c>
       <c r="E207" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F207" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ぼ、ボーナスを…？ あ、ありがとうございます…大切に使わせていただきます…</t>
+          <t xml:space="preserve">…か、勝てて、よかったです…</t>
         </is>
       </c>
     </row>
     <row r="208" ht="40" customHeight="1">
       <c r="A208" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.polite.shy[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus_repeat.polite.shy[1]</t>
         </is>
       </c>
       <c r="B208" t="inlineStr" s="2">
@@ -6966,7 +6988,7 @@
       </c>
       <c r="D208" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">camp.polite.shy[1]</t>
+          <t xml:space="preserve">bonus_repeat.polite.shy[1]</t>
         </is>
       </c>
       <c r="E208" t="inlineStr" s="2">
@@ -6976,14 +6998,14 @@
       </c>
       <c r="F208" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">が、合宿…ですか…緊張しますけど…頑張ります…!</t>
+          <t xml:space="preserve">ま、また…？ そんな、毎回いただいては…申し訳ないです…</t>
         </is>
       </c>
     </row>
     <row r="209" ht="40" customHeight="1">
       <c r="A209" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.polite.shy[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.polite.shy[1]</t>
         </is>
       </c>
       <c r="B209" t="inlineStr" s="2">
@@ -6998,7 +7020,7 @@
       </c>
       <c r="D209" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage_high_trust.polite.shy[1]</t>
+          <t xml:space="preserve">bonus.polite.shy[1]</t>
         </is>
       </c>
       <c r="E209" t="inlineStr" s="2">
@@ -7008,14 +7030,14 @@
       </c>
       <c r="F209" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いつも気にかけてくださって…あ、あの、本当に感謝しています…</t>
+          <t xml:space="preserve">ぼ、ボーナスを…？ あ、ありがとうございます…大切に使わせていただきます…</t>
         </is>
       </c>
     </row>
     <row r="210" ht="40" customHeight="1">
       <c r="A210" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.polite.shy[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.polite.shy[1]</t>
         </is>
       </c>
       <c r="B210" t="inlineStr" s="2">
@@ -7030,7 +7052,7 @@
       </c>
       <c r="D210" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage.polite.shy[1]</t>
+          <t xml:space="preserve">camp.polite.shy[1]</t>
         </is>
       </c>
       <c r="E210" t="inlineStr" s="2">
@@ -7040,14 +7062,14 @@
       </c>
       <c r="F210" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、ありがとうございます…そう言っていただけると、頑張れます…</t>
+          <t xml:space="preserve">が、合宿…ですか…緊張しますけど…頑張ります…！</t>
         </is>
       </c>
     </row>
     <row r="211" ht="40" customHeight="1">
       <c r="A211" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.polite.shy[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.polite.shy[1]</t>
         </is>
       </c>
       <c r="B211" t="inlineStr" s="2">
@@ -7062,7 +7084,7 @@
       </c>
       <c r="D211" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faction_decree.polite.shy[1]</t>
+          <t xml:space="preserve">encourage_high_trust.polite.shy[1]</t>
         </is>
       </c>
       <c r="E211" t="inlineStr" s="2">
@@ -7072,14 +7094,14 @@
       </c>
       <c r="F211" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……あの。皆には、わたしから……</t>
+          <t xml:space="preserve">いつも気にかけてくださって…あ、あの、本当に感謝しています…</t>
         </is>
       </c>
     </row>
     <row r="212" ht="40" customHeight="1">
       <c r="A212" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.polite.shy[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.polite.shy[1]</t>
         </is>
       </c>
       <c r="B212" t="inlineStr" s="2">
@@ -7094,7 +7116,7 @@
       </c>
       <c r="D212" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">media.polite.shy[1]</t>
+          <t xml:space="preserve">encourage.polite.shy[1]</t>
         </is>
       </c>
       <c r="E212" t="inlineStr" s="2">
@@ -7104,14 +7126,14 @@
       </c>
       <c r="F212" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">メ、メディア出演…ですか…き、緊張しますけど…や、やってみます…</t>
+          <t xml:space="preserve">あ、ありがとうございます…そう言っていただけると、頑張れます…</t>
         </is>
       </c>
     </row>
     <row r="213" ht="40" customHeight="1">
       <c r="A213" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.polite.shy[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.polite.shy[1]</t>
         </is>
       </c>
       <c r="B213" t="inlineStr" s="2">
@@ -7126,7 +7148,7 @@
       </c>
       <c r="D213" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">party.polite.shy[1]</t>
+          <t xml:space="preserve">faction_decree.polite.shy[1]</t>
         </is>
       </c>
       <c r="E213" t="inlineStr" s="2">
@@ -7136,14 +7158,14 @@
       </c>
       <c r="F213" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">パ、パーティー…人が多いところは少し苦手ですけど…頑張って参加します…</t>
+          <t xml:space="preserve">……あの。皆には、わたしから……</t>
         </is>
       </c>
     </row>
     <row r="214" ht="40" customHeight="1">
       <c r="A214" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.polite.shy[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.polite.shy[1]</t>
         </is>
       </c>
       <c r="B214" t="inlineStr" s="2">
@@ -7158,7 +7180,7 @@
       </c>
       <c r="D214" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refresh_leave.polite.shy[1]</t>
+          <t xml:space="preserve">media.polite.shy[1]</t>
         </is>
       </c>
       <c r="E214" t="inlineStr" s="2">
@@ -7168,14 +7190,14 @@
       </c>
       <c r="F214" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お休みを…？ あ、あの…ありがとうございます、ゆっくり休ませていただきます…</t>
+          <t xml:space="preserve">メ、メディア出演…ですか…き、緊張しますけど…や、やってみます…</t>
         </is>
       </c>
     </row>
     <row r="215" ht="40" customHeight="1">
       <c r="A215" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.polite.shy[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.polite.shy[1]</t>
         </is>
       </c>
       <c r="B215" t="inlineStr" s="2">
@@ -7190,7 +7212,7 @@
       </c>
       <c r="D215" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">special_treatment.polite.shy[1]</t>
+          <t xml:space="preserve">party.polite.shy[1]</t>
         </is>
       </c>
       <c r="E215" t="inlineStr" s="2">
@@ -7200,14 +7222,14 @@
       </c>
       <c r="F215" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こ、こんな特別扱い…わたしなんかに、もったいないです…</t>
+          <t xml:space="preserve">パ、パーティー…人が多いところは少し苦手ですけど…頑張って参加します…</t>
         </is>
       </c>
     </row>
     <row r="216" ht="40" customHeight="1">
       <c r="A216" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.polite.shy[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.polite.shy[1]</t>
         </is>
       </c>
       <c r="B216" t="inlineStr" s="2">
@@ -7222,7 +7244,7 @@
       </c>
       <c r="D216" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trainer.polite.shy[1]</t>
+          <t xml:space="preserve">refresh_leave.polite.shy[1]</t>
         </is>
       </c>
       <c r="E216" t="inlineStr" s="2">
@@ -7232,14 +7254,14 @@
       </c>
       <c r="F216" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">専属トレーナー…ですか…あ、あの、よろしくお願いいたします…</t>
+          <t xml:space="preserve">お休みを…？ あ、あの…ありがとうございます、ゆっくり休ませていただきます…</t>
         </is>
       </c>
     </row>
     <row r="217" ht="40" customHeight="1">
       <c r="A217" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.polite.shy[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.polite.shy[1]</t>
         </is>
       </c>
       <c r="B217" t="inlineStr" s="2">
@@ -7249,12 +7271,12 @@
       </c>
       <c r="C217" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D217" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.polite.shy[1]</t>
+          <t xml:space="preserve">special_treatment.polite.shy[1]</t>
         </is>
       </c>
       <c r="E217" t="inlineStr" s="2">
@@ -7264,14 +7286,14 @@
       </c>
       <c r="F217" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、あの…どうしたら、いいんでしょうか…</t>
+          <t xml:space="preserve">こ、こんな特別扱い…わたしなんかに、もったいないです…</t>
         </is>
       </c>
     </row>
     <row r="218" ht="40" customHeight="1">
       <c r="A218" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E4.polite.shy[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.polite.shy[1]</t>
         </is>
       </c>
       <c r="B218" t="inlineStr" s="2">
@@ -7281,12 +7303,12 @@
       </c>
       <c r="C218" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D218" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E4.polite.shy[1]</t>
+          <t xml:space="preserve">trainer.polite.shy[1]</t>
         </is>
       </c>
       <c r="E218" t="inlineStr" s="2">
@@ -7296,14 +7318,14 @@
       </c>
       <c r="F218" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">え、ええと…そ、その件は…</t>
+          <t xml:space="preserve">専属トレーナー…ですか…あ、あの、よろしくお願いいたします…</t>
         </is>
       </c>
     </row>
     <row r="219" ht="40" customHeight="1">
       <c r="A219" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.polite.shy[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.polite.shy[1]</t>
         </is>
       </c>
       <c r="B219" t="inlineStr" s="2">
@@ -7318,7 +7340,7 @@
       </c>
       <c r="D219" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E6.polite.shy[1]</t>
+          <t xml:space="preserve">E1.polite.shy[1]</t>
         </is>
       </c>
       <c r="E219" t="inlineStr" s="2">
@@ -7328,14 +7350,14 @@
       </c>
       <c r="F219" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">は、はい…わかりました…やってみます…</t>
+          <t xml:space="preserve">あ、あの…どうしたら、いいんでしょうか…</t>
         </is>
       </c>
     </row>
     <row r="220" ht="40" customHeight="1">
       <c r="A220" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.polite.shy[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E4.polite.shy[1]</t>
         </is>
       </c>
       <c r="B220" t="inlineStr" s="2">
@@ -7350,7 +7372,7 @@
       </c>
       <c r="D220" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_boycott.polite.shy[1]</t>
+          <t xml:space="preserve">E4.polite.shy[1]</t>
         </is>
       </c>
       <c r="E220" t="inlineStr" s="2">
@@ -7360,14 +7382,14 @@
       </c>
       <c r="F220" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、あの…これは、納得できません…</t>
+          <t xml:space="preserve">え、ええと…そ、その件は…</t>
         </is>
       </c>
     </row>
     <row r="221" ht="40" customHeight="1">
       <c r="A221" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.polite.shy[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.polite.shy[1]</t>
         </is>
       </c>
       <c r="B221" t="inlineStr" s="2">
@@ -7382,7 +7404,7 @@
       </c>
       <c r="D221" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_grumble.polite.shy[1]</t>
+          <t xml:space="preserve">E6.polite.shy[1]</t>
         </is>
       </c>
       <c r="E221" t="inlineStr" s="2">
@@ -7392,14 +7414,14 @@
       </c>
       <c r="F221" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">すみません…少し、不満があります…</t>
+          <t xml:space="preserve">は、はい…わかりました…やってみます…</t>
         </is>
       </c>
     </row>
     <row r="222" ht="40" customHeight="1">
       <c r="A222" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.polite.shy[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.polite.shy[1]</t>
         </is>
       </c>
       <c r="B222" t="inlineStr" s="2">
@@ -7414,7 +7436,7 @@
       </c>
       <c r="D222" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_sns.polite.shy[1]</t>
+          <t xml:space="preserve">S_boycott.polite.shy[1]</t>
         </is>
       </c>
       <c r="E222" t="inlineStr" s="2">
@@ -7424,14 +7446,14 @@
       </c>
       <c r="F222" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">え、SNSで…そんな風に書かれてしまって…</t>
+          <t xml:space="preserve">あ、あの…これは、納得できません…</t>
         </is>
       </c>
     </row>
     <row r="223" ht="40" customHeight="1">
       <c r="A223" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.polite.shy[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.polite.shy[1]</t>
         </is>
       </c>
       <c r="B223" t="inlineStr" s="2">
@@ -7446,7 +7468,7 @@
       </c>
       <c r="D223" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S1.polite.shy[1]</t>
+          <t xml:space="preserve">S_grumble.polite.shy[1]</t>
         </is>
       </c>
       <c r="E223" t="inlineStr" s="2">
@@ -7456,14 +7478,14 @@
       </c>
       <c r="F223" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、あの…ご相談したいことが…</t>
+          <t xml:space="preserve">すみません…少し、不満があります…</t>
         </is>
       </c>
     </row>
     <row r="224" ht="40" customHeight="1">
       <c r="A224" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.polite.shy[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.polite.shy[1]</t>
         </is>
       </c>
       <c r="B224" t="inlineStr" s="2">
@@ -7478,7 +7500,7 @@
       </c>
       <c r="D224" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S2.polite.shy[1]</t>
+          <t xml:space="preserve">S_sns.polite.shy[1]</t>
         </is>
       </c>
       <c r="E224" t="inlineStr" s="2">
@@ -7488,14 +7510,14 @@
       </c>
       <c r="F224" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">す、すみません…少しお時間いただけますか…</t>
+          <t xml:space="preserve">え、SNSで…そんな風に書かれてしまって…</t>
         </is>
       </c>
     </row>
     <row r="225" ht="40" customHeight="1">
       <c r="A225" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.polite.shy[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.polite.shy[1]</t>
         </is>
       </c>
       <c r="B225" t="inlineStr" s="2">
@@ -7510,7 +7532,7 @@
       </c>
       <c r="D225" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S3.polite.shy[1]</t>
+          <t xml:space="preserve">S1.polite.shy[1]</t>
         </is>
       </c>
       <c r="E225" t="inlineStr" s="2">
@@ -7520,14 +7542,14 @@
       </c>
       <c r="F225" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、あの…どう答えたらいいか、わからなくて…</t>
+          <t xml:space="preserve">あ、あの…ご相談したいことが…</t>
         </is>
       </c>
     </row>
     <row r="226" ht="40" customHeight="1">
       <c r="A226" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.polite.shy[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.polite.shy[1]</t>
         </is>
       </c>
       <c r="B226" t="inlineStr" s="2">
@@ -7542,7 +7564,7 @@
       </c>
       <c r="D226" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_direct.polite.shy[1]</t>
+          <t xml:space="preserve">S2.polite.shy[1]</t>
         </is>
       </c>
       <c r="E226" t="inlineStr" s="2">
@@ -7552,14 +7574,14 @@
       </c>
       <c r="F226" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">は、はっきり言わせていただきます…わたしは…</t>
+          <t xml:space="preserve">す、すみません…少しお時間いただけますか…</t>
         </is>
       </c>
     </row>
     <row r="227" ht="40" customHeight="1">
       <c r="A227" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.polite.shy[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.polite.shy[1]</t>
         </is>
       </c>
       <c r="B227" t="inlineStr" s="2">
@@ -7574,7 +7596,7 @@
       </c>
       <c r="D227" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_silent.polite.shy[1]</t>
+          <t xml:space="preserve">S3.polite.shy[1]</t>
         </is>
       </c>
       <c r="E227" t="inlineStr" s="2">
@@ -7584,14 +7606,14 @@
       </c>
       <c r="F227" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………あの…なにも、言えません…</t>
+          <t xml:space="preserve">あ、あの…どう答えたらいいか、わからなくて…</t>
         </is>
       </c>
     </row>
     <row r="228" ht="40" customHeight="1">
       <c r="A228" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.polite.shy[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.polite.shy[1]</t>
         </is>
       </c>
       <c r="B228" t="inlineStr" s="2">
@@ -7606,7 +7628,7 @@
       </c>
       <c r="D228" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S5.polite.shy[1]</t>
+          <t xml:space="preserve">S4_direct.polite.shy[1]</t>
         </is>
       </c>
       <c r="E228" t="inlineStr" s="2">
@@ -7616,14 +7638,14 @@
       </c>
       <c r="F228" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">考えさせて…いただけますか…？</t>
+          <t xml:space="preserve">は、はっきり言わせていただきます…わたしは…</t>
         </is>
       </c>
     </row>
     <row r="229" ht="40" customHeight="1">
       <c r="A229" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.polite.shy[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.polite.shy[1]</t>
         </is>
       </c>
       <c r="B229" t="inlineStr" s="2">
@@ -7638,7 +7660,7 @@
       </c>
       <c r="D229" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S6.polite.shy[1]</t>
+          <t xml:space="preserve">S4_silent.polite.shy[1]</t>
         </is>
       </c>
       <c r="E229" t="inlineStr" s="2">
@@ -7648,14 +7670,14 @@
       </c>
       <c r="F229" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">決めました…これで、いいんですよね…？</t>
+          <t xml:space="preserve">………あの…なにも、言えません…</t>
         </is>
       </c>
     </row>
     <row r="230" ht="40" customHeight="1">
       <c r="A230" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.polite.shy[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.polite.shy[1]</t>
         </is>
       </c>
       <c r="B230" t="inlineStr" s="2">
@@ -7665,12 +7687,12 @@
       </c>
       <c r="C230" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D230" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1.polite.shy[1]</t>
+          <t xml:space="preserve">S5.polite.shy[1]</t>
         </is>
       </c>
       <c r="E230" t="inlineStr" s="2">
@@ -7680,14 +7702,14 @@
       </c>
       <c r="F230" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、あの…これから、頑張りたいことがあります…</t>
+          <t xml:space="preserve">考えさせて…いただけますか…？</t>
         </is>
       </c>
     </row>
     <row r="231" ht="40" customHeight="1">
       <c r="A231" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.polite.shy[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.polite.shy[1]</t>
         </is>
       </c>
       <c r="B231" t="inlineStr" s="2">
@@ -7697,12 +7719,12 @@
       </c>
       <c r="C231" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D231" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter1.polite.shy[1]</t>
+          <t xml:space="preserve">S6.polite.shy[1]</t>
         </is>
       </c>
       <c r="E231" t="inlineStr" s="2">
@@ -7712,14 +7734,14 @@
       </c>
       <c r="F231" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お、お話を聞かせていただけますか…？</t>
+          <t xml:space="preserve">決めました…これで、いいんですよね…？</t>
         </is>
       </c>
     </row>
     <row r="232" ht="40" customHeight="1">
       <c r="A232" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.polite.shy[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.polite.shy[1]</t>
         </is>
       </c>
       <c r="B232" t="inlineStr" s="2">
@@ -7734,7 +7756,7 @@
       </c>
       <c r="D232" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter2.polite.shy[1]</t>
+          <t xml:space="preserve">B1.polite.shy[1]</t>
         </is>
       </c>
       <c r="E232" t="inlineStr" s="2">
@@ -7744,14 +7766,14 @@
       </c>
       <c r="F232" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">は、はい…お聞きします…</t>
+          <t xml:space="preserve">あ、あの…これから、頑張りたいことがあります…</t>
         </is>
       </c>
     </row>
     <row r="233" ht="40" customHeight="1">
       <c r="A233" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.polite.shy[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.polite.shy[1]</t>
         </is>
       </c>
       <c r="B233" t="inlineStr" s="2">
@@ -7766,7 +7788,7 @@
       </c>
       <c r="D233" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_brand.polite.shy[1]</t>
+          <t xml:space="preserve">B2_fighter1.polite.shy[1]</t>
         </is>
       </c>
       <c r="E233" t="inlineStr" s="2">
@@ -7776,14 +7798,14 @@
       </c>
       <c r="F233" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ブランドのお仕事…ですか…？ あ、あの、精一杯やらせていただきます…</t>
+          <t xml:space="preserve">お、お話を聞かせていただけますか…？</t>
         </is>
       </c>
     </row>
     <row r="234" ht="40" customHeight="1">
       <c r="A234" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.polite.shy[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.polite.shy[1]</t>
         </is>
       </c>
       <c r="B234" t="inlineStr" s="2">
@@ -7798,7 +7820,7 @@
       </c>
       <c r="D234" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_cm.polite.shy[1]</t>
+          <t xml:space="preserve">B2_fighter2.polite.shy[1]</t>
         </is>
       </c>
       <c r="E234" t="inlineStr" s="2">
@@ -7808,14 +7830,14 @@
       </c>
       <c r="F234" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">CM…ですか…？ わ、わたしなんかで、いいんでしょうか…</t>
+          <t xml:space="preserve">は、はい…お聞きします…</t>
         </is>
       </c>
     </row>
     <row r="235" ht="40" customHeight="1">
       <c r="A235" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.polite.shy[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.polite.shy[1]</t>
         </is>
       </c>
       <c r="B235" t="inlineStr" s="2">
@@ -7830,7 +7852,7 @@
       </c>
       <c r="D235" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fan.polite.shy[1]</t>
+          <t xml:space="preserve">B4_brand.polite.shy[1]</t>
         </is>
       </c>
       <c r="E235" t="inlineStr" s="2">
@@ -7840,14 +7862,14 @@
       </c>
       <c r="F235" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ファンの方に…直接、お会いできるんですか…？ う、嬉しいです…</t>
+          <t xml:space="preserve">ブランドのお仕事…ですか…？ あ、あの、精一杯やらせていただきます…</t>
         </is>
       </c>
     </row>
     <row r="236" ht="40" customHeight="1">
       <c r="A236" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.polite.shy[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.polite.shy[1]</t>
         </is>
       </c>
       <c r="B236" t="inlineStr" s="2">
@@ -7862,7 +7884,7 @@
       </c>
       <c r="D236" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fashion.polite.shy[1]</t>
+          <t xml:space="preserve">B4_cm.polite.shy[1]</t>
         </is>
       </c>
       <c r="E236" t="inlineStr" s="2">
@@ -7872,14 +7894,14 @@
       </c>
       <c r="F236" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">フ、ファッション関連のお仕事…似合うでしょうか…</t>
+          <t xml:space="preserve">CM…ですか…？ わ、わたしなんかで、いいんでしょうか…</t>
         </is>
       </c>
     </row>
     <row r="237" ht="40" customHeight="1">
       <c r="A237" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.polite.shy[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.polite.shy[1]</t>
         </is>
       </c>
       <c r="B237" t="inlineStr" s="2">
@@ -7894,7 +7916,7 @@
       </c>
       <c r="D237" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_gravure.polite.shy[1]</t>
+          <t xml:space="preserve">B4_fan.polite.shy[1]</t>
         </is>
       </c>
       <c r="E237" t="inlineStr" s="2">
@@ -7904,14 +7926,14 @@
       </c>
       <c r="F237" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">グ、グラビア…ですか…？ は、恥ずかしいです…でも、頑張ります…</t>
+          <t xml:space="preserve">ファンの方に…直接、お会いできるんですか…？ う、嬉しいです…</t>
         </is>
       </c>
     </row>
     <row r="238" ht="40" customHeight="1">
       <c r="A238" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.polite.shy[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.polite.shy[1]</t>
         </is>
       </c>
       <c r="B238" t="inlineStr" s="2">
@@ -7926,7 +7948,7 @@
       </c>
       <c r="D238" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_variety.polite.shy[1]</t>
+          <t xml:space="preserve">B4_fashion.polite.shy[1]</t>
         </is>
       </c>
       <c r="E238" t="inlineStr" s="2">
@@ -7936,14 +7958,14 @@
       </c>
       <c r="F238" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">バ、バラエティ番組…ちゃんと、お話できるか不安です…</t>
+          <t xml:space="preserve">フ、ファッション関連のお仕事…似合うでしょうか…</t>
         </is>
       </c>
     </row>
     <row r="239" ht="40" customHeight="1">
       <c r="A239" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.polite.shy[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.polite.shy[1]</t>
         </is>
       </c>
       <c r="B239" t="inlineStr" s="2">
@@ -7958,7 +7980,7 @@
       </c>
       <c r="D239" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4.polite.shy[1]</t>
+          <t xml:space="preserve">B4_gravure.polite.shy[1]</t>
         </is>
       </c>
       <c r="E239" t="inlineStr" s="2">
@@ -7968,14 +7990,14 @@
       </c>
       <c r="F239" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こ、こんなお仕事、わたしに務まるでしょうか…</t>
+          <t xml:space="preserve">グ、グラビア…ですか…？ は、恥ずかしいです…でも、頑張ります…</t>
         </is>
       </c>
     </row>
     <row r="240" ht="40" customHeight="1">
       <c r="A240" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.polite.shy[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.polite.shy[1]</t>
         </is>
       </c>
       <c r="B240" t="inlineStr" s="2">
@@ -7985,29 +8007,29 @@
       </c>
       <c r="C240" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D240" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.shy[1]</t>
+          <t xml:space="preserve">B4_variety.polite.shy[1]</t>
         </is>
       </c>
       <c r="E240" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F240" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、あの…私などでよろしければ…せ、精一杯務めます…</t>
+          <t xml:space="preserve">バ、バラエティ番組…ちゃんと、お話できるか不安です…</t>
         </is>
       </c>
     </row>
     <row r="241" ht="40" customHeight="1">
       <c r="A241" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.polite.shy[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.polite.shy[1]</t>
         </is>
       </c>
       <c r="B241" t="inlineStr" s="2">
@@ -8017,29 +8039,29 @@
       </c>
       <c r="C241" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D241" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.shy[1]</t>
+          <t xml:space="preserve">B4.polite.shy[1]</t>
         </is>
       </c>
       <c r="E241" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F241" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、あの…よ、よろしくお願いいたします…</t>
+          <t xml:space="preserve">こ、こんなお仕事、わたしに務まるでしょうか…</t>
         </is>
       </c>
     </row>
     <row r="242" ht="40" customHeight="1">
       <c r="A242" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.polite.shy[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.polite.shy[1]</t>
         </is>
       </c>
       <c r="B242" t="inlineStr" s="2">
@@ -8049,7 +8071,7 @@
       </c>
       <c r="C242" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
         </is>
       </c>
       <c r="D242" t="inlineStr" s="12">
@@ -8064,14 +8086,14 @@
       </c>
       <c r="F242" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、あの…よろしくお願いいたします…精一杯やります…</t>
+          <t xml:space="preserve">あ、あの…わたしなどでよろしければ…せ、精一杯務めます…</t>
         </is>
       </c>
     </row>
     <row r="243" ht="40" customHeight="1">
       <c r="A243" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.polite.shy[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.polite.shy[1]</t>
         </is>
       </c>
       <c r="B243" t="inlineStr" s="2">
@@ -8081,7 +8103,7 @@
       </c>
       <c r="C243" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D243" t="inlineStr" s="12">
@@ -8096,14 +8118,14 @@
       </c>
       <c r="F243" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よ、よろしくお願いいたします…が、頑張ります…！</t>
+          <t xml:space="preserve">あ、あの…よ、よろしくお願いいたします…</t>
         </is>
       </c>
     </row>
     <row r="244" ht="40" customHeight="1">
       <c r="A244" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.polite.shy[1]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.polite.shy[1]</t>
         </is>
       </c>
       <c r="B244" t="inlineStr" s="2">
@@ -8113,7 +8135,7 @@
       </c>
       <c r="C244" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
         </is>
       </c>
       <c r="D244" t="inlineStr" s="12">
@@ -8128,14 +8150,14 @@
       </c>
       <c r="F244" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">す、すみません…少しだけ休ませてください…</t>
+          <t xml:space="preserve">あ、あの…よろしくお願いいたします…精一杯やります…</t>
         </is>
       </c>
     </row>
     <row r="245" ht="40" customHeight="1">
       <c r="A245" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.polite.shy[1]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.polite.shy[1]</t>
         </is>
       </c>
       <c r="B245" t="inlineStr" s="2">
@@ -8145,12 +8167,12 @@
       </c>
       <c r="C245" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
         </is>
       </c>
       <c r="D245" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.ahead.polite.shy[1]</t>
+          <t xml:space="preserve">polite.shy[1]</t>
         </is>
       </c>
       <c r="E245" t="inlineStr" s="2">
@@ -8160,14 +8182,14 @@
       </c>
       <c r="F245" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝たせて…いただきました。…なのに、怖いままです…</t>
+          <t xml:space="preserve">よ、よろしくお願いいたします…が、頑張ります…！</t>
         </is>
       </c>
     </row>
     <row r="246" ht="40" customHeight="1">
       <c r="A246" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.polite.shy[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.polite.shy[1]</t>
         </is>
       </c>
       <c r="B246" t="inlineStr" s="2">
@@ -8177,12 +8199,12 @@
       </c>
       <c r="C246" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D246" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.behind.polite.shy[1]</t>
+          <t xml:space="preserve">polite.shy[1]</t>
         </is>
       </c>
       <c r="E246" t="inlineStr" s="2">
@@ -8192,14 +8214,14 @@
       </c>
       <c r="F246" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…もう終わったって…言われました。…言われただけです…</t>
+          <t xml:space="preserve">す、すみません…少しだけ休ませてください…</t>
         </is>
       </c>
     </row>
     <row r="247" ht="40" customHeight="1">
       <c r="A247" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.polite.shy[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.polite.shy[1]</t>
         </is>
       </c>
       <c r="B247" t="inlineStr" s="2">
@@ -8214,7 +8236,7 @@
       </c>
       <c r="D247" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftInterest.polite.shy[1]</t>
+          <t xml:space="preserve">bitterPrematch.ahead.polite.shy[1]</t>
         </is>
       </c>
       <c r="E247" t="inlineStr" s="2">
@@ -8224,14 +8246,14 @@
       </c>
       <c r="F247" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、あの…私などでよろしければ…せ、精一杯務めます…</t>
+          <t xml:space="preserve">勝たせて…いただきました。…なのに、怖いままです…</t>
         </is>
       </c>
     </row>
     <row r="248" ht="40" customHeight="1">
       <c r="A248" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.polite.shy[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.polite.shy[1]</t>
         </is>
       </c>
       <c r="B248" t="inlineStr" s="2">
@@ -8246,7 +8268,7 @@
       </c>
       <c r="D248" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.polite.shy[1]</t>
+          <t xml:space="preserve">bitterPrematch.behind.polite.shy[1]</t>
         </is>
       </c>
       <c r="E248" t="inlineStr" s="2">
@@ -8256,14 +8278,14 @@
       </c>
       <c r="F248" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、あの…よ、よろしくお願いいたします…</t>
+          <t xml:space="preserve">…もう終わったって…言われました。…言われただけです…</t>
         </is>
       </c>
     </row>
     <row r="249" ht="40" customHeight="1">
       <c r="A249" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.polite.shy[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.polite.shy[1]</t>
         </is>
       </c>
       <c r="B249" t="inlineStr" s="2">
@@ -8278,7 +8300,7 @@
       </c>
       <c r="D249" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faGreeting.polite.shy[1]</t>
+          <t xml:space="preserve">draftInterest.polite.shy[1]</t>
         </is>
       </c>
       <c r="E249" t="inlineStr" s="2">
@@ -8288,14 +8310,14 @@
       </c>
       <c r="F249" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、あの…契約してもらえて…感謝しています…！</t>
+          <t xml:space="preserve">あ、あの…わたしなどでよろしければ…せ、精一杯務めます…</t>
         </is>
       </c>
     </row>
     <row r="250" ht="40" customHeight="1">
       <c r="A250" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.polite.shy[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.polite.shy[1]</t>
         </is>
       </c>
       <c r="B250" t="inlineStr" s="2">
@@ -8310,7 +8332,7 @@
       </c>
       <c r="D250" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faSigning.polite.shy[1]</t>
+          <t xml:space="preserve">draftJoin.polite.shy[1]</t>
         </is>
       </c>
       <c r="E250" t="inlineStr" s="2">
@@ -8320,14 +8342,14 @@
       </c>
       <c r="F250" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、あの…よろしくお願いいたします…精一杯やります…</t>
+          <t xml:space="preserve">あ、あの…よ、よろしくお願いいたします…</t>
         </is>
       </c>
     </row>
     <row r="251" ht="40" customHeight="1">
       <c r="A251" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.polite.shy[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.polite.shy[1]</t>
         </is>
       </c>
       <c r="B251" t="inlineStr" s="2">
@@ -8342,7 +8364,7 @@
       </c>
       <c r="D251" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faWelcome.polite.shy[1]</t>
+          <t xml:space="preserve">faGreeting.polite.shy[1]</t>
         </is>
       </c>
       <c r="E251" t="inlineStr" s="2">
@@ -8352,14 +8374,14 @@
       </c>
       <c r="F251" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よ、よろしくお願いいたします…が、頑張ります…！</t>
+          <t xml:space="preserve">あ、あの…契約してもらえて…感謝しています…！</t>
         </is>
       </c>
     </row>
     <row r="252" ht="40" customHeight="1">
       <c r="A252" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.fresh.polite.shy[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.polite.shy[1]</t>
         </is>
       </c>
       <c r="B252" t="inlineStr" s="2">
@@ -8374,7 +8396,7 @@
       </c>
       <c r="D252" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.fresh.polite.shy[1]</t>
+          <t xml:space="preserve">faSigning.polite.shy[1]</t>
         </is>
       </c>
       <c r="E252" t="inlineStr" s="2">
@@ -8384,14 +8406,14 @@
       </c>
       <c r="F252" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、あの…今日は体が軽くて…もっと、やれます…!</t>
+          <t xml:space="preserve">あ、あの…よろしくお願いいたします…精一杯やります…</t>
         </is>
       </c>
     </row>
     <row r="253" ht="40" customHeight="1">
       <c r="A253" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.heavy.polite.shy[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.polite.shy[1]</t>
         </is>
       </c>
       <c r="B253" t="inlineStr" s="2">
@@ -8406,7 +8428,7 @@
       </c>
       <c r="D253" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.heavy.polite.shy[1]</t>
+          <t xml:space="preserve">faWelcome.polite.shy[1]</t>
         </is>
       </c>
       <c r="E253" t="inlineStr" s="2">
@@ -8416,14 +8438,14 @@
       </c>
       <c r="F253" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">すみません…動けてはいるんですけど…空回りしてしまって</t>
+          <t xml:space="preserve">よ、よろしくお願いいたします…が、頑張ります…！</t>
         </is>
       </c>
     </row>
     <row r="254" ht="40" customHeight="1">
       <c r="A254" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.warm.polite.shy[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.fresh.polite.shy[1]</t>
         </is>
       </c>
       <c r="B254" t="inlineStr" s="2">
@@ -8438,7 +8460,7 @@
       </c>
       <c r="D254" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.warm.polite.shy[1]</t>
+          <t xml:space="preserve">heatSelf.fresh.polite.shy[1]</t>
         </is>
       </c>
       <c r="E254" t="inlineStr" s="2">
@@ -8448,14 +8470,14 @@
       </c>
       <c r="F254" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの…できてはいるんです。ただ、残らなくて…</t>
+          <t xml:space="preserve">あ、あの…今日は体が軽くて…もっと、やれます…！</t>
         </is>
       </c>
     </row>
     <row r="255" ht="40" customHeight="1">
       <c r="A255" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.polite.shy[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.heavy.polite.shy[1]</t>
         </is>
       </c>
       <c r="B255" t="inlineStr" s="2">
@@ -8470,7 +8492,7 @@
       </c>
       <c r="D255" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.polite.shy[1]</t>
+          <t xml:space="preserve">heatSelf.heavy.polite.shy[1]</t>
         </is>
       </c>
       <c r="E255" t="inlineStr" s="2">
@@ -8480,14 +8502,14 @@
       </c>
       <c r="F255" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">す、すみません…少しだけ休ませてください…</t>
+          <t xml:space="preserve">すみません…動けてはいるんですけど…空回りしてしまって</t>
         </is>
       </c>
     </row>
     <row r="256" ht="40" customHeight="1">
       <c r="A256" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.polite.shy[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.warm.polite.shy[1]</t>
         </is>
       </c>
       <c r="B256" t="inlineStr" s="2">
@@ -8502,7 +8524,7 @@
       </c>
       <c r="D256" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.polite.shy[1]</t>
+          <t xml:space="preserve">heatSelf.warm.polite.shy[1]</t>
         </is>
       </c>
       <c r="E256" t="inlineStr" s="2">
@@ -8512,14 +8534,14 @@
       </c>
       <c r="F256" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ご、ごめんなさい…お、お世話になりました…</t>
+          <t xml:space="preserve">あの…できてはいるんです。ただ、残らなくて…</t>
         </is>
       </c>
     </row>
     <row r="257" ht="40" customHeight="1">
       <c r="A257" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.polite.shy[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.polite.shy[1]</t>
         </is>
       </c>
       <c r="B257" t="inlineStr" s="2">
@@ -8534,7 +8556,7 @@
       </c>
       <c r="D257" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreeting.polite.shy[1]</t>
+          <t xml:space="preserve">injury.polite.shy[1]</t>
         </is>
       </c>
       <c r="E257" t="inlineStr" s="2">
@@ -8544,14 +8566,14 @@
       </c>
       <c r="F257" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、あの…短い間ではございますが…よろしくお願いいたします…</t>
+          <t xml:space="preserve">す、すみません…少しだけ休ませてください…</t>
         </is>
       </c>
     </row>
     <row r="258" ht="40" customHeight="1">
       <c r="A258" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.polite.shy[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.polite.shy[1]</t>
         </is>
       </c>
       <c r="B258" t="inlineStr" s="2">
@@ -8566,7 +8588,7 @@
       </c>
       <c r="D258" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">scoutGreeting.polite.shy[1]</t>
+          <t xml:space="preserve">release.polite.shy[1]</t>
         </is>
       </c>
       <c r="E258" t="inlineStr" s="2">
@@ -8576,14 +8598,14 @@
       </c>
       <c r="F258" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、あの…お声がけ、光栄です…！</t>
+          <t xml:space="preserve">ご、ごめんなさい…お、お世話になりました…</t>
         </is>
       </c>
     </row>
     <row r="259" ht="40" customHeight="1">
       <c r="A259" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.polite.shy[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.polite.shy[1]</t>
         </is>
       </c>
       <c r="B259" t="inlineStr" s="2">
@@ -8598,7 +8620,7 @@
       </c>
       <c r="D259" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleChallengeLoss.polite.shy[1]</t>
+          <t xml:space="preserve">rentalGreeting.polite.shy[1]</t>
         </is>
       </c>
       <c r="E259" t="inlineStr" s="2">
@@ -8608,14 +8630,14 @@
       </c>
       <c r="F259" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…申し訳ありません…でも…諦めたくないんです…</t>
+          <t xml:space="preserve">あ、あの…短い間ではございますが…よろしくお願いいたします…</t>
         </is>
       </c>
     </row>
     <row r="260" ht="40" customHeight="1">
       <c r="A260" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.polite.shy[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.polite.shy[1]</t>
         </is>
       </c>
       <c r="B260" t="inlineStr" s="2">
@@ -8630,7 +8652,7 @@
       </c>
       <c r="D260" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleDefense.polite.shy[1]</t>
+          <t xml:space="preserve">scoutGreeting.polite.shy[1]</t>
         </is>
       </c>
       <c r="E260" t="inlineStr" s="2">
@@ -8640,14 +8662,14 @@
       </c>
       <c r="F260" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よ、よかった…守れました…（ほっとしている）</t>
+          <t xml:space="preserve">あ、あの…お声がけ、光栄です…！</t>
         </is>
       </c>
     </row>
     <row r="261" ht="40" customHeight="1">
       <c r="A261" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.polite.shy[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.polite.shy[1]</t>
         </is>
       </c>
       <c r="B261" t="inlineStr" s="2">
@@ -8662,7 +8684,7 @@
       </c>
       <c r="D261" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleLoss.polite.shy[1]</t>
+          <t xml:space="preserve">titleChallengeLoss.polite.shy[1]</t>
         </is>
       </c>
       <c r="E261" t="inlineStr" s="2">
@@ -8672,14 +8694,14 @@
       </c>
       <c r="F261" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…申し訳ありません…ベルト…守れませんでした…</t>
+          <t xml:space="preserve">…申し訳ありません…でも…諦めたくないんです…</t>
         </is>
       </c>
     </row>
     <row r="262" ht="40" customHeight="1">
       <c r="A262" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.polite.shy[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.polite.shy[1]</t>
         </is>
       </c>
       <c r="B262" t="inlineStr" s="2">
@@ -8694,7 +8716,7 @@
       </c>
       <c r="D262" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.polite.shy[1]</t>
+          <t xml:space="preserve">titleDefense.polite.shy[1]</t>
         </is>
       </c>
       <c r="E262" t="inlineStr" s="2">
@@ -8704,14 +8726,14 @@
       </c>
       <c r="F262" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">え…わ、私が…チャンピオン、ですか…？ 夢のようです…</t>
+          <t xml:space="preserve">よ、よかった…守れました…（ほっとしている）</t>
         </is>
       </c>
     </row>
     <row r="263" ht="40" customHeight="1">
       <c r="A263" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.polite.shy[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.polite.shy[1]</t>
         </is>
       </c>
       <c r="B263" t="inlineStr" s="2">
@@ -8721,12 +8743,12 @@
       </c>
       <c r="C263" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D263" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.shy[1]</t>
+          <t xml:space="preserve">titleLoss.polite.shy[1]</t>
         </is>
       </c>
       <c r="E263" t="inlineStr" s="2">
@@ -8736,14 +8758,14 @@
       </c>
       <c r="F263" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ご、ごめんなさい…お、お世話になりました…</t>
+          <t xml:space="preserve">…申し訳ありません…ベルト…守れませんでした…</t>
         </is>
       </c>
     </row>
     <row r="264" ht="40" customHeight="1">
       <c r="A264" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.polite.shy[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.polite.shy[1]</t>
         </is>
       </c>
       <c r="B264" t="inlineStr" s="2">
@@ -8753,12 +8775,12 @@
       </c>
       <c r="C264" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D264" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.shy[1]</t>
+          <t xml:space="preserve">titleWin.polite.shy[1]</t>
         </is>
       </c>
       <c r="E264" t="inlineStr" s="2">
@@ -8768,14 +8790,14 @@
       </c>
       <c r="F264" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、あの…短い間ではございますが…よろしくお願いいたします…</t>
+          <t xml:space="preserve">え…わ、わたしが…チャンピオン、ですか…？ 夢のようです…</t>
         </is>
       </c>
     </row>
     <row r="265" ht="40" customHeight="1">
       <c r="A265" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.polite.shy[1]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.polite.shy[1]</t>
         </is>
       </c>
       <c r="B265" t="inlineStr" s="2">
@@ -8785,7 +8807,7 @@
       </c>
       <c r="C265" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D265" t="inlineStr" s="12">
@@ -8800,14 +8822,14 @@
       </c>
       <c r="F265" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…申し訳ありません…でも…諦めたくないんです…</t>
+          <t xml:space="preserve">ご、ごめんなさい…お、お世話になりました…</t>
         </is>
       </c>
     </row>
     <row r="266" ht="40" customHeight="1">
       <c r="A266" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.polite.shy[1]</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.polite.shy[1]</t>
         </is>
       </c>
       <c r="B266" t="inlineStr" s="2">
@@ -8817,7 +8839,7 @@
       </c>
       <c r="C266" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
         </is>
       </c>
       <c r="D266" t="inlineStr" s="12">
@@ -8832,14 +8854,14 @@
       </c>
       <c r="F266" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よ、よかった…守れました…（ほっとしている）</t>
+          <t xml:space="preserve">あ、あの…短い間ではございますが…よろしくお願いいたします…</t>
         </is>
       </c>
     </row>
     <row r="267" ht="40" customHeight="1">
       <c r="A267" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.polite.shy[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.polite.shy[1]</t>
         </is>
       </c>
       <c r="B267" t="inlineStr" s="2">
@@ -8849,7 +8871,7 @@
       </c>
       <c r="C267" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D267" t="inlineStr" s="12">
@@ -8864,14 +8886,14 @@
       </c>
       <c r="F267" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…申し訳ありません…ベルト…守れませんでした…</t>
+          <t xml:space="preserve">…申し訳ありません…でも…諦めたくないんです…</t>
         </is>
       </c>
     </row>
     <row r="268" ht="40" customHeight="1">
       <c r="A268" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.polite.shy[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.polite.shy[1]</t>
         </is>
       </c>
       <c r="B268" t="inlineStr" s="2">
@@ -8881,7 +8903,7 @@
       </c>
       <c r="C268" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
         </is>
       </c>
       <c r="D268" t="inlineStr" s="12">
@@ -8896,14 +8918,14 @@
       </c>
       <c r="F268" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">え…わ、私が…チャンピオン、ですか…？ 夢のようです…</t>
+          <t xml:space="preserve">よ、よかった…守れました…（ほっとしている）</t>
         </is>
       </c>
     </row>
     <row r="269" ht="40" customHeight="1">
       <c r="A269" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.shy.polite[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.polite.shy[1]</t>
         </is>
       </c>
       <c r="B269" t="inlineStr" s="2">
@@ -8913,29 +8935,29 @@
       </c>
       <c r="C269" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D269" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_39_down.shy.polite[1]</t>
+          <t xml:space="preserve">polite.shy[1]</t>
         </is>
       </c>
       <c r="E269" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F269" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…もう…同じ部屋にいるだけで…苦しいんです…</t>
+          <t xml:space="preserve">…申し訳ありません…ベルト…守れませんでした…</t>
         </is>
       </c>
     </row>
     <row r="270" ht="40" customHeight="1">
       <c r="A270" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.shy.polite[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.polite.shy[1]</t>
         </is>
       </c>
       <c r="B270" t="inlineStr" s="2">
@@ -8945,29 +8967,29 @@
       </c>
       <c r="C270" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
         </is>
       </c>
       <c r="D270" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.shy.polite[1]</t>
+          <t xml:space="preserve">polite.shy[1]</t>
         </is>
       </c>
       <c r="E270" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F270" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最近…目を合わせるのが怖くて…私、何かしてしまったんでしょうか…</t>
+          <t xml:space="preserve">え…わ、わたしが…チャンピオン、ですか…？ 夢のようです…</t>
         </is>
       </c>
     </row>
     <row r="271" ht="40" customHeight="1">
       <c r="A271" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.shy.polite[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.shy.polite[1]</t>
         </is>
       </c>
       <c r="B271" t="inlineStr" s="2">
@@ -8982,7 +9004,7 @@
       </c>
       <c r="D271" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.shy.polite[2]</t>
+          <t xml:space="preserve">bond_39_down.shy.polite[1]</t>
         </is>
       </c>
       <c r="E271" t="inlineStr" s="2">
@@ -8992,14 +9014,14 @@
       </c>
       <c r="F271" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの方の態度が…前と違うんです…私のせい…ですよね…</t>
+          <t xml:space="preserve">…もう…同じ部屋にいるだけで…苦しいんです…</t>
         </is>
       </c>
     </row>
     <row r="272" ht="40" customHeight="1">
       <c r="A272" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.shy.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.shy.polite[1]</t>
         </is>
       </c>
       <c r="B272" t="inlineStr" s="2">
@@ -9014,7 +9036,7 @@
       </c>
       <c r="D272" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_60_up.shy.polite[1]</t>
+          <t xml:space="preserve">bond_59_down.shy.polite[1]</t>
         </is>
       </c>
       <c r="E272" t="inlineStr" s="2">
@@ -9024,14 +9046,14 @@
       </c>
       <c r="F272" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一緒にいると…少しだけ自分に自信が持てるんです…</t>
+          <t xml:space="preserve">最近…目を合わせるのが怖くて…わたし、何かしてしまったんでしょうか…</t>
         </is>
       </c>
     </row>
     <row r="273" ht="40" customHeight="1">
       <c r="A273" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.shy.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.shy.polite[2]</t>
         </is>
       </c>
       <c r="B273" t="inlineStr" s="2">
@@ -9046,7 +9068,7 @@
       </c>
       <c r="D273" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_80_up.shy.polite[1]</t>
+          <t xml:space="preserve">bond_59_down.shy.polite[2]</t>
         </is>
       </c>
       <c r="E273" t="inlineStr" s="2">
@@ -9056,14 +9078,14 @@
       </c>
       <c r="F273" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの方がいなければ…私、とっくに駄目になっていたと思います…</t>
+          <t xml:space="preserve">あの方の態度が…前と違うんです…わたしのせい…ですよね…</t>
         </is>
       </c>
     </row>
     <row r="274" ht="40" customHeight="1">
       <c r="A274" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.shy.polite[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.shy.polite[1]</t>
         </is>
       </c>
       <c r="B274" t="inlineStr" s="2">
@@ -9078,7 +9100,7 @@
       </c>
       <c r="D274" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_80_up.shy.polite[2]</t>
+          <t xml:space="preserve">bond_60_up.shy.polite[1]</t>
         </is>
       </c>
       <c r="E274" t="inlineStr" s="2">
@@ -9088,14 +9110,14 @@
       </c>
       <c r="F274" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">隣にいてくださるだけで…なんでも頑張れる気がするんです…</t>
+          <t xml:space="preserve">一緒にいると…少しだけ自分に自信が持てるんです…</t>
         </is>
       </c>
     </row>
     <row r="275" ht="40" customHeight="1">
       <c r="A275" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.shy.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.shy.polite[1]</t>
         </is>
       </c>
       <c r="B275" t="inlineStr" s="2">
@@ -9110,7 +9132,7 @@
       </c>
       <c r="D275" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.shy.polite[1]</t>
+          <t xml:space="preserve">bond_80_up.shy.polite[1]</t>
         </is>
       </c>
       <c r="E275" t="inlineStr" s="2">
@@ -9120,14 +9142,14 @@
       </c>
       <c r="F275" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最近…あの方のこと、前ほど気にならなくなった…かもしれません…</t>
+          <t xml:space="preserve">あの方がいなければ…わたし、とっくに駄目になっていたと思います…</t>
         </is>
       </c>
     </row>
     <row r="276" ht="40" customHeight="1">
       <c r="A276" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.shy.polite[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.shy.polite[2]</t>
         </is>
       </c>
       <c r="B276" t="inlineStr" s="2">
@@ -9142,7 +9164,7 @@
       </c>
       <c r="D276" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.shy.polite[2]</t>
+          <t xml:space="preserve">bond_80_up.shy.polite[2]</t>
         </is>
       </c>
       <c r="E276" t="inlineStr" s="2">
@@ -9152,14 +9174,14 @@
       </c>
       <c r="F276" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの頃の張りつめた感じ…もうないんでしょうか…</t>
+          <t xml:space="preserve">隣にいてくださるだけで…なんでも頑張れる気がするんです…</t>
         </is>
       </c>
     </row>
     <row r="277" ht="40" customHeight="1">
       <c r="A277" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.shy.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.shy.polite[1]</t>
         </is>
       </c>
       <c r="B277" t="inlineStr" s="2">
@@ -9174,7 +9196,7 @@
       </c>
       <c r="D277" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_30_up.shy.polite[1]</t>
+          <t xml:space="preserve">rivalry_29_down.shy.polite[1]</t>
         </is>
       </c>
       <c r="E277" t="inlineStr" s="2">
@@ -9184,14 +9206,14 @@
       </c>
       <c r="F277" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの方のことを考えると…胸が締めつけられて…負けたくないんです…</t>
+          <t xml:space="preserve">最近…あの方のこと、前ほど気にならなくなった…かもしれません…</t>
         </is>
       </c>
     </row>
     <row r="278" ht="40" customHeight="1">
       <c r="A278" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.shy.polite[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.shy.polite[2]</t>
         </is>
       </c>
       <c r="B278" t="inlineStr" s="2">
@@ -9206,7 +9228,7 @@
       </c>
       <c r="D278" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_30_up.shy.polite[2]</t>
+          <t xml:space="preserve">rivalry_29_down.shy.polite[2]</t>
         </is>
       </c>
       <c r="E278" t="inlineStr" s="2">
@@ -9216,14 +9238,14 @@
       </c>
       <c r="F278" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">練習しているのを見かけると…私も走り出したくなります…</t>
+          <t xml:space="preserve">あの頃の張りつめた感じ…もうないんでしょうか…</t>
         </is>
       </c>
     </row>
     <row r="279" ht="40" customHeight="1">
       <c r="A279" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.shy.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.shy.polite[1]</t>
         </is>
       </c>
       <c r="B279" t="inlineStr" s="2">
@@ -9238,7 +9260,7 @@
       </c>
       <c r="D279" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_50_up.shy.polite[1]</t>
+          <t xml:space="preserve">rivalry_30_up.shy.polite[1]</t>
         </is>
       </c>
       <c r="E279" t="inlineStr" s="2">
@@ -9248,14 +9270,14 @@
       </c>
       <c r="F279" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの方にだけは…絶対に負けたくありません…今はそれだけです…</t>
+          <t xml:space="preserve">あの方のことを考えると…胸が締めつけられて…負けたくないんです…</t>
         </is>
       </c>
     </row>
     <row r="280" ht="40" customHeight="1">
       <c r="A280" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.shy.polite[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.shy.polite[2]</t>
         </is>
       </c>
       <c r="B280" t="inlineStr" s="2">
@@ -9270,7 +9292,7 @@
       </c>
       <c r="D280" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_50_up.shy.polite[2]</t>
+          <t xml:space="preserve">rivalry_30_up.shy.polite[2]</t>
         </is>
       </c>
       <c r="E280" t="inlineStr" s="2">
@@ -9280,14 +9302,14 @@
       </c>
       <c r="F280" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">怖いです…けれど、逃げたらもっと後悔します…だから…</t>
+          <t xml:space="preserve">練習しているのを見かけると…わたしも走り出したくなります…</t>
         </is>
       </c>
     </row>
     <row r="281" ht="40" customHeight="1">
       <c r="A281" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.shy.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.shy.polite[1]</t>
         </is>
       </c>
       <c r="B281" t="inlineStr" s="2">
@@ -9302,7 +9324,7 @@
       </c>
       <c r="D281" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.shy.polite[1]</t>
+          <t xml:space="preserve">rivalry_50_up.shy.polite[1]</t>
         </is>
       </c>
       <c r="E281" t="inlineStr" s="2">
@@ -9312,14 +9334,14 @@
       </c>
       <c r="F281" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの方がいなければ…今の私はいません。それだけは…わかるんです…</t>
+          <t xml:space="preserve">あの方にだけは…絶対に負けたくありません…今はそれだけです…</t>
         </is>
       </c>
     </row>
     <row r="282" ht="40" customHeight="1">
       <c r="A282" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.shy.polite[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.shy.polite[2]</t>
         </is>
       </c>
       <c r="B282" t="inlineStr" s="2">
@@ -9334,7 +9356,7 @@
       </c>
       <c r="D282" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.shy.polite[2]</t>
+          <t xml:space="preserve">rivalry_50_up.shy.polite[2]</t>
         </is>
       </c>
       <c r="E282" t="inlineStr" s="2">
@@ -9344,14 +9366,14 @@
       </c>
       <c r="F282" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">逃げたい…でも…あの方からだけは逃げてはいけない…</t>
+          <t xml:space="preserve">怖いです…けれど、逃げたらもっと後悔します…だから…</t>
         </is>
       </c>
     </row>
     <row r="283" ht="40" customHeight="1">
       <c r="A283" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.shy.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.shy.polite[1]</t>
         </is>
       </c>
       <c r="B283" t="inlineStr" s="2">
@@ -9366,7 +9388,7 @@
       </c>
       <c r="D283" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_above_75.shy.polite[1]</t>
+          <t xml:space="preserve">rivalry_70_up.shy.polite[1]</t>
         </is>
       </c>
       <c r="E283" t="inlineStr" s="2">
@@ -9376,14 +9398,14 @@
       </c>
       <c r="F283" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここにいてもいいんだと…最近ようやく思えるようになったんです…</t>
+          <t xml:space="preserve">あの方がいなければ…今のわたしはいません。それだけは…わかるんです…</t>
         </is>
       </c>
     </row>
     <row r="284" ht="40" customHeight="1">
       <c r="A284" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.shy.polite[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.shy.polite[2]</t>
         </is>
       </c>
       <c r="B284" t="inlineStr" s="2">
@@ -9398,7 +9420,7 @@
       </c>
       <c r="D284" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_above_75.shy.polite[2]</t>
+          <t xml:space="preserve">rivalry_70_up.shy.polite[2]</t>
         </is>
       </c>
       <c r="E284" t="inlineStr" s="2">
@@ -9408,14 +9430,14 @@
       </c>
       <c r="F284" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この団体に来られて…本当によかったです…心からそう思います…</t>
+          <t xml:space="preserve">逃げたい…でも…あの方からだけは逃げてはいけない…</t>
         </is>
       </c>
     </row>
     <row r="285" ht="40" customHeight="1">
       <c r="A285" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.shy.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.shy.polite[1]</t>
         </is>
       </c>
       <c r="B285" t="inlineStr" s="2">
@@ -9430,7 +9452,7 @@
       </c>
       <c r="D285" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_20.shy.polite[1]</t>
+          <t xml:space="preserve">trust_above_75.shy.polite[1]</t>
         </is>
       </c>
       <c r="E285" t="inlineStr" s="2">
@@ -9440,14 +9462,14 @@
       </c>
       <c r="F285" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…もう…無理です…ここにいてはいけない気がするんです……</t>
+          <t xml:space="preserve">ここにいてもいいんだと…最近ようやく思えるようになったんです…</t>
         </is>
       </c>
     </row>
     <row r="286" ht="40" customHeight="1">
       <c r="A286" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.shy.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.shy.polite[2]</t>
         </is>
       </c>
       <c r="B286" t="inlineStr" s="2">
@@ -9462,7 +9484,7 @@
       </c>
       <c r="D286" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_35.shy.polite[1]</t>
+          <t xml:space="preserve">trust_above_75.shy.polite[2]</t>
         </is>
       </c>
       <c r="E286" t="inlineStr" s="2">
@@ -9472,14 +9494,14 @@
       </c>
       <c r="F286" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ここに私の居場所なんて…あるんでしょうか……</t>
+          <t xml:space="preserve">この団体に来られて…本当によかったです…心からそう思います…</t>
         </is>
       </c>
     </row>
     <row r="287" ht="40" customHeight="1">
       <c r="A287" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.goodLoss.polite.shy[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.shy.polite[1]</t>
         </is>
       </c>
       <c r="B287" t="inlineStr" s="2">
@@ -9489,12 +9511,12 @@
       </c>
       <c r="C287" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D287" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.goodLoss.polite.shy[1]</t>
+          <t xml:space="preserve">trust_below_20.shy.polite[1]</t>
         </is>
       </c>
       <c r="E287" t="inlineStr" s="2">
@@ -9504,14 +9526,14 @@
       </c>
       <c r="F287" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けてしまいましたが…悔いはありません…</t>
+          <t xml:space="preserve">…もう…無理です…ここにいてはいけない気がするんです……</t>
         </is>
       </c>
     </row>
     <row r="288" ht="40" customHeight="1">
       <c r="A288" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.goodLoss.polite.shy[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.shy.polite[1]</t>
         </is>
       </c>
       <c r="B288" t="inlineStr" s="2">
@@ -9521,12 +9543,12 @@
       </c>
       <c r="C288" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D288" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.goodLoss.polite.shy[2]</t>
+          <t xml:space="preserve">trust_below_35.shy.polite[1]</t>
         </is>
       </c>
       <c r="E288" t="inlineStr" s="2">
@@ -9536,14 +9558,14 @@
       </c>
       <c r="F288" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">全力は、出せたと思います…</t>
+          <t xml:space="preserve">…ここにわたしの居場所なんて…あるんでしょうか……</t>
         </is>
       </c>
     </row>
     <row r="289" ht="40" customHeight="1">
       <c r="A289" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin.polite.shy[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.goodLoss.polite.shy[1]</t>
         </is>
       </c>
       <c r="B289" t="inlineStr" s="2">
@@ -9558,7 +9580,7 @@
       </c>
       <c r="D289" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.greatWin.polite.shy[1]</t>
+          <t xml:space="preserve">GL-01.goodLoss.polite.shy[1]</t>
         </is>
       </c>
       <c r="E289" t="inlineStr" s="2">
@@ -9568,14 +9590,14 @@
       </c>
       <c r="F289" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こ、こんな大きな勝利…信じられません…ありがとうございます…</t>
+          <t xml:space="preserve">負けてしまいましたが…悔いはありません…</t>
         </is>
       </c>
     </row>
     <row r="290" ht="40" customHeight="1">
       <c r="A290" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin.polite.shy[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.goodLoss.polite.shy[2]</t>
         </is>
       </c>
       <c r="B290" t="inlineStr" s="2">
@@ -9590,7 +9612,7 @@
       </c>
       <c r="D290" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.greatWin.polite.shy[2]</t>
+          <t xml:space="preserve">GL-01.goodLoss.polite.shy[2]</t>
         </is>
       </c>
       <c r="E290" t="inlineStr" s="2">
@@ -9600,14 +9622,14 @@
       </c>
       <c r="F290" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こんな日が、来るなんて…夢みたいです…</t>
+          <t xml:space="preserve">全力は、出せたと思います…</t>
         </is>
       </c>
     </row>
     <row r="291" ht="40" customHeight="1">
       <c r="A291" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.polite.shy[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin.polite.shy[1]</t>
         </is>
       </c>
       <c r="B291" t="inlineStr" s="2">
@@ -9622,7 +9644,7 @@
       </c>
       <c r="D291" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.loss.polite.shy[1]</t>
+          <t xml:space="preserve">GL-01.greatWin.polite.shy[1]</t>
         </is>
       </c>
       <c r="E291" t="inlineStr" s="2">
@@ -9632,14 +9654,14 @@
       </c>
       <c r="F291" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ま、負けてしまいました…ご、ごめんなさい…</t>
+          <t xml:space="preserve">こ、こんな大きな勝利…信じられません…ありがとうございます…</t>
         </is>
       </c>
     </row>
     <row r="292" ht="40" customHeight="1">
       <c r="A292" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.polite.shy[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin.polite.shy[2]</t>
         </is>
       </c>
       <c r="B292" t="inlineStr" s="2">
@@ -9654,7 +9676,7 @@
       </c>
       <c r="D292" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.loss.polite.shy[2]</t>
+          <t xml:space="preserve">GL-01.greatWin.polite.shy[2]</t>
         </is>
       </c>
       <c r="E292" t="inlineStr" s="2">
@@ -9664,14 +9686,14 @@
       </c>
       <c r="F292" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次こそは…勝ちたいです…</t>
+          <t xml:space="preserve">こんな日が、来るなんて…夢みたいです…</t>
         </is>
       </c>
     </row>
     <row r="293" ht="40" customHeight="1">
       <c r="A293" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.polite.shy[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.polite.shy[1]</t>
         </is>
       </c>
       <c r="B293" t="inlineStr" s="2">
@@ -9686,7 +9708,7 @@
       </c>
       <c r="D293" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.win.polite.shy[1]</t>
+          <t xml:space="preserve">GL-01.loss.polite.shy[1]</t>
         </is>
       </c>
       <c r="E293" t="inlineStr" s="2">
@@ -9696,14 +9718,14 @@
       </c>
       <c r="F293" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">か、勝てました…応援、ありがとうございます…</t>
+          <t xml:space="preserve">ま、負けてしまいました…ご、ごめんなさい…</t>
         </is>
       </c>
     </row>
     <row r="294" ht="40" customHeight="1">
       <c r="A294" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.polite.shy[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.polite.shy[2]</t>
         </is>
       </c>
       <c r="B294" t="inlineStr" s="2">
@@ -9718,7 +9740,7 @@
       </c>
       <c r="D294" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.win.polite.shy[2]</t>
+          <t xml:space="preserve">GL-01.loss.polite.shy[2]</t>
         </is>
       </c>
       <c r="E294" t="inlineStr" s="2">
@@ -9728,14 +9750,14 @@
       </c>
       <c r="F294" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今日は…良い試合が、できたと思います…</t>
+          <t xml:space="preserve">次こそは…勝ちたいです…</t>
         </is>
       </c>
     </row>
     <row r="295" ht="40" customHeight="1">
       <c r="A295" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.polite.shy[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.polite.shy[1]</t>
         </is>
       </c>
       <c r="B295" t="inlineStr" s="2">
@@ -9750,7 +9772,7 @@
       </c>
       <c r="D295" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-02.polite.shy[1]</t>
+          <t xml:space="preserve">GL-01.win.polite.shy[1]</t>
         </is>
       </c>
       <c r="E295" t="inlineStr" s="2">
@@ -9760,14 +9782,14 @@
       </c>
       <c r="F295" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、あの…今日は、よろしくお願いいたします…</t>
+          <t xml:space="preserve">か、勝てました…応援、ありがとうございます…</t>
         </is>
       </c>
     </row>
     <row r="296" ht="40" customHeight="1">
       <c r="A296" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.polite.shy[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.polite.shy[2]</t>
         </is>
       </c>
       <c r="B296" t="inlineStr" s="2">
@@ -9782,7 +9804,7 @@
       </c>
       <c r="D296" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-02.polite.shy[2]</t>
+          <t xml:space="preserve">GL-01.win.polite.shy[2]</t>
         </is>
       </c>
       <c r="E296" t="inlineStr" s="2">
@@ -9792,14 +9814,14 @@
       </c>
       <c r="F296" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">頑張ります…</t>
+          <t xml:space="preserve">今日は…良い試合が、できたと思います…</t>
         </is>
       </c>
     </row>
     <row r="297" ht="40" customHeight="1">
       <c r="A297" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.down.polite.shy[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.polite.shy[1]</t>
         </is>
       </c>
       <c r="B297" t="inlineStr" s="2">
@@ -9814,7 +9836,7 @@
       </c>
       <c r="D297" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-03.down.polite.shy[1]</t>
+          <t xml:space="preserve">GL-02.polite.shy[1]</t>
         </is>
       </c>
       <c r="E297" t="inlineStr" s="2">
@@ -9824,14 +9846,14 @@
       </c>
       <c r="F297" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">う、うまくいきません…どうしたら…</t>
+          <t xml:space="preserve">あ、あの…今日は、よろしくお願いいたします…</t>
         </is>
       </c>
     </row>
     <row r="298" ht="40" customHeight="1">
       <c r="A298" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.up.polite.shy[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.polite.shy[2]</t>
         </is>
       </c>
       <c r="B298" t="inlineStr" s="2">
@@ -9846,7 +9868,7 @@
       </c>
       <c r="D298" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-03.up.polite.shy[1]</t>
+          <t xml:space="preserve">GL-02.polite.shy[2]</t>
         </is>
       </c>
       <c r="E298" t="inlineStr" s="2">
@@ -9856,14 +9878,14 @@
       </c>
       <c r="F298" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">調子が…良い気がします…</t>
+          <t xml:space="preserve">頑張ります…</t>
         </is>
       </c>
     </row>
     <row r="299" ht="40" customHeight="1">
       <c r="A299" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04.polite.shy[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.down.polite.shy[1]</t>
         </is>
       </c>
       <c r="B299" t="inlineStr" s="2">
@@ -9878,7 +9900,7 @@
       </c>
       <c r="D299" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-04.polite.shy[1]</t>
+          <t xml:space="preserve">GL-03.down.polite.shy[1]</t>
         </is>
       </c>
       <c r="E299" t="inlineStr" s="2">
@@ -9888,14 +9910,14 @@
       </c>
       <c r="F299" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">練習…させていただきます…</t>
+          <t xml:space="preserve">う、うまくいきません…どうしたら…</t>
         </is>
       </c>
     </row>
     <row r="300" ht="40" customHeight="1">
       <c r="A300" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04.polite.shy[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.up.polite.shy[1]</t>
         </is>
       </c>
       <c r="B300" t="inlineStr" s="2">
@@ -9910,7 +9932,7 @@
       </c>
       <c r="D300" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-04.polite.shy[2]</t>
+          <t xml:space="preserve">GL-03.up.polite.shy[1]</t>
         </is>
       </c>
       <c r="E300" t="inlineStr" s="2">
@@ -9920,14 +9942,14 @@
       </c>
       <c r="F300" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もう少し…頑張ります…</t>
+          <t xml:space="preserve">調子が…良い気がします…</t>
         </is>
       </c>
     </row>
     <row r="301" ht="40" customHeight="1">
       <c r="A301" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05.polite.shy[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04.polite.shy[1]</t>
         </is>
       </c>
       <c r="B301" t="inlineStr" s="2">
@@ -9942,7 +9964,7 @@
       </c>
       <c r="D301" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-05.polite.shy[1]</t>
+          <t xml:space="preserve">GL-04.polite.shy[1]</t>
         </is>
       </c>
       <c r="E301" t="inlineStr" s="2">
@@ -9952,14 +9974,14 @@
       </c>
       <c r="F301" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、あの…大丈夫です、心配しないでください…</t>
+          <t xml:space="preserve">練習…させていただきます…</t>
         </is>
       </c>
     </row>
     <row r="302" ht="40" customHeight="1">
       <c r="A302" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05.polite.shy[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04.polite.shy[2]</t>
         </is>
       </c>
       <c r="B302" t="inlineStr" s="2">
@@ -9974,7 +9996,7 @@
       </c>
       <c r="D302" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-05.polite.shy[2]</t>
+          <t xml:space="preserve">GL-04.polite.shy[2]</t>
         </is>
       </c>
       <c r="E302" t="inlineStr" s="2">
@@ -9984,14 +10006,14 @@
       </c>
       <c r="F302" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ご心配を、おかけして…</t>
+          <t xml:space="preserve">もう少し…頑張ります…</t>
         </is>
       </c>
     </row>
     <row r="303" ht="40" customHeight="1">
       <c r="A303" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.polite.shy[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05.polite.shy[1]</t>
         </is>
       </c>
       <c r="B303" t="inlineStr" s="2">
@@ -10006,7 +10028,7 @@
       </c>
       <c r="D303" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-06.polite.shy[1]</t>
+          <t xml:space="preserve">GL-05.polite.shy[1]</t>
         </is>
       </c>
       <c r="E303" t="inlineStr" s="2">
@@ -10016,14 +10038,14 @@
       </c>
       <c r="F303" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">みんなと…一緒だと、心強いです…</t>
+          <t xml:space="preserve">あ、あの…大丈夫です、心配しないでください…</t>
         </is>
       </c>
     </row>
     <row r="304" ht="40" customHeight="1">
       <c r="A304" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.polite.shy[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05.polite.shy[2]</t>
         </is>
       </c>
       <c r="B304" t="inlineStr" s="2">
@@ -10038,7 +10060,7 @@
       </c>
       <c r="D304" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-06.polite.shy[2]</t>
+          <t xml:space="preserve">GL-05.polite.shy[2]</t>
         </is>
       </c>
       <c r="E304" t="inlineStr" s="2">
@@ -10048,14 +10070,14 @@
       </c>
       <c r="F304" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">仲間って、いいですね…</t>
+          <t xml:space="preserve">ご心配を、おかけして…</t>
         </is>
       </c>
     </row>
     <row r="305" ht="40" customHeight="1">
       <c r="A305" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07.polite.shy[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.polite.shy[1]</t>
         </is>
       </c>
       <c r="B305" t="inlineStr" s="2">
@@ -10070,7 +10092,7 @@
       </c>
       <c r="D305" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-07.polite.shy[1]</t>
+          <t xml:space="preserve">GL-06.polite.shy[1]</t>
         </is>
       </c>
       <c r="E305" t="inlineStr" s="2">
@@ -10080,14 +10102,14 @@
       </c>
       <c r="F305" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お、お客さんがいっぱいで…き、緊張します…</t>
+          <t xml:space="preserve">みんなと…一緒だと、心強いです…</t>
         </is>
       </c>
     </row>
     <row r="306" ht="40" customHeight="1">
       <c r="A306" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07.polite.shy[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.polite.shy[2]</t>
         </is>
       </c>
       <c r="B306" t="inlineStr" s="2">
@@ -10102,7 +10124,7 @@
       </c>
       <c r="D306" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-07.polite.shy[2]</t>
+          <t xml:space="preserve">GL-06.polite.shy[2]</t>
         </is>
       </c>
       <c r="E306" t="inlineStr" s="2">
@@ -10112,14 +10134,14 @@
       </c>
       <c r="F306" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">がんばります…</t>
+          <t xml:space="preserve">仲間って、いいですね…</t>
         </is>
       </c>
     </row>
     <row r="307" ht="40" customHeight="1">
       <c r="A307" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.polite.shy[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07.polite.shy[1]</t>
         </is>
       </c>
       <c r="B307" t="inlineStr" s="2">
@@ -10134,7 +10156,7 @@
       </c>
       <c r="D307" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-08.polite.shy[1]</t>
+          <t xml:space="preserve">GL-07.polite.shy[1]</t>
         </is>
       </c>
       <c r="E307" t="inlineStr" s="2">
@@ -10144,14 +10166,14 @@
       </c>
       <c r="F307" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、あの…体調は、大丈夫です…</t>
+          <t xml:space="preserve">お、お客さんがいっぱいで…き、緊張します…</t>
         </is>
       </c>
     </row>
     <row r="308" ht="40" customHeight="1">
       <c r="A308" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.polite.shy[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07.polite.shy[2]</t>
         </is>
       </c>
       <c r="B308" t="inlineStr" s="2">
@@ -10166,7 +10188,7 @@
       </c>
       <c r="D308" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-08.polite.shy[2]</t>
+          <t xml:space="preserve">GL-07.polite.shy[2]</t>
         </is>
       </c>
       <c r="E308" t="inlineStr" s="2">
@@ -10176,14 +10198,14 @@
       </c>
       <c r="F308" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">無理はしません…</t>
+          <t xml:space="preserve">がんばります…</t>
         </is>
       </c>
     </row>
     <row r="309" ht="40" customHeight="1">
       <c r="A309" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.polite.shy[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.polite.shy[1]</t>
         </is>
       </c>
       <c r="B309" t="inlineStr" s="2">
@@ -10198,7 +10220,7 @@
       </c>
       <c r="D309" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-09.polite.shy[1]</t>
+          <t xml:space="preserve">GL-08.polite.shy[1]</t>
         </is>
       </c>
       <c r="E309" t="inlineStr" s="2">
@@ -10208,14 +10230,14 @@
       </c>
       <c r="F309" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次の試合…が、頑張ります…</t>
+          <t xml:space="preserve">あ、あの…体調は、大丈夫です…</t>
         </is>
       </c>
     </row>
     <row r="310" ht="40" customHeight="1">
       <c r="A310" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.polite.shy[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.polite.shy[2]</t>
         </is>
       </c>
       <c r="B310" t="inlineStr" s="2">
@@ -10230,7 +10252,7 @@
       </c>
       <c r="D310" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-09.polite.shy[2]</t>
+          <t xml:space="preserve">GL-08.polite.shy[2]</t>
         </is>
       </c>
       <c r="E310" t="inlineStr" s="2">
@@ -10240,14 +10262,14 @@
       </c>
       <c r="F310" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">しっかり、準備します…</t>
+          <t xml:space="preserve">無理はしません…</t>
         </is>
       </c>
     </row>
     <row r="311" ht="40" customHeight="1">
       <c r="A311" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.polite.shy[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.polite.shy[1]</t>
         </is>
       </c>
       <c r="B311" t="inlineStr" s="2">
@@ -10262,7 +10284,7 @@
       </c>
       <c r="D311" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-10.polite.shy[1]</t>
+          <t xml:space="preserve">GL-09.polite.shy[1]</t>
         </is>
       </c>
       <c r="E311" t="inlineStr" s="2">
@@ -10272,14 +10294,14 @@
       </c>
       <c r="F311" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、あの…ありがとうございます…</t>
+          <t xml:space="preserve">次の試合…が、頑張ります…</t>
         </is>
       </c>
     </row>
     <row r="312" ht="40" customHeight="1">
       <c r="A312" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.polite.shy[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.polite.shy[2]</t>
         </is>
       </c>
       <c r="B312" t="inlineStr" s="2">
@@ -10294,7 +10316,7 @@
       </c>
       <c r="D312" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-10.polite.shy[2]</t>
+          <t xml:space="preserve">GL-09.polite.shy[2]</t>
         </is>
       </c>
       <c r="E312" t="inlineStr" s="2">
@@ -10304,14 +10326,14 @@
       </c>
       <c r="F312" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">感謝、しています…</t>
+          <t xml:space="preserve">しっかり、準備します…</t>
         </is>
       </c>
     </row>
     <row r="313" ht="40" customHeight="1">
       <c r="A313" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.polite.shy[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.polite.shy[1]</t>
         </is>
       </c>
       <c r="B313" t="inlineStr" s="2">
@@ -10321,12 +10343,12 @@
       </c>
       <c r="C313" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D313" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.shy[1]</t>
+          <t xml:space="preserve">GL-10.polite.shy[1]</t>
         </is>
       </c>
       <c r="E313" t="inlineStr" s="2">
@@ -10336,14 +10358,14 @@
       </c>
       <c r="F313" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">良い流れが…止まってしまいました…で、でも、また頑張ります…</t>
+          <t xml:space="preserve">あ、あの…ありがとうございます…</t>
         </is>
       </c>
     </row>
     <row r="314" ht="40" customHeight="1">
       <c r="A314" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.polite.shy[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.polite.shy[2]</t>
         </is>
       </c>
       <c r="B314" t="inlineStr" s="2">
@@ -10353,29 +10375,29 @@
       </c>
       <c r="C314" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D314" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.polite.shy[1]</t>
+          <t xml:space="preserve">GL-10.polite.shy[2]</t>
         </is>
       </c>
       <c r="E314" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F314" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">け、決勝…。信じられないけど…最後まで、立たせてください…</t>
+          <t xml:space="preserve">感謝、しています…</t>
         </is>
       </c>
     </row>
     <row r="315" ht="40" customHeight="1">
       <c r="A315" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.polite.shy[2]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.polite.shy[1]</t>
         </is>
       </c>
       <c r="B315" t="inlineStr" s="2">
@@ -10385,29 +10407,29 @@
       </c>
       <c r="C315" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
         </is>
       </c>
       <c r="D315" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.polite.shy[2]</t>
+          <t xml:space="preserve">polite.shy[1]</t>
         </is>
       </c>
       <c r="E315" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F315" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">身体は痛いです…でも、ここで退いたら、繋いでくれた分が…</t>
+          <t xml:space="preserve">良い流れが…止まってしまいました…で、でも、また頑張ります…</t>
         </is>
       </c>
     </row>
     <row r="316" ht="40" customHeight="1">
       <c r="A316" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.polite.shy[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.polite.shy[1]</t>
         </is>
       </c>
       <c r="B316" t="inlineStr" s="2">
@@ -10422,7 +10444,7 @@
       </c>
       <c r="D316" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.polite.shy[1]</t>
+          <t xml:space="preserve">preFinal.polite.shy[1]</t>
         </is>
       </c>
       <c r="E316" t="inlineStr" s="2">
@@ -10432,14 +10454,14 @@
       </c>
       <c r="F316" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">つ、相手の方…がんばります。仲間が待ってるので、退けません…</t>
+          <t xml:space="preserve">け、決勝…。信じられないけど…最後まで、立たせてください…</t>
         </is>
       </c>
     </row>
     <row r="317" ht="40" customHeight="1">
       <c r="A317" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.polite.shy[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.polite.shy[2]</t>
         </is>
       </c>
       <c r="B317" t="inlineStr" s="2">
@@ -10454,7 +10476,7 @@
       </c>
       <c r="D317" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.polite.shy[2]</t>
+          <t xml:space="preserve">preFinal.polite.shy[2]</t>
         </is>
       </c>
       <c r="E317" t="inlineStr" s="2">
@@ -10464,14 +10486,14 @@
       </c>
       <c r="F317" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こ、怖いです…でも、ここで止まったら、みんなに申し訳なくて…</t>
+          <t xml:space="preserve">身体は痛いです…でも、ここで退いたら、繋いでくれた分が…</t>
         </is>
       </c>
     </row>
     <row r="318" ht="40" customHeight="1">
       <c r="A318" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.polite.shy[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.polite.shy[1]</t>
         </is>
       </c>
       <c r="B318" t="inlineStr" s="2">
@@ -10486,7 +10508,7 @@
       </c>
       <c r="D318" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.polite.shy[1]</t>
+          <t xml:space="preserve">preMatch.polite.shy[1]</t>
         </is>
       </c>
       <c r="E318" t="inlineStr" s="2">
@@ -10496,14 +10518,14 @@
       </c>
       <c r="F318" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">い、一人、倒せました…! はぁ…まだ、退けません…次の方、来てください…!</t>
+          <t xml:space="preserve">あ、相手の方…がんばります。仲間が待ってるので、退けません…</t>
         </is>
       </c>
     </row>
     <row r="319" ht="40" customHeight="1">
       <c r="A319" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.polite.shy[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.polite.shy[2]</t>
         </is>
       </c>
       <c r="B319" t="inlineStr" s="2">
@@ -10518,7 +10540,7 @@
       </c>
       <c r="D319" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.polite.shy[2]</t>
+          <t xml:space="preserve">preMatch.polite.shy[2]</t>
         </is>
       </c>
       <c r="E319" t="inlineStr" s="2">
@@ -10528,14 +10550,14 @@
       </c>
       <c r="F319" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">怖いです…でも、まだ立ってます。仲間に繋ぐまで、ここは…次、どうぞ…</t>
+          <t xml:space="preserve">こ、怖いです…でも、ここで止まったら、みんなに申し訳なくて…</t>
         </is>
       </c>
     </row>
     <row r="320" ht="40" customHeight="1">
       <c r="A320" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.polite.shy[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.polite.shy[1]</t>
         </is>
       </c>
       <c r="B320" t="inlineStr" s="2">
@@ -10545,12 +10567,12 @@
       </c>
       <c r="C320" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D320" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.polite.shy[1]</t>
+          <t xml:space="preserve">survivor.polite.shy[1]</t>
         </is>
       </c>
       <c r="E320" t="inlineStr" s="2">
@@ -10560,14 +10582,14 @@
       </c>
       <c r="F320" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わ、私がMVPなんて……二人がいてくれたから、ここまで来られたんです</t>
+          <t xml:space="preserve">い、一人、倒せました…！ はぁ…まだ、退けません…次の方、来てください…！</t>
         </is>
       </c>
     </row>
     <row r="321" ht="40" customHeight="1">
       <c r="A321" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.polite.shy[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.polite.shy[2]</t>
         </is>
       </c>
       <c r="B321" t="inlineStr" s="2">
@@ -10577,12 +10599,12 @@
       </c>
       <c r="C321" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D321" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.polite.shy[2]</t>
+          <t xml:space="preserve">survivor.polite.shy[2]</t>
         </is>
       </c>
       <c r="E321" t="inlineStr" s="2">
@@ -10592,14 +10614,14 @@
       </c>
       <c r="F321" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">三人で勝てて、本当によかったです。私は……二人に助けられてばかりで</t>
+          <t xml:space="preserve">怖いです…でも、まだ立ってます。仲間に繋ぐまで、ここは…次、どうぞ…</t>
         </is>
       </c>
     </row>
     <row r="322" ht="40" customHeight="1">
       <c r="A322" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.polite.shy[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.polite.shy[1]</t>
         </is>
       </c>
       <c r="B322" t="inlineStr" s="2">
@@ -10614,7 +10636,7 @@
       </c>
       <c r="D322" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.polite.shy[1]</t>
+          <t xml:space="preserve">champion.polite.shy[1]</t>
         </is>
       </c>
       <c r="E322" t="inlineStr" s="2">
@@ -10624,14 +10646,14 @@
       </c>
       <c r="F322" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">MVPは……嬉しいです。でも、みんなで勝ちたかったです。次こそは……</t>
+          <t xml:space="preserve">わ、わたしがMVPなんて……二人がいてくれたから、ここまで来られたんです</t>
         </is>
       </c>
     </row>
     <row r="323" ht="40" customHeight="1">
       <c r="A323" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.polite.shy[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.polite.shy[2]</t>
         </is>
       </c>
       <c r="B323" t="inlineStr" s="2">
@@ -10646,7 +10668,7 @@
       </c>
       <c r="D323" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.polite.shy[2]</t>
+          <t xml:space="preserve">champion.polite.shy[2]</t>
         </is>
       </c>
       <c r="E323" t="inlineStr" s="2">
@@ -10656,14 +10678,14 @@
       </c>
       <c r="F323" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人だけ褒められても……素直に喜べなくて。次は一緒に笑いたいです</t>
+          <t xml:space="preserve">三人で勝てて、本当によかったです。わたしは……二人に助けられてばかりで</t>
         </is>
       </c>
     </row>
     <row r="324" ht="40" customHeight="1">
       <c r="A324" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.polite.shy[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.polite.shy[1]</t>
         </is>
       </c>
       <c r="B324" t="inlineStr" s="2">
@@ -10678,7 +10700,7 @@
       </c>
       <c r="D324" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.polite.shy[1]</t>
+          <t xml:space="preserve">defiant.polite.shy[1]</t>
         </is>
       </c>
       <c r="E324" t="inlineStr" s="2">
@@ -10688,14 +10710,14 @@
       </c>
       <c r="F324" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ず、ずっと怖かったです。でも……最後まで立っていられたのは、応援のおかげです</t>
+          <t xml:space="preserve">MVPは……嬉しいです。でも、みんなで勝ちたかったです。次こそは……</t>
         </is>
       </c>
     </row>
     <row r="325" ht="40" customHeight="1">
       <c r="A325" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.polite.shy[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.polite.shy[2]</t>
         </is>
       </c>
       <c r="B325" t="inlineStr" s="2">
@@ -10710,7 +10732,7 @@
       </c>
       <c r="D325" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.polite.shy[2]</t>
+          <t xml:space="preserve">defiant.polite.shy[2]</t>
         </is>
       </c>
       <c r="E325" t="inlineStr" s="2">
@@ -10720,14 +10742,14 @@
       </c>
       <c r="F325" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">身体が震えてます。でも……逃げなかったこと、褒めてもらえますか……</t>
+          <t xml:space="preserve">一人だけ褒められても……素直に喜べなくて。次は一緒に笑いたいです</t>
         </is>
       </c>
     </row>
     <row r="326" ht="40" customHeight="1">
       <c r="A326" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.polite.shy[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.polite.shy[1]</t>
         </is>
       </c>
       <c r="B326" t="inlineStr" s="2">
@@ -10737,12 +10759,12 @@
       </c>
       <c r="C326" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D326" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.polite.shy[1]</t>
+          <t xml:space="preserve">gauntlet.polite.shy[1]</t>
         </is>
       </c>
       <c r="E326" t="inlineStr" s="2">
@@ -10752,14 +10774,14 @@
       </c>
       <c r="F326" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ゆ、優勝…ですか…？ ほ、本当に…？ あ、ありがとうございます…!</t>
+          <t xml:space="preserve">ず、ずっと怖かったです。でも……最後まで立っていられたのは、応援のおかげです</t>
         </is>
       </c>
     </row>
     <row r="327" ht="40" customHeight="1">
       <c r="A327" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.polite.shy[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.polite.shy[2]</t>
         </is>
       </c>
       <c r="B327" t="inlineStr" s="2">
@@ -10769,12 +10791,12 @@
       </c>
       <c r="C327" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D327" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.polite.shy[2]</t>
+          <t xml:space="preserve">gauntlet.polite.shy[2]</t>
         </is>
       </c>
       <c r="E327" t="inlineStr" s="2">
@@ -10784,14 +10806,14 @@
       </c>
       <c r="F327" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">夢みたいで…まだ、信じられません…</t>
+          <t xml:space="preserve">身体が震えてます。でも……逃げなかったこと、褒めてもらえますか……</t>
         </is>
       </c>
     </row>
     <row r="328" ht="40" customHeight="1">
       <c r="A328" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.polite.shy[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.polite.shy[1]</t>
         </is>
       </c>
       <c r="B328" t="inlineStr" s="2">
@@ -10806,7 +10828,7 @@
       </c>
       <c r="D328" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.polite.shy[1]</t>
+          <t xml:space="preserve">champion.polite.shy[1]</t>
         </is>
       </c>
       <c r="E328" t="inlineStr" s="2">
@@ -10816,14 +10838,14 @@
       </c>
       <c r="F328" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ま、負けてしまいました…ごめんなさい…</t>
+          <t xml:space="preserve">ゆ、優勝…ですか…？ ほ、本当に…？ あ、ありがとうございます…！</t>
         </is>
       </c>
     </row>
     <row r="329" ht="40" customHeight="1">
       <c r="A329" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.polite.shy[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.polite.shy[2]</t>
         </is>
       </c>
       <c r="B329" t="inlineStr" s="2">
@@ -10838,7 +10860,7 @@
       </c>
       <c r="D329" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.polite.shy[2]</t>
+          <t xml:space="preserve">champion.polite.shy[2]</t>
         </is>
       </c>
       <c r="E329" t="inlineStr" s="2">
@@ -10848,14 +10870,14 @@
       </c>
       <c r="F329" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もっと…強くならないと…</t>
+          <t xml:space="preserve">夢みたいで…まだ、信じられません…</t>
         </is>
       </c>
     </row>
     <row r="330" ht="40" customHeight="1">
       <c r="A330" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.polite.shy[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.polite.shy[1]</t>
         </is>
       </c>
       <c r="B330" t="inlineStr" s="2">
@@ -10870,7 +10892,7 @@
       </c>
       <c r="D330" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.polite.shy[1]</t>
+          <t xml:space="preserve">postLose.polite.shy[1]</t>
         </is>
       </c>
       <c r="E330" t="inlineStr" s="2">
@@ -10880,14 +10902,14 @@
       </c>
       <c r="F330" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">か、勝てました…次もがんばります…</t>
+          <t xml:space="preserve">ま、負けてしまいました…ごめんなさい…</t>
         </is>
       </c>
     </row>
     <row r="331" ht="40" customHeight="1">
       <c r="A331" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.polite.shy[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.polite.shy[2]</t>
         </is>
       </c>
       <c r="B331" t="inlineStr" s="2">
@@ -10902,7 +10924,7 @@
       </c>
       <c r="D331" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.polite.shy[2]</t>
+          <t xml:space="preserve">postLose.polite.shy[2]</t>
         </is>
       </c>
       <c r="E331" t="inlineStr" s="2">
@@ -10912,14 +10934,14 @@
       </c>
       <c r="F331" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一勝、できました…</t>
+          <t xml:space="preserve">もっと…強くならないと…</t>
         </is>
       </c>
     </row>
     <row r="332" ht="40" customHeight="1">
       <c r="A332" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.polite.shy[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.polite.shy[1]</t>
         </is>
       </c>
       <c r="B332" t="inlineStr" s="2">
@@ -10934,7 +10956,7 @@
       </c>
       <c r="D332" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.polite.shy[1]</t>
+          <t xml:space="preserve">postMatchWin.polite.shy[1]</t>
         </is>
       </c>
       <c r="E332" t="inlineStr" s="2">
@@ -10944,14 +10966,14 @@
       </c>
       <c r="F332" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">か、勝ち上がれました…信じられません…</t>
+          <t xml:space="preserve">か、勝てました…次もがんばります…</t>
         </is>
       </c>
     </row>
     <row r="333" ht="40" customHeight="1">
       <c r="A333" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.polite.shy[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.polite.shy[2]</t>
         </is>
       </c>
       <c r="B333" t="inlineStr" s="2">
@@ -10966,7 +10988,7 @@
       </c>
       <c r="D333" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.polite.shy[2]</t>
+          <t xml:space="preserve">postMatchWin.polite.shy[2]</t>
         </is>
       </c>
       <c r="E333" t="inlineStr" s="2">
@@ -10976,14 +10998,14 @@
       </c>
       <c r="F333" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ…続けられるんですね…</t>
+          <t xml:space="preserve">一勝、できました…</t>
         </is>
       </c>
     </row>
     <row r="334" ht="40" customHeight="1">
       <c r="A334" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.polite.shy[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.polite.shy[1]</t>
         </is>
       </c>
       <c r="B334" t="inlineStr" s="2">
@@ -10998,7 +11020,7 @@
       </c>
       <c r="D334" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.polite.shy[1]</t>
+          <t xml:space="preserve">postWin.polite.shy[1]</t>
         </is>
       </c>
       <c r="E334" t="inlineStr" s="2">
@@ -11008,14 +11030,14 @@
       </c>
       <c r="F334" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">け、決勝戦…ですか…し、信じられません…</t>
+          <t xml:space="preserve">か、勝ち上がれました…信じられません…</t>
         </is>
       </c>
     </row>
     <row r="335" ht="40" customHeight="1">
       <c r="A335" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.polite.shy[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.polite.shy[2]</t>
         </is>
       </c>
       <c r="B335" t="inlineStr" s="2">
@@ -11030,7 +11052,7 @@
       </c>
       <c r="D335" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.polite.shy[2]</t>
+          <t xml:space="preserve">postWin.polite.shy[2]</t>
         </is>
       </c>
       <c r="E335" t="inlineStr" s="2">
@@ -11040,14 +11062,14 @@
       </c>
       <c r="F335" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">夢みたい、です…</t>
+          <t xml:space="preserve">まだ…続けられるんですね…</t>
         </is>
       </c>
     </row>
     <row r="336" ht="40" customHeight="1">
       <c r="A336" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.polite.shy[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.polite.shy[1]</t>
         </is>
       </c>
       <c r="B336" t="inlineStr" s="2">
@@ -11062,7 +11084,7 @@
       </c>
       <c r="D336" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.polite.shy[1]</t>
+          <t xml:space="preserve">preFinal.polite.shy[1]</t>
         </is>
       </c>
       <c r="E336" t="inlineStr" s="2">
@@ -11072,14 +11094,14 @@
       </c>
       <c r="F336" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">き、緊張します…でも、精一杯やります…</t>
+          <t xml:space="preserve">け、決勝戦…ですか…し、信じられません…</t>
         </is>
       </c>
     </row>
     <row r="337" ht="40" customHeight="1">
       <c r="A337" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.polite.shy[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.polite.shy[2]</t>
         </is>
       </c>
       <c r="B337" t="inlineStr" s="2">
@@ -11094,7 +11116,7 @@
       </c>
       <c r="D337" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.polite.shy[2]</t>
+          <t xml:space="preserve">preFinal.polite.shy[2]</t>
         </is>
       </c>
       <c r="E337" t="inlineStr" s="2">
@@ -11104,14 +11126,14 @@
       </c>
       <c r="F337" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふ、深呼吸…落ち着かないと…</t>
+          <t xml:space="preserve">夢みたい、です…</t>
         </is>
       </c>
     </row>
     <row r="338" ht="40" customHeight="1">
       <c r="A338" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.polite.shy[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.polite.shy[1]</t>
         </is>
       </c>
       <c r="B338" t="inlineStr" s="2">
@@ -11126,7 +11148,7 @@
       </c>
       <c r="D338" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.polite.shy[1]</t>
+          <t xml:space="preserve">preMatch.polite.shy[1]</t>
         </is>
       </c>
       <c r="E338" t="inlineStr" s="2">
@@ -11136,14 +11158,14 @@
       </c>
       <c r="F338" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">え、わたしが…ジュニアトーナメントに…？ あ、あの、頑張ります…!</t>
+          <t xml:space="preserve">き、緊張します…でも、精一杯やります…</t>
         </is>
       </c>
     </row>
     <row r="339" ht="40" customHeight="1">
       <c r="A339" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.polite.shy[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.polite.shy[2]</t>
         </is>
       </c>
       <c r="B339" t="inlineStr" s="2">
@@ -11158,7 +11180,7 @@
       </c>
       <c r="D339" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.polite.shy[2]</t>
+          <t xml:space="preserve">preMatch.polite.shy[2]</t>
         </is>
       </c>
       <c r="E339" t="inlineStr" s="2">
@@ -11168,14 +11190,14 @@
       </c>
       <c r="F339" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">選んでいただいて…あ、ありがとうございます…</t>
+          <t xml:space="preserve">ふ、深呼吸…落ち着かないと…</t>
         </is>
       </c>
     </row>
     <row r="340" ht="40" customHeight="1">
       <c r="A340" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.polite.shy[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.polite.shy[1]</t>
         </is>
       </c>
       <c r="B340" t="inlineStr" s="2">
@@ -11185,12 +11207,12 @@
       </c>
       <c r="C340" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D340" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.shy[1]</t>
+          <t xml:space="preserve">summon.polite.shy[1]</t>
         </is>
       </c>
       <c r="E340" t="inlineStr" s="2">
@@ -11200,14 +11222,14 @@
       </c>
       <c r="F340" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、あの方が…相手なんですね…せ、精一杯戦います…</t>
+          <t xml:space="preserve">え、わたしが…ジュニアトーナメントに…？ あ、あの、頑張ります…！</t>
         </is>
       </c>
     </row>
     <row r="341" ht="40" customHeight="1">
       <c r="A341" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.polite.shy[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.polite.shy[2]</t>
         </is>
       </c>
       <c r="B341" t="inlineStr" s="2">
@@ -11217,12 +11239,12 @@
       </c>
       <c r="C341" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D341" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.shy[1]</t>
+          <t xml:space="preserve">summon.polite.shy[2]</t>
         </is>
       </c>
       <c r="E341" t="inlineStr" s="2">
@@ -11232,14 +11254,14 @@
       </c>
       <c r="F341" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">か、勝てました……本当に……ありがとうございます……</t>
+          <t xml:space="preserve">選んでいただいて…あ、ありがとうございます…</t>
         </is>
       </c>
     </row>
     <row r="342" ht="40" customHeight="1">
       <c r="A342" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.polite.shy[1]</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.polite.shy[1]</t>
         </is>
       </c>
       <c r="B342" t="inlineStr" s="2">
@@ -11249,7 +11271,7 @@
       </c>
       <c r="C342" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
         </is>
       </c>
       <c r="D342" t="inlineStr" s="12">
@@ -11264,14 +11286,14 @@
       </c>
       <c r="F342" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、あの…団体として、挑戦させてください…</t>
+          <t xml:space="preserve">あ、あの方が…相手なんですね…せ、精一杯戦います…</t>
         </is>
       </c>
     </row>
     <row r="343" ht="40" customHeight="1">
       <c r="A343" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.polite.shy[2]</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.polite.shy[1]</t>
         </is>
       </c>
       <c r="B343" t="inlineStr" s="2">
@@ -11281,12 +11303,12 @@
       </c>
       <c r="C343" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D343" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.shy[2]</t>
+          <t xml:space="preserve">polite.shy[1]</t>
         </is>
       </c>
       <c r="E343" t="inlineStr" s="2">
@@ -11296,14 +11318,14 @@
       </c>
       <c r="F343" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">み、みんなで戦います…</t>
+          <t xml:space="preserve">か、勝てました……本当に……ありがとうございます……</t>
         </is>
       </c>
     </row>
     <row r="344" ht="40" customHeight="1">
       <c r="A344" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.polite.shy[1]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.polite.shy[1]</t>
         </is>
       </c>
       <c r="B344" t="inlineStr" s="2">
@@ -11313,7 +11335,7 @@
       </c>
       <c r="C344" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
         </is>
       </c>
       <c r="D344" t="inlineStr" s="12">
@@ -11328,14 +11350,14 @@
       </c>
       <c r="F344" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">す、すみません…今回は、お断りさせてください…</t>
+          <t xml:space="preserve">あ、あの…団体として、挑戦させてください…</t>
         </is>
       </c>
     </row>
     <row r="345" ht="40" customHeight="1">
       <c r="A345" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.polite.shy[2]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.polite.shy[2]</t>
         </is>
       </c>
       <c r="B345" t="inlineStr" s="2">
@@ -11345,7 +11367,7 @@
       </c>
       <c r="C345" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
         </is>
       </c>
       <c r="D345" t="inlineStr" s="12">
@@ -11360,14 +11382,14 @@
       </c>
       <c r="F345" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ま、また機会があれば…</t>
+          <t xml:space="preserve">み、みんなで戦います…</t>
         </is>
       </c>
     </row>
     <row r="346" ht="40" customHeight="1">
       <c r="A346" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.polite.shy[1]</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.polite.shy[1]</t>
         </is>
       </c>
       <c r="B346" t="inlineStr" s="2">
@@ -11377,12 +11399,12 @@
       </c>
       <c r="C346" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
         </is>
       </c>
       <c r="D346" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.polite.shy[1]</t>
+          <t xml:space="preserve">polite.shy[1]</t>
         </is>
       </c>
       <c r="E346" t="inlineStr" s="2">
@@ -11392,14 +11414,14 @@
       </c>
       <c r="F346" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ま、負けてしまいました…ご、ごめんなさい…</t>
+          <t xml:space="preserve">す、すみません…今回は、お断りさせてください…</t>
         </is>
       </c>
     </row>
     <row r="347" ht="40" customHeight="1">
       <c r="A347" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.polite.shy[2]</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.polite.shy[2]</t>
         </is>
       </c>
       <c r="B347" t="inlineStr" s="2">
@@ -11409,12 +11431,12 @@
       </c>
       <c r="C347" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
         </is>
       </c>
       <c r="D347" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.polite.shy[2]</t>
+          <t xml:space="preserve">polite.shy[2]</t>
         </is>
       </c>
       <c r="E347" t="inlineStr" s="2">
@@ -11424,14 +11446,14 @@
       </c>
       <c r="F347" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次は…次こそは…</t>
+          <t xml:space="preserve">ま、また機会があれば…</t>
         </is>
       </c>
     </row>
     <row r="348" ht="40" customHeight="1">
       <c r="A348" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.polite.shy[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.polite.shy[1]</t>
         </is>
       </c>
       <c r="B348" t="inlineStr" s="2">
@@ -11446,7 +11468,7 @@
       </c>
       <c r="D348" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.polite.shy[1]</t>
+          <t xml:space="preserve">result_lose.polite.shy[1]</t>
         </is>
       </c>
       <c r="E348" t="inlineStr" s="2">
@@ -11456,14 +11478,14 @@
       </c>
       <c r="F348" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">か、勝てました…団体のみなさんのおかげです…</t>
+          <t xml:space="preserve">ま、負けてしまいました…ご、ごめんなさい…</t>
         </is>
       </c>
     </row>
     <row r="349" ht="40" customHeight="1">
       <c r="A349" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.polite.shy[2]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.polite.shy[2]</t>
         </is>
       </c>
       <c r="B349" t="inlineStr" s="2">
@@ -11478,7 +11500,7 @@
       </c>
       <c r="D349" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.polite.shy[2]</t>
+          <t xml:space="preserve">result_lose.polite.shy[2]</t>
         </is>
       </c>
       <c r="E349" t="inlineStr" s="2">
@@ -11488,14 +11510,14 @@
       </c>
       <c r="F349" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">応援、ありがとうございました…</t>
+          <t xml:space="preserve">次は…次こそは…</t>
         </is>
       </c>
     </row>
     <row r="350" ht="40" customHeight="1">
       <c r="A350" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.polite.shy[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.polite.shy[1]</t>
         </is>
       </c>
       <c r="B350" t="inlineStr" s="2">
@@ -11505,12 +11527,12 @@
       </c>
       <c r="C350" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
         </is>
       </c>
       <c r="D350" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.shy[1]</t>
+          <t xml:space="preserve">result_win.polite.shy[1]</t>
         </is>
       </c>
       <c r="E350" t="inlineStr" s="2">
@@ -11520,14 +11542,14 @@
       </c>
       <c r="F350" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">か、勝てました…！ 団体のみなさまに恥じない試合が…できたでしょうか…</t>
+          <t xml:space="preserve">か、勝てました…団体のみなさんのおかげです…</t>
         </is>
       </c>
     </row>
     <row r="351" ht="40" customHeight="1">
       <c r="A351" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.polite.shy[2]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.polite.shy[2]</t>
         </is>
       </c>
       <c r="B351" t="inlineStr" s="2">
@@ -11537,12 +11559,12 @@
       </c>
       <c r="C351" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
         </is>
       </c>
       <c r="D351" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.shy[2]</t>
+          <t xml:space="preserve">result_win.polite.shy[2]</t>
         </is>
       </c>
       <c r="E351" t="inlineStr" s="2">
@@ -11552,14 +11574,14 @@
       </c>
       <c r="F351" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">か、勝たせていただきました…。団体のみなさまに…少しは恩返しできたでしょうか…</t>
+          <t xml:space="preserve">応援、ありがとうございました…</t>
         </is>
       </c>
     </row>
     <row r="352" ht="40" customHeight="1">
       <c r="A352" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.polite.shy[3]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.polite.shy[1]</t>
         </is>
       </c>
       <c r="B352" t="inlineStr" s="2">
@@ -11574,7 +11596,7 @@
       </c>
       <c r="D352" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.shy[3]</t>
+          <t xml:space="preserve">polite.shy[1]</t>
         </is>
       </c>
       <c r="E352" t="inlineStr" s="2">
@@ -11584,14 +11606,14 @@
       </c>
       <c r="F352" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">か、勝てました…！ 団体のみなさまに恥じない試合が…できていたら嬉しいです…</t>
+          <t xml:space="preserve">か、勝てました…！ 団体のみなさまに恥じない試合が…できたでしょうか…</t>
         </is>
       </c>
     </row>
     <row r="353" ht="40" customHeight="1">
       <c r="A353" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.polite.shy[1]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.polite.shy[2]</t>
         </is>
       </c>
       <c r="B353" t="inlineStr" s="2">
@@ -11601,29 +11623,29 @@
       </c>
       <c r="C353" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ENDING_LINES</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D353" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.polite.shy[1]</t>
+          <t xml:space="preserve">polite.shy[2]</t>
         </is>
       </c>
       <c r="E353" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">18 経営危機・エンディング</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F353" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こ、これで…リングを降ります…あ、あの、応援してくれた皆さま…本当に、ありがとうございました…</t>
+          <t xml:space="preserve">か、勝たせていただきました…。団体のみなさまに…少しは恩返しできたでしょうか…</t>
         </is>
       </c>
     </row>
     <row r="354" ht="40" customHeight="1">
       <c r="A354" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.polite.shy[1]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.polite.shy[3]</t>
         </is>
       </c>
       <c r="B354" t="inlineStr" s="2">
@@ -11633,59 +11655,123 @@
       </c>
       <c r="C354" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D354" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.shy[1]</t>
+          <t xml:space="preserve">polite.shy[3]</t>
         </is>
       </c>
       <c r="E354" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">19 ドラフト・スカウト</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F354" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、あの…契約してもらえて…感謝しています…！</t>
+          <t xml:space="preserve">か、勝てました…！ 団体のみなさまに恥じない試合が…できていたら嬉しいです…</t>
         </is>
       </c>
     </row>
     <row r="355" ht="40" customHeight="1">
       <c r="A355" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">ENDING_LINES.fighter.polite.shy[1]</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ENDING_LINES</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">fighter.polite.shy[1]</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">18 経営危機・エンディング</t>
+        </is>
+      </c>
+      <c r="F355" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">こ、これで…リングを降ります…あ、あの、応援してくれた皆さま…本当に、ありがとうございました…</t>
+        </is>
+      </c>
+    </row>
+    <row r="356" ht="40" customHeight="1">
+      <c r="A356" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES.polite.shy[1]</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">polite.shy[1]</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F356" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あ、あの…契約してもらえて…感謝しています…！</t>
+        </is>
+      </c>
+    </row>
+    <row r="357" ht="40" customHeight="1">
+      <c r="A357" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES.polite.shy[1]</t>
         </is>
       </c>
-      <c r="B355" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C355" t="inlineStr" s="2">
+      <c r="B357" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES</t>
         </is>
       </c>
-      <c r="D355" t="inlineStr" s="12">
+      <c r="D357" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">polite.shy[1]</t>
         </is>
       </c>
-      <c r="E355" t="inlineStr" s="2">
+      <c r="E357" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">19 ドラフト・スカウト</t>
         </is>
       </c>
-      <c r="F355" t="inlineStr" s="3">
+      <c r="F357" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">あ、あの…お声がけ、光栄です…！</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H355"/>
+  <autoFilter ref="A1:H357"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/キャラタイプ別/丁寧×内気.xlsx
+++ b/セリフ編集/キャラタイプ別/丁寧×内気.xlsx
@@ -323,7 +323,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H357"/>
+  <dimension ref="A1:H364"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -3869,7 +3869,7 @@
     <row r="111" ht="40" customHeight="1">
       <c r="A111" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.polite.shy[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_accept.polite.shy[1]</t>
         </is>
       </c>
       <c r="B111" t="inlineStr" s="2">
@@ -3884,7 +3884,7 @@
       </c>
       <c r="D111" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_accept.polite.shy[1]</t>
+          <t xml:space="preserve">decline_accept.polite.shy[1]</t>
         </is>
       </c>
       <c r="E111" t="inlineStr" s="2">
@@ -3894,14 +3894,14 @@
       </c>
       <c r="F111" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こ、こんな良いお話…あ、ありがとうございます…精一杯頑張ります…</t>
+          <t xml:space="preserve">は、はい……。ちゃんと数字にしてもらえたほうが……わたし、かえって落ち着きます……。</t>
         </is>
       </c>
     </row>
     <row r="112" ht="40" customHeight="1">
       <c r="A112" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.polite.shy[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_hold.polite.shy[1]</t>
         </is>
       </c>
       <c r="B112" t="inlineStr" s="2">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="D112" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_accept.polite.shy[1]</t>
+          <t xml:space="preserve">decline_hold.polite.shy[1]</t>
         </is>
       </c>
       <c r="E112" t="inlineStr" s="2">
@@ -3926,14 +3926,14 @@
       </c>
       <c r="F112" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">は、はい…その条件で…お受けします…</t>
+          <t xml:space="preserve">な、なんで……ですか……。わたし、下がって当然なのに……。……絶対、無駄にしません……！</t>
         </is>
       </c>
     </row>
     <row r="113" ht="40" customHeight="1">
       <c r="A113" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.polite.shy[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_open.polite.shy[1]</t>
         </is>
       </c>
       <c r="B113" t="inlineStr" s="2">
@@ -3948,7 +3948,7 @@
       </c>
       <c r="D113" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_refuse.polite.shy[1]</t>
+          <t xml:space="preserve">decline_open.polite.shy[1]</t>
         </is>
       </c>
       <c r="E113" t="inlineStr" s="2">
@@ -3958,14 +3958,14 @@
       </c>
       <c r="F113" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">考えさせていただいたんですが…やっぱり、難しいです…</t>
+          <t xml:space="preserve">あ……はい……。わたし、ちゃんと分かってます……去年みたいには、動けてないって……。</t>
         </is>
       </c>
     </row>
     <row r="114" ht="40" customHeight="1">
       <c r="A114" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.polite.shy[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_strict.polite.shy[1]</t>
         </is>
       </c>
       <c r="B114" t="inlineStr" s="2">
@@ -3980,7 +3980,7 @@
       </c>
       <c r="D114" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_open.polite.shy[1]</t>
+          <t xml:space="preserve">decline_strict.polite.shy[1]</t>
         </is>
       </c>
       <c r="E114" t="inlineStr" s="2">
@@ -3990,14 +3990,14 @@
       </c>
       <c r="F114" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、あの…契約のことで、お話があるんです…</t>
+          <t xml:space="preserve">……はい……。あの……わたし、そんなに、いらない人になっちゃいましたか……？</t>
         </is>
       </c>
     </row>
     <row r="115" ht="40" customHeight="1">
       <c r="A115" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.polite.shy[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_voluntary_accept.polite.shy[1]</t>
         </is>
       </c>
       <c r="B115" t="inlineStr" s="2">
@@ -4012,7 +4012,7 @@
       </c>
       <c r="D115" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_refuse.polite.shy[1]</t>
+          <t xml:space="preserve">decline_voluntary_accept.polite.shy[1]</t>
         </is>
       </c>
       <c r="E115" t="inlineStr" s="2">
@@ -4022,14 +4022,14 @@
       </c>
       <c r="F115" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">すみません…この条件では、ちょっと…</t>
+          <t xml:space="preserve">……ありがとうございます。ちゃんと聞いてもらえて……わたし、少し、背筋が伸びました……。</t>
         </is>
       </c>
     </row>
     <row r="116" ht="40" customHeight="1">
       <c r="A116" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.polite.shy[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_voluntary_hold.polite.shy[1]</t>
         </is>
       </c>
       <c r="B116" t="inlineStr" s="2">
@@ -4044,7 +4044,7 @@
       </c>
       <c r="D116" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.polite.shy[1]</t>
+          <t xml:space="preserve">decline_voluntary_hold.polite.shy[1]</t>
         </is>
       </c>
       <c r="E116" t="inlineStr" s="2">
@@ -4054,14 +4054,14 @@
       </c>
       <c r="F116" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……あの、辞め……辞めさせていただけますか……。もう、無理なんです……。</t>
+          <t xml:space="preserve">そ、そんな……わたしが言い出したのに……。……はい……。もう一年、やってみます……！</t>
         </is>
       </c>
     </row>
     <row r="117" ht="40" customHeight="1">
       <c r="A117" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.polite.shy[2]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_voluntary_open.polite.shy[1]</t>
         </is>
       </c>
       <c r="B117" t="inlineStr" s="2">
@@ -4076,7 +4076,7 @@
       </c>
       <c r="D117" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.polite.shy[2]</t>
+          <t xml:space="preserve">decline_voluntary_open.polite.shy[1]</t>
         </is>
       </c>
       <c r="E117" t="inlineStr" s="2">
@@ -4086,14 +4086,14 @@
       </c>
       <c r="F117" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……申し訳ありません。もう、ここには居られません……。</t>
+          <t xml:space="preserve">あ、あの……わたしから、お願いがあって……。お給料、下げてもらって、いいんです……。</t>
         </is>
       </c>
     </row>
     <row r="118" ht="40" customHeight="1">
       <c r="A118" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.polite.shy[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.polite.shy[1]</t>
         </is>
       </c>
       <c r="B118" t="inlineStr" s="2">
@@ -4108,7 +4108,7 @@
       </c>
       <c r="D118" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_listen.polite.shy[1]</t>
+          <t xml:space="preserve">raise_accept.polite.shy[1]</t>
         </is>
       </c>
       <c r="E118" t="inlineStr" s="2">
@@ -4118,14 +4118,14 @@
       </c>
       <c r="F118" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お、お話だけは…聞かせていただきます…</t>
+          <t xml:space="preserve">こ、こんな良いお話…あ、ありがとうございます…精一杯頑張ります…</t>
         </is>
       </c>
     </row>
     <row r="119" ht="40" customHeight="1">
       <c r="A119" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.polite.shy[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.polite.shy[1]</t>
         </is>
       </c>
       <c r="B119" t="inlineStr" s="2">
@@ -4140,7 +4140,7 @@
       </c>
       <c r="D119" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_open.polite.shy[1]</t>
+          <t xml:space="preserve">raise_negotiate_accept.polite.shy[1]</t>
         </is>
       </c>
       <c r="E119" t="inlineStr" s="2">
@@ -4150,14 +4150,14 @@
       </c>
       <c r="F119" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、あの…他の団体からも、お話をいただいていて…</t>
+          <t xml:space="preserve">は、はい…その条件で…お受けします…</t>
         </is>
       </c>
     </row>
     <row r="120" ht="40" customHeight="1">
       <c r="A120" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.polite.shy[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.polite.shy[1]</t>
         </is>
       </c>
       <c r="B120" t="inlineStr" s="2">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="D120" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_release.polite.shy[1]</t>
+          <t xml:space="preserve">raise_negotiate_refuse.polite.shy[1]</t>
         </is>
       </c>
       <c r="E120" t="inlineStr" s="2">
@@ -4182,14 +4182,14 @@
       </c>
       <c r="F120" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、あの…移籍させてください…お、お世話になりました…</t>
+          <t xml:space="preserve">考えさせていただいたんですが…やっぱり、難しいです…</t>
         </is>
       </c>
     </row>
     <row r="121" ht="40" customHeight="1">
       <c r="A121" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.polite.shy[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.polite.shy[1]</t>
         </is>
       </c>
       <c r="B121" t="inlineStr" s="2">
@@ -4204,7 +4204,7 @@
       </c>
       <c r="D121" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_fail.polite.shy[1]</t>
+          <t xml:space="preserve">raise_open.polite.shy[1]</t>
         </is>
       </c>
       <c r="E121" t="inlineStr" s="2">
@@ -4214,14 +4214,14 @@
       </c>
       <c r="F121" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ご、ごめんなさい…やっぱり、行かせてください…</t>
+          <t xml:space="preserve">あ、あの…契約のことで、お話があるんです…</t>
         </is>
       </c>
     </row>
     <row r="122" ht="40" customHeight="1">
       <c r="A122" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.polite.shy[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.polite.shy[1]</t>
         </is>
       </c>
       <c r="B122" t="inlineStr" s="2">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="D122" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_success.polite.shy[1]</t>
+          <t xml:space="preserve">raise_refuse.polite.shy[1]</t>
         </is>
       </c>
       <c r="E122" t="inlineStr" s="2">
@@ -4246,14 +4246,14 @@
       </c>
       <c r="F122" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こ、ここに残ります…引き止めてくださって、ありがとうございます…</t>
+          <t xml:space="preserve">すみません…この条件では、ちょっと…</t>
         </is>
       </c>
     </row>
     <row r="123" ht="40" customHeight="1">
       <c r="A123" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.blocked.polite.shy[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.polite.shy[1]</t>
         </is>
       </c>
       <c r="B123" t="inlineStr" s="2">
@@ -4263,12 +4263,12 @@
       </c>
       <c r="C123" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D123" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">blocked.polite.shy[1]</t>
+          <t xml:space="preserve">sudden_departure.polite.shy[1]</t>
         </is>
       </c>
       <c r="E123" t="inlineStr" s="2">
@@ -4278,14 +4278,14 @@
       </c>
       <c r="F123" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、あの…この件は、お話できません…</t>
+          <t xml:space="preserve">……あの、辞め……辞めさせていただけますか……。もう、無理なんです……。</t>
         </is>
       </c>
     </row>
     <row r="124" ht="40" customHeight="1">
       <c r="A124" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.fail.polite.shy[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.polite.shy[2]</t>
         </is>
       </c>
       <c r="B124" t="inlineStr" s="2">
@@ -4295,12 +4295,12 @@
       </c>
       <c r="C124" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D124" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fail.polite.shy[1]</t>
+          <t xml:space="preserve">sudden_departure.polite.shy[2]</t>
         </is>
       </c>
       <c r="E124" t="inlineStr" s="2">
@@ -4310,14 +4310,14 @@
       </c>
       <c r="F124" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">す、すみません…今回は、難しいです…</t>
+          <t xml:space="preserve">……申し訳ありません。もう、ここには居られません……。</t>
         </is>
       </c>
     </row>
     <row r="125" ht="40" customHeight="1">
       <c r="A125" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.start.polite.shy[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.polite.shy[1]</t>
         </is>
       </c>
       <c r="B125" t="inlineStr" s="2">
@@ -4327,12 +4327,12 @@
       </c>
       <c r="C125" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D125" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">start.polite.shy[1]</t>
+          <t xml:space="preserve">transfer_listen.polite.shy[1]</t>
         </is>
       </c>
       <c r="E125" t="inlineStr" s="2">
@@ -4342,14 +4342,14 @@
       </c>
       <c r="F125" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、あの…交渉、始めさせていただきます…</t>
+          <t xml:space="preserve">お、お話だけは…聞かせていただきます…</t>
         </is>
       </c>
     </row>
     <row r="126" ht="40" customHeight="1">
       <c r="A126" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.success.polite.shy[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.polite.shy[1]</t>
         </is>
       </c>
       <c r="B126" t="inlineStr" s="2">
@@ -4359,12 +4359,12 @@
       </c>
       <c r="C126" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D126" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">success.polite.shy[1]</t>
+          <t xml:space="preserve">transfer_open.polite.shy[1]</t>
         </is>
       </c>
       <c r="E126" t="inlineStr" s="2">
@@ -4374,14 +4374,14 @@
       </c>
       <c r="F126" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こ、こちらでお願いします…ありがとうございます…</t>
+          <t xml:space="preserve">あ、あの…他の団体からも、お話をいただいていて…</t>
         </is>
       </c>
     </row>
     <row r="127" ht="40" customHeight="1">
       <c r="A127" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_ABSTRACT.polite.shy[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.polite.shy[1]</t>
         </is>
       </c>
       <c r="B127" t="inlineStr" s="2">
@@ -4391,29 +4391,29 @@
       </c>
       <c r="C127" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">F07_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D127" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">leaderDemand.DEMAND_ABSTRACT.polite.shy[1]</t>
+          <t xml:space="preserve">transfer_release.polite.shy[1]</t>
         </is>
       </c>
       <c r="E127" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F127" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…社長、あの…わたしたちのメンバーのこと、気にかけていただけると…嬉しいです。</t>
+          <t xml:space="preserve">あ、あの…移籍させてください…お、お世話になりました…</t>
         </is>
       </c>
     </row>
     <row r="128" ht="40" customHeight="1">
       <c r="A128" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MAIN.polite.shy[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.polite.shy[1]</t>
         </is>
       </c>
       <c r="B128" t="inlineStr" s="2">
@@ -4423,29 +4423,29 @@
       </c>
       <c r="C128" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">F07_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D128" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">leaderDemand.DEMAND_MAIN.polite.shy[1]</t>
+          <t xml:space="preserve">transfer_retain_fail.polite.shy[1]</t>
         </is>
       </c>
       <c r="E128" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F128" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…社長、あの…次のメイン、わたしたちに…お任せいただけたら、嬉しいです。</t>
+          <t xml:space="preserve">ご、ごめんなさい…やっぱり、行かせてください…</t>
         </is>
       </c>
     </row>
     <row r="129" ht="40" customHeight="1">
       <c r="A129" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MONEY.polite.shy[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.polite.shy[1]</t>
         </is>
       </c>
       <c r="B129" t="inlineStr" s="2">
@@ -4455,29 +4455,29 @@
       </c>
       <c r="C129" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">F07_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D129" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">leaderDemand.DEMAND_MONEY.polite.shy[1]</t>
+          <t xml:space="preserve">transfer_retain_success.polite.shy[1]</t>
         </is>
       </c>
       <c r="E129" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F129" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…社長、あの…待遇のこと、少しだけお話、させていただけませんか。</t>
+          <t xml:space="preserve">こ、ここに残ります…引き止めてくださって、ありがとうございます…</t>
         </is>
       </c>
     </row>
     <row r="130" ht="40" customHeight="1">
       <c r="A130" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_RECOGNITION.polite.shy[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.blocked.polite.shy[1]</t>
         </is>
       </c>
       <c r="B130" t="inlineStr" s="2">
@@ -4487,29 +4487,29 @@
       </c>
       <c r="C130" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">F07_LINES</t>
+          <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
       <c r="D130" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">leaderDemand.DEMAND_RECOGNITION.polite.shy[1]</t>
+          <t xml:space="preserve">blocked.polite.shy[1]</t>
         </is>
       </c>
       <c r="E130" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F130" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…社長、あの…わたしたちのこと、見ていてくださると…うれしいです。</t>
+          <t xml:space="preserve">あ、あの…この件は、お話できません…</t>
         </is>
       </c>
     </row>
     <row r="131" ht="40" customHeight="1">
       <c r="A131" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.A.polite.shy[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.fail.polite.shy[1]</t>
         </is>
       </c>
       <c r="B131" t="inlineStr" s="2">
@@ -4519,29 +4519,29 @@
       </c>
       <c r="C131" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">F07_LINES</t>
+          <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
       <c r="D131" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.A.polite.shy[1]</t>
+          <t xml:space="preserve">fail.polite.shy[1]</t>
         </is>
       </c>
       <c r="E131" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F131" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…あの、ありがとうございます。…嬉しい、です。</t>
+          <t xml:space="preserve">す、すみません…今回は、難しいです…</t>
         </is>
       </c>
     </row>
     <row r="132" ht="40" customHeight="1">
       <c r="A132" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.B.polite.shy[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.start.polite.shy[1]</t>
         </is>
       </c>
       <c r="B132" t="inlineStr" s="2">
@@ -4551,29 +4551,29 @@
       </c>
       <c r="C132" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">F07_LINES</t>
+          <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
       <c r="D132" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.B.polite.shy[1]</t>
+          <t xml:space="preserve">start.polite.shy[1]</t>
         </is>
       </c>
       <c r="E132" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F132" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…はい…ごめんなさい。</t>
+          <t xml:space="preserve">あ、あの…交渉、始めさせていただきます…</t>
         </is>
       </c>
     </row>
     <row r="133" ht="40" customHeight="1">
       <c r="A133" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.C.polite.shy[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.success.polite.shy[1]</t>
         </is>
       </c>
       <c r="B133" t="inlineStr" s="2">
@@ -4583,29 +4583,29 @@
       </c>
       <c r="C133" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">F07_LINES</t>
+          <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
       <c r="D133" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.C.polite.shy[1]</t>
+          <t xml:space="preserve">success.polite.shy[1]</t>
         </is>
       </c>
       <c r="E133" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F133" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…あの、ありがとうございます。…嬉しいです。</t>
+          <t xml:space="preserve">こ、こちらでお願いします…ありがとうございます…</t>
         </is>
       </c>
     </row>
     <row r="134" ht="40" customHeight="1">
       <c r="A134" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.A.polite.shy[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_ABSTRACT.polite.shy[1]</t>
         </is>
       </c>
       <c r="B134" t="inlineStr" s="2">
@@ -4620,7 +4620,7 @@
       </c>
       <c r="D134" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MAIN.A.polite.shy[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_ABSTRACT.polite.shy[1]</t>
         </is>
       </c>
       <c r="E134" t="inlineStr" s="2">
@@ -4630,14 +4630,14 @@
       </c>
       <c r="F134" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…あの、ありがとうございます。…精一杯、がんばります。</t>
+          <t xml:space="preserve">…社長、あの…わたしたちのメンバーのこと、気にかけていただけると…嬉しいです。</t>
         </is>
       </c>
     </row>
     <row r="135" ht="40" customHeight="1">
       <c r="A135" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.B.polite.shy[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MAIN.polite.shy[1]</t>
         </is>
       </c>
       <c r="B135" t="inlineStr" s="2">
@@ -4652,7 +4652,7 @@
       </c>
       <c r="D135" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MAIN.B.polite.shy[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_MAIN.polite.shy[1]</t>
         </is>
       </c>
       <c r="E135" t="inlineStr" s="2">
@@ -4662,14 +4662,14 @@
       </c>
       <c r="F135" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…はい…承知しました。失礼いたしました。</t>
+          <t xml:space="preserve">…社長、あの…次のメイン、わたしたちに…お任せいただけたら、嬉しいです。</t>
         </is>
       </c>
     </row>
     <row r="136" ht="40" customHeight="1">
       <c r="A136" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.C.polite.shy[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MONEY.polite.shy[1]</t>
         </is>
       </c>
       <c r="B136" t="inlineStr" s="2">
@@ -4684,7 +4684,7 @@
       </c>
       <c r="D136" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MAIN.C.polite.shy[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_MONEY.polite.shy[1]</t>
         </is>
       </c>
       <c r="E136" t="inlineStr" s="2">
@@ -4694,14 +4694,14 @@
       </c>
       <c r="F136" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…あの、ありがとうございます。</t>
+          <t xml:space="preserve">…社長、あの…待遇のこと、少しだけお話、させていただけませんか。</t>
         </is>
       </c>
     </row>
     <row r="137" ht="40" customHeight="1">
       <c r="A137" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.A.polite.shy[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_RECOGNITION.polite.shy[1]</t>
         </is>
       </c>
       <c r="B137" t="inlineStr" s="2">
@@ -4716,7 +4716,7 @@
       </c>
       <c r="D137" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MONEY.A.polite.shy[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_RECOGNITION.polite.shy[1]</t>
         </is>
       </c>
       <c r="E137" t="inlineStr" s="2">
@@ -4726,14 +4726,14 @@
       </c>
       <c r="F137" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…あの、ありがとう、ございます。…みんなに、伝えます。</t>
+          <t xml:space="preserve">…社長、あの…わたしたちのこと、見ていてくださると…うれしいです。</t>
         </is>
       </c>
     </row>
     <row r="138" ht="40" customHeight="1">
       <c r="A138" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.B.polite.shy[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.A.polite.shy[1]</t>
         </is>
       </c>
       <c r="B138" t="inlineStr" s="2">
@@ -4748,7 +4748,7 @@
       </c>
       <c r="D138" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MONEY.B.polite.shy[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.A.polite.shy[1]</t>
         </is>
       </c>
       <c r="E138" t="inlineStr" s="2">
@@ -4758,14 +4758,14 @@
       </c>
       <c r="F138" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…はい…承知しました。失礼いたしました。</t>
+          <t xml:space="preserve">…あの、ありがとうございます。…嬉しい、です。</t>
         </is>
       </c>
     </row>
     <row r="139" ht="40" customHeight="1">
       <c r="A139" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.C.polite.shy[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.B.polite.shy[1]</t>
         </is>
       </c>
       <c r="B139" t="inlineStr" s="2">
@@ -4780,7 +4780,7 @@
       </c>
       <c r="D139" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MONEY.C.polite.shy[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.B.polite.shy[1]</t>
         </is>
       </c>
       <c r="E139" t="inlineStr" s="2">
@@ -4790,14 +4790,14 @@
       </c>
       <c r="F139" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…あの、ありがとうございます。…嬉しいです。</t>
+          <t xml:space="preserve">…はい…ごめんなさい。</t>
         </is>
       </c>
     </row>
     <row r="140" ht="40" customHeight="1">
       <c r="A140" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.A.polite.shy[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.C.polite.shy[1]</t>
         </is>
       </c>
       <c r="B140" t="inlineStr" s="2">
@@ -4812,7 +4812,7 @@
       </c>
       <c r="D140" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.A.polite.shy[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.C.polite.shy[1]</t>
         </is>
       </c>
       <c r="E140" t="inlineStr" s="2">
@@ -4822,14 +4822,14 @@
       </c>
       <c r="F140" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…あの、ありがとうございます。…がんばります。</t>
+          <t xml:space="preserve">…あの、ありがとうございます。…嬉しいです。</t>
         </is>
       </c>
     </row>
     <row r="141" ht="40" customHeight="1">
       <c r="A141" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.B.polite.shy[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.A.polite.shy[1]</t>
         </is>
       </c>
       <c r="B141" t="inlineStr" s="2">
@@ -4844,7 +4844,7 @@
       </c>
       <c r="D141" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.B.polite.shy[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.A.polite.shy[1]</t>
         </is>
       </c>
       <c r="E141" t="inlineStr" s="2">
@@ -4854,14 +4854,14 @@
       </c>
       <c r="F141" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…はい…ごめんなさい。</t>
+          <t xml:space="preserve">…あの、ありがとうございます。…精一杯、がんばります。</t>
         </is>
       </c>
     </row>
     <row r="142" ht="40" customHeight="1">
       <c r="A142" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.C.polite.shy[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.B.polite.shy[1]</t>
         </is>
       </c>
       <c r="B142" t="inlineStr" s="2">
@@ -4876,7 +4876,7 @@
       </c>
       <c r="D142" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.C.polite.shy[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.B.polite.shy[1]</t>
         </is>
       </c>
       <c r="E142" t="inlineStr" s="2">
@@ -4886,14 +4886,14 @@
       </c>
       <c r="F142" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…あの、ありがとうございます。…嬉しいです。</t>
+          <t xml:space="preserve">…はい…承知しました。失礼いたしました。</t>
         </is>
       </c>
     </row>
     <row r="143" ht="40" customHeight="1">
       <c r="A143" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.A.polite.shy[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.C.polite.shy[1]</t>
         </is>
       </c>
       <c r="B143" t="inlineStr" s="2">
@@ -4908,7 +4908,7 @@
       </c>
       <c r="D143" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.A.polite.shy[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.C.polite.shy[1]</t>
         </is>
       </c>
       <c r="E143" t="inlineStr" s="2">
@@ -4918,14 +4918,14 @@
       </c>
       <c r="F143" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ごめんなさい…次は、声、かけます。</t>
+          <t xml:space="preserve">…あの、ありがとうございます。</t>
         </is>
       </c>
     </row>
     <row r="144" ht="40" customHeight="1">
       <c r="A144" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.B.polite.shy[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.A.polite.shy[1]</t>
         </is>
       </c>
       <c r="B144" t="inlineStr" s="2">
@@ -4940,7 +4940,7 @@
       </c>
       <c r="D144" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.B.polite.shy[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.A.polite.shy[1]</t>
         </is>
       </c>
       <c r="E144" t="inlineStr" s="2">
@@ -4950,14 +4950,14 @@
       </c>
       <c r="F144" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…はい…ありがとうございます。…でも、少し、考えます。</t>
+          <t xml:space="preserve">…あの、ありがとう、ございます。…みんなに、伝えます。</t>
         </is>
       </c>
     </row>
     <row r="145" ht="40" customHeight="1">
       <c r="A145" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.A.polite.shy[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.B.polite.shy[1]</t>
         </is>
       </c>
       <c r="B145" t="inlineStr" s="2">
@@ -4972,7 +4972,7 @@
       </c>
       <c r="D145" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.A.polite.shy[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.B.polite.shy[1]</t>
         </is>
       </c>
       <c r="E145" t="inlineStr" s="2">
@@ -4982,14 +4982,14 @@
       </c>
       <c r="F145" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…はい…ごめんなさい。</t>
+          <t xml:space="preserve">…はい…承知しました。失礼いたしました。</t>
         </is>
       </c>
     </row>
     <row r="146" ht="40" customHeight="1">
       <c r="A146" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.B.polite.shy[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.C.polite.shy[1]</t>
         </is>
       </c>
       <c r="B146" t="inlineStr" s="2">
@@ -5004,7 +5004,7 @@
       </c>
       <c r="D146" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.B.polite.shy[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.C.polite.shy[1]</t>
         </is>
       </c>
       <c r="E146" t="inlineStr" s="2">
@@ -5014,14 +5014,14 @@
       </c>
       <c r="F146" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…はい…ありがとうございます。</t>
+          <t xml:space="preserve">…あの、ありがとうございます。…嬉しいです。</t>
         </is>
       </c>
     </row>
     <row r="147" ht="40" customHeight="1">
       <c r="A147" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.A.polite.shy[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.A.polite.shy[1]</t>
         </is>
       </c>
       <c r="B147" t="inlineStr" s="2">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="D147" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.A.polite.shy[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.A.polite.shy[1]</t>
         </is>
       </c>
       <c r="E147" t="inlineStr" s="2">
@@ -5046,14 +5046,14 @@
       </c>
       <c r="F147" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…はい…ごめんなさい、控えます。</t>
+          <t xml:space="preserve">…あの、ありがとうございます。…がんばります。</t>
         </is>
       </c>
     </row>
     <row r="148" ht="40" customHeight="1">
       <c r="A148" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.B.polite.shy[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.B.polite.shy[1]</t>
         </is>
       </c>
       <c r="B148" t="inlineStr" s="2">
@@ -5068,7 +5068,7 @@
       </c>
       <c r="D148" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.B.polite.shy[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.B.polite.shy[1]</t>
         </is>
       </c>
       <c r="E148" t="inlineStr" s="2">
@@ -5078,14 +5078,14 @@
       </c>
       <c r="F148" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…はい…ありがとうございます。…続けます。</t>
+          <t xml:space="preserve">…はい…ごめんなさい。</t>
         </is>
       </c>
     </row>
     <row r="149" ht="40" customHeight="1">
       <c r="A149" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.A.polite.shy[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.C.polite.shy[1]</t>
         </is>
       </c>
       <c r="B149" t="inlineStr" s="2">
@@ -5100,7 +5100,7 @@
       </c>
       <c r="D149" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.A.polite.shy[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.C.polite.shy[1]</t>
         </is>
       </c>
       <c r="E149" t="inlineStr" s="2">
@@ -5110,14 +5110,14 @@
       </c>
       <c r="F149" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ごめんなさい…明日から、ちゃんと、出ます。</t>
+          <t xml:space="preserve">…あの、ありがとうございます。…嬉しいです。</t>
         </is>
       </c>
     </row>
     <row r="150" ht="40" customHeight="1">
       <c r="A150" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.B.polite.shy[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.A.polite.shy[1]</t>
         </is>
       </c>
       <c r="B150" t="inlineStr" s="2">
@@ -5132,7 +5132,7 @@
       </c>
       <c r="D150" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.B.polite.shy[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.A.polite.shy[1]</t>
         </is>
       </c>
       <c r="E150" t="inlineStr" s="2">
@@ -5142,14 +5142,14 @@
       </c>
       <c r="F150" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…はい…ありがとうございます。…嬉しい、です。</t>
+          <t xml:space="preserve">…ごめんなさい…次は、声、かけます。</t>
         </is>
       </c>
     </row>
     <row r="151" ht="40" customHeight="1">
       <c r="A151" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.C.polite.shy[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.B.polite.shy[1]</t>
         </is>
       </c>
       <c r="B151" t="inlineStr" s="2">
@@ -5164,7 +5164,7 @@
       </c>
       <c r="D151" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.C.polite.shy[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.B.polite.shy[1]</t>
         </is>
       </c>
       <c r="E151" t="inlineStr" s="2">
@@ -5174,14 +5174,14 @@
       </c>
       <c r="F151" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…あの、ありがとうございます。…嬉しいです。</t>
+          <t xml:space="preserve">…はい…ありがとうございます。…でも、少し、考えます。</t>
         </is>
       </c>
     </row>
     <row r="152" ht="40" customHeight="1">
       <c r="A152" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.A.polite.shy[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.A.polite.shy[1]</t>
         </is>
       </c>
       <c r="B152" t="inlineStr" s="2">
@@ -5196,7 +5196,7 @@
       </c>
       <c r="D152" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.A.polite.shy[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.A.polite.shy[1]</t>
         </is>
       </c>
       <c r="E152" t="inlineStr" s="2">
@@ -5206,14 +5206,14 @@
       </c>
       <c r="F152" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…はい…ありがとうございます。…休ませて、いただきます。</t>
+          <t xml:space="preserve">…はい…ごめんなさい。</t>
         </is>
       </c>
     </row>
     <row r="153" ht="40" customHeight="1">
       <c r="A153" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.B.polite.shy[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.B.polite.shy[1]</t>
         </is>
       </c>
       <c r="B153" t="inlineStr" s="2">
@@ -5228,7 +5228,7 @@
       </c>
       <c r="D153" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.B.polite.shy[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.B.polite.shy[1]</t>
         </is>
       </c>
       <c r="E153" t="inlineStr" s="2">
@@ -5238,14 +5238,14 @@
       </c>
       <c r="F153" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…はい…大丈夫、です。</t>
+          <t xml:space="preserve">…はい…ありがとうございます。</t>
         </is>
       </c>
     </row>
     <row r="154" ht="40" customHeight="1">
       <c r="A154" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.C.polite.shy[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.A.polite.shy[1]</t>
         </is>
       </c>
       <c r="B154" t="inlineStr" s="2">
@@ -5260,7 +5260,7 @@
       </c>
       <c r="D154" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.C.polite.shy[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.A.polite.shy[1]</t>
         </is>
       </c>
       <c r="E154" t="inlineStr" s="2">
@@ -5270,14 +5270,14 @@
       </c>
       <c r="F154" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…あの、ありがとうございます。…嬉しいです。</t>
+          <t xml:space="preserve">…はい…ごめんなさい、控えます。</t>
         </is>
       </c>
     </row>
     <row r="155" ht="40" customHeight="1">
       <c r="A155" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.A.polite.shy[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.B.polite.shy[1]</t>
         </is>
       </c>
       <c r="B155" t="inlineStr" s="2">
@@ -5292,7 +5292,7 @@
       </c>
       <c r="D155" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.A.polite.shy[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.B.polite.shy[1]</t>
         </is>
       </c>
       <c r="E155" t="inlineStr" s="2">
@@ -5302,14 +5302,14 @@
       </c>
       <c r="F155" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…はい…ごめんなさい、注意します。</t>
+          <t xml:space="preserve">…はい…ありがとうございます。…続けます。</t>
         </is>
       </c>
     </row>
     <row r="156" ht="40" customHeight="1">
       <c r="A156" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.B.polite.shy[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.A.polite.shy[1]</t>
         </is>
       </c>
       <c r="B156" t="inlineStr" s="2">
@@ -5324,7 +5324,7 @@
       </c>
       <c r="D156" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.B.polite.shy[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.A.polite.shy[1]</t>
         </is>
       </c>
       <c r="E156" t="inlineStr" s="2">
@@ -5334,14 +5334,14 @@
       </c>
       <c r="F156" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…はい…ありがとうございます。</t>
+          <t xml:space="preserve">…ごめんなさい…明日から、ちゃんと、出ます。</t>
         </is>
       </c>
     </row>
     <row r="157" ht="40" customHeight="1">
       <c r="A157" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.C.polite.shy[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.B.polite.shy[1]</t>
         </is>
       </c>
       <c r="B157" t="inlineStr" s="2">
@@ -5356,7 +5356,7 @@
       </c>
       <c r="D157" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.C.polite.shy[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.B.polite.shy[1]</t>
         </is>
       </c>
       <c r="E157" t="inlineStr" s="2">
@@ -5366,14 +5366,14 @@
       </c>
       <c r="F157" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…あの、ありがとうございます。…嬉しいです。</t>
+          <t xml:space="preserve">…はい…ありがとうございます。…嬉しい、です。</t>
         </is>
       </c>
     </row>
     <row r="158" ht="40" customHeight="1">
       <c r="A158" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.A.polite.shy[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.C.polite.shy[1]</t>
         </is>
       </c>
       <c r="B158" t="inlineStr" s="2">
@@ -5388,7 +5388,7 @@
       </c>
       <c r="D158" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.A.polite.shy[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.C.polite.shy[1]</t>
         </is>
       </c>
       <c r="E158" t="inlineStr" s="2">
@@ -5398,14 +5398,14 @@
       </c>
       <c r="F158" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…はい…ごめんなさい。</t>
+          <t xml:space="preserve">…あの、ありがとうございます。…嬉しいです。</t>
         </is>
       </c>
     </row>
     <row r="159" ht="40" customHeight="1">
       <c r="A159" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.B.polite.shy[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.A.polite.shy[1]</t>
         </is>
       </c>
       <c r="B159" t="inlineStr" s="2">
@@ -5420,7 +5420,7 @@
       </c>
       <c r="D159" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.B.polite.shy[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.A.polite.shy[1]</t>
         </is>
       </c>
       <c r="E159" t="inlineStr" s="2">
@@ -5430,14 +5430,14 @@
       </c>
       <c r="F159" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（…俯いて、口を閉ざした）</t>
+          <t xml:space="preserve">…はい…ありがとうございます。…休ませて、いただきます。</t>
         </is>
       </c>
     </row>
     <row r="160" ht="40" customHeight="1">
       <c r="A160" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.C.polite.shy[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.B.polite.shy[1]</t>
         </is>
       </c>
       <c r="B160" t="inlineStr" s="2">
@@ -5452,7 +5452,7 @@
       </c>
       <c r="D160" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.C.polite.shy[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.B.polite.shy[1]</t>
         </is>
       </c>
       <c r="E160" t="inlineStr" s="2">
@@ -5462,14 +5462,14 @@
       </c>
       <c r="F160" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…あの、ありがとうございます。…嬉しいです。</t>
+          <t xml:space="preserve">…はい…大丈夫、です。</t>
         </is>
       </c>
     </row>
     <row r="161" ht="40" customHeight="1">
       <c r="A161" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.A.polite.shy[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.C.polite.shy[1]</t>
         </is>
       </c>
       <c r="B161" t="inlineStr" s="2">
@@ -5484,7 +5484,7 @@
       </c>
       <c r="D161" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.A.polite.shy[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.C.polite.shy[1]</t>
         </is>
       </c>
       <c r="E161" t="inlineStr" s="2">
@@ -5494,14 +5494,14 @@
       </c>
       <c r="F161" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…はい…ごめんなさい、加減します。</t>
+          <t xml:space="preserve">…あの、ありがとうございます。…嬉しいです。</t>
         </is>
       </c>
     </row>
     <row r="162" ht="40" customHeight="1">
       <c r="A162" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.B.polite.shy[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.A.polite.shy[1]</t>
         </is>
       </c>
       <c r="B162" t="inlineStr" s="2">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="D162" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.B.polite.shy[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.A.polite.shy[1]</t>
         </is>
       </c>
       <c r="E162" t="inlineStr" s="2">
@@ -5526,14 +5526,14 @@
       </c>
       <c r="F162" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…はい…ありがとうございます。…続けます。</t>
+          <t xml:space="preserve">…はい…ごめんなさい、注意します。</t>
         </is>
       </c>
     </row>
     <row r="163" ht="40" customHeight="1">
       <c r="A163" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.C.polite.shy[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.B.polite.shy[1]</t>
         </is>
       </c>
       <c r="B163" t="inlineStr" s="2">
@@ -5548,7 +5548,7 @@
       </c>
       <c r="D163" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.C.polite.shy[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.B.polite.shy[1]</t>
         </is>
       </c>
       <c r="E163" t="inlineStr" s="2">
@@ -5558,14 +5558,14 @@
       </c>
       <c r="F163" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…あの、ありがとうございます。…嬉しいです。</t>
+          <t xml:space="preserve">…はい…ありがとうございます。</t>
         </is>
       </c>
     </row>
     <row r="164" ht="40" customHeight="1">
       <c r="A164" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES.shy.attack.polite</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.C.polite.shy[1]</t>
         </is>
       </c>
       <c r="B164" t="inlineStr" s="2">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="C164" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D164" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">shy.attack.polite</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.C.polite.shy[1]</t>
         </is>
       </c>
       <c r="E164" t="inlineStr" s="2">
@@ -5590,14 +5590,14 @@
       </c>
       <c r="F164" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの、もう…ご一緒には、いられません…</t>
+          <t xml:space="preserve">…あの、ありがとうございます。…嬉しいです。</t>
         </is>
       </c>
     </row>
     <row r="165" ht="40" customHeight="1">
       <c r="A165" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES.shy.defend.polite</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.A.polite.shy[1]</t>
         </is>
       </c>
       <c r="B165" t="inlineStr" s="2">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="C165" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D165" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">shy.defend.polite</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.A.polite.shy[1]</t>
         </is>
       </c>
       <c r="E165" t="inlineStr" s="2">
@@ -5622,14 +5622,14 @@
       </c>
       <c r="F165" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…やるしか、ないんです</t>
+          <t xml:space="preserve">…はい…ごめんなさい。</t>
         </is>
       </c>
     </row>
     <row r="166" ht="40" customHeight="1">
       <c r="A166" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES.polite.shy[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.B.polite.shy[1]</t>
         </is>
       </c>
       <c r="B166" t="inlineStr" s="2">
@@ -5639,29 +5639,29 @@
       </c>
       <c r="C166" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D166" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.shy[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.B.polite.shy[1]</t>
         </is>
       </c>
       <c r="E166" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F166" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、あの…何かが、変わった気がします…壁を、越えられたかも…しれません…</t>
+          <t xml:space="preserve">（…俯いて、口を閉ざした）</t>
         </is>
       </c>
     </row>
     <row r="167" ht="40" customHeight="1">
       <c r="A167" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BT_HINT_LINES.polite.shy[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.C.polite.shy[1]</t>
         </is>
       </c>
       <c r="B167" t="inlineStr" s="2">
@@ -5671,29 +5671,29 @@
       </c>
       <c r="C167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BT_HINT_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D167" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.shy[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.C.polite.shy[1]</t>
         </is>
       </c>
       <c r="E167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F167" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最近…なにかが、掴めそうな…そんな気がするんです…</t>
+          <t xml:space="preserve">…あの、ありがとうございます。…嬉しいです。</t>
         </is>
       </c>
     </row>
     <row r="168" ht="40" customHeight="1">
       <c r="A168" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES.fresh.polite.shy[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.A.polite.shy[1]</t>
         </is>
       </c>
       <c r="B168" t="inlineStr" s="2">
@@ -5703,29 +5703,29 @@
       </c>
       <c r="C168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D168" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fresh.polite.shy[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.A.polite.shy[1]</t>
         </is>
       </c>
       <c r="E168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F168" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、あの…今日は体が軽くて…もっと、やれます…！</t>
+          <t xml:space="preserve">…はい…ごめんなさい、加減します。</t>
         </is>
       </c>
     </row>
     <row r="169" ht="40" customHeight="1">
       <c r="A169" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES.heavy.polite.shy[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.B.polite.shy[1]</t>
         </is>
       </c>
       <c r="B169" t="inlineStr" s="2">
@@ -5735,29 +5735,29 @@
       </c>
       <c r="C169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D169" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heavy.polite.shy[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.B.polite.shy[1]</t>
         </is>
       </c>
       <c r="E169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F169" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">すみません…動けてはいるんですけど…空回りしてしまって</t>
+          <t xml:space="preserve">…はい…ありがとうございます。…続けます。</t>
         </is>
       </c>
     </row>
     <row r="170" ht="40" customHeight="1">
       <c r="A170" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES.warm.polite.shy[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.C.polite.shy[1]</t>
         </is>
       </c>
       <c r="B170" t="inlineStr" s="2">
@@ -5767,29 +5767,29 @@
       </c>
       <c r="C170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D170" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">warm.polite.shy[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.C.polite.shy[1]</t>
         </is>
       </c>
       <c r="E170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F170" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの…できてはいるんです。ただ、残らなくて…</t>
+          <t xml:space="preserve">…あの、ありがとうございます。…嬉しいです。</t>
         </is>
       </c>
     </row>
     <row r="171" ht="40" customHeight="1">
       <c r="A171" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES.polite.shy[1]</t>
+          <t xml:space="preserve">FACTION_F02_LINES.shy.attack.polite</t>
         </is>
       </c>
       <c r="B171" t="inlineStr" s="2">
@@ -5799,29 +5799,29 @@
       </c>
       <c r="C171" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
+          <t xml:space="preserve">FACTION_F02_LINES</t>
         </is>
       </c>
       <c r="D171" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.shy[1]</t>
+          <t xml:space="preserve">shy.attack.polite</t>
         </is>
       </c>
       <c r="E171" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F171" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">な、なんだか…やる気が、出ません…ご、ごめんなさい…</t>
+          <t xml:space="preserve">あの、もう…ご一緒には、いられません…</t>
         </is>
       </c>
     </row>
     <row r="172" ht="40" customHeight="1">
       <c r="A172" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.polite.shy[1]</t>
+          <t xml:space="preserve">FACTION_F02_LINES.shy.defend.polite</t>
         </is>
       </c>
       <c r="B172" t="inlineStr" s="2">
@@ -5831,29 +5831,29 @@
       </c>
       <c r="C172" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
+          <t xml:space="preserve">FACTION_F02_LINES</t>
         </is>
       </c>
       <c r="D172" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.shy[1]</t>
+          <t xml:space="preserve">shy.defend.polite</t>
         </is>
       </c>
       <c r="E172" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F172" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、あの…また、頑張ろうって思えてきました…</t>
+          <t xml:space="preserve">…やるしか、ないんです</t>
         </is>
       </c>
     </row>
     <row r="173" ht="40" customHeight="1">
       <c r="A173" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES.polite.shy[1]</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES.polite.shy[1]</t>
         </is>
       </c>
       <c r="B173" t="inlineStr" s="2">
@@ -5863,7 +5863,7 @@
       </c>
       <c r="C173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES</t>
         </is>
       </c>
       <c r="D173" t="inlineStr" s="12">
@@ -5878,14 +5878,14 @@
       </c>
       <c r="F173" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やっと…調子が、戻ってきました…</t>
+          <t xml:space="preserve">あ、あの…何かが、変わった気がします…壁を、越えられたかも…しれません…</t>
         </is>
       </c>
     </row>
     <row r="174" ht="40" customHeight="1">
       <c r="A174" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.defeat.polite.shy[1]</t>
+          <t xml:space="preserve">BT_HINT_LINES.polite.shy[1]</t>
         </is>
       </c>
       <c r="B174" t="inlineStr" s="2">
@@ -5895,12 +5895,12 @@
       </c>
       <c r="C174" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">BT_HINT_LINES</t>
         </is>
       </c>
       <c r="D174" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defeat.polite.shy[1]</t>
+          <t xml:space="preserve">polite.shy[1]</t>
         </is>
       </c>
       <c r="E174" t="inlineStr" s="2">
@@ -5910,14 +5910,14 @@
       </c>
       <c r="F174" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ま、負けが続いて…自信が、なくなりそうです…</t>
+          <t xml:space="preserve">最近…なにかが、掴めそうな…そんな気がするんです…</t>
         </is>
       </c>
     </row>
     <row r="175" ht="40" customHeight="1">
       <c r="A175" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery.polite.shy[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.fresh.polite.shy[1]</t>
         </is>
       </c>
       <c r="B175" t="inlineStr" s="2">
@@ -5927,12 +5927,12 @@
       </c>
       <c r="C175" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
         </is>
       </c>
       <c r="D175" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_moderate_recovery.polite.shy[1]</t>
+          <t xml:space="preserve">fresh.polite.shy[1]</t>
         </is>
       </c>
       <c r="E175" t="inlineStr" s="2">
@@ -5942,14 +5942,14 @@
       </c>
       <c r="F175" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">け、怪我が治って…でも、まだ感覚が戻りません…</t>
+          <t xml:space="preserve">あ、あの…今日は体が軽くて…もっと、やれます…！</t>
         </is>
       </c>
     </row>
     <row r="176" ht="40" customHeight="1">
       <c r="A176" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery.polite.shy[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.heavy.polite.shy[1]</t>
         </is>
       </c>
       <c r="B176" t="inlineStr" s="2">
@@ -5959,12 +5959,12 @@
       </c>
       <c r="C176" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
         </is>
       </c>
       <c r="D176" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_severe_recovery.polite.shy[1]</t>
+          <t xml:space="preserve">heavy.polite.shy[1]</t>
         </is>
       </c>
       <c r="E176" t="inlineStr" s="2">
@@ -5974,14 +5974,14 @@
       </c>
       <c r="F176" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お、大きな怪我から復帰しました…でも、不安です…</t>
+          <t xml:space="preserve">すみません…動けてはいるんですけど…空回りしてしまって</t>
         </is>
       </c>
     </row>
     <row r="177" ht="40" customHeight="1">
       <c r="A177" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.penalty_end.polite.shy[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.warm.polite.shy[1]</t>
         </is>
       </c>
       <c r="B177" t="inlineStr" s="2">
@@ -5991,12 +5991,12 @@
       </c>
       <c r="C177" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
         </is>
       </c>
       <c r="D177" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">penalty_end.polite.shy[1]</t>
+          <t xml:space="preserve">warm.polite.shy[1]</t>
         </is>
       </c>
       <c r="E177" t="inlineStr" s="2">
@@ -6006,14 +6006,14 @@
       </c>
       <c r="F177" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">け、謹慎が明けました…ま、また頑張ります…</t>
+          <t xml:space="preserve">あの…できてはいるんです。ただ、残らなくて…</t>
         </is>
       </c>
     </row>
     <row r="178" ht="40" customHeight="1">
       <c r="A178" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.autumnWarChampion.polite.shy[1]</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES.polite.shy[1]</t>
         </is>
       </c>
       <c r="B178" t="inlineStr" s="2">
@@ -6023,29 +6023,29 @@
       </c>
       <c r="C178" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
         </is>
       </c>
       <c r="D178" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">autumnWarChampion.polite.shy[1]</t>
+          <t xml:space="preserve">polite.shy[1]</t>
         </is>
       </c>
       <c r="E178" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F178" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">仲間の声があったから、最後まで頑張れました。</t>
+          <t xml:space="preserve">な、なんだか…やる気が、出ません…ご、ごめんなさい…</t>
         </is>
       </c>
     </row>
     <row r="179" ht="40" customHeight="1">
       <c r="A179" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.bestMatch.polite.shy[1]</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.polite.shy[1]</t>
         </is>
       </c>
       <c r="B179" t="inlineStr" s="2">
@@ -6055,29 +6055,29 @@
       </c>
       <c r="C179" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
         </is>
       </c>
       <c r="D179" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bestMatch.polite.shy[1]</t>
+          <t xml:space="preserve">polite.shy[1]</t>
         </is>
       </c>
       <c r="E179" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F179" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、あの…ベストバウトに選んでいただけるなんて…相手の方のおかげです…</t>
+          <t xml:space="preserve">あ、あの…また、頑張ろうって思えてきました…</t>
         </is>
       </c>
     </row>
     <row r="180" ht="40" customHeight="1">
       <c r="A180" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.champion.polite.shy[1]</t>
+          <t xml:space="preserve">SLUMP_END_LINES.polite.shy[1]</t>
         </is>
       </c>
       <c r="B180" t="inlineStr" s="2">
@@ -6087,29 +6087,29 @@
       </c>
       <c r="C180" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_END_LINES</t>
         </is>
       </c>
       <c r="D180" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.polite.shy[1]</t>
+          <t xml:space="preserve">polite.shy[1]</t>
         </is>
       </c>
       <c r="E180" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F180" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わ、わたしが…チャンピオンに…？ こ、このベルトを汚さないように頑張ります…</t>
+          <t xml:space="preserve">やっと…調子が、戻ってきました…</t>
         </is>
       </c>
     </row>
     <row r="181" ht="40" customHeight="1">
       <c r="A181" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.hallOfFame.polite.shy[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.defeat.polite.shy[1]</t>
         </is>
       </c>
       <c r="B181" t="inlineStr" s="2">
@@ -6119,29 +6119,29 @@
       </c>
       <c r="C181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D181" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hallOfFame.polite.shy[1]</t>
+          <t xml:space="preserve">defeat.polite.shy[1]</t>
         </is>
       </c>
       <c r="E181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F181" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">で、殿堂入り…ですか…？ わたしなんかが…本当に、いいんでしょうか…</t>
+          <t xml:space="preserve">ま、負けが続いて…自信が、なくなりそうです…</t>
         </is>
       </c>
     </row>
     <row r="182" ht="40" customHeight="1">
       <c r="A182" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mediaAward.polite.shy[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery.polite.shy[1]</t>
         </is>
       </c>
       <c r="B182" t="inlineStr" s="2">
@@ -6151,29 +6151,29 @@
       </c>
       <c r="C182" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D182" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mediaAward.polite.shy[1]</t>
+          <t xml:space="preserve">injury_moderate_recovery.polite.shy[1]</t>
         </is>
       </c>
       <c r="E182" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F182" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">メディアの方々に…評価していただけて…あ、あの、本当に光栄です…</t>
+          <t xml:space="preserve">け、怪我が治って…でも、まだ感覚が戻りません…</t>
         </is>
       </c>
     </row>
     <row r="183" ht="40" customHeight="1">
       <c r="A183" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mvp.polite.shy[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery.polite.shy[1]</t>
         </is>
       </c>
       <c r="B183" t="inlineStr" s="2">
@@ -6183,29 +6183,29 @@
       </c>
       <c r="C183" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D183" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mvp.polite.shy[1]</t>
+          <t xml:space="preserve">injury_severe_recovery.polite.shy[1]</t>
         </is>
       </c>
       <c r="E183" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F183" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">M、MVP…ですか…？ そ、そんな大それた賞、わたしには…</t>
+          <t xml:space="preserve">お、大きな怪我から復帰しました…でも、不安です…</t>
         </is>
       </c>
     </row>
     <row r="184" ht="40" customHeight="1">
       <c r="A184" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.rookie.polite.shy[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.penalty_end.polite.shy[1]</t>
         </is>
       </c>
       <c r="B184" t="inlineStr" s="2">
@@ -6215,29 +6215,29 @@
       </c>
       <c r="C184" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D184" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rookie.polite.shy[1]</t>
+          <t xml:space="preserve">penalty_end.polite.shy[1]</t>
         </is>
       </c>
       <c r="E184" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F184" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">え…わたし、ですか…？ …ありがとうございます…</t>
+          <t xml:space="preserve">け、謹慎が明けました…ま、また頑張ります…</t>
         </is>
       </c>
     </row>
     <row r="185" ht="40" customHeight="1">
       <c r="A185" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.springTagChampion.polite.shy[1]</t>
+          <t xml:space="preserve">AWARD_LINES.autumnWarChampion.polite.shy[1]</t>
         </is>
       </c>
       <c r="B185" t="inlineStr" s="2">
@@ -6252,7 +6252,7 @@
       </c>
       <c r="D185" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">springTagChampion.polite.shy[1]</t>
+          <t xml:space="preserve">autumnWarChampion.polite.shy[1]</t>
         </is>
       </c>
       <c r="E185" t="inlineStr" s="2">
@@ -6262,14 +6262,14 @@
       </c>
       <c r="F185" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">相棒が隣にいてくれたので、落ち着いて戦えました。</t>
+          <t xml:space="preserve">仲間の声があったから、最後まで頑張れました。</t>
         </is>
       </c>
     </row>
     <row r="186" ht="40" customHeight="1">
       <c r="A186" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.polite.shy[1]</t>
+          <t xml:space="preserve">AWARD_LINES.bestMatch.polite.shy[1]</t>
         </is>
       </c>
       <c r="B186" t="inlineStr" s="2">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="C186" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D186" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.shy[1]</t>
+          <t xml:space="preserve">bestMatch.polite.shy[1]</t>
         </is>
       </c>
       <c r="E186" t="inlineStr" s="2">
@@ -6294,14 +6294,14 @@
       </c>
       <c r="F186" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの…ありがとうございます、ここまで連れてきてくださって</t>
+          <t xml:space="preserve">あ、あの…ベストバウトに選んでいただけるなんて…相手の方のおかげです…</t>
         </is>
       </c>
     </row>
     <row r="187" ht="40" customHeight="1">
       <c r="A187" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.polite.shy[2]</t>
+          <t xml:space="preserve">AWARD_LINES.champion.polite.shy[1]</t>
         </is>
       </c>
       <c r="B187" t="inlineStr" s="2">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="C187" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D187" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.shy[2]</t>
+          <t xml:space="preserve">champion.polite.shy[1]</t>
         </is>
       </c>
       <c r="E187" t="inlineStr" s="2">
@@ -6326,14 +6326,14 @@
       </c>
       <c r="F187" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…精一杯、やります</t>
+          <t xml:space="preserve">わ、わたしが…チャンピオンに…？ こ、このベルトを汚さないように頑張ります…</t>
         </is>
       </c>
     </row>
     <row r="188" ht="40" customHeight="1">
       <c r="A188" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.polite.shy[3]</t>
+          <t xml:space="preserve">AWARD_LINES.hallOfFame.polite.shy[1]</t>
         </is>
       </c>
       <c r="B188" t="inlineStr" s="2">
@@ -6343,12 +6343,12 @@
       </c>
       <c r="C188" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D188" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.shy[3]</t>
+          <t xml:space="preserve">hallOfFame.polite.shy[1]</t>
         </is>
       </c>
       <c r="E188" t="inlineStr" s="2">
@@ -6358,14 +6358,14 @@
       </c>
       <c r="F188" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…この恩は、一生、忘れません</t>
+          <t xml:space="preserve">で、殿堂入り…ですか…？ わたしなんかが…本当に、いいんでしょうか…</t>
         </is>
       </c>
     </row>
     <row r="189" ht="40" customHeight="1">
       <c r="A189" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.polite.shy[1]</t>
+          <t xml:space="preserve">AWARD_LINES.mediaAward.polite.shy[1]</t>
         </is>
       </c>
       <c r="B189" t="inlineStr" s="2">
@@ -6375,12 +6375,12 @@
       </c>
       <c r="C189" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D189" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.shy[1]</t>
+          <t xml:space="preserve">mediaAward.polite.shy[1]</t>
         </is>
       </c>
       <c r="E189" t="inlineStr" s="2">
@@ -6390,14 +6390,14 @@
       </c>
       <c r="F189" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…満員、ありがとうございます…ありがとうございます…</t>
+          <t xml:space="preserve">メディアの方々に…評価していただけて…あ、あの、本当に光栄です…</t>
         </is>
       </c>
     </row>
     <row r="190" ht="40" customHeight="1">
       <c r="A190" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.polite.shy[2]</t>
+          <t xml:space="preserve">AWARD_LINES.mvp.polite.shy[1]</t>
         </is>
       </c>
       <c r="B190" t="inlineStr" s="2">
@@ -6407,12 +6407,12 @@
       </c>
       <c r="C190" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D190" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.shy[2]</t>
+          <t xml:space="preserve">mvp.polite.shy[1]</t>
         </is>
       </c>
       <c r="E190" t="inlineStr" s="2">
@@ -6422,14 +6422,14 @@
       </c>
       <c r="F190" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…こんなわたしを、応援してくださって…</t>
+          <t xml:space="preserve">M、MVP…ですか…？ そ、そんな大それた賞、わたしには…</t>
         </is>
       </c>
     </row>
     <row r="191" ht="40" customHeight="1">
       <c r="A191" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.polite.shy[3]</t>
+          <t xml:space="preserve">AWARD_LINES.rookie.polite.shy[1]</t>
         </is>
       </c>
       <c r="B191" t="inlineStr" s="2">
@@ -6439,12 +6439,12 @@
       </c>
       <c r="C191" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D191" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.shy[3]</t>
+          <t xml:space="preserve">rookie.polite.shy[1]</t>
         </is>
       </c>
       <c r="E191" t="inlineStr" s="2">
@@ -6454,14 +6454,14 @@
       </c>
       <c r="F191" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…この恩、一生忘れません…</t>
+          <t xml:space="preserve">え…わたし、ですか…？ …ありがとうございます…</t>
         </is>
       </c>
     </row>
     <row r="192" ht="40" customHeight="1">
       <c r="A192" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N1.polite.shy[1]</t>
+          <t xml:space="preserve">AWARD_LINES.springTagChampion.polite.shy[1]</t>
         </is>
       </c>
       <c r="B192" t="inlineStr" s="2">
@@ -6471,29 +6471,29 @@
       </c>
       <c r="C192" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D192" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N1.polite.shy[1]</t>
+          <t xml:space="preserve">springTagChampion.polite.shy[1]</t>
         </is>
       </c>
       <c r="E192" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F192" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、あの…お知らせがあります…</t>
+          <t xml:space="preserve">相棒が隣にいてくれたので、落ち着いて戦えました。</t>
         </is>
       </c>
     </row>
     <row r="193" ht="40" customHeight="1">
       <c r="A193" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N2.polite.shy[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.polite.shy[1]</t>
         </is>
       </c>
       <c r="B193" t="inlineStr" s="2">
@@ -6503,29 +6503,29 @@
       </c>
       <c r="C193" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D193" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N2.polite.shy[1]</t>
+          <t xml:space="preserve">polite.shy[1]</t>
         </is>
       </c>
       <c r="E193" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F193" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ちょ、ちょっとお伝えしたいことが…</t>
+          <t xml:space="preserve">あの…ありがとうございます、ここまで連れてきてくださって</t>
         </is>
       </c>
     </row>
     <row r="194" ht="40" customHeight="1">
       <c r="A194" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N3.polite.shy[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.polite.shy[2]</t>
         </is>
       </c>
       <c r="B194" t="inlineStr" s="2">
@@ -6535,29 +6535,29 @@
       </c>
       <c r="C194" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D194" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N3.polite.shy[1]</t>
+          <t xml:space="preserve">polite.shy[2]</t>
         </is>
       </c>
       <c r="E194" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F194" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">報告です…あ、あの…</t>
+          <t xml:space="preserve">…精一杯、やります</t>
         </is>
       </c>
     </row>
     <row r="195" ht="40" customHeight="1">
       <c r="A195" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N4.polite.shy[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.polite.shy[3]</t>
         </is>
       </c>
       <c r="B195" t="inlineStr" s="2">
@@ -6567,29 +6567,29 @@
       </c>
       <c r="C195" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D195" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N4.polite.shy[1]</t>
+          <t xml:space="preserve">polite.shy[3]</t>
         </is>
       </c>
       <c r="E195" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F195" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お、大事なお知らせです…</t>
+          <t xml:space="preserve">…この恩は、一生、忘れません</t>
         </is>
       </c>
     </row>
     <row r="196" ht="40" customHeight="1">
       <c r="A196" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.polite.shy[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.polite.shy[1]</t>
         </is>
       </c>
       <c r="B196" t="inlineStr" s="2">
@@ -6599,29 +6599,29 @@
       </c>
       <c r="C196" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D196" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_low.polite.shy[1]</t>
+          <t xml:space="preserve">polite.shy[1]</t>
         </is>
       </c>
       <c r="E196" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F196" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、あの…ちょっと、心配なことが…</t>
+          <t xml:space="preserve">…満員、ありがとうございます…ありがとうございます…</t>
         </is>
       </c>
     </row>
     <row r="197" ht="40" customHeight="1">
       <c r="A197" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.polite.shy[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.polite.shy[2]</t>
         </is>
       </c>
       <c r="B197" t="inlineStr" s="2">
@@ -6631,29 +6631,29 @@
       </c>
       <c r="C197" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D197" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_warning.polite.shy[1]</t>
+          <t xml:space="preserve">polite.shy[2]</t>
         </is>
       </c>
       <c r="E197" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F197" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">き、緊急のお知らせです…！</t>
+          <t xml:space="preserve">…こんなわたしを、応援してくださって…</t>
         </is>
       </c>
     </row>
     <row r="198" ht="40" customHeight="1">
       <c r="A198" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.breakthrough.voice.polite.shy[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.polite.shy[3]</t>
         </is>
       </c>
       <c r="B198" t="inlineStr" s="2">
@@ -6663,29 +6663,29 @@
       </c>
       <c r="C198" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D198" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">breakthrough.voice.polite.shy[1]</t>
+          <t xml:space="preserve">polite.shy[3]</t>
         </is>
       </c>
       <c r="E198" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F198" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…な、何かが、変わった気がします…</t>
+          <t xml:space="preserve">…この恩、一生忘れません…</t>
         </is>
       </c>
     </row>
     <row r="199" ht="40" customHeight="1">
       <c r="A199" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G1.voice.polite.shy[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N1.polite.shy[1]</t>
         </is>
       </c>
       <c r="B199" t="inlineStr" s="2">
@@ -6695,12 +6695,12 @@
       </c>
       <c r="C199" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D199" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G1.voice.polite.shy[1]</t>
+          <t xml:space="preserve">N1.polite.shy[1]</t>
         </is>
       </c>
       <c r="E199" t="inlineStr" s="2">
@@ -6710,14 +6710,14 @@
       </c>
       <c r="F199" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…もう少し、お給料が、上がったらいいな…</t>
+          <t xml:space="preserve">あ、あの…お知らせがあります…</t>
         </is>
       </c>
     </row>
     <row r="200" ht="40" customHeight="1">
       <c r="A200" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G2.voice.polite.shy[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N2.polite.shy[1]</t>
         </is>
       </c>
       <c r="B200" t="inlineStr" s="2">
@@ -6727,12 +6727,12 @@
       </c>
       <c r="C200" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D200" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G2.voice.polite.shy[1]</t>
+          <t xml:space="preserve">N2.polite.shy[1]</t>
         </is>
       </c>
       <c r="E200" t="inlineStr" s="2">
@@ -6742,14 +6742,14 @@
       </c>
       <c r="F200" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ひ、ひとりだと、寂しいです…</t>
+          <t xml:space="preserve">ちょ、ちょっとお伝えしたいことが…</t>
         </is>
       </c>
     </row>
     <row r="201" ht="40" customHeight="1">
       <c r="A201" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G3.voice.polite.shy[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N3.polite.shy[1]</t>
         </is>
       </c>
       <c r="B201" t="inlineStr" s="2">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="C201" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D201" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G3.voice.polite.shy[1]</t>
+          <t xml:space="preserve">N3.polite.shy[1]</t>
         </is>
       </c>
       <c r="E201" t="inlineStr" s="2">
@@ -6774,14 +6774,14 @@
       </c>
       <c r="F201" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…も、もっと注目されないと、ダメですよね…</t>
+          <t xml:space="preserve">報告です…あ、あの…</t>
         </is>
       </c>
     </row>
     <row r="202" ht="40" customHeight="1">
       <c r="A202" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G4.voice.polite.shy[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N4.polite.shy[1]</t>
         </is>
       </c>
       <c r="B202" t="inlineStr" s="2">
@@ -6791,12 +6791,12 @@
       </c>
       <c r="C202" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D202" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G4.voice.polite.shy[1]</t>
+          <t xml:space="preserve">N4.polite.shy[1]</t>
         </is>
       </c>
       <c r="E202" t="inlineStr" s="2">
@@ -6806,14 +6806,14 @@
       </c>
       <c r="F202" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…つ、強くなりたい、です…</t>
+          <t xml:space="preserve">お、大事なお知らせです…</t>
         </is>
       </c>
     </row>
     <row r="203" ht="40" customHeight="1">
       <c r="A203" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R2.voice.polite.shy[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.polite.shy[1]</t>
         </is>
       </c>
       <c r="B203" t="inlineStr" s="2">
@@ -6823,12 +6823,12 @@
       </c>
       <c r="C203" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D203" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R2.voice.polite.shy[1]</t>
+          <t xml:space="preserve">N5_low.polite.shy[1]</t>
         </is>
       </c>
       <c r="E203" t="inlineStr" s="2">
@@ -6838,14 +6838,14 @@
       </c>
       <c r="F203" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…あ、あの人と、また話せたらいいな…</t>
+          <t xml:space="preserve">あ、あの…ちょっと、心配なことが…</t>
         </is>
       </c>
     </row>
     <row r="204" ht="40" customHeight="1">
       <c r="A204" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R3.modal.polite.shy[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.polite.shy[1]</t>
         </is>
       </c>
       <c r="B204" t="inlineStr" s="2">
@@ -6855,12 +6855,12 @@
       </c>
       <c r="C204" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D204" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R3.modal.polite.shy[1]</t>
+          <t xml:space="preserve">N5_warning.polite.shy[1]</t>
         </is>
       </c>
       <c r="E204" t="inlineStr" s="2">
@@ -6870,14 +6870,14 @@
       </c>
       <c r="F204" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、あの…少し、お話できますか…</t>
+          <t xml:space="preserve">き、緊急のお知らせです…！</t>
         </is>
       </c>
     </row>
     <row r="205" ht="40" customHeight="1">
       <c r="A205" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R4.voice.polite.shy[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.breakthrough.voice.polite.shy[1]</t>
         </is>
       </c>
       <c r="B205" t="inlineStr" s="2">
@@ -6892,7 +6892,7 @@
       </c>
       <c r="D205" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R4.voice.polite.shy[1]</t>
+          <t xml:space="preserve">breakthrough.voice.polite.shy[1]</t>
         </is>
       </c>
       <c r="E205" t="inlineStr" s="2">
@@ -6902,14 +6902,14 @@
       </c>
       <c r="F205" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…あ、あの人とは、距離を置きたい、かも…</t>
+          <t xml:space="preserve">…な、何かが、変わった気がします…</t>
         </is>
       </c>
     </row>
     <row r="206" ht="40" customHeight="1">
       <c r="A206" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R5.voice.polite.shy[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G1.voice.polite.shy[1]</t>
         </is>
       </c>
       <c r="B206" t="inlineStr" s="2">
@@ -6924,7 +6924,7 @@
       </c>
       <c r="D206" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R5.voice.polite.shy[1]</t>
+          <t xml:space="preserve">G1.voice.polite.shy[1]</t>
         </is>
       </c>
       <c r="E206" t="inlineStr" s="2">
@@ -6934,14 +6934,14 @@
       </c>
       <c r="F206" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ま、負けたく、ないです…</t>
+          <t xml:space="preserve">…もう少し、お給料が、上がったらいいな…</t>
         </is>
       </c>
     </row>
     <row r="207" ht="40" customHeight="1">
       <c r="A207" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.warVictory.voice.polite.shy[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G2.voice.polite.shy[1]</t>
         </is>
       </c>
       <c r="B207" t="inlineStr" s="2">
@@ -6956,7 +6956,7 @@
       </c>
       <c r="D207" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">warVictory.voice.polite.shy[1]</t>
+          <t xml:space="preserve">G2.voice.polite.shy[1]</t>
         </is>
       </c>
       <c r="E207" t="inlineStr" s="2">
@@ -6966,14 +6966,14 @@
       </c>
       <c r="F207" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…か、勝てて、よかったです…</t>
+          <t xml:space="preserve">…ひ、ひとりだと、寂しいです…</t>
         </is>
       </c>
     </row>
     <row r="208" ht="40" customHeight="1">
       <c r="A208" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus_repeat.polite.shy[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G3.voice.polite.shy[1]</t>
         </is>
       </c>
       <c r="B208" t="inlineStr" s="2">
@@ -6983,29 +6983,29 @@
       </c>
       <c r="C208" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D208" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus_repeat.polite.shy[1]</t>
+          <t xml:space="preserve">G3.voice.polite.shy[1]</t>
         </is>
       </c>
       <c r="E208" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F208" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ま、また…？ そんな、毎回いただいては…申し訳ないです…</t>
+          <t xml:space="preserve">…も、もっと注目されないと、ダメですよね…</t>
         </is>
       </c>
     </row>
     <row r="209" ht="40" customHeight="1">
       <c r="A209" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.polite.shy[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G4.voice.polite.shy[1]</t>
         </is>
       </c>
       <c r="B209" t="inlineStr" s="2">
@@ -7015,29 +7015,29 @@
       </c>
       <c r="C209" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D209" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus.polite.shy[1]</t>
+          <t xml:space="preserve">G4.voice.polite.shy[1]</t>
         </is>
       </c>
       <c r="E209" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F209" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ぼ、ボーナスを…？ あ、ありがとうございます…大切に使わせていただきます…</t>
+          <t xml:space="preserve">…つ、強くなりたい、です…</t>
         </is>
       </c>
     </row>
     <row r="210" ht="40" customHeight="1">
       <c r="A210" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.polite.shy[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R2.voice.polite.shy[1]</t>
         </is>
       </c>
       <c r="B210" t="inlineStr" s="2">
@@ -7047,29 +7047,29 @@
       </c>
       <c r="C210" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D210" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">camp.polite.shy[1]</t>
+          <t xml:space="preserve">R2.voice.polite.shy[1]</t>
         </is>
       </c>
       <c r="E210" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F210" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">が、合宿…ですか…緊張しますけど…頑張ります…！</t>
+          <t xml:space="preserve">…あ、あの人と、また話せたらいいな…</t>
         </is>
       </c>
     </row>
     <row r="211" ht="40" customHeight="1">
       <c r="A211" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.polite.shy[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R3.modal.polite.shy[1]</t>
         </is>
       </c>
       <c r="B211" t="inlineStr" s="2">
@@ -7079,29 +7079,29 @@
       </c>
       <c r="C211" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D211" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage_high_trust.polite.shy[1]</t>
+          <t xml:space="preserve">R3.modal.polite.shy[1]</t>
         </is>
       </c>
       <c r="E211" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F211" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いつも気にかけてくださって…あ、あの、本当に感謝しています…</t>
+          <t xml:space="preserve">あ、あの…少し、お話できますか…</t>
         </is>
       </c>
     </row>
     <row r="212" ht="40" customHeight="1">
       <c r="A212" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.polite.shy[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R4.voice.polite.shy[1]</t>
         </is>
       </c>
       <c r="B212" t="inlineStr" s="2">
@@ -7111,29 +7111,29 @@
       </c>
       <c r="C212" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D212" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage.polite.shy[1]</t>
+          <t xml:space="preserve">R4.voice.polite.shy[1]</t>
         </is>
       </c>
       <c r="E212" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F212" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、ありがとうございます…そう言っていただけると、頑張れます…</t>
+          <t xml:space="preserve">…あ、あの人とは、距離を置きたい、かも…</t>
         </is>
       </c>
     </row>
     <row r="213" ht="40" customHeight="1">
       <c r="A213" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.polite.shy[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R5.voice.polite.shy[1]</t>
         </is>
       </c>
       <c r="B213" t="inlineStr" s="2">
@@ -7143,29 +7143,29 @@
       </c>
       <c r="C213" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D213" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faction_decree.polite.shy[1]</t>
+          <t xml:space="preserve">R5.voice.polite.shy[1]</t>
         </is>
       </c>
       <c r="E213" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F213" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……あの。皆には、わたしから……</t>
+          <t xml:space="preserve">…ま、負けたく、ないです…</t>
         </is>
       </c>
     </row>
     <row r="214" ht="40" customHeight="1">
       <c r="A214" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.polite.shy[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.warVictory.voice.polite.shy[1]</t>
         </is>
       </c>
       <c r="B214" t="inlineStr" s="2">
@@ -7175,29 +7175,29 @@
       </c>
       <c r="C214" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D214" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">media.polite.shy[1]</t>
+          <t xml:space="preserve">warVictory.voice.polite.shy[1]</t>
         </is>
       </c>
       <c r="E214" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F214" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">メ、メディア出演…ですか…き、緊張しますけど…や、やってみます…</t>
+          <t xml:space="preserve">…か、勝てて、よかったです…</t>
         </is>
       </c>
     </row>
     <row r="215" ht="40" customHeight="1">
       <c r="A215" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.polite.shy[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus_repeat.polite.shy[1]</t>
         </is>
       </c>
       <c r="B215" t="inlineStr" s="2">
@@ -7212,7 +7212,7 @@
       </c>
       <c r="D215" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">party.polite.shy[1]</t>
+          <t xml:space="preserve">bonus_repeat.polite.shy[1]</t>
         </is>
       </c>
       <c r="E215" t="inlineStr" s="2">
@@ -7222,14 +7222,14 @@
       </c>
       <c r="F215" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">パ、パーティー…人が多いところは少し苦手ですけど…頑張って参加します…</t>
+          <t xml:space="preserve">ま、また…？ そんな、毎回いただいては…申し訳ないです…</t>
         </is>
       </c>
     </row>
     <row r="216" ht="40" customHeight="1">
       <c r="A216" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.polite.shy[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.polite.shy[1]</t>
         </is>
       </c>
       <c r="B216" t="inlineStr" s="2">
@@ -7244,7 +7244,7 @@
       </c>
       <c r="D216" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refresh_leave.polite.shy[1]</t>
+          <t xml:space="preserve">bonus.polite.shy[1]</t>
         </is>
       </c>
       <c r="E216" t="inlineStr" s="2">
@@ -7254,14 +7254,14 @@
       </c>
       <c r="F216" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お休みを…？ あ、あの…ありがとうございます、ゆっくり休ませていただきます…</t>
+          <t xml:space="preserve">ぼ、ボーナスを…？ あ、ありがとうございます…大切に使わせていただきます…</t>
         </is>
       </c>
     </row>
     <row r="217" ht="40" customHeight="1">
       <c r="A217" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.polite.shy[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.polite.shy[1]</t>
         </is>
       </c>
       <c r="B217" t="inlineStr" s="2">
@@ -7276,7 +7276,7 @@
       </c>
       <c r="D217" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">special_treatment.polite.shy[1]</t>
+          <t xml:space="preserve">camp.polite.shy[1]</t>
         </is>
       </c>
       <c r="E217" t="inlineStr" s="2">
@@ -7286,14 +7286,14 @@
       </c>
       <c r="F217" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こ、こんな特別扱い…わたしなんかに、もったいないです…</t>
+          <t xml:space="preserve">が、合宿…ですか…緊張しますけど…頑張ります…！</t>
         </is>
       </c>
     </row>
     <row r="218" ht="40" customHeight="1">
       <c r="A218" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.polite.shy[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.polite.shy[1]</t>
         </is>
       </c>
       <c r="B218" t="inlineStr" s="2">
@@ -7308,7 +7308,7 @@
       </c>
       <c r="D218" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trainer.polite.shy[1]</t>
+          <t xml:space="preserve">encourage_high_trust.polite.shy[1]</t>
         </is>
       </c>
       <c r="E218" t="inlineStr" s="2">
@@ -7318,14 +7318,14 @@
       </c>
       <c r="F218" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">専属トレーナー…ですか…あ、あの、よろしくお願いいたします…</t>
+          <t xml:space="preserve">いつも気にかけてくださって…あ、あの、本当に感謝しています…</t>
         </is>
       </c>
     </row>
     <row r="219" ht="40" customHeight="1">
       <c r="A219" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.polite.shy[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.polite.shy[1]</t>
         </is>
       </c>
       <c r="B219" t="inlineStr" s="2">
@@ -7335,12 +7335,12 @@
       </c>
       <c r="C219" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D219" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.polite.shy[1]</t>
+          <t xml:space="preserve">encourage.polite.shy[1]</t>
         </is>
       </c>
       <c r="E219" t="inlineStr" s="2">
@@ -7350,14 +7350,14 @@
       </c>
       <c r="F219" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、あの…どうしたら、いいんでしょうか…</t>
+          <t xml:space="preserve">あ、ありがとうございます…そう言っていただけると、頑張れます…</t>
         </is>
       </c>
     </row>
     <row r="220" ht="40" customHeight="1">
       <c r="A220" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E4.polite.shy[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.polite.shy[1]</t>
         </is>
       </c>
       <c r="B220" t="inlineStr" s="2">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="C220" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D220" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E4.polite.shy[1]</t>
+          <t xml:space="preserve">faction_decree.polite.shy[1]</t>
         </is>
       </c>
       <c r="E220" t="inlineStr" s="2">
@@ -7382,14 +7382,14 @@
       </c>
       <c r="F220" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">え、ええと…そ、その件は…</t>
+          <t xml:space="preserve">……あの。皆には、わたしから……</t>
         </is>
       </c>
     </row>
     <row r="221" ht="40" customHeight="1">
       <c r="A221" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.polite.shy[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.polite.shy[1]</t>
         </is>
       </c>
       <c r="B221" t="inlineStr" s="2">
@@ -7399,12 +7399,12 @@
       </c>
       <c r="C221" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D221" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E6.polite.shy[1]</t>
+          <t xml:space="preserve">media.polite.shy[1]</t>
         </is>
       </c>
       <c r="E221" t="inlineStr" s="2">
@@ -7414,14 +7414,14 @@
       </c>
       <c r="F221" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">は、はい…わかりました…やってみます…</t>
+          <t xml:space="preserve">メ、メディア出演…ですか…き、緊張しますけど…や、やってみます…</t>
         </is>
       </c>
     </row>
     <row r="222" ht="40" customHeight="1">
       <c r="A222" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.polite.shy[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.polite.shy[1]</t>
         </is>
       </c>
       <c r="B222" t="inlineStr" s="2">
@@ -7431,12 +7431,12 @@
       </c>
       <c r="C222" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D222" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_boycott.polite.shy[1]</t>
+          <t xml:space="preserve">party.polite.shy[1]</t>
         </is>
       </c>
       <c r="E222" t="inlineStr" s="2">
@@ -7446,14 +7446,14 @@
       </c>
       <c r="F222" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、あの…これは、納得できません…</t>
+          <t xml:space="preserve">パ、パーティー…人が多いところは少し苦手ですけど…頑張って参加します…</t>
         </is>
       </c>
     </row>
     <row r="223" ht="40" customHeight="1">
       <c r="A223" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.polite.shy[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.polite.shy[1]</t>
         </is>
       </c>
       <c r="B223" t="inlineStr" s="2">
@@ -7463,12 +7463,12 @@
       </c>
       <c r="C223" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D223" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_grumble.polite.shy[1]</t>
+          <t xml:space="preserve">refresh_leave.polite.shy[1]</t>
         </is>
       </c>
       <c r="E223" t="inlineStr" s="2">
@@ -7478,14 +7478,14 @@
       </c>
       <c r="F223" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">すみません…少し、不満があります…</t>
+          <t xml:space="preserve">お休みを…？ あ、あの…ありがとうございます、ゆっくり休ませていただきます…</t>
         </is>
       </c>
     </row>
     <row r="224" ht="40" customHeight="1">
       <c r="A224" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.polite.shy[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.polite.shy[1]</t>
         </is>
       </c>
       <c r="B224" t="inlineStr" s="2">
@@ -7495,12 +7495,12 @@
       </c>
       <c r="C224" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D224" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_sns.polite.shy[1]</t>
+          <t xml:space="preserve">special_treatment.polite.shy[1]</t>
         </is>
       </c>
       <c r="E224" t="inlineStr" s="2">
@@ -7510,14 +7510,14 @@
       </c>
       <c r="F224" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">え、SNSで…そんな風に書かれてしまって…</t>
+          <t xml:space="preserve">こ、こんな特別扱い…わたしなんかに、もったいないです…</t>
         </is>
       </c>
     </row>
     <row r="225" ht="40" customHeight="1">
       <c r="A225" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.polite.shy[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.polite.shy[1]</t>
         </is>
       </c>
       <c r="B225" t="inlineStr" s="2">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="C225" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D225" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S1.polite.shy[1]</t>
+          <t xml:space="preserve">trainer.polite.shy[1]</t>
         </is>
       </c>
       <c r="E225" t="inlineStr" s="2">
@@ -7542,14 +7542,14 @@
       </c>
       <c r="F225" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、あの…ご相談したいことが…</t>
+          <t xml:space="preserve">専属トレーナー…ですか…あ、あの、よろしくお願いいたします…</t>
         </is>
       </c>
     </row>
     <row r="226" ht="40" customHeight="1">
       <c r="A226" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.polite.shy[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.polite.shy[1]</t>
         </is>
       </c>
       <c r="B226" t="inlineStr" s="2">
@@ -7564,7 +7564,7 @@
       </c>
       <c r="D226" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S2.polite.shy[1]</t>
+          <t xml:space="preserve">E1.polite.shy[1]</t>
         </is>
       </c>
       <c r="E226" t="inlineStr" s="2">
@@ -7574,14 +7574,14 @@
       </c>
       <c r="F226" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">す、すみません…少しお時間いただけますか…</t>
+          <t xml:space="preserve">あ、あの…どうしたら、いいんでしょうか…</t>
         </is>
       </c>
     </row>
     <row r="227" ht="40" customHeight="1">
       <c r="A227" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.polite.shy[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E4.polite.shy[1]</t>
         </is>
       </c>
       <c r="B227" t="inlineStr" s="2">
@@ -7596,7 +7596,7 @@
       </c>
       <c r="D227" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S3.polite.shy[1]</t>
+          <t xml:space="preserve">E4.polite.shy[1]</t>
         </is>
       </c>
       <c r="E227" t="inlineStr" s="2">
@@ -7606,14 +7606,14 @@
       </c>
       <c r="F227" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、あの…どう答えたらいいか、わからなくて…</t>
+          <t xml:space="preserve">え、ええと…そ、その件は…</t>
         </is>
       </c>
     </row>
     <row r="228" ht="40" customHeight="1">
       <c r="A228" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.polite.shy[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.polite.shy[1]</t>
         </is>
       </c>
       <c r="B228" t="inlineStr" s="2">
@@ -7628,7 +7628,7 @@
       </c>
       <c r="D228" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_direct.polite.shy[1]</t>
+          <t xml:space="preserve">E6.polite.shy[1]</t>
         </is>
       </c>
       <c r="E228" t="inlineStr" s="2">
@@ -7638,14 +7638,14 @@
       </c>
       <c r="F228" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">は、はっきり言わせていただきます…わたしは…</t>
+          <t xml:space="preserve">は、はい…わかりました…やってみます…</t>
         </is>
       </c>
     </row>
     <row r="229" ht="40" customHeight="1">
       <c r="A229" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.polite.shy[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.polite.shy[1]</t>
         </is>
       </c>
       <c r="B229" t="inlineStr" s="2">
@@ -7660,7 +7660,7 @@
       </c>
       <c r="D229" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_silent.polite.shy[1]</t>
+          <t xml:space="preserve">S_boycott.polite.shy[1]</t>
         </is>
       </c>
       <c r="E229" t="inlineStr" s="2">
@@ -7670,14 +7670,14 @@
       </c>
       <c r="F229" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………あの…なにも、言えません…</t>
+          <t xml:space="preserve">あ、あの…これは、納得できません…</t>
         </is>
       </c>
     </row>
     <row r="230" ht="40" customHeight="1">
       <c r="A230" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.polite.shy[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.polite.shy[1]</t>
         </is>
       </c>
       <c r="B230" t="inlineStr" s="2">
@@ -7692,7 +7692,7 @@
       </c>
       <c r="D230" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S5.polite.shy[1]</t>
+          <t xml:space="preserve">S_grumble.polite.shy[1]</t>
         </is>
       </c>
       <c r="E230" t="inlineStr" s="2">
@@ -7702,14 +7702,14 @@
       </c>
       <c r="F230" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">考えさせて…いただけますか…？</t>
+          <t xml:space="preserve">すみません…少し、不満があります…</t>
         </is>
       </c>
     </row>
     <row r="231" ht="40" customHeight="1">
       <c r="A231" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.polite.shy[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.polite.shy[1]</t>
         </is>
       </c>
       <c r="B231" t="inlineStr" s="2">
@@ -7724,7 +7724,7 @@
       </c>
       <c r="D231" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S6.polite.shy[1]</t>
+          <t xml:space="preserve">S_sns.polite.shy[1]</t>
         </is>
       </c>
       <c r="E231" t="inlineStr" s="2">
@@ -7734,14 +7734,14 @@
       </c>
       <c r="F231" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">決めました…これで、いいんですよね…？</t>
+          <t xml:space="preserve">え、SNSで…そんな風に書かれてしまって…</t>
         </is>
       </c>
     </row>
     <row r="232" ht="40" customHeight="1">
       <c r="A232" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.polite.shy[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.polite.shy[1]</t>
         </is>
       </c>
       <c r="B232" t="inlineStr" s="2">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="C232" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D232" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1.polite.shy[1]</t>
+          <t xml:space="preserve">S1.polite.shy[1]</t>
         </is>
       </c>
       <c r="E232" t="inlineStr" s="2">
@@ -7766,14 +7766,14 @@
       </c>
       <c r="F232" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、あの…これから、頑張りたいことがあります…</t>
+          <t xml:space="preserve">あ、あの…ご相談したいことが…</t>
         </is>
       </c>
     </row>
     <row r="233" ht="40" customHeight="1">
       <c r="A233" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.polite.shy[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.polite.shy[1]</t>
         </is>
       </c>
       <c r="B233" t="inlineStr" s="2">
@@ -7783,12 +7783,12 @@
       </c>
       <c r="C233" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D233" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter1.polite.shy[1]</t>
+          <t xml:space="preserve">S2.polite.shy[1]</t>
         </is>
       </c>
       <c r="E233" t="inlineStr" s="2">
@@ -7798,14 +7798,14 @@
       </c>
       <c r="F233" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お、お話を聞かせていただけますか…？</t>
+          <t xml:space="preserve">す、すみません…少しお時間いただけますか…</t>
         </is>
       </c>
     </row>
     <row r="234" ht="40" customHeight="1">
       <c r="A234" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.polite.shy[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.polite.shy[1]</t>
         </is>
       </c>
       <c r="B234" t="inlineStr" s="2">
@@ -7815,12 +7815,12 @@
       </c>
       <c r="C234" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D234" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter2.polite.shy[1]</t>
+          <t xml:space="preserve">S3.polite.shy[1]</t>
         </is>
       </c>
       <c r="E234" t="inlineStr" s="2">
@@ -7830,14 +7830,14 @@
       </c>
       <c r="F234" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">は、はい…お聞きします…</t>
+          <t xml:space="preserve">あ、あの…どう答えたらいいか、わからなくて…</t>
         </is>
       </c>
     </row>
     <row r="235" ht="40" customHeight="1">
       <c r="A235" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.polite.shy[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.polite.shy[1]</t>
         </is>
       </c>
       <c r="B235" t="inlineStr" s="2">
@@ -7847,12 +7847,12 @@
       </c>
       <c r="C235" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D235" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_brand.polite.shy[1]</t>
+          <t xml:space="preserve">S4_direct.polite.shy[1]</t>
         </is>
       </c>
       <c r="E235" t="inlineStr" s="2">
@@ -7862,14 +7862,14 @@
       </c>
       <c r="F235" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ブランドのお仕事…ですか…？ あ、あの、精一杯やらせていただきます…</t>
+          <t xml:space="preserve">は、はっきり言わせていただきます…わたしは…</t>
         </is>
       </c>
     </row>
     <row r="236" ht="40" customHeight="1">
       <c r="A236" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.polite.shy[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.polite.shy[1]</t>
         </is>
       </c>
       <c r="B236" t="inlineStr" s="2">
@@ -7879,12 +7879,12 @@
       </c>
       <c r="C236" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D236" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_cm.polite.shy[1]</t>
+          <t xml:space="preserve">S4_silent.polite.shy[1]</t>
         </is>
       </c>
       <c r="E236" t="inlineStr" s="2">
@@ -7894,14 +7894,14 @@
       </c>
       <c r="F236" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">CM…ですか…？ わ、わたしなんかで、いいんでしょうか…</t>
+          <t xml:space="preserve">………あの…なにも、言えません…</t>
         </is>
       </c>
     </row>
     <row r="237" ht="40" customHeight="1">
       <c r="A237" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.polite.shy[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.polite.shy[1]</t>
         </is>
       </c>
       <c r="B237" t="inlineStr" s="2">
@@ -7911,12 +7911,12 @@
       </c>
       <c r="C237" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D237" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fan.polite.shy[1]</t>
+          <t xml:space="preserve">S5.polite.shy[1]</t>
         </is>
       </c>
       <c r="E237" t="inlineStr" s="2">
@@ -7926,14 +7926,14 @@
       </c>
       <c r="F237" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ファンの方に…直接、お会いできるんですか…？ う、嬉しいです…</t>
+          <t xml:space="preserve">考えさせて…いただけますか…？</t>
         </is>
       </c>
     </row>
     <row r="238" ht="40" customHeight="1">
       <c r="A238" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.polite.shy[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.polite.shy[1]</t>
         </is>
       </c>
       <c r="B238" t="inlineStr" s="2">
@@ -7943,12 +7943,12 @@
       </c>
       <c r="C238" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D238" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fashion.polite.shy[1]</t>
+          <t xml:space="preserve">S6.polite.shy[1]</t>
         </is>
       </c>
       <c r="E238" t="inlineStr" s="2">
@@ -7958,14 +7958,14 @@
       </c>
       <c r="F238" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">フ、ファッション関連のお仕事…似合うでしょうか…</t>
+          <t xml:space="preserve">決めました…これで、いいんですよね…？</t>
         </is>
       </c>
     </row>
     <row r="239" ht="40" customHeight="1">
       <c r="A239" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.polite.shy[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.polite.shy[1]</t>
         </is>
       </c>
       <c r="B239" t="inlineStr" s="2">
@@ -7980,7 +7980,7 @@
       </c>
       <c r="D239" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_gravure.polite.shy[1]</t>
+          <t xml:space="preserve">B1.polite.shy[1]</t>
         </is>
       </c>
       <c r="E239" t="inlineStr" s="2">
@@ -7990,14 +7990,14 @@
       </c>
       <c r="F239" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">グ、グラビア…ですか…？ は、恥ずかしいです…でも、頑張ります…</t>
+          <t xml:space="preserve">あ、あの…これから、頑張りたいことがあります…</t>
         </is>
       </c>
     </row>
     <row r="240" ht="40" customHeight="1">
       <c r="A240" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.polite.shy[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.polite.shy[1]</t>
         </is>
       </c>
       <c r="B240" t="inlineStr" s="2">
@@ -8012,7 +8012,7 @@
       </c>
       <c r="D240" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_variety.polite.shy[1]</t>
+          <t xml:space="preserve">B2_fighter1.polite.shy[1]</t>
         </is>
       </c>
       <c r="E240" t="inlineStr" s="2">
@@ -8022,14 +8022,14 @@
       </c>
       <c r="F240" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">バ、バラエティ番組…ちゃんと、お話できるか不安です…</t>
+          <t xml:space="preserve">お、お話を聞かせていただけますか…？</t>
         </is>
       </c>
     </row>
     <row r="241" ht="40" customHeight="1">
       <c r="A241" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.polite.shy[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.polite.shy[1]</t>
         </is>
       </c>
       <c r="B241" t="inlineStr" s="2">
@@ -8044,7 +8044,7 @@
       </c>
       <c r="D241" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4.polite.shy[1]</t>
+          <t xml:space="preserve">B2_fighter2.polite.shy[1]</t>
         </is>
       </c>
       <c r="E241" t="inlineStr" s="2">
@@ -8054,14 +8054,14 @@
       </c>
       <c r="F241" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こ、こんなお仕事、わたしに務まるでしょうか…</t>
+          <t xml:space="preserve">は、はい…お聞きします…</t>
         </is>
       </c>
     </row>
     <row r="242" ht="40" customHeight="1">
       <c r="A242" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.polite.shy[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.polite.shy[1]</t>
         </is>
       </c>
       <c r="B242" t="inlineStr" s="2">
@@ -8071,29 +8071,29 @@
       </c>
       <c r="C242" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D242" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.shy[1]</t>
+          <t xml:space="preserve">B4_brand.polite.shy[1]</t>
         </is>
       </c>
       <c r="E242" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F242" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、あの…わたしなどでよろしければ…せ、精一杯務めます…</t>
+          <t xml:space="preserve">ブランドのお仕事…ですか…？ あ、あの、精一杯やらせていただきます…</t>
         </is>
       </c>
     </row>
     <row r="243" ht="40" customHeight="1">
       <c r="A243" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.polite.shy[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.polite.shy[1]</t>
         </is>
       </c>
       <c r="B243" t="inlineStr" s="2">
@@ -8103,29 +8103,29 @@
       </c>
       <c r="C243" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D243" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.shy[1]</t>
+          <t xml:space="preserve">B4_cm.polite.shy[1]</t>
         </is>
       </c>
       <c r="E243" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F243" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、あの…よ、よろしくお願いいたします…</t>
+          <t xml:space="preserve">CM…ですか…？ わ、わたしなんかで、いいんでしょうか…</t>
         </is>
       </c>
     </row>
     <row r="244" ht="40" customHeight="1">
       <c r="A244" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.polite.shy[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.polite.shy[1]</t>
         </is>
       </c>
       <c r="B244" t="inlineStr" s="2">
@@ -8135,29 +8135,29 @@
       </c>
       <c r="C244" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D244" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.shy[1]</t>
+          <t xml:space="preserve">B4_fan.polite.shy[1]</t>
         </is>
       </c>
       <c r="E244" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F244" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、あの…よろしくお願いいたします…精一杯やります…</t>
+          <t xml:space="preserve">ファンの方に…直接、お会いできるんですか…？ う、嬉しいです…</t>
         </is>
       </c>
     </row>
     <row r="245" ht="40" customHeight="1">
       <c r="A245" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.polite.shy[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.polite.shy[1]</t>
         </is>
       </c>
       <c r="B245" t="inlineStr" s="2">
@@ -8167,29 +8167,29 @@
       </c>
       <c r="C245" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D245" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.shy[1]</t>
+          <t xml:space="preserve">B4_fashion.polite.shy[1]</t>
         </is>
       </c>
       <c r="E245" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F245" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よ、よろしくお願いいたします…が、頑張ります…！</t>
+          <t xml:space="preserve">フ、ファッション関連のお仕事…似合うでしょうか…</t>
         </is>
       </c>
     </row>
     <row r="246" ht="40" customHeight="1">
       <c r="A246" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.polite.shy[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.polite.shy[1]</t>
         </is>
       </c>
       <c r="B246" t="inlineStr" s="2">
@@ -8199,29 +8199,29 @@
       </c>
       <c r="C246" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D246" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.shy[1]</t>
+          <t xml:space="preserve">B4_gravure.polite.shy[1]</t>
         </is>
       </c>
       <c r="E246" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F246" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">す、すみません…少しだけ休ませてください…</t>
+          <t xml:space="preserve">グ、グラビア…ですか…？ は、恥ずかしいです…でも、頑張ります…</t>
         </is>
       </c>
     </row>
     <row r="247" ht="40" customHeight="1">
       <c r="A247" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.polite.shy[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.polite.shy[1]</t>
         </is>
       </c>
       <c r="B247" t="inlineStr" s="2">
@@ -8231,29 +8231,29 @@
       </c>
       <c r="C247" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D247" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.ahead.polite.shy[1]</t>
+          <t xml:space="preserve">B4_variety.polite.shy[1]</t>
         </is>
       </c>
       <c r="E247" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F247" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝たせて…いただきました。…なのに、怖いままです…</t>
+          <t xml:space="preserve">バ、バラエティ番組…ちゃんと、お話できるか不安です…</t>
         </is>
       </c>
     </row>
     <row r="248" ht="40" customHeight="1">
       <c r="A248" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.polite.shy[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.polite.shy[1]</t>
         </is>
       </c>
       <c r="B248" t="inlineStr" s="2">
@@ -8263,29 +8263,29 @@
       </c>
       <c r="C248" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D248" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.behind.polite.shy[1]</t>
+          <t xml:space="preserve">B4.polite.shy[1]</t>
         </is>
       </c>
       <c r="E248" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F248" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…もう終わったって…言われました。…言われただけです…</t>
+          <t xml:space="preserve">こ、こんなお仕事、わたしに務まるでしょうか…</t>
         </is>
       </c>
     </row>
     <row r="249" ht="40" customHeight="1">
       <c r="A249" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.polite.shy[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.polite.shy[1]</t>
         </is>
       </c>
       <c r="B249" t="inlineStr" s="2">
@@ -8295,12 +8295,12 @@
       </c>
       <c r="C249" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
         </is>
       </c>
       <c r="D249" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftInterest.polite.shy[1]</t>
+          <t xml:space="preserve">polite.shy[1]</t>
         </is>
       </c>
       <c r="E249" t="inlineStr" s="2">
@@ -8317,7 +8317,7 @@
     <row r="250" ht="40" customHeight="1">
       <c r="A250" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.polite.shy[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.polite.shy[1]</t>
         </is>
       </c>
       <c r="B250" t="inlineStr" s="2">
@@ -8327,12 +8327,12 @@
       </c>
       <c r="C250" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D250" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.polite.shy[1]</t>
+          <t xml:space="preserve">polite.shy[1]</t>
         </is>
       </c>
       <c r="E250" t="inlineStr" s="2">
@@ -8349,7 +8349,7 @@
     <row r="251" ht="40" customHeight="1">
       <c r="A251" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.polite.shy[1]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.polite.shy[1]</t>
         </is>
       </c>
       <c r="B251" t="inlineStr" s="2">
@@ -8359,12 +8359,12 @@
       </c>
       <c r="C251" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
         </is>
       </c>
       <c r="D251" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faGreeting.polite.shy[1]</t>
+          <t xml:space="preserve">polite.shy[1]</t>
         </is>
       </c>
       <c r="E251" t="inlineStr" s="2">
@@ -8374,14 +8374,14 @@
       </c>
       <c r="F251" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、あの…契約してもらえて…感謝しています…！</t>
+          <t xml:space="preserve">あ、あの…よろしくお願いいたします…精一杯やります…</t>
         </is>
       </c>
     </row>
     <row r="252" ht="40" customHeight="1">
       <c r="A252" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.polite.shy[1]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.polite.shy[1]</t>
         </is>
       </c>
       <c r="B252" t="inlineStr" s="2">
@@ -8391,12 +8391,12 @@
       </c>
       <c r="C252" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
         </is>
       </c>
       <c r="D252" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faSigning.polite.shy[1]</t>
+          <t xml:space="preserve">polite.shy[1]</t>
         </is>
       </c>
       <c r="E252" t="inlineStr" s="2">
@@ -8406,14 +8406,14 @@
       </c>
       <c r="F252" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、あの…よろしくお願いいたします…精一杯やります…</t>
+          <t xml:space="preserve">よ、よろしくお願いいたします…が、頑張ります…！</t>
         </is>
       </c>
     </row>
     <row r="253" ht="40" customHeight="1">
       <c r="A253" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.polite.shy[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.polite.shy[1]</t>
         </is>
       </c>
       <c r="B253" t="inlineStr" s="2">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="C253" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D253" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faWelcome.polite.shy[1]</t>
+          <t xml:space="preserve">polite.shy[1]</t>
         </is>
       </c>
       <c r="E253" t="inlineStr" s="2">
@@ -8438,14 +8438,14 @@
       </c>
       <c r="F253" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よ、よろしくお願いいたします…が、頑張ります…！</t>
+          <t xml:space="preserve">す、すみません…少しだけ休ませてください…</t>
         </is>
       </c>
     </row>
     <row r="254" ht="40" customHeight="1">
       <c r="A254" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.fresh.polite.shy[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.polite.shy[1]</t>
         </is>
       </c>
       <c r="B254" t="inlineStr" s="2">
@@ -8460,7 +8460,7 @@
       </c>
       <c r="D254" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.fresh.polite.shy[1]</t>
+          <t xml:space="preserve">bitterPrematch.ahead.polite.shy[1]</t>
         </is>
       </c>
       <c r="E254" t="inlineStr" s="2">
@@ -8470,14 +8470,14 @@
       </c>
       <c r="F254" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、あの…今日は体が軽くて…もっと、やれます…！</t>
+          <t xml:space="preserve">勝たせて…いただきました。…なのに、怖いままです…</t>
         </is>
       </c>
     </row>
     <row r="255" ht="40" customHeight="1">
       <c r="A255" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.heavy.polite.shy[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.polite.shy[1]</t>
         </is>
       </c>
       <c r="B255" t="inlineStr" s="2">
@@ -8492,7 +8492,7 @@
       </c>
       <c r="D255" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.heavy.polite.shy[1]</t>
+          <t xml:space="preserve">bitterPrematch.behind.polite.shy[1]</t>
         </is>
       </c>
       <c r="E255" t="inlineStr" s="2">
@@ -8502,14 +8502,14 @@
       </c>
       <c r="F255" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">すみません…動けてはいるんですけど…空回りしてしまって</t>
+          <t xml:space="preserve">…もう終わったって…言われました。…言われただけです…</t>
         </is>
       </c>
     </row>
     <row r="256" ht="40" customHeight="1">
       <c r="A256" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.warm.polite.shy[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.polite.shy[1]</t>
         </is>
       </c>
       <c r="B256" t="inlineStr" s="2">
@@ -8524,7 +8524,7 @@
       </c>
       <c r="D256" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.warm.polite.shy[1]</t>
+          <t xml:space="preserve">draftInterest.polite.shy[1]</t>
         </is>
       </c>
       <c r="E256" t="inlineStr" s="2">
@@ -8534,14 +8534,14 @@
       </c>
       <c r="F256" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの…できてはいるんです。ただ、残らなくて…</t>
+          <t xml:space="preserve">あ、あの…わたしなどでよろしければ…せ、精一杯務めます…</t>
         </is>
       </c>
     </row>
     <row r="257" ht="40" customHeight="1">
       <c r="A257" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.polite.shy[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.polite.shy[1]</t>
         </is>
       </c>
       <c r="B257" t="inlineStr" s="2">
@@ -8556,7 +8556,7 @@
       </c>
       <c r="D257" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.polite.shy[1]</t>
+          <t xml:space="preserve">draftJoin.polite.shy[1]</t>
         </is>
       </c>
       <c r="E257" t="inlineStr" s="2">
@@ -8566,14 +8566,14 @@
       </c>
       <c r="F257" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">す、すみません…少しだけ休ませてください…</t>
+          <t xml:space="preserve">あ、あの…よ、よろしくお願いいたします…</t>
         </is>
       </c>
     </row>
     <row r="258" ht="40" customHeight="1">
       <c r="A258" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.polite.shy[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.polite.shy[1]</t>
         </is>
       </c>
       <c r="B258" t="inlineStr" s="2">
@@ -8588,7 +8588,7 @@
       </c>
       <c r="D258" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.polite.shy[1]</t>
+          <t xml:space="preserve">faGreeting.polite.shy[1]</t>
         </is>
       </c>
       <c r="E258" t="inlineStr" s="2">
@@ -8598,14 +8598,14 @@
       </c>
       <c r="F258" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ご、ごめんなさい…お、お世話になりました…</t>
+          <t xml:space="preserve">あ、あの…契約してもらえて…感謝しています…！</t>
         </is>
       </c>
     </row>
     <row r="259" ht="40" customHeight="1">
       <c r="A259" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.polite.shy[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.polite.shy[1]</t>
         </is>
       </c>
       <c r="B259" t="inlineStr" s="2">
@@ -8620,7 +8620,7 @@
       </c>
       <c r="D259" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreeting.polite.shy[1]</t>
+          <t xml:space="preserve">faSigning.polite.shy[1]</t>
         </is>
       </c>
       <c r="E259" t="inlineStr" s="2">
@@ -8630,14 +8630,14 @@
       </c>
       <c r="F259" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、あの…短い間ではございますが…よろしくお願いいたします…</t>
+          <t xml:space="preserve">あ、あの…よろしくお願いいたします…精一杯やります…</t>
         </is>
       </c>
     </row>
     <row r="260" ht="40" customHeight="1">
       <c r="A260" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.polite.shy[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.polite.shy[1]</t>
         </is>
       </c>
       <c r="B260" t="inlineStr" s="2">
@@ -8652,7 +8652,7 @@
       </c>
       <c r="D260" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">scoutGreeting.polite.shy[1]</t>
+          <t xml:space="preserve">faWelcome.polite.shy[1]</t>
         </is>
       </c>
       <c r="E260" t="inlineStr" s="2">
@@ -8662,14 +8662,14 @@
       </c>
       <c r="F260" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、あの…お声がけ、光栄です…！</t>
+          <t xml:space="preserve">よ、よろしくお願いいたします…が、頑張ります…！</t>
         </is>
       </c>
     </row>
     <row r="261" ht="40" customHeight="1">
       <c r="A261" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.polite.shy[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.fresh.polite.shy[1]</t>
         </is>
       </c>
       <c r="B261" t="inlineStr" s="2">
@@ -8684,7 +8684,7 @@
       </c>
       <c r="D261" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleChallengeLoss.polite.shy[1]</t>
+          <t xml:space="preserve">heatSelf.fresh.polite.shy[1]</t>
         </is>
       </c>
       <c r="E261" t="inlineStr" s="2">
@@ -8694,14 +8694,14 @@
       </c>
       <c r="F261" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…申し訳ありません…でも…諦めたくないんです…</t>
+          <t xml:space="preserve">あ、あの…今日は体が軽くて…もっと、やれます…！</t>
         </is>
       </c>
     </row>
     <row r="262" ht="40" customHeight="1">
       <c r="A262" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.polite.shy[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.heavy.polite.shy[1]</t>
         </is>
       </c>
       <c r="B262" t="inlineStr" s="2">
@@ -8716,7 +8716,7 @@
       </c>
       <c r="D262" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleDefense.polite.shy[1]</t>
+          <t xml:space="preserve">heatSelf.heavy.polite.shy[1]</t>
         </is>
       </c>
       <c r="E262" t="inlineStr" s="2">
@@ -8726,14 +8726,14 @@
       </c>
       <c r="F262" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よ、よかった…守れました…（ほっとしている）</t>
+          <t xml:space="preserve">すみません…動けてはいるんですけど…空回りしてしまって</t>
         </is>
       </c>
     </row>
     <row r="263" ht="40" customHeight="1">
       <c r="A263" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.polite.shy[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.warm.polite.shy[1]</t>
         </is>
       </c>
       <c r="B263" t="inlineStr" s="2">
@@ -8748,7 +8748,7 @@
       </c>
       <c r="D263" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleLoss.polite.shy[1]</t>
+          <t xml:space="preserve">heatSelf.warm.polite.shy[1]</t>
         </is>
       </c>
       <c r="E263" t="inlineStr" s="2">
@@ -8758,14 +8758,14 @@
       </c>
       <c r="F263" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…申し訳ありません…ベルト…守れませんでした…</t>
+          <t xml:space="preserve">あの…できてはいるんです。ただ、残らなくて…</t>
         </is>
       </c>
     </row>
     <row r="264" ht="40" customHeight="1">
       <c r="A264" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.polite.shy[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.polite.shy[1]</t>
         </is>
       </c>
       <c r="B264" t="inlineStr" s="2">
@@ -8780,7 +8780,7 @@
       </c>
       <c r="D264" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.polite.shy[1]</t>
+          <t xml:space="preserve">injury.polite.shy[1]</t>
         </is>
       </c>
       <c r="E264" t="inlineStr" s="2">
@@ -8790,14 +8790,14 @@
       </c>
       <c r="F264" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">え…わ、わたしが…チャンピオン、ですか…？ 夢のようです…</t>
+          <t xml:space="preserve">す、すみません…少しだけ休ませてください…</t>
         </is>
       </c>
     </row>
     <row r="265" ht="40" customHeight="1">
       <c r="A265" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.polite.shy[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.polite.shy[1]</t>
         </is>
       </c>
       <c r="B265" t="inlineStr" s="2">
@@ -8807,12 +8807,12 @@
       </c>
       <c r="C265" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D265" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.shy[1]</t>
+          <t xml:space="preserve">release.polite.shy[1]</t>
         </is>
       </c>
       <c r="E265" t="inlineStr" s="2">
@@ -8829,7 +8829,7 @@
     <row r="266" ht="40" customHeight="1">
       <c r="A266" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.polite.shy[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.polite.shy[1]</t>
         </is>
       </c>
       <c r="B266" t="inlineStr" s="2">
@@ -8839,12 +8839,12 @@
       </c>
       <c r="C266" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D266" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.shy[1]</t>
+          <t xml:space="preserve">rentalGreeting.polite.shy[1]</t>
         </is>
       </c>
       <c r="E266" t="inlineStr" s="2">
@@ -8861,7 +8861,7 @@
     <row r="267" ht="40" customHeight="1">
       <c r="A267" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.polite.shy[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.polite.shy[1]</t>
         </is>
       </c>
       <c r="B267" t="inlineStr" s="2">
@@ -8871,12 +8871,12 @@
       </c>
       <c r="C267" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D267" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.shy[1]</t>
+          <t xml:space="preserve">scoutGreeting.polite.shy[1]</t>
         </is>
       </c>
       <c r="E267" t="inlineStr" s="2">
@@ -8886,14 +8886,14 @@
       </c>
       <c r="F267" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…申し訳ありません…でも…諦めたくないんです…</t>
+          <t xml:space="preserve">あ、あの…お声がけ、光栄です…！</t>
         </is>
       </c>
     </row>
     <row r="268" ht="40" customHeight="1">
       <c r="A268" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.polite.shy[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.polite.shy[1]</t>
         </is>
       </c>
       <c r="B268" t="inlineStr" s="2">
@@ -8903,12 +8903,12 @@
       </c>
       <c r="C268" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D268" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.shy[1]</t>
+          <t xml:space="preserve">titleChallengeLoss.polite.shy[1]</t>
         </is>
       </c>
       <c r="E268" t="inlineStr" s="2">
@@ -8918,14 +8918,14 @@
       </c>
       <c r="F268" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よ、よかった…守れました…（ほっとしている）</t>
+          <t xml:space="preserve">…申し訳ありません…でも…諦めたくないんです…</t>
         </is>
       </c>
     </row>
     <row r="269" ht="40" customHeight="1">
       <c r="A269" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.polite.shy[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.polite.shy[1]</t>
         </is>
       </c>
       <c r="B269" t="inlineStr" s="2">
@@ -8935,12 +8935,12 @@
       </c>
       <c r="C269" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D269" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.shy[1]</t>
+          <t xml:space="preserve">titleDefense.polite.shy[1]</t>
         </is>
       </c>
       <c r="E269" t="inlineStr" s="2">
@@ -8950,14 +8950,14 @@
       </c>
       <c r="F269" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…申し訳ありません…ベルト…守れませんでした…</t>
+          <t xml:space="preserve">よ、よかった…守れました…（ほっとしている）</t>
         </is>
       </c>
     </row>
     <row r="270" ht="40" customHeight="1">
       <c r="A270" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.polite.shy[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.polite.shy[1]</t>
         </is>
       </c>
       <c r="B270" t="inlineStr" s="2">
@@ -8967,12 +8967,12 @@
       </c>
       <c r="C270" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D270" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.shy[1]</t>
+          <t xml:space="preserve">titleLoss.polite.shy[1]</t>
         </is>
       </c>
       <c r="E270" t="inlineStr" s="2">
@@ -8982,14 +8982,14 @@
       </c>
       <c r="F270" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">え…わ、わたしが…チャンピオン、ですか…？ 夢のようです…</t>
+          <t xml:space="preserve">…申し訳ありません…ベルト…守れませんでした…</t>
         </is>
       </c>
     </row>
     <row r="271" ht="40" customHeight="1">
       <c r="A271" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.shy.polite[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.polite.shy[1]</t>
         </is>
       </c>
       <c r="B271" t="inlineStr" s="2">
@@ -8999,29 +8999,29 @@
       </c>
       <c r="C271" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D271" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_39_down.shy.polite[1]</t>
+          <t xml:space="preserve">titleWin.polite.shy[1]</t>
         </is>
       </c>
       <c r="E271" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F271" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…もう…同じ部屋にいるだけで…苦しいんです…</t>
+          <t xml:space="preserve">え…わ、わたしが…チャンピオン、ですか…？ 夢のようです…</t>
         </is>
       </c>
     </row>
     <row r="272" ht="40" customHeight="1">
       <c r="A272" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.shy.polite[1]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.polite.shy[1]</t>
         </is>
       </c>
       <c r="B272" t="inlineStr" s="2">
@@ -9031,29 +9031,29 @@
       </c>
       <c r="C272" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D272" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.shy.polite[1]</t>
+          <t xml:space="preserve">polite.shy[1]</t>
         </is>
       </c>
       <c r="E272" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F272" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最近…目を合わせるのが怖くて…わたし、何かしてしまったんでしょうか…</t>
+          <t xml:space="preserve">ご、ごめんなさい…お、お世話になりました…</t>
         </is>
       </c>
     </row>
     <row r="273" ht="40" customHeight="1">
       <c r="A273" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.shy.polite[2]</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.polite.shy[1]</t>
         </is>
       </c>
       <c r="B273" t="inlineStr" s="2">
@@ -9063,29 +9063,29 @@
       </c>
       <c r="C273" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
         </is>
       </c>
       <c r="D273" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.shy.polite[2]</t>
+          <t xml:space="preserve">polite.shy[1]</t>
         </is>
       </c>
       <c r="E273" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F273" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの方の態度が…前と違うんです…わたしのせい…ですよね…</t>
+          <t xml:space="preserve">あ、あの…短い間ではございますが…よろしくお願いいたします…</t>
         </is>
       </c>
     </row>
     <row r="274" ht="40" customHeight="1">
       <c r="A274" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.shy.polite[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.polite.shy[1]</t>
         </is>
       </c>
       <c r="B274" t="inlineStr" s="2">
@@ -9095,29 +9095,29 @@
       </c>
       <c r="C274" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D274" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_60_up.shy.polite[1]</t>
+          <t xml:space="preserve">polite.shy[1]</t>
         </is>
       </c>
       <c r="E274" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F274" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一緒にいると…少しだけ自分に自信が持てるんです…</t>
+          <t xml:space="preserve">…申し訳ありません…でも…諦めたくないんです…</t>
         </is>
       </c>
     </row>
     <row r="275" ht="40" customHeight="1">
       <c r="A275" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.shy.polite[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.polite.shy[1]</t>
         </is>
       </c>
       <c r="B275" t="inlineStr" s="2">
@@ -9127,29 +9127,29 @@
       </c>
       <c r="C275" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
         </is>
       </c>
       <c r="D275" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_80_up.shy.polite[1]</t>
+          <t xml:space="preserve">polite.shy[1]</t>
         </is>
       </c>
       <c r="E275" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F275" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの方がいなければ…わたし、とっくに駄目になっていたと思います…</t>
+          <t xml:space="preserve">よ、よかった…守れました…（ほっとしている）</t>
         </is>
       </c>
     </row>
     <row r="276" ht="40" customHeight="1">
       <c r="A276" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.shy.polite[2]</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.polite.shy[1]</t>
         </is>
       </c>
       <c r="B276" t="inlineStr" s="2">
@@ -9159,29 +9159,29 @@
       </c>
       <c r="C276" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D276" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_80_up.shy.polite[2]</t>
+          <t xml:space="preserve">polite.shy[1]</t>
         </is>
       </c>
       <c r="E276" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F276" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">隣にいてくださるだけで…なんでも頑張れる気がするんです…</t>
+          <t xml:space="preserve">…申し訳ありません…ベルト…守れませんでした…</t>
         </is>
       </c>
     </row>
     <row r="277" ht="40" customHeight="1">
       <c r="A277" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.shy.polite[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.polite.shy[1]</t>
         </is>
       </c>
       <c r="B277" t="inlineStr" s="2">
@@ -9191,29 +9191,29 @@
       </c>
       <c r="C277" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
         </is>
       </c>
       <c r="D277" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.shy.polite[1]</t>
+          <t xml:space="preserve">polite.shy[1]</t>
         </is>
       </c>
       <c r="E277" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F277" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最近…あの方のこと、前ほど気にならなくなった…かもしれません…</t>
+          <t xml:space="preserve">え…わ、わたしが…チャンピオン、ですか…？ 夢のようです…</t>
         </is>
       </c>
     </row>
     <row r="278" ht="40" customHeight="1">
       <c r="A278" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.shy.polite[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.shy.polite[1]</t>
         </is>
       </c>
       <c r="B278" t="inlineStr" s="2">
@@ -9228,7 +9228,7 @@
       </c>
       <c r="D278" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.shy.polite[2]</t>
+          <t xml:space="preserve">bond_39_down.shy.polite[1]</t>
         </is>
       </c>
       <c r="E278" t="inlineStr" s="2">
@@ -9238,14 +9238,14 @@
       </c>
       <c r="F278" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの頃の張りつめた感じ…もうないんでしょうか…</t>
+          <t xml:space="preserve">…もう…同じ部屋にいるだけで…苦しいんです…</t>
         </is>
       </c>
     </row>
     <row r="279" ht="40" customHeight="1">
       <c r="A279" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.shy.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.shy.polite[1]</t>
         </is>
       </c>
       <c r="B279" t="inlineStr" s="2">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="D279" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_30_up.shy.polite[1]</t>
+          <t xml:space="preserve">bond_59_down.shy.polite[1]</t>
         </is>
       </c>
       <c r="E279" t="inlineStr" s="2">
@@ -9270,14 +9270,14 @@
       </c>
       <c r="F279" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの方のことを考えると…胸が締めつけられて…負けたくないんです…</t>
+          <t xml:space="preserve">最近…目を合わせるのが怖くて…わたし、何かしてしまったんでしょうか…</t>
         </is>
       </c>
     </row>
     <row r="280" ht="40" customHeight="1">
       <c r="A280" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.shy.polite[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.shy.polite[2]</t>
         </is>
       </c>
       <c r="B280" t="inlineStr" s="2">
@@ -9292,7 +9292,7 @@
       </c>
       <c r="D280" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_30_up.shy.polite[2]</t>
+          <t xml:space="preserve">bond_59_down.shy.polite[2]</t>
         </is>
       </c>
       <c r="E280" t="inlineStr" s="2">
@@ -9302,14 +9302,14 @@
       </c>
       <c r="F280" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">練習しているのを見かけると…わたしも走り出したくなります…</t>
+          <t xml:space="preserve">あの方の態度が…前と違うんです…わたしのせい…ですよね…</t>
         </is>
       </c>
     </row>
     <row r="281" ht="40" customHeight="1">
       <c r="A281" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.shy.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.shy.polite[1]</t>
         </is>
       </c>
       <c r="B281" t="inlineStr" s="2">
@@ -9324,7 +9324,7 @@
       </c>
       <c r="D281" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_50_up.shy.polite[1]</t>
+          <t xml:space="preserve">bond_60_up.shy.polite[1]</t>
         </is>
       </c>
       <c r="E281" t="inlineStr" s="2">
@@ -9334,14 +9334,14 @@
       </c>
       <c r="F281" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの方にだけは…絶対に負けたくありません…今はそれだけです…</t>
+          <t xml:space="preserve">一緒にいると…少しだけ自分に自信が持てるんです…</t>
         </is>
       </c>
     </row>
     <row r="282" ht="40" customHeight="1">
       <c r="A282" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.shy.polite[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.shy.polite[1]</t>
         </is>
       </c>
       <c r="B282" t="inlineStr" s="2">
@@ -9356,7 +9356,7 @@
       </c>
       <c r="D282" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_50_up.shy.polite[2]</t>
+          <t xml:space="preserve">bond_80_up.shy.polite[1]</t>
         </is>
       </c>
       <c r="E282" t="inlineStr" s="2">
@@ -9366,14 +9366,14 @@
       </c>
       <c r="F282" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">怖いです…けれど、逃げたらもっと後悔します…だから…</t>
+          <t xml:space="preserve">あの方がいなければ…わたし、とっくに駄目になっていたと思います…</t>
         </is>
       </c>
     </row>
     <row r="283" ht="40" customHeight="1">
       <c r="A283" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.shy.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.shy.polite[2]</t>
         </is>
       </c>
       <c r="B283" t="inlineStr" s="2">
@@ -9388,7 +9388,7 @@
       </c>
       <c r="D283" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.shy.polite[1]</t>
+          <t xml:space="preserve">bond_80_up.shy.polite[2]</t>
         </is>
       </c>
       <c r="E283" t="inlineStr" s="2">
@@ -9398,14 +9398,14 @@
       </c>
       <c r="F283" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの方がいなければ…今のわたしはいません。それだけは…わかるんです…</t>
+          <t xml:space="preserve">隣にいてくださるだけで…なんでも頑張れる気がするんです…</t>
         </is>
       </c>
     </row>
     <row r="284" ht="40" customHeight="1">
       <c r="A284" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.shy.polite[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.shy.polite[1]</t>
         </is>
       </c>
       <c r="B284" t="inlineStr" s="2">
@@ -9420,7 +9420,7 @@
       </c>
       <c r="D284" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.shy.polite[2]</t>
+          <t xml:space="preserve">rivalry_29_down.shy.polite[1]</t>
         </is>
       </c>
       <c r="E284" t="inlineStr" s="2">
@@ -9430,14 +9430,14 @@
       </c>
       <c r="F284" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">逃げたい…でも…あの方からだけは逃げてはいけない…</t>
+          <t xml:space="preserve">最近…あの方のこと、前ほど気にならなくなった…かもしれません…</t>
         </is>
       </c>
     </row>
     <row r="285" ht="40" customHeight="1">
       <c r="A285" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.shy.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.shy.polite[2]</t>
         </is>
       </c>
       <c r="B285" t="inlineStr" s="2">
@@ -9452,7 +9452,7 @@
       </c>
       <c r="D285" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_above_75.shy.polite[1]</t>
+          <t xml:space="preserve">rivalry_29_down.shy.polite[2]</t>
         </is>
       </c>
       <c r="E285" t="inlineStr" s="2">
@@ -9462,14 +9462,14 @@
       </c>
       <c r="F285" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここにいてもいいんだと…最近ようやく思えるようになったんです…</t>
+          <t xml:space="preserve">あの頃の張りつめた感じ…もうないんでしょうか…</t>
         </is>
       </c>
     </row>
     <row r="286" ht="40" customHeight="1">
       <c r="A286" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.shy.polite[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.shy.polite[1]</t>
         </is>
       </c>
       <c r="B286" t="inlineStr" s="2">
@@ -9484,7 +9484,7 @@
       </c>
       <c r="D286" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_above_75.shy.polite[2]</t>
+          <t xml:space="preserve">rivalry_30_up.shy.polite[1]</t>
         </is>
       </c>
       <c r="E286" t="inlineStr" s="2">
@@ -9494,14 +9494,14 @@
       </c>
       <c r="F286" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この団体に来られて…本当によかったです…心からそう思います…</t>
+          <t xml:space="preserve">あの方のことを考えると…胸が締めつけられて…負けたくないんです…</t>
         </is>
       </c>
     </row>
     <row r="287" ht="40" customHeight="1">
       <c r="A287" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.shy.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.shy.polite[2]</t>
         </is>
       </c>
       <c r="B287" t="inlineStr" s="2">
@@ -9516,7 +9516,7 @@
       </c>
       <c r="D287" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_20.shy.polite[1]</t>
+          <t xml:space="preserve">rivalry_30_up.shy.polite[2]</t>
         </is>
       </c>
       <c r="E287" t="inlineStr" s="2">
@@ -9526,14 +9526,14 @@
       </c>
       <c r="F287" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…もう…無理です…ここにいてはいけない気がするんです……</t>
+          <t xml:space="preserve">練習しているのを見かけると…わたしも走り出したくなります…</t>
         </is>
       </c>
     </row>
     <row r="288" ht="40" customHeight="1">
       <c r="A288" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.shy.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.shy.polite[1]</t>
         </is>
       </c>
       <c r="B288" t="inlineStr" s="2">
@@ -9548,7 +9548,7 @@
       </c>
       <c r="D288" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_35.shy.polite[1]</t>
+          <t xml:space="preserve">rivalry_50_up.shy.polite[1]</t>
         </is>
       </c>
       <c r="E288" t="inlineStr" s="2">
@@ -9558,14 +9558,14 @@
       </c>
       <c r="F288" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ここにわたしの居場所なんて…あるんでしょうか……</t>
+          <t xml:space="preserve">あの方にだけは…絶対に負けたくありません…今はそれだけです…</t>
         </is>
       </c>
     </row>
     <row r="289" ht="40" customHeight="1">
       <c r="A289" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.goodLoss.polite.shy[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.shy.polite[2]</t>
         </is>
       </c>
       <c r="B289" t="inlineStr" s="2">
@@ -9575,12 +9575,12 @@
       </c>
       <c r="C289" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D289" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.goodLoss.polite.shy[1]</t>
+          <t xml:space="preserve">rivalry_50_up.shy.polite[2]</t>
         </is>
       </c>
       <c r="E289" t="inlineStr" s="2">
@@ -9590,14 +9590,14 @@
       </c>
       <c r="F289" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けてしまいましたが…悔いはありません…</t>
+          <t xml:space="preserve">怖いです…けれど、逃げたらもっと後悔します…だから…</t>
         </is>
       </c>
     </row>
     <row r="290" ht="40" customHeight="1">
       <c r="A290" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.goodLoss.polite.shy[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.shy.polite[1]</t>
         </is>
       </c>
       <c r="B290" t="inlineStr" s="2">
@@ -9607,12 +9607,12 @@
       </c>
       <c r="C290" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D290" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.goodLoss.polite.shy[2]</t>
+          <t xml:space="preserve">rivalry_70_up.shy.polite[1]</t>
         </is>
       </c>
       <c r="E290" t="inlineStr" s="2">
@@ -9622,14 +9622,14 @@
       </c>
       <c r="F290" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">全力は、出せたと思います…</t>
+          <t xml:space="preserve">あの方がいなければ…今のわたしはいません。それだけは…わかるんです…</t>
         </is>
       </c>
     </row>
     <row r="291" ht="40" customHeight="1">
       <c r="A291" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin.polite.shy[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.shy.polite[2]</t>
         </is>
       </c>
       <c r="B291" t="inlineStr" s="2">
@@ -9639,12 +9639,12 @@
       </c>
       <c r="C291" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D291" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.greatWin.polite.shy[1]</t>
+          <t xml:space="preserve">rivalry_70_up.shy.polite[2]</t>
         </is>
       </c>
       <c r="E291" t="inlineStr" s="2">
@@ -9654,14 +9654,14 @@
       </c>
       <c r="F291" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こ、こんな大きな勝利…信じられません…ありがとうございます…</t>
+          <t xml:space="preserve">逃げたい…でも…あの方からだけは逃げてはいけない…</t>
         </is>
       </c>
     </row>
     <row r="292" ht="40" customHeight="1">
       <c r="A292" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin.polite.shy[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.shy.polite[1]</t>
         </is>
       </c>
       <c r="B292" t="inlineStr" s="2">
@@ -9671,12 +9671,12 @@
       </c>
       <c r="C292" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D292" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.greatWin.polite.shy[2]</t>
+          <t xml:space="preserve">trust_above_75.shy.polite[1]</t>
         </is>
       </c>
       <c r="E292" t="inlineStr" s="2">
@@ -9686,14 +9686,14 @@
       </c>
       <c r="F292" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こんな日が、来るなんて…夢みたいです…</t>
+          <t xml:space="preserve">ここにいてもいいんだと…最近ようやく思えるようになったんです…</t>
         </is>
       </c>
     </row>
     <row r="293" ht="40" customHeight="1">
       <c r="A293" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.polite.shy[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.shy.polite[2]</t>
         </is>
       </c>
       <c r="B293" t="inlineStr" s="2">
@@ -9703,12 +9703,12 @@
       </c>
       <c r="C293" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D293" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.loss.polite.shy[1]</t>
+          <t xml:space="preserve">trust_above_75.shy.polite[2]</t>
         </is>
       </c>
       <c r="E293" t="inlineStr" s="2">
@@ -9718,14 +9718,14 @@
       </c>
       <c r="F293" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ま、負けてしまいました…ご、ごめんなさい…</t>
+          <t xml:space="preserve">この団体に来られて…本当によかったです…心からそう思います…</t>
         </is>
       </c>
     </row>
     <row r="294" ht="40" customHeight="1">
       <c r="A294" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.polite.shy[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.shy.polite[1]</t>
         </is>
       </c>
       <c r="B294" t="inlineStr" s="2">
@@ -9735,12 +9735,12 @@
       </c>
       <c r="C294" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D294" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.loss.polite.shy[2]</t>
+          <t xml:space="preserve">trust_below_20.shy.polite[1]</t>
         </is>
       </c>
       <c r="E294" t="inlineStr" s="2">
@@ -9750,14 +9750,14 @@
       </c>
       <c r="F294" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次こそは…勝ちたいです…</t>
+          <t xml:space="preserve">…もう…無理です…ここにいてはいけない気がするんです……</t>
         </is>
       </c>
     </row>
     <row r="295" ht="40" customHeight="1">
       <c r="A295" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.polite.shy[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.shy.polite[1]</t>
         </is>
       </c>
       <c r="B295" t="inlineStr" s="2">
@@ -9767,12 +9767,12 @@
       </c>
       <c r="C295" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D295" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.win.polite.shy[1]</t>
+          <t xml:space="preserve">trust_below_35.shy.polite[1]</t>
         </is>
       </c>
       <c r="E295" t="inlineStr" s="2">
@@ -9782,14 +9782,14 @@
       </c>
       <c r="F295" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">か、勝てました…応援、ありがとうございます…</t>
+          <t xml:space="preserve">…ここにわたしの居場所なんて…あるんでしょうか……</t>
         </is>
       </c>
     </row>
     <row r="296" ht="40" customHeight="1">
       <c r="A296" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.polite.shy[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.goodLoss.polite.shy[1]</t>
         </is>
       </c>
       <c r="B296" t="inlineStr" s="2">
@@ -9804,7 +9804,7 @@
       </c>
       <c r="D296" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.win.polite.shy[2]</t>
+          <t xml:space="preserve">GL-01.goodLoss.polite.shy[1]</t>
         </is>
       </c>
       <c r="E296" t="inlineStr" s="2">
@@ -9814,14 +9814,14 @@
       </c>
       <c r="F296" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今日は…良い試合が、できたと思います…</t>
+          <t xml:space="preserve">負けてしまいましたが…悔いはありません…</t>
         </is>
       </c>
     </row>
     <row r="297" ht="40" customHeight="1">
       <c r="A297" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.polite.shy[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.goodLoss.polite.shy[2]</t>
         </is>
       </c>
       <c r="B297" t="inlineStr" s="2">
@@ -9836,7 +9836,7 @@
       </c>
       <c r="D297" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-02.polite.shy[1]</t>
+          <t xml:space="preserve">GL-01.goodLoss.polite.shy[2]</t>
         </is>
       </c>
       <c r="E297" t="inlineStr" s="2">
@@ -9846,14 +9846,14 @@
       </c>
       <c r="F297" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、あの…今日は、よろしくお願いいたします…</t>
+          <t xml:space="preserve">全力は、出せたと思います…</t>
         </is>
       </c>
     </row>
     <row r="298" ht="40" customHeight="1">
       <c r="A298" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.polite.shy[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin.polite.shy[1]</t>
         </is>
       </c>
       <c r="B298" t="inlineStr" s="2">
@@ -9868,7 +9868,7 @@
       </c>
       <c r="D298" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-02.polite.shy[2]</t>
+          <t xml:space="preserve">GL-01.greatWin.polite.shy[1]</t>
         </is>
       </c>
       <c r="E298" t="inlineStr" s="2">
@@ -9878,14 +9878,14 @@
       </c>
       <c r="F298" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">頑張ります…</t>
+          <t xml:space="preserve">こ、こんな大きな勝利…信じられません…ありがとうございます…</t>
         </is>
       </c>
     </row>
     <row r="299" ht="40" customHeight="1">
       <c r="A299" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.down.polite.shy[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin.polite.shy[2]</t>
         </is>
       </c>
       <c r="B299" t="inlineStr" s="2">
@@ -9900,7 +9900,7 @@
       </c>
       <c r="D299" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-03.down.polite.shy[1]</t>
+          <t xml:space="preserve">GL-01.greatWin.polite.shy[2]</t>
         </is>
       </c>
       <c r="E299" t="inlineStr" s="2">
@@ -9910,14 +9910,14 @@
       </c>
       <c r="F299" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">う、うまくいきません…どうしたら…</t>
+          <t xml:space="preserve">こんな日が、来るなんて…夢みたいです…</t>
         </is>
       </c>
     </row>
     <row r="300" ht="40" customHeight="1">
       <c r="A300" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.up.polite.shy[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.polite.shy[1]</t>
         </is>
       </c>
       <c r="B300" t="inlineStr" s="2">
@@ -9932,7 +9932,7 @@
       </c>
       <c r="D300" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-03.up.polite.shy[1]</t>
+          <t xml:space="preserve">GL-01.loss.polite.shy[1]</t>
         </is>
       </c>
       <c r="E300" t="inlineStr" s="2">
@@ -9942,14 +9942,14 @@
       </c>
       <c r="F300" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">調子が…良い気がします…</t>
+          <t xml:space="preserve">ま、負けてしまいました…ご、ごめんなさい…</t>
         </is>
       </c>
     </row>
     <row r="301" ht="40" customHeight="1">
       <c r="A301" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04.polite.shy[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.polite.shy[2]</t>
         </is>
       </c>
       <c r="B301" t="inlineStr" s="2">
@@ -9964,7 +9964,7 @@
       </c>
       <c r="D301" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-04.polite.shy[1]</t>
+          <t xml:space="preserve">GL-01.loss.polite.shy[2]</t>
         </is>
       </c>
       <c r="E301" t="inlineStr" s="2">
@@ -9974,14 +9974,14 @@
       </c>
       <c r="F301" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">練習…させていただきます…</t>
+          <t xml:space="preserve">次こそは…勝ちたいです…</t>
         </is>
       </c>
     </row>
     <row r="302" ht="40" customHeight="1">
       <c r="A302" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04.polite.shy[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.polite.shy[1]</t>
         </is>
       </c>
       <c r="B302" t="inlineStr" s="2">
@@ -9996,7 +9996,7 @@
       </c>
       <c r="D302" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-04.polite.shy[2]</t>
+          <t xml:space="preserve">GL-01.win.polite.shy[1]</t>
         </is>
       </c>
       <c r="E302" t="inlineStr" s="2">
@@ -10006,14 +10006,14 @@
       </c>
       <c r="F302" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もう少し…頑張ります…</t>
+          <t xml:space="preserve">か、勝てました…応援、ありがとうございます…</t>
         </is>
       </c>
     </row>
     <row r="303" ht="40" customHeight="1">
       <c r="A303" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05.polite.shy[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.polite.shy[2]</t>
         </is>
       </c>
       <c r="B303" t="inlineStr" s="2">
@@ -10028,7 +10028,7 @@
       </c>
       <c r="D303" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-05.polite.shy[1]</t>
+          <t xml:space="preserve">GL-01.win.polite.shy[2]</t>
         </is>
       </c>
       <c r="E303" t="inlineStr" s="2">
@@ -10038,14 +10038,14 @@
       </c>
       <c r="F303" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、あの…大丈夫です、心配しないでください…</t>
+          <t xml:space="preserve">今日は…良い試合が、できたと思います…</t>
         </is>
       </c>
     </row>
     <row r="304" ht="40" customHeight="1">
       <c r="A304" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05.polite.shy[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.polite.shy[1]</t>
         </is>
       </c>
       <c r="B304" t="inlineStr" s="2">
@@ -10060,7 +10060,7 @@
       </c>
       <c r="D304" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-05.polite.shy[2]</t>
+          <t xml:space="preserve">GL-02.polite.shy[1]</t>
         </is>
       </c>
       <c r="E304" t="inlineStr" s="2">
@@ -10070,14 +10070,14 @@
       </c>
       <c r="F304" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ご心配を、おかけして…</t>
+          <t xml:space="preserve">あ、あの…今日は、よろしくお願いいたします…</t>
         </is>
       </c>
     </row>
     <row r="305" ht="40" customHeight="1">
       <c r="A305" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.polite.shy[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.polite.shy[2]</t>
         </is>
       </c>
       <c r="B305" t="inlineStr" s="2">
@@ -10092,7 +10092,7 @@
       </c>
       <c r="D305" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-06.polite.shy[1]</t>
+          <t xml:space="preserve">GL-02.polite.shy[2]</t>
         </is>
       </c>
       <c r="E305" t="inlineStr" s="2">
@@ -10102,14 +10102,14 @@
       </c>
       <c r="F305" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">みんなと…一緒だと、心強いです…</t>
+          <t xml:space="preserve">頑張ります…</t>
         </is>
       </c>
     </row>
     <row r="306" ht="40" customHeight="1">
       <c r="A306" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.polite.shy[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.down.polite.shy[1]</t>
         </is>
       </c>
       <c r="B306" t="inlineStr" s="2">
@@ -10124,7 +10124,7 @@
       </c>
       <c r="D306" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-06.polite.shy[2]</t>
+          <t xml:space="preserve">GL-03.down.polite.shy[1]</t>
         </is>
       </c>
       <c r="E306" t="inlineStr" s="2">
@@ -10134,14 +10134,14 @@
       </c>
       <c r="F306" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">仲間って、いいですね…</t>
+          <t xml:space="preserve">う、うまくいきません…どうしたら…</t>
         </is>
       </c>
     </row>
     <row r="307" ht="40" customHeight="1">
       <c r="A307" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07.polite.shy[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.up.polite.shy[1]</t>
         </is>
       </c>
       <c r="B307" t="inlineStr" s="2">
@@ -10156,7 +10156,7 @@
       </c>
       <c r="D307" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-07.polite.shy[1]</t>
+          <t xml:space="preserve">GL-03.up.polite.shy[1]</t>
         </is>
       </c>
       <c r="E307" t="inlineStr" s="2">
@@ -10166,14 +10166,14 @@
       </c>
       <c r="F307" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お、お客さんがいっぱいで…き、緊張します…</t>
+          <t xml:space="preserve">調子が…良い気がします…</t>
         </is>
       </c>
     </row>
     <row r="308" ht="40" customHeight="1">
       <c r="A308" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07.polite.shy[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04.polite.shy[1]</t>
         </is>
       </c>
       <c r="B308" t="inlineStr" s="2">
@@ -10188,7 +10188,7 @@
       </c>
       <c r="D308" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-07.polite.shy[2]</t>
+          <t xml:space="preserve">GL-04.polite.shy[1]</t>
         </is>
       </c>
       <c r="E308" t="inlineStr" s="2">
@@ -10198,14 +10198,14 @@
       </c>
       <c r="F308" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">がんばります…</t>
+          <t xml:space="preserve">練習…させていただきます…</t>
         </is>
       </c>
     </row>
     <row r="309" ht="40" customHeight="1">
       <c r="A309" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.polite.shy[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04.polite.shy[2]</t>
         </is>
       </c>
       <c r="B309" t="inlineStr" s="2">
@@ -10220,7 +10220,7 @@
       </c>
       <c r="D309" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-08.polite.shy[1]</t>
+          <t xml:space="preserve">GL-04.polite.shy[2]</t>
         </is>
       </c>
       <c r="E309" t="inlineStr" s="2">
@@ -10230,14 +10230,14 @@
       </c>
       <c r="F309" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、あの…体調は、大丈夫です…</t>
+          <t xml:space="preserve">もう少し…頑張ります…</t>
         </is>
       </c>
     </row>
     <row r="310" ht="40" customHeight="1">
       <c r="A310" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.polite.shy[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05.polite.shy[1]</t>
         </is>
       </c>
       <c r="B310" t="inlineStr" s="2">
@@ -10252,7 +10252,7 @@
       </c>
       <c r="D310" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-08.polite.shy[2]</t>
+          <t xml:space="preserve">GL-05.polite.shy[1]</t>
         </is>
       </c>
       <c r="E310" t="inlineStr" s="2">
@@ -10262,14 +10262,14 @@
       </c>
       <c r="F310" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">無理はしません…</t>
+          <t xml:space="preserve">あ、あの…大丈夫です、心配しないでください…</t>
         </is>
       </c>
     </row>
     <row r="311" ht="40" customHeight="1">
       <c r="A311" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.polite.shy[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05.polite.shy[2]</t>
         </is>
       </c>
       <c r="B311" t="inlineStr" s="2">
@@ -10284,7 +10284,7 @@
       </c>
       <c r="D311" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-09.polite.shy[1]</t>
+          <t xml:space="preserve">GL-05.polite.shy[2]</t>
         </is>
       </c>
       <c r="E311" t="inlineStr" s="2">
@@ -10294,14 +10294,14 @@
       </c>
       <c r="F311" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次の試合…が、頑張ります…</t>
+          <t xml:space="preserve">ご心配を、おかけして…</t>
         </is>
       </c>
     </row>
     <row r="312" ht="40" customHeight="1">
       <c r="A312" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.polite.shy[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.polite.shy[1]</t>
         </is>
       </c>
       <c r="B312" t="inlineStr" s="2">
@@ -10316,7 +10316,7 @@
       </c>
       <c r="D312" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-09.polite.shy[2]</t>
+          <t xml:space="preserve">GL-06.polite.shy[1]</t>
         </is>
       </c>
       <c r="E312" t="inlineStr" s="2">
@@ -10326,14 +10326,14 @@
       </c>
       <c r="F312" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">しっかり、準備します…</t>
+          <t xml:space="preserve">みんなと…一緒だと、心強いです…</t>
         </is>
       </c>
     </row>
     <row r="313" ht="40" customHeight="1">
       <c r="A313" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.polite.shy[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.polite.shy[2]</t>
         </is>
       </c>
       <c r="B313" t="inlineStr" s="2">
@@ -10348,7 +10348,7 @@
       </c>
       <c r="D313" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-10.polite.shy[1]</t>
+          <t xml:space="preserve">GL-06.polite.shy[2]</t>
         </is>
       </c>
       <c r="E313" t="inlineStr" s="2">
@@ -10358,14 +10358,14 @@
       </c>
       <c r="F313" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、あの…ありがとうございます…</t>
+          <t xml:space="preserve">仲間って、いいですね…</t>
         </is>
       </c>
     </row>
     <row r="314" ht="40" customHeight="1">
       <c r="A314" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.polite.shy[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07.polite.shy[1]</t>
         </is>
       </c>
       <c r="B314" t="inlineStr" s="2">
@@ -10380,7 +10380,7 @@
       </c>
       <c r="D314" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-10.polite.shy[2]</t>
+          <t xml:space="preserve">GL-07.polite.shy[1]</t>
         </is>
       </c>
       <c r="E314" t="inlineStr" s="2">
@@ -10390,14 +10390,14 @@
       </c>
       <c r="F314" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">感謝、しています…</t>
+          <t xml:space="preserve">お、お客さんがいっぱいで…き、緊張します…</t>
         </is>
       </c>
     </row>
     <row r="315" ht="40" customHeight="1">
       <c r="A315" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.polite.shy[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07.polite.shy[2]</t>
         </is>
       </c>
       <c r="B315" t="inlineStr" s="2">
@@ -10407,12 +10407,12 @@
       </c>
       <c r="C315" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D315" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.shy[1]</t>
+          <t xml:space="preserve">GL-07.polite.shy[2]</t>
         </is>
       </c>
       <c r="E315" t="inlineStr" s="2">
@@ -10422,14 +10422,14 @@
       </c>
       <c r="F315" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">良い流れが…止まってしまいました…で、でも、また頑張ります…</t>
+          <t xml:space="preserve">がんばります…</t>
         </is>
       </c>
     </row>
     <row r="316" ht="40" customHeight="1">
       <c r="A316" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.polite.shy[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.polite.shy[1]</t>
         </is>
       </c>
       <c r="B316" t="inlineStr" s="2">
@@ -10439,29 +10439,29 @@
       </c>
       <c r="C316" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D316" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.polite.shy[1]</t>
+          <t xml:space="preserve">GL-08.polite.shy[1]</t>
         </is>
       </c>
       <c r="E316" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F316" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">け、決勝…。信じられないけど…最後まで、立たせてください…</t>
+          <t xml:space="preserve">あ、あの…体調は、大丈夫です…</t>
         </is>
       </c>
     </row>
     <row r="317" ht="40" customHeight="1">
       <c r="A317" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.polite.shy[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.polite.shy[2]</t>
         </is>
       </c>
       <c r="B317" t="inlineStr" s="2">
@@ -10471,29 +10471,29 @@
       </c>
       <c r="C317" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D317" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.polite.shy[2]</t>
+          <t xml:space="preserve">GL-08.polite.shy[2]</t>
         </is>
       </c>
       <c r="E317" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F317" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">身体は痛いです…でも、ここで退いたら、繋いでくれた分が…</t>
+          <t xml:space="preserve">無理はしません…</t>
         </is>
       </c>
     </row>
     <row r="318" ht="40" customHeight="1">
       <c r="A318" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.polite.shy[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.polite.shy[1]</t>
         </is>
       </c>
       <c r="B318" t="inlineStr" s="2">
@@ -10503,29 +10503,29 @@
       </c>
       <c r="C318" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D318" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.polite.shy[1]</t>
+          <t xml:space="preserve">GL-09.polite.shy[1]</t>
         </is>
       </c>
       <c r="E318" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F318" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、相手の方…がんばります。仲間が待ってるので、退けません…</t>
+          <t xml:space="preserve">次の試合…が、頑張ります…</t>
         </is>
       </c>
     </row>
     <row r="319" ht="40" customHeight="1">
       <c r="A319" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.polite.shy[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.polite.shy[2]</t>
         </is>
       </c>
       <c r="B319" t="inlineStr" s="2">
@@ -10535,29 +10535,29 @@
       </c>
       <c r="C319" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D319" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.polite.shy[2]</t>
+          <t xml:space="preserve">GL-09.polite.shy[2]</t>
         </is>
       </c>
       <c r="E319" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F319" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こ、怖いです…でも、ここで止まったら、みんなに申し訳なくて…</t>
+          <t xml:space="preserve">しっかり、準備します…</t>
         </is>
       </c>
     </row>
     <row r="320" ht="40" customHeight="1">
       <c r="A320" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.polite.shy[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.polite.shy[1]</t>
         </is>
       </c>
       <c r="B320" t="inlineStr" s="2">
@@ -10567,29 +10567,29 @@
       </c>
       <c r="C320" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D320" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.polite.shy[1]</t>
+          <t xml:space="preserve">GL-10.polite.shy[1]</t>
         </is>
       </c>
       <c r="E320" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F320" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">い、一人、倒せました…！ はぁ…まだ、退けません…次の方、来てください…！</t>
+          <t xml:space="preserve">あ、あの…ありがとうございます…</t>
         </is>
       </c>
     </row>
     <row r="321" ht="40" customHeight="1">
       <c r="A321" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.polite.shy[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.polite.shy[2]</t>
         </is>
       </c>
       <c r="B321" t="inlineStr" s="2">
@@ -10599,29 +10599,29 @@
       </c>
       <c r="C321" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D321" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.polite.shy[2]</t>
+          <t xml:space="preserve">GL-10.polite.shy[2]</t>
         </is>
       </c>
       <c r="E321" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F321" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">怖いです…でも、まだ立ってます。仲間に繋ぐまで、ここは…次、どうぞ…</t>
+          <t xml:space="preserve">感謝、しています…</t>
         </is>
       </c>
     </row>
     <row r="322" ht="40" customHeight="1">
       <c r="A322" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.polite.shy[1]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.polite.shy[1]</t>
         </is>
       </c>
       <c r="B322" t="inlineStr" s="2">
@@ -10631,29 +10631,29 @@
       </c>
       <c r="C322" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
         </is>
       </c>
       <c r="D322" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.polite.shy[1]</t>
+          <t xml:space="preserve">polite.shy[1]</t>
         </is>
       </c>
       <c r="E322" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F322" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わ、わたしがMVPなんて……二人がいてくれたから、ここまで来られたんです</t>
+          <t xml:space="preserve">良い流れが…止まってしまいました…で、でも、また頑張ります…</t>
         </is>
       </c>
     </row>
     <row r="323" ht="40" customHeight="1">
       <c r="A323" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.polite.shy[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.polite.shy[1]</t>
         </is>
       </c>
       <c r="B323" t="inlineStr" s="2">
@@ -10663,12 +10663,12 @@
       </c>
       <c r="C323" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D323" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.polite.shy[2]</t>
+          <t xml:space="preserve">preFinal.polite.shy[1]</t>
         </is>
       </c>
       <c r="E323" t="inlineStr" s="2">
@@ -10678,14 +10678,14 @@
       </c>
       <c r="F323" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">三人で勝てて、本当によかったです。わたしは……二人に助けられてばかりで</t>
+          <t xml:space="preserve">け、決勝…。信じられないけど…最後まで、立たせてください…</t>
         </is>
       </c>
     </row>
     <row r="324" ht="40" customHeight="1">
       <c r="A324" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.polite.shy[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.polite.shy[2]</t>
         </is>
       </c>
       <c r="B324" t="inlineStr" s="2">
@@ -10695,12 +10695,12 @@
       </c>
       <c r="C324" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D324" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.polite.shy[1]</t>
+          <t xml:space="preserve">preFinal.polite.shy[2]</t>
         </is>
       </c>
       <c r="E324" t="inlineStr" s="2">
@@ -10710,14 +10710,14 @@
       </c>
       <c r="F324" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">MVPは……嬉しいです。でも、みんなで勝ちたかったです。次こそは……</t>
+          <t xml:space="preserve">身体は痛いです…でも、ここで退いたら、繋いでくれた分が…</t>
         </is>
       </c>
     </row>
     <row r="325" ht="40" customHeight="1">
       <c r="A325" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.polite.shy[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.polite.shy[1]</t>
         </is>
       </c>
       <c r="B325" t="inlineStr" s="2">
@@ -10727,12 +10727,12 @@
       </c>
       <c r="C325" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D325" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.polite.shy[2]</t>
+          <t xml:space="preserve">preMatch.polite.shy[1]</t>
         </is>
       </c>
       <c r="E325" t="inlineStr" s="2">
@@ -10742,14 +10742,14 @@
       </c>
       <c r="F325" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人だけ褒められても……素直に喜べなくて。次は一緒に笑いたいです</t>
+          <t xml:space="preserve">あ、相手の方…がんばります。仲間が待ってるので、退けません…</t>
         </is>
       </c>
     </row>
     <row r="326" ht="40" customHeight="1">
       <c r="A326" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.polite.shy[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.polite.shy[2]</t>
         </is>
       </c>
       <c r="B326" t="inlineStr" s="2">
@@ -10759,12 +10759,12 @@
       </c>
       <c r="C326" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D326" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.polite.shy[1]</t>
+          <t xml:space="preserve">preMatch.polite.shy[2]</t>
         </is>
       </c>
       <c r="E326" t="inlineStr" s="2">
@@ -10774,14 +10774,14 @@
       </c>
       <c r="F326" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ず、ずっと怖かったです。でも……最後まで立っていられたのは、応援のおかげです</t>
+          <t xml:space="preserve">こ、怖いです…でも、ここで止まったら、みんなに申し訳なくて…</t>
         </is>
       </c>
     </row>
     <row r="327" ht="40" customHeight="1">
       <c r="A327" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.polite.shy[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.polite.shy[1]</t>
         </is>
       </c>
       <c r="B327" t="inlineStr" s="2">
@@ -10791,12 +10791,12 @@
       </c>
       <c r="C327" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D327" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.polite.shy[2]</t>
+          <t xml:space="preserve">survivor.polite.shy[1]</t>
         </is>
       </c>
       <c r="E327" t="inlineStr" s="2">
@@ -10806,14 +10806,14 @@
       </c>
       <c r="F327" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">身体が震えてます。でも……逃げなかったこと、褒めてもらえますか……</t>
+          <t xml:space="preserve">い、一人、倒せました…！ はぁ…まだ、退けません…次の方、来てください…！</t>
         </is>
       </c>
     </row>
     <row r="328" ht="40" customHeight="1">
       <c r="A328" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.polite.shy[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.polite.shy[2]</t>
         </is>
       </c>
       <c r="B328" t="inlineStr" s="2">
@@ -10823,12 +10823,12 @@
       </c>
       <c r="C328" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D328" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.polite.shy[1]</t>
+          <t xml:space="preserve">survivor.polite.shy[2]</t>
         </is>
       </c>
       <c r="E328" t="inlineStr" s="2">
@@ -10838,14 +10838,14 @@
       </c>
       <c r="F328" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ゆ、優勝…ですか…？ ほ、本当に…？ あ、ありがとうございます…！</t>
+          <t xml:space="preserve">怖いです…でも、まだ立ってます。仲間に繋ぐまで、ここは…次、どうぞ…</t>
         </is>
       </c>
     </row>
     <row r="329" ht="40" customHeight="1">
       <c r="A329" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.polite.shy[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.polite.shy[1]</t>
         </is>
       </c>
       <c r="B329" t="inlineStr" s="2">
@@ -10855,12 +10855,12 @@
       </c>
       <c r="C329" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D329" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.polite.shy[2]</t>
+          <t xml:space="preserve">champion.polite.shy[1]</t>
         </is>
       </c>
       <c r="E329" t="inlineStr" s="2">
@@ -10870,14 +10870,14 @@
       </c>
       <c r="F329" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">夢みたいで…まだ、信じられません…</t>
+          <t xml:space="preserve">わ、わたしがMVPなんて……二人がいてくれたから、ここまで来られたんです</t>
         </is>
       </c>
     </row>
     <row r="330" ht="40" customHeight="1">
       <c r="A330" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.polite.shy[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.polite.shy[2]</t>
         </is>
       </c>
       <c r="B330" t="inlineStr" s="2">
@@ -10887,12 +10887,12 @@
       </c>
       <c r="C330" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D330" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.polite.shy[1]</t>
+          <t xml:space="preserve">champion.polite.shy[2]</t>
         </is>
       </c>
       <c r="E330" t="inlineStr" s="2">
@@ -10902,14 +10902,14 @@
       </c>
       <c r="F330" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ま、負けてしまいました…ごめんなさい…</t>
+          <t xml:space="preserve">三人で勝てて、本当によかったです。わたしは……二人に助けられてばかりで</t>
         </is>
       </c>
     </row>
     <row r="331" ht="40" customHeight="1">
       <c r="A331" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.polite.shy[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.polite.shy[1]</t>
         </is>
       </c>
       <c r="B331" t="inlineStr" s="2">
@@ -10919,12 +10919,12 @@
       </c>
       <c r="C331" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D331" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.polite.shy[2]</t>
+          <t xml:space="preserve">defiant.polite.shy[1]</t>
         </is>
       </c>
       <c r="E331" t="inlineStr" s="2">
@@ -10934,14 +10934,14 @@
       </c>
       <c r="F331" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もっと…強くならないと…</t>
+          <t xml:space="preserve">MVPは……嬉しいです。でも、みんなで勝ちたかったです。次こそは……</t>
         </is>
       </c>
     </row>
     <row r="332" ht="40" customHeight="1">
       <c r="A332" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.polite.shy[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.polite.shy[2]</t>
         </is>
       </c>
       <c r="B332" t="inlineStr" s="2">
@@ -10951,12 +10951,12 @@
       </c>
       <c r="C332" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D332" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.polite.shy[1]</t>
+          <t xml:space="preserve">defiant.polite.shy[2]</t>
         </is>
       </c>
       <c r="E332" t="inlineStr" s="2">
@@ -10966,14 +10966,14 @@
       </c>
       <c r="F332" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">か、勝てました…次もがんばります…</t>
+          <t xml:space="preserve">一人だけ褒められても……素直に喜べなくて。次は一緒に笑いたいです</t>
         </is>
       </c>
     </row>
     <row r="333" ht="40" customHeight="1">
       <c r="A333" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.polite.shy[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.polite.shy[1]</t>
         </is>
       </c>
       <c r="B333" t="inlineStr" s="2">
@@ -10983,12 +10983,12 @@
       </c>
       <c r="C333" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D333" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.polite.shy[2]</t>
+          <t xml:space="preserve">gauntlet.polite.shy[1]</t>
         </is>
       </c>
       <c r="E333" t="inlineStr" s="2">
@@ -10998,14 +10998,14 @@
       </c>
       <c r="F333" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一勝、できました…</t>
+          <t xml:space="preserve">ず、ずっと怖かったです。でも……最後まで立っていられたのは、応援のおかげです</t>
         </is>
       </c>
     </row>
     <row r="334" ht="40" customHeight="1">
       <c r="A334" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.polite.shy[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.polite.shy[2]</t>
         </is>
       </c>
       <c r="B334" t="inlineStr" s="2">
@@ -11015,12 +11015,12 @@
       </c>
       <c r="C334" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D334" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.polite.shy[1]</t>
+          <t xml:space="preserve">gauntlet.polite.shy[2]</t>
         </is>
       </c>
       <c r="E334" t="inlineStr" s="2">
@@ -11030,14 +11030,14 @@
       </c>
       <c r="F334" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">か、勝ち上がれました…信じられません…</t>
+          <t xml:space="preserve">身体が震えてます。でも……逃げなかったこと、褒めてもらえますか……</t>
         </is>
       </c>
     </row>
     <row r="335" ht="40" customHeight="1">
       <c r="A335" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.polite.shy[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.polite.shy[1]</t>
         </is>
       </c>
       <c r="B335" t="inlineStr" s="2">
@@ -11052,7 +11052,7 @@
       </c>
       <c r="D335" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.polite.shy[2]</t>
+          <t xml:space="preserve">champion.polite.shy[1]</t>
         </is>
       </c>
       <c r="E335" t="inlineStr" s="2">
@@ -11062,14 +11062,14 @@
       </c>
       <c r="F335" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ…続けられるんですね…</t>
+          <t xml:space="preserve">ゆ、優勝…ですか…？ ほ、本当に…？ あ、ありがとうございます…！</t>
         </is>
       </c>
     </row>
     <row r="336" ht="40" customHeight="1">
       <c r="A336" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.polite.shy[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.polite.shy[2]</t>
         </is>
       </c>
       <c r="B336" t="inlineStr" s="2">
@@ -11084,7 +11084,7 @@
       </c>
       <c r="D336" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.polite.shy[1]</t>
+          <t xml:space="preserve">champion.polite.shy[2]</t>
         </is>
       </c>
       <c r="E336" t="inlineStr" s="2">
@@ -11094,14 +11094,14 @@
       </c>
       <c r="F336" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">け、決勝戦…ですか…し、信じられません…</t>
+          <t xml:space="preserve">夢みたいで…まだ、信じられません…</t>
         </is>
       </c>
     </row>
     <row r="337" ht="40" customHeight="1">
       <c r="A337" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.polite.shy[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.polite.shy[1]</t>
         </is>
       </c>
       <c r="B337" t="inlineStr" s="2">
@@ -11116,7 +11116,7 @@
       </c>
       <c r="D337" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.polite.shy[2]</t>
+          <t xml:space="preserve">postLose.polite.shy[1]</t>
         </is>
       </c>
       <c r="E337" t="inlineStr" s="2">
@@ -11126,14 +11126,14 @@
       </c>
       <c r="F337" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">夢みたい、です…</t>
+          <t xml:space="preserve">ま、負けてしまいました…ごめんなさい…</t>
         </is>
       </c>
     </row>
     <row r="338" ht="40" customHeight="1">
       <c r="A338" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.polite.shy[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.polite.shy[2]</t>
         </is>
       </c>
       <c r="B338" t="inlineStr" s="2">
@@ -11148,7 +11148,7 @@
       </c>
       <c r="D338" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.polite.shy[1]</t>
+          <t xml:space="preserve">postLose.polite.shy[2]</t>
         </is>
       </c>
       <c r="E338" t="inlineStr" s="2">
@@ -11158,14 +11158,14 @@
       </c>
       <c r="F338" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">き、緊張します…でも、精一杯やります…</t>
+          <t xml:space="preserve">もっと…強くならないと…</t>
         </is>
       </c>
     </row>
     <row r="339" ht="40" customHeight="1">
       <c r="A339" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.polite.shy[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.polite.shy[1]</t>
         </is>
       </c>
       <c r="B339" t="inlineStr" s="2">
@@ -11180,7 +11180,7 @@
       </c>
       <c r="D339" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.polite.shy[2]</t>
+          <t xml:space="preserve">postMatchWin.polite.shy[1]</t>
         </is>
       </c>
       <c r="E339" t="inlineStr" s="2">
@@ -11190,14 +11190,14 @@
       </c>
       <c r="F339" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふ、深呼吸…落ち着かないと…</t>
+          <t xml:space="preserve">か、勝てました…次もがんばります…</t>
         </is>
       </c>
     </row>
     <row r="340" ht="40" customHeight="1">
       <c r="A340" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.polite.shy[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.polite.shy[2]</t>
         </is>
       </c>
       <c r="B340" t="inlineStr" s="2">
@@ -11212,7 +11212,7 @@
       </c>
       <c r="D340" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.polite.shy[1]</t>
+          <t xml:space="preserve">postMatchWin.polite.shy[2]</t>
         </is>
       </c>
       <c r="E340" t="inlineStr" s="2">
@@ -11222,14 +11222,14 @@
       </c>
       <c r="F340" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">え、わたしが…ジュニアトーナメントに…？ あ、あの、頑張ります…！</t>
+          <t xml:space="preserve">一勝、できました…</t>
         </is>
       </c>
     </row>
     <row r="341" ht="40" customHeight="1">
       <c r="A341" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.polite.shy[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.polite.shy[1]</t>
         </is>
       </c>
       <c r="B341" t="inlineStr" s="2">
@@ -11244,7 +11244,7 @@
       </c>
       <c r="D341" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.polite.shy[2]</t>
+          <t xml:space="preserve">postWin.polite.shy[1]</t>
         </is>
       </c>
       <c r="E341" t="inlineStr" s="2">
@@ -11254,14 +11254,14 @@
       </c>
       <c r="F341" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">選んでいただいて…あ、ありがとうございます…</t>
+          <t xml:space="preserve">か、勝ち上がれました…信じられません…</t>
         </is>
       </c>
     </row>
     <row r="342" ht="40" customHeight="1">
       <c r="A342" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.polite.shy[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.polite.shy[2]</t>
         </is>
       </c>
       <c r="B342" t="inlineStr" s="2">
@@ -11271,12 +11271,12 @@
       </c>
       <c r="C342" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D342" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.shy[1]</t>
+          <t xml:space="preserve">postWin.polite.shy[2]</t>
         </is>
       </c>
       <c r="E342" t="inlineStr" s="2">
@@ -11286,14 +11286,14 @@
       </c>
       <c r="F342" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、あの方が…相手なんですね…せ、精一杯戦います…</t>
+          <t xml:space="preserve">まだ…続けられるんですね…</t>
         </is>
       </c>
     </row>
     <row r="343" ht="40" customHeight="1">
       <c r="A343" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.polite.shy[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.polite.shy[1]</t>
         </is>
       </c>
       <c r="B343" t="inlineStr" s="2">
@@ -11303,12 +11303,12 @@
       </c>
       <c r="C343" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D343" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.shy[1]</t>
+          <t xml:space="preserve">preFinal.polite.shy[1]</t>
         </is>
       </c>
       <c r="E343" t="inlineStr" s="2">
@@ -11318,14 +11318,14 @@
       </c>
       <c r="F343" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">か、勝てました……本当に……ありがとうございます……</t>
+          <t xml:space="preserve">け、決勝戦…ですか…し、信じられません…</t>
         </is>
       </c>
     </row>
     <row r="344" ht="40" customHeight="1">
       <c r="A344" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.polite.shy[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.polite.shy[2]</t>
         </is>
       </c>
       <c r="B344" t="inlineStr" s="2">
@@ -11335,12 +11335,12 @@
       </c>
       <c r="C344" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D344" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.shy[1]</t>
+          <t xml:space="preserve">preFinal.polite.shy[2]</t>
         </is>
       </c>
       <c r="E344" t="inlineStr" s="2">
@@ -11350,14 +11350,14 @@
       </c>
       <c r="F344" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、あの…団体として、挑戦させてください…</t>
+          <t xml:space="preserve">夢みたい、です…</t>
         </is>
       </c>
     </row>
     <row r="345" ht="40" customHeight="1">
       <c r="A345" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.polite.shy[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.polite.shy[1]</t>
         </is>
       </c>
       <c r="B345" t="inlineStr" s="2">
@@ -11367,12 +11367,12 @@
       </c>
       <c r="C345" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D345" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.shy[2]</t>
+          <t xml:space="preserve">preMatch.polite.shy[1]</t>
         </is>
       </c>
       <c r="E345" t="inlineStr" s="2">
@@ -11382,14 +11382,14 @@
       </c>
       <c r="F345" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">み、みんなで戦います…</t>
+          <t xml:space="preserve">き、緊張します…でも、精一杯やります…</t>
         </is>
       </c>
     </row>
     <row r="346" ht="40" customHeight="1">
       <c r="A346" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.polite.shy[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.polite.shy[2]</t>
         </is>
       </c>
       <c r="B346" t="inlineStr" s="2">
@@ -11399,12 +11399,12 @@
       </c>
       <c r="C346" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D346" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.shy[1]</t>
+          <t xml:space="preserve">preMatch.polite.shy[2]</t>
         </is>
       </c>
       <c r="E346" t="inlineStr" s="2">
@@ -11414,14 +11414,14 @@
       </c>
       <c r="F346" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">す、すみません…今回は、お断りさせてください…</t>
+          <t xml:space="preserve">ふ、深呼吸…落ち着かないと…</t>
         </is>
       </c>
     </row>
     <row r="347" ht="40" customHeight="1">
       <c r="A347" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.polite.shy[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.polite.shy[1]</t>
         </is>
       </c>
       <c r="B347" t="inlineStr" s="2">
@@ -11431,12 +11431,12 @@
       </c>
       <c r="C347" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D347" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.shy[2]</t>
+          <t xml:space="preserve">summon.polite.shy[1]</t>
         </is>
       </c>
       <c r="E347" t="inlineStr" s="2">
@@ -11446,14 +11446,14 @@
       </c>
       <c r="F347" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ま、また機会があれば…</t>
+          <t xml:space="preserve">え、わたしが…ジュニアトーナメントに…？ あ、あの、頑張ります…！</t>
         </is>
       </c>
     </row>
     <row r="348" ht="40" customHeight="1">
       <c r="A348" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.polite.shy[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.polite.shy[2]</t>
         </is>
       </c>
       <c r="B348" t="inlineStr" s="2">
@@ -11463,12 +11463,12 @@
       </c>
       <c r="C348" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D348" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.polite.shy[1]</t>
+          <t xml:space="preserve">summon.polite.shy[2]</t>
         </is>
       </c>
       <c r="E348" t="inlineStr" s="2">
@@ -11478,14 +11478,14 @@
       </c>
       <c r="F348" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ま、負けてしまいました…ご、ごめんなさい…</t>
+          <t xml:space="preserve">選んでいただいて…あ、ありがとうございます…</t>
         </is>
       </c>
     </row>
     <row r="349" ht="40" customHeight="1">
       <c r="A349" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.polite.shy[2]</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.polite.shy[1]</t>
         </is>
       </c>
       <c r="B349" t="inlineStr" s="2">
@@ -11495,12 +11495,12 @@
       </c>
       <c r="C349" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
         </is>
       </c>
       <c r="D349" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.polite.shy[2]</t>
+          <t xml:space="preserve">polite.shy[1]</t>
         </is>
       </c>
       <c r="E349" t="inlineStr" s="2">
@@ -11510,14 +11510,14 @@
       </c>
       <c r="F349" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次は…次こそは…</t>
+          <t xml:space="preserve">あ、あの方が…相手なんですね…せ、精一杯戦います…</t>
         </is>
       </c>
     </row>
     <row r="350" ht="40" customHeight="1">
       <c r="A350" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.polite.shy[1]</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.polite.shy[1]</t>
         </is>
       </c>
       <c r="B350" t="inlineStr" s="2">
@@ -11527,12 +11527,12 @@
       </c>
       <c r="C350" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D350" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.polite.shy[1]</t>
+          <t xml:space="preserve">polite.shy[1]</t>
         </is>
       </c>
       <c r="E350" t="inlineStr" s="2">
@@ -11542,14 +11542,14 @@
       </c>
       <c r="F350" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">か、勝てました…団体のみなさんのおかげです…</t>
+          <t xml:space="preserve">か、勝てました……本当に……ありがとうございます……</t>
         </is>
       </c>
     </row>
     <row r="351" ht="40" customHeight="1">
       <c r="A351" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.polite.shy[2]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.polite.shy[1]</t>
         </is>
       </c>
       <c r="B351" t="inlineStr" s="2">
@@ -11559,12 +11559,12 @@
       </c>
       <c r="C351" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
         </is>
       </c>
       <c r="D351" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.polite.shy[2]</t>
+          <t xml:space="preserve">polite.shy[1]</t>
         </is>
       </c>
       <c r="E351" t="inlineStr" s="2">
@@ -11574,14 +11574,14 @@
       </c>
       <c r="F351" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">応援、ありがとうございました…</t>
+          <t xml:space="preserve">あ、あの…団体として、挑戦させてください…</t>
         </is>
       </c>
     </row>
     <row r="352" ht="40" customHeight="1">
       <c r="A352" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.polite.shy[1]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.polite.shy[2]</t>
         </is>
       </c>
       <c r="B352" t="inlineStr" s="2">
@@ -11591,12 +11591,12 @@
       </c>
       <c r="C352" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
         </is>
       </c>
       <c r="D352" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.shy[1]</t>
+          <t xml:space="preserve">polite.shy[2]</t>
         </is>
       </c>
       <c r="E352" t="inlineStr" s="2">
@@ -11606,14 +11606,14 @@
       </c>
       <c r="F352" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">か、勝てました…！ 団体のみなさまに恥じない試合が…できたでしょうか…</t>
+          <t xml:space="preserve">み、みんなで戦います…</t>
         </is>
       </c>
     </row>
     <row r="353" ht="40" customHeight="1">
       <c r="A353" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.polite.shy[2]</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.polite.shy[1]</t>
         </is>
       </c>
       <c r="B353" t="inlineStr" s="2">
@@ -11623,12 +11623,12 @@
       </c>
       <c r="C353" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
         </is>
       </c>
       <c r="D353" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.shy[2]</t>
+          <t xml:space="preserve">polite.shy[1]</t>
         </is>
       </c>
       <c r="E353" t="inlineStr" s="2">
@@ -11638,14 +11638,14 @@
       </c>
       <c r="F353" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">か、勝たせていただきました…。団体のみなさまに…少しは恩返しできたでしょうか…</t>
+          <t xml:space="preserve">す、すみません…今回は、お断りさせてください…</t>
         </is>
       </c>
     </row>
     <row r="354" ht="40" customHeight="1">
       <c r="A354" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.polite.shy[3]</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.polite.shy[2]</t>
         </is>
       </c>
       <c r="B354" t="inlineStr" s="2">
@@ -11655,12 +11655,12 @@
       </c>
       <c r="C354" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
         </is>
       </c>
       <c r="D354" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.shy[3]</t>
+          <t xml:space="preserve">polite.shy[2]</t>
         </is>
       </c>
       <c r="E354" t="inlineStr" s="2">
@@ -11670,14 +11670,14 @@
       </c>
       <c r="F354" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">か、勝てました…！ 団体のみなさまに恥じない試合が…できていたら嬉しいです…</t>
+          <t xml:space="preserve">ま、また機会があれば…</t>
         </is>
       </c>
     </row>
     <row r="355" ht="40" customHeight="1">
       <c r="A355" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.polite.shy[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.polite.shy[1]</t>
         </is>
       </c>
       <c r="B355" t="inlineStr" s="2">
@@ -11687,29 +11687,29 @@
       </c>
       <c r="C355" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ENDING_LINES</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
         </is>
       </c>
       <c r="D355" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.polite.shy[1]</t>
+          <t xml:space="preserve">result_lose.polite.shy[1]</t>
         </is>
       </c>
       <c r="E355" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">18 経営危機・エンディング</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F355" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こ、これで…リングを降ります…あ、あの、応援してくれた皆さま…本当に、ありがとうございました…</t>
+          <t xml:space="preserve">ま、負けてしまいました…ご、ごめんなさい…</t>
         </is>
       </c>
     </row>
     <row r="356" ht="40" customHeight="1">
       <c r="A356" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.polite.shy[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.polite.shy[2]</t>
         </is>
       </c>
       <c r="B356" t="inlineStr" s="2">
@@ -11719,59 +11719,283 @@
       </c>
       <c r="C356" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
         </is>
       </c>
       <c r="D356" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.shy[1]</t>
+          <t xml:space="preserve">result_lose.polite.shy[2]</t>
         </is>
       </c>
       <c r="E356" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">19 ドラフト・スカウト</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F356" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、あの…契約してもらえて…感謝しています…！</t>
+          <t xml:space="preserve">次は…次こそは…</t>
         </is>
       </c>
     </row>
     <row r="357" ht="40" customHeight="1">
       <c r="A357" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.polite.shy[1]</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">result_win.polite.shy[1]</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F357" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">か、勝てました…団体のみなさんのおかげです…</t>
+        </is>
+      </c>
+    </row>
+    <row r="358" ht="40" customHeight="1">
+      <c r="A358" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.polite.shy[2]</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">result_win.polite.shy[2]</t>
+        </is>
+      </c>
+      <c r="E358" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F358" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">応援、ありがとうございました…</t>
+        </is>
+      </c>
+    </row>
+    <row r="359" ht="40" customHeight="1">
+      <c r="A359" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.polite.shy[1]</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">polite.shy[1]</t>
+        </is>
+      </c>
+      <c r="E359" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F359" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">か、勝てました…！ 団体のみなさまに恥じない試合が…できたでしょうか…</t>
+        </is>
+      </c>
+    </row>
+    <row r="360" ht="40" customHeight="1">
+      <c r="A360" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.polite.shy[2]</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">polite.shy[2]</t>
+        </is>
+      </c>
+      <c r="E360" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F360" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">か、勝たせていただきました…。団体のみなさまに…少しは恩返しできたでしょうか…</t>
+        </is>
+      </c>
+    </row>
+    <row r="361" ht="40" customHeight="1">
+      <c r="A361" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.polite.shy[3]</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">polite.shy[3]</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F361" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">か、勝てました…！ 団体のみなさまに恥じない試合が…できていたら嬉しいです…</t>
+        </is>
+      </c>
+    </row>
+    <row r="362" ht="40" customHeight="1">
+      <c r="A362" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">ENDING_LINES.fighter.polite.shy[1]</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ENDING_LINES</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">fighter.polite.shy[1]</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">18 経営危機・エンディング</t>
+        </is>
+      </c>
+      <c r="F362" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">こ、これで…リングを降ります…あ、あの、応援してくれた皆さま…本当に、ありがとうございました…</t>
+        </is>
+      </c>
+    </row>
+    <row r="363" ht="40" customHeight="1">
+      <c r="A363" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES.polite.shy[1]</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">polite.shy[1]</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F363" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あ、あの…契約してもらえて…感謝しています…！</t>
+        </is>
+      </c>
+    </row>
+    <row r="364" ht="40" customHeight="1">
+      <c r="A364" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES.polite.shy[1]</t>
         </is>
       </c>
-      <c r="B357" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C357" t="inlineStr" s="2">
+      <c r="B364" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES</t>
         </is>
       </c>
-      <c r="D357" t="inlineStr" s="12">
+      <c r="D364" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">polite.shy[1]</t>
         </is>
       </c>
-      <c r="E357" t="inlineStr" s="2">
+      <c r="E364" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">19 ドラフト・スカウト</t>
         </is>
       </c>
-      <c r="F357" t="inlineStr" s="3">
+      <c r="F364" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">あ、あの…お声がけ、光栄です…！</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H357"/>
+  <autoFilter ref="A1:H364"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/キャラタイプ別/丁寧×内気.xlsx
+++ b/セリフ編集/キャラタイプ別/丁寧×内気.xlsx
@@ -323,7 +323,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H357"/>
+  <dimension ref="A1:H339"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -9821,7 +9821,7 @@
     <row r="297" ht="40" customHeight="1">
       <c r="A297" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.polite.shy[1]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.polite.shy[1]</t>
         </is>
       </c>
       <c r="B297" t="inlineStr" s="2">
@@ -9831,12 +9831,12 @@
       </c>
       <c r="C297" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
         </is>
       </c>
       <c r="D297" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-02.polite.shy[1]</t>
+          <t xml:space="preserve">polite.shy[1]</t>
         </is>
       </c>
       <c r="E297" t="inlineStr" s="2">
@@ -9846,14 +9846,14 @@
       </c>
       <c r="F297" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、あの…今日は、よろしくお願いいたします…</t>
+          <t xml:space="preserve">良い流れが…止まってしまいました…で、でも、また頑張ります…</t>
         </is>
       </c>
     </row>
     <row r="298" ht="40" customHeight="1">
       <c r="A298" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.polite.shy[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.polite.shy[1]</t>
         </is>
       </c>
       <c r="B298" t="inlineStr" s="2">
@@ -9863,29 +9863,29 @@
       </c>
       <c r="C298" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D298" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-02.polite.shy[2]</t>
+          <t xml:space="preserve">preFinal.polite.shy[1]</t>
         </is>
       </c>
       <c r="E298" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F298" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">頑張ります…</t>
+          <t xml:space="preserve">け、決勝…。信じられないけど…最後まで、立たせてください…</t>
         </is>
       </c>
     </row>
     <row r="299" ht="40" customHeight="1">
       <c r="A299" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.down.polite.shy[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.polite.shy[2]</t>
         </is>
       </c>
       <c r="B299" t="inlineStr" s="2">
@@ -9895,29 +9895,29 @@
       </c>
       <c r="C299" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D299" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-03.down.polite.shy[1]</t>
+          <t xml:space="preserve">preFinal.polite.shy[2]</t>
         </is>
       </c>
       <c r="E299" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F299" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">う、うまくいきません…どうしたら…</t>
+          <t xml:space="preserve">身体は痛いです…でも、ここで退いたら、繋いでくれた分が…</t>
         </is>
       </c>
     </row>
     <row r="300" ht="40" customHeight="1">
       <c r="A300" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.up.polite.shy[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.polite.shy[1]</t>
         </is>
       </c>
       <c r="B300" t="inlineStr" s="2">
@@ -9927,29 +9927,29 @@
       </c>
       <c r="C300" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D300" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-03.up.polite.shy[1]</t>
+          <t xml:space="preserve">preMatch.polite.shy[1]</t>
         </is>
       </c>
       <c r="E300" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F300" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">調子が…良い気がします…</t>
+          <t xml:space="preserve">あ、相手の方…がんばります。仲間が待ってるので、退けません…</t>
         </is>
       </c>
     </row>
     <row r="301" ht="40" customHeight="1">
       <c r="A301" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04.polite.shy[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.polite.shy[2]</t>
         </is>
       </c>
       <c r="B301" t="inlineStr" s="2">
@@ -9959,29 +9959,29 @@
       </c>
       <c r="C301" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D301" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-04.polite.shy[1]</t>
+          <t xml:space="preserve">preMatch.polite.shy[2]</t>
         </is>
       </c>
       <c r="E301" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F301" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">練習…させていただきます…</t>
+          <t xml:space="preserve">こ、怖いです…でも、ここで止まったら、みんなに申し訳なくて…</t>
         </is>
       </c>
     </row>
     <row r="302" ht="40" customHeight="1">
       <c r="A302" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04.polite.shy[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.polite.shy[1]</t>
         </is>
       </c>
       <c r="B302" t="inlineStr" s="2">
@@ -9991,29 +9991,29 @@
       </c>
       <c r="C302" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D302" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-04.polite.shy[2]</t>
+          <t xml:space="preserve">survivor.polite.shy[1]</t>
         </is>
       </c>
       <c r="E302" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F302" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もう少し…頑張ります…</t>
+          <t xml:space="preserve">い、一人、倒せました…！ はぁ…まだ、退けません…次の方、来てください…！</t>
         </is>
       </c>
     </row>
     <row r="303" ht="40" customHeight="1">
       <c r="A303" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05.polite.shy[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.polite.shy[2]</t>
         </is>
       </c>
       <c r="B303" t="inlineStr" s="2">
@@ -10023,29 +10023,29 @@
       </c>
       <c r="C303" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D303" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-05.polite.shy[1]</t>
+          <t xml:space="preserve">survivor.polite.shy[2]</t>
         </is>
       </c>
       <c r="E303" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F303" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、あの…大丈夫です、心配しないでください…</t>
+          <t xml:space="preserve">怖いです…でも、まだ立ってます。仲間に繋ぐまで、ここは…次、どうぞ…</t>
         </is>
       </c>
     </row>
     <row r="304" ht="40" customHeight="1">
       <c r="A304" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05.polite.shy[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.polite.shy[1]</t>
         </is>
       </c>
       <c r="B304" t="inlineStr" s="2">
@@ -10055,29 +10055,29 @@
       </c>
       <c r="C304" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D304" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-05.polite.shy[2]</t>
+          <t xml:space="preserve">champion.polite.shy[1]</t>
         </is>
       </c>
       <c r="E304" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F304" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ご心配を、おかけして…</t>
+          <t xml:space="preserve">わ、わたしがMVPなんて……二人がいてくれたから、ここまで来られたんです</t>
         </is>
       </c>
     </row>
     <row r="305" ht="40" customHeight="1">
       <c r="A305" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.polite.shy[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.polite.shy[2]</t>
         </is>
       </c>
       <c r="B305" t="inlineStr" s="2">
@@ -10087,29 +10087,29 @@
       </c>
       <c r="C305" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D305" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-06.polite.shy[1]</t>
+          <t xml:space="preserve">champion.polite.shy[2]</t>
         </is>
       </c>
       <c r="E305" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F305" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">みんなと…一緒だと、心強いです…</t>
+          <t xml:space="preserve">三人で勝てて、本当によかったです。わたしは……二人に助けられてばかりで</t>
         </is>
       </c>
     </row>
     <row r="306" ht="40" customHeight="1">
       <c r="A306" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.polite.shy[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.polite.shy[1]</t>
         </is>
       </c>
       <c r="B306" t="inlineStr" s="2">
@@ -10119,29 +10119,29 @@
       </c>
       <c r="C306" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D306" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-06.polite.shy[2]</t>
+          <t xml:space="preserve">defiant.polite.shy[1]</t>
         </is>
       </c>
       <c r="E306" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F306" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">仲間って、いいですね…</t>
+          <t xml:space="preserve">MVPは……嬉しいです。でも、みんなで勝ちたかったです。次こそは……</t>
         </is>
       </c>
     </row>
     <row r="307" ht="40" customHeight="1">
       <c r="A307" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07.polite.shy[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.polite.shy[2]</t>
         </is>
       </c>
       <c r="B307" t="inlineStr" s="2">
@@ -10151,29 +10151,29 @@
       </c>
       <c r="C307" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D307" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-07.polite.shy[1]</t>
+          <t xml:space="preserve">defiant.polite.shy[2]</t>
         </is>
       </c>
       <c r="E307" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F307" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お、お客さんがいっぱいで…き、緊張します…</t>
+          <t xml:space="preserve">一人だけ褒められても……素直に喜べなくて。次は一緒に笑いたいです</t>
         </is>
       </c>
     </row>
     <row r="308" ht="40" customHeight="1">
       <c r="A308" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07.polite.shy[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.polite.shy[1]</t>
         </is>
       </c>
       <c r="B308" t="inlineStr" s="2">
@@ -10183,29 +10183,29 @@
       </c>
       <c r="C308" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D308" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-07.polite.shy[2]</t>
+          <t xml:space="preserve">gauntlet.polite.shy[1]</t>
         </is>
       </c>
       <c r="E308" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F308" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">がんばります…</t>
+          <t xml:space="preserve">ず、ずっと怖かったです。でも……最後まで立っていられたのは、応援のおかげです</t>
         </is>
       </c>
     </row>
     <row r="309" ht="40" customHeight="1">
       <c r="A309" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.polite.shy[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.polite.shy[2]</t>
         </is>
       </c>
       <c r="B309" t="inlineStr" s="2">
@@ -10215,29 +10215,29 @@
       </c>
       <c r="C309" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D309" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-08.polite.shy[1]</t>
+          <t xml:space="preserve">gauntlet.polite.shy[2]</t>
         </is>
       </c>
       <c r="E309" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F309" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、あの…体調は、大丈夫です…</t>
+          <t xml:space="preserve">身体が震えてます。でも……逃げなかったこと、褒めてもらえますか……</t>
         </is>
       </c>
     </row>
     <row r="310" ht="40" customHeight="1">
       <c r="A310" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.polite.shy[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.polite.shy[1]</t>
         </is>
       </c>
       <c r="B310" t="inlineStr" s="2">
@@ -10247,29 +10247,29 @@
       </c>
       <c r="C310" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D310" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-08.polite.shy[2]</t>
+          <t xml:space="preserve">champion.polite.shy[1]</t>
         </is>
       </c>
       <c r="E310" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F310" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">無理はしません…</t>
+          <t xml:space="preserve">ゆ、優勝…ですか…？ ほ、本当に…？ あ、ありがとうございます…！</t>
         </is>
       </c>
     </row>
     <row r="311" ht="40" customHeight="1">
       <c r="A311" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.polite.shy[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.polite.shy[2]</t>
         </is>
       </c>
       <c r="B311" t="inlineStr" s="2">
@@ -10279,29 +10279,29 @@
       </c>
       <c r="C311" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D311" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-09.polite.shy[1]</t>
+          <t xml:space="preserve">champion.polite.shy[2]</t>
         </is>
       </c>
       <c r="E311" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F311" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次の試合…が、頑張ります…</t>
+          <t xml:space="preserve">夢みたいで…まだ、信じられません…</t>
         </is>
       </c>
     </row>
     <row r="312" ht="40" customHeight="1">
       <c r="A312" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.polite.shy[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.polite.shy[1]</t>
         </is>
       </c>
       <c r="B312" t="inlineStr" s="2">
@@ -10311,29 +10311,29 @@
       </c>
       <c r="C312" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D312" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-09.polite.shy[2]</t>
+          <t xml:space="preserve">postLose.polite.shy[1]</t>
         </is>
       </c>
       <c r="E312" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F312" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">しっかり、準備します…</t>
+          <t xml:space="preserve">ま、負けてしまいました…ごめんなさい…</t>
         </is>
       </c>
     </row>
     <row r="313" ht="40" customHeight="1">
       <c r="A313" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.polite.shy[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.polite.shy[2]</t>
         </is>
       </c>
       <c r="B313" t="inlineStr" s="2">
@@ -10343,29 +10343,29 @@
       </c>
       <c r="C313" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D313" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-10.polite.shy[1]</t>
+          <t xml:space="preserve">postLose.polite.shy[2]</t>
         </is>
       </c>
       <c r="E313" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F313" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、あの…ありがとうございます…</t>
+          <t xml:space="preserve">もっと…強くならないと…</t>
         </is>
       </c>
     </row>
     <row r="314" ht="40" customHeight="1">
       <c r="A314" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.polite.shy[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.polite.shy[1]</t>
         </is>
       </c>
       <c r="B314" t="inlineStr" s="2">
@@ -10375,29 +10375,29 @@
       </c>
       <c r="C314" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D314" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-10.polite.shy[2]</t>
+          <t xml:space="preserve">postMatchWin.polite.shy[1]</t>
         </is>
       </c>
       <c r="E314" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F314" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">感謝、しています…</t>
+          <t xml:space="preserve">か、勝てました…次もがんばります…</t>
         </is>
       </c>
     </row>
     <row r="315" ht="40" customHeight="1">
       <c r="A315" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.polite.shy[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.polite.shy[2]</t>
         </is>
       </c>
       <c r="B315" t="inlineStr" s="2">
@@ -10407,29 +10407,29 @@
       </c>
       <c r="C315" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D315" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.shy[1]</t>
+          <t xml:space="preserve">postMatchWin.polite.shy[2]</t>
         </is>
       </c>
       <c r="E315" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F315" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">良い流れが…止まってしまいました…で、でも、また頑張ります…</t>
+          <t xml:space="preserve">一勝、できました…</t>
         </is>
       </c>
     </row>
     <row r="316" ht="40" customHeight="1">
       <c r="A316" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.polite.shy[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.polite.shy[1]</t>
         </is>
       </c>
       <c r="B316" t="inlineStr" s="2">
@@ -10439,12 +10439,12 @@
       </c>
       <c r="C316" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D316" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.polite.shy[1]</t>
+          <t xml:space="preserve">postWin.polite.shy[1]</t>
         </is>
       </c>
       <c r="E316" t="inlineStr" s="2">
@@ -10454,14 +10454,14 @@
       </c>
       <c r="F316" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">け、決勝…。信じられないけど…最後まで、立たせてください…</t>
+          <t xml:space="preserve">か、勝ち上がれました…信じられません…</t>
         </is>
       </c>
     </row>
     <row r="317" ht="40" customHeight="1">
       <c r="A317" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.polite.shy[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.polite.shy[2]</t>
         </is>
       </c>
       <c r="B317" t="inlineStr" s="2">
@@ -10471,12 +10471,12 @@
       </c>
       <c r="C317" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D317" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.polite.shy[2]</t>
+          <t xml:space="preserve">postWin.polite.shy[2]</t>
         </is>
       </c>
       <c r="E317" t="inlineStr" s="2">
@@ -10486,14 +10486,14 @@
       </c>
       <c r="F317" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">身体は痛いです…でも、ここで退いたら、繋いでくれた分が…</t>
+          <t xml:space="preserve">まだ…続けられるんですね…</t>
         </is>
       </c>
     </row>
     <row r="318" ht="40" customHeight="1">
       <c r="A318" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.polite.shy[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.polite.shy[1]</t>
         </is>
       </c>
       <c r="B318" t="inlineStr" s="2">
@@ -10503,12 +10503,12 @@
       </c>
       <c r="C318" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D318" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.polite.shy[1]</t>
+          <t xml:space="preserve">preFinal.polite.shy[1]</t>
         </is>
       </c>
       <c r="E318" t="inlineStr" s="2">
@@ -10518,14 +10518,14 @@
       </c>
       <c r="F318" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、相手の方…がんばります。仲間が待ってるので、退けません…</t>
+          <t xml:space="preserve">け、決勝戦…ですか…し、信じられません…</t>
         </is>
       </c>
     </row>
     <row r="319" ht="40" customHeight="1">
       <c r="A319" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.polite.shy[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.polite.shy[2]</t>
         </is>
       </c>
       <c r="B319" t="inlineStr" s="2">
@@ -10535,12 +10535,12 @@
       </c>
       <c r="C319" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D319" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.polite.shy[2]</t>
+          <t xml:space="preserve">preFinal.polite.shy[2]</t>
         </is>
       </c>
       <c r="E319" t="inlineStr" s="2">
@@ -10550,14 +10550,14 @@
       </c>
       <c r="F319" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こ、怖いです…でも、ここで止まったら、みんなに申し訳なくて…</t>
+          <t xml:space="preserve">夢みたい、です…</t>
         </is>
       </c>
     </row>
     <row r="320" ht="40" customHeight="1">
       <c r="A320" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.polite.shy[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.polite.shy[1]</t>
         </is>
       </c>
       <c r="B320" t="inlineStr" s="2">
@@ -10567,12 +10567,12 @@
       </c>
       <c r="C320" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D320" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.polite.shy[1]</t>
+          <t xml:space="preserve">preMatch.polite.shy[1]</t>
         </is>
       </c>
       <c r="E320" t="inlineStr" s="2">
@@ -10582,14 +10582,14 @@
       </c>
       <c r="F320" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">い、一人、倒せました…！ はぁ…まだ、退けません…次の方、来てください…！</t>
+          <t xml:space="preserve">き、緊張します…でも、精一杯やります…</t>
         </is>
       </c>
     </row>
     <row r="321" ht="40" customHeight="1">
       <c r="A321" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.polite.shy[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.polite.shy[2]</t>
         </is>
       </c>
       <c r="B321" t="inlineStr" s="2">
@@ -10599,12 +10599,12 @@
       </c>
       <c r="C321" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D321" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.polite.shy[2]</t>
+          <t xml:space="preserve">preMatch.polite.shy[2]</t>
         </is>
       </c>
       <c r="E321" t="inlineStr" s="2">
@@ -10614,14 +10614,14 @@
       </c>
       <c r="F321" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">怖いです…でも、まだ立ってます。仲間に繋ぐまで、ここは…次、どうぞ…</t>
+          <t xml:space="preserve">ふ、深呼吸…落ち着かないと…</t>
         </is>
       </c>
     </row>
     <row r="322" ht="40" customHeight="1">
       <c r="A322" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.polite.shy[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.polite.shy[1]</t>
         </is>
       </c>
       <c r="B322" t="inlineStr" s="2">
@@ -10631,12 +10631,12 @@
       </c>
       <c r="C322" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D322" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.polite.shy[1]</t>
+          <t xml:space="preserve">summon.polite.shy[1]</t>
         </is>
       </c>
       <c r="E322" t="inlineStr" s="2">
@@ -10646,14 +10646,14 @@
       </c>
       <c r="F322" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わ、わたしがMVPなんて……二人がいてくれたから、ここまで来られたんです</t>
+          <t xml:space="preserve">え、わたしが…ジュニアトーナメントに…？ あ、あの、頑張ります…！</t>
         </is>
       </c>
     </row>
     <row r="323" ht="40" customHeight="1">
       <c r="A323" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.polite.shy[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.polite.shy[2]</t>
         </is>
       </c>
       <c r="B323" t="inlineStr" s="2">
@@ -10663,12 +10663,12 @@
       </c>
       <c r="C323" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D323" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.polite.shy[2]</t>
+          <t xml:space="preserve">summon.polite.shy[2]</t>
         </is>
       </c>
       <c r="E323" t="inlineStr" s="2">
@@ -10678,14 +10678,14 @@
       </c>
       <c r="F323" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">三人で勝てて、本当によかったです。わたしは……二人に助けられてばかりで</t>
+          <t xml:space="preserve">選んでいただいて…あ、ありがとうございます…</t>
         </is>
       </c>
     </row>
     <row r="324" ht="40" customHeight="1">
       <c r="A324" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.polite.shy[1]</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.polite.shy[1]</t>
         </is>
       </c>
       <c r="B324" t="inlineStr" s="2">
@@ -10695,12 +10695,12 @@
       </c>
       <c r="C324" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
         </is>
       </c>
       <c r="D324" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.polite.shy[1]</t>
+          <t xml:space="preserve">polite.shy[1]</t>
         </is>
       </c>
       <c r="E324" t="inlineStr" s="2">
@@ -10710,14 +10710,14 @@
       </c>
       <c r="F324" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">MVPは……嬉しいです。でも、みんなで勝ちたかったです。次こそは……</t>
+          <t xml:space="preserve">あ、あの方が…相手なんですね…せ、精一杯戦います…</t>
         </is>
       </c>
     </row>
     <row r="325" ht="40" customHeight="1">
       <c r="A325" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.polite.shy[2]</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.polite.shy[1]</t>
         </is>
       </c>
       <c r="B325" t="inlineStr" s="2">
@@ -10727,12 +10727,12 @@
       </c>
       <c r="C325" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D325" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.polite.shy[2]</t>
+          <t xml:space="preserve">polite.shy[1]</t>
         </is>
       </c>
       <c r="E325" t="inlineStr" s="2">
@@ -10742,14 +10742,14 @@
       </c>
       <c r="F325" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人だけ褒められても……素直に喜べなくて。次は一緒に笑いたいです</t>
+          <t xml:space="preserve">か、勝てました……本当に……ありがとうございます……</t>
         </is>
       </c>
     </row>
     <row r="326" ht="40" customHeight="1">
       <c r="A326" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.polite.shy[1]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.polite.shy[1]</t>
         </is>
       </c>
       <c r="B326" t="inlineStr" s="2">
@@ -10759,12 +10759,12 @@
       </c>
       <c r="C326" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
         </is>
       </c>
       <c r="D326" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.polite.shy[1]</t>
+          <t xml:space="preserve">polite.shy[1]</t>
         </is>
       </c>
       <c r="E326" t="inlineStr" s="2">
@@ -10774,14 +10774,14 @@
       </c>
       <c r="F326" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ず、ずっと怖かったです。でも……最後まで立っていられたのは、応援のおかげです</t>
+          <t xml:space="preserve">あ、あの…団体として、挑戦させてください…</t>
         </is>
       </c>
     </row>
     <row r="327" ht="40" customHeight="1">
       <c r="A327" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.polite.shy[2]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.polite.shy[2]</t>
         </is>
       </c>
       <c r="B327" t="inlineStr" s="2">
@@ -10791,12 +10791,12 @@
       </c>
       <c r="C327" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
         </is>
       </c>
       <c r="D327" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.polite.shy[2]</t>
+          <t xml:space="preserve">polite.shy[2]</t>
         </is>
       </c>
       <c r="E327" t="inlineStr" s="2">
@@ -10806,14 +10806,14 @@
       </c>
       <c r="F327" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">身体が震えてます。でも……逃げなかったこと、褒めてもらえますか……</t>
+          <t xml:space="preserve">み、みんなで戦います…</t>
         </is>
       </c>
     </row>
     <row r="328" ht="40" customHeight="1">
       <c r="A328" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.polite.shy[1]</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.polite.shy[1]</t>
         </is>
       </c>
       <c r="B328" t="inlineStr" s="2">
@@ -10823,12 +10823,12 @@
       </c>
       <c r="C328" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
         </is>
       </c>
       <c r="D328" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.polite.shy[1]</t>
+          <t xml:space="preserve">polite.shy[1]</t>
         </is>
       </c>
       <c r="E328" t="inlineStr" s="2">
@@ -10838,14 +10838,14 @@
       </c>
       <c r="F328" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ゆ、優勝…ですか…？ ほ、本当に…？ あ、ありがとうございます…！</t>
+          <t xml:space="preserve">す、すみません…今回は、お断りさせてください…</t>
         </is>
       </c>
     </row>
     <row r="329" ht="40" customHeight="1">
       <c r="A329" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.polite.shy[2]</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.polite.shy[2]</t>
         </is>
       </c>
       <c r="B329" t="inlineStr" s="2">
@@ -10855,12 +10855,12 @@
       </c>
       <c r="C329" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
         </is>
       </c>
       <c r="D329" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.polite.shy[2]</t>
+          <t xml:space="preserve">polite.shy[2]</t>
         </is>
       </c>
       <c r="E329" t="inlineStr" s="2">
@@ -10870,14 +10870,14 @@
       </c>
       <c r="F329" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">夢みたいで…まだ、信じられません…</t>
+          <t xml:space="preserve">ま、また機会があれば…</t>
         </is>
       </c>
     </row>
     <row r="330" ht="40" customHeight="1">
       <c r="A330" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.polite.shy[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.polite.shy[1]</t>
         </is>
       </c>
       <c r="B330" t="inlineStr" s="2">
@@ -10887,12 +10887,12 @@
       </c>
       <c r="C330" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
         </is>
       </c>
       <c r="D330" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.polite.shy[1]</t>
+          <t xml:space="preserve">result_lose.polite.shy[1]</t>
         </is>
       </c>
       <c r="E330" t="inlineStr" s="2">
@@ -10902,14 +10902,14 @@
       </c>
       <c r="F330" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ま、負けてしまいました…ごめんなさい…</t>
+          <t xml:space="preserve">ま、負けてしまいました…ご、ごめんなさい…</t>
         </is>
       </c>
     </row>
     <row r="331" ht="40" customHeight="1">
       <c r="A331" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.polite.shy[2]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.polite.shy[2]</t>
         </is>
       </c>
       <c r="B331" t="inlineStr" s="2">
@@ -10919,12 +10919,12 @@
       </c>
       <c r="C331" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
         </is>
       </c>
       <c r="D331" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.polite.shy[2]</t>
+          <t xml:space="preserve">result_lose.polite.shy[2]</t>
         </is>
       </c>
       <c r="E331" t="inlineStr" s="2">
@@ -10934,14 +10934,14 @@
       </c>
       <c r="F331" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もっと…強くならないと…</t>
+          <t xml:space="preserve">次は…次こそは…</t>
         </is>
       </c>
     </row>
     <row r="332" ht="40" customHeight="1">
       <c r="A332" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.polite.shy[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.polite.shy[1]</t>
         </is>
       </c>
       <c r="B332" t="inlineStr" s="2">
@@ -10951,12 +10951,12 @@
       </c>
       <c r="C332" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
         </is>
       </c>
       <c r="D332" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.polite.shy[1]</t>
+          <t xml:space="preserve">result_win.polite.shy[1]</t>
         </is>
       </c>
       <c r="E332" t="inlineStr" s="2">
@@ -10966,14 +10966,14 @@
       </c>
       <c r="F332" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">か、勝てました…次もがんばります…</t>
+          <t xml:space="preserve">か、勝てました…団体のみなさんのおかげです…</t>
         </is>
       </c>
     </row>
     <row r="333" ht="40" customHeight="1">
       <c r="A333" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.polite.shy[2]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.polite.shy[2]</t>
         </is>
       </c>
       <c r="B333" t="inlineStr" s="2">
@@ -10983,12 +10983,12 @@
       </c>
       <c r="C333" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
         </is>
       </c>
       <c r="D333" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.polite.shy[2]</t>
+          <t xml:space="preserve">result_win.polite.shy[2]</t>
         </is>
       </c>
       <c r="E333" t="inlineStr" s="2">
@@ -10998,14 +10998,14 @@
       </c>
       <c r="F333" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一勝、できました…</t>
+          <t xml:space="preserve">応援、ありがとうございました…</t>
         </is>
       </c>
     </row>
     <row r="334" ht="40" customHeight="1">
       <c r="A334" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.polite.shy[1]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.polite.shy[1]</t>
         </is>
       </c>
       <c r="B334" t="inlineStr" s="2">
@@ -11015,12 +11015,12 @@
       </c>
       <c r="C334" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D334" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.polite.shy[1]</t>
+          <t xml:space="preserve">polite.shy[1]</t>
         </is>
       </c>
       <c r="E334" t="inlineStr" s="2">
@@ -11030,14 +11030,14 @@
       </c>
       <c r="F334" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">か、勝ち上がれました…信じられません…</t>
+          <t xml:space="preserve">か、勝てました…！ 団体のみなさまに恥じない試合が…できたでしょうか…</t>
         </is>
       </c>
     </row>
     <row r="335" ht="40" customHeight="1">
       <c r="A335" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.polite.shy[2]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.polite.shy[2]</t>
         </is>
       </c>
       <c r="B335" t="inlineStr" s="2">
@@ -11047,12 +11047,12 @@
       </c>
       <c r="C335" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D335" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.polite.shy[2]</t>
+          <t xml:space="preserve">polite.shy[2]</t>
         </is>
       </c>
       <c r="E335" t="inlineStr" s="2">
@@ -11062,14 +11062,14 @@
       </c>
       <c r="F335" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ…続けられるんですね…</t>
+          <t xml:space="preserve">か、勝たせていただきました…。団体のみなさまに…少しは恩返しできたでしょうか…</t>
         </is>
       </c>
     </row>
     <row r="336" ht="40" customHeight="1">
       <c r="A336" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.polite.shy[1]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.polite.shy[3]</t>
         </is>
       </c>
       <c r="B336" t="inlineStr" s="2">
@@ -11079,12 +11079,12 @@
       </c>
       <c r="C336" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D336" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.polite.shy[1]</t>
+          <t xml:space="preserve">polite.shy[3]</t>
         </is>
       </c>
       <c r="E336" t="inlineStr" s="2">
@@ -11094,14 +11094,14 @@
       </c>
       <c r="F336" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">け、決勝戦…ですか…し、信じられません…</t>
+          <t xml:space="preserve">か、勝てました…！ 団体のみなさまに恥じない試合が…できていたら嬉しいです…</t>
         </is>
       </c>
     </row>
     <row r="337" ht="40" customHeight="1">
       <c r="A337" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.polite.shy[2]</t>
+          <t xml:space="preserve">ENDING_LINES.fighter.polite.shy[1]</t>
         </is>
       </c>
       <c r="B337" t="inlineStr" s="2">
@@ -11111,29 +11111,29 @@
       </c>
       <c r="C337" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">ENDING_LINES</t>
         </is>
       </c>
       <c r="D337" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.polite.shy[2]</t>
+          <t xml:space="preserve">fighter.polite.shy[1]</t>
         </is>
       </c>
       <c r="E337" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">18 経営危機・エンディング</t>
         </is>
       </c>
       <c r="F337" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">夢みたい、です…</t>
+          <t xml:space="preserve">こ、これで…リングを降ります…あ、あの、応援してくれた皆さま…本当に、ありがとうございました…</t>
         </is>
       </c>
     </row>
     <row r="338" ht="40" customHeight="1">
       <c r="A338" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.polite.shy[1]</t>
+          <t xml:space="preserve">FA_GREETING_LINES.polite.shy[1]</t>
         </is>
       </c>
       <c r="B338" t="inlineStr" s="2">
@@ -11143,29 +11143,29 @@
       </c>
       <c r="C338" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
         </is>
       </c>
       <c r="D338" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.polite.shy[1]</t>
+          <t xml:space="preserve">polite.shy[1]</t>
         </is>
       </c>
       <c r="E338" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
         </is>
       </c>
       <c r="F338" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">き、緊張します…でも、精一杯やります…</t>
+          <t xml:space="preserve">あ、あの…契約してもらえて…感謝しています…！</t>
         </is>
       </c>
     </row>
     <row r="339" ht="40" customHeight="1">
       <c r="A339" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.polite.shy[2]</t>
+          <t xml:space="preserve">SCOUT_GREETING_LINES.polite.shy[1]</t>
         </is>
       </c>
       <c r="B339" t="inlineStr" s="2">
@@ -11175,603 +11175,27 @@
       </c>
       <c r="C339" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">SCOUT_GREETING_LINES</t>
         </is>
       </c>
       <c r="D339" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.polite.shy[2]</t>
+          <t xml:space="preserve">polite.shy[1]</t>
         </is>
       </c>
       <c r="E339" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
         </is>
       </c>
       <c r="F339" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふ、深呼吸…落ち着かないと…</t>
-        </is>
-      </c>
-    </row>
-    <row r="340" ht="40" customHeight="1">
-      <c r="A340" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.polite.shy[1]</t>
-        </is>
-      </c>
-      <c r="B340" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C340" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
-        </is>
-      </c>
-      <c r="D340" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">summon.polite.shy[1]</t>
-        </is>
-      </c>
-      <c r="E340" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
-        </is>
-      </c>
-      <c r="F340" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">え、わたしが…ジュニアトーナメントに…？ あ、あの、頑張ります…！</t>
-        </is>
-      </c>
-    </row>
-    <row r="341" ht="40" customHeight="1">
-      <c r="A341" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.polite.shy[2]</t>
-        </is>
-      </c>
-      <c r="B341" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C341" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
-        </is>
-      </c>
-      <c r="D341" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">summon.polite.shy[2]</t>
-        </is>
-      </c>
-      <c r="E341" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
-        </is>
-      </c>
-      <c r="F341" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">選んでいただいて…あ、ありがとうございます…</t>
-        </is>
-      </c>
-    </row>
-    <row r="342" ht="40" customHeight="1">
-      <c r="A342" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.polite.shy[1]</t>
-        </is>
-      </c>
-      <c r="B342" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C342" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
-        </is>
-      </c>
-      <c r="D342" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">polite.shy[1]</t>
-        </is>
-      </c>
-      <c r="E342" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
-        </is>
-      </c>
-      <c r="F342" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">あ、あの方が…相手なんですね…せ、精一杯戦います…</t>
-        </is>
-      </c>
-    </row>
-    <row r="343" ht="40" customHeight="1">
-      <c r="A343" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.polite.shy[1]</t>
-        </is>
-      </c>
-      <c r="B343" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C343" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
-        </is>
-      </c>
-      <c r="D343" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">polite.shy[1]</t>
-        </is>
-      </c>
-      <c r="E343" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
-        </is>
-      </c>
-      <c r="F343" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">か、勝てました……本当に……ありがとうございます……</t>
-        </is>
-      </c>
-    </row>
-    <row r="344" ht="40" customHeight="1">
-      <c r="A344" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.polite.shy[1]</t>
-        </is>
-      </c>
-      <c r="B344" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C344" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
-        </is>
-      </c>
-      <c r="D344" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">polite.shy[1]</t>
-        </is>
-      </c>
-      <c r="E344" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
-        </is>
-      </c>
-      <c r="F344" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">あ、あの…団体として、挑戦させてください…</t>
-        </is>
-      </c>
-    </row>
-    <row r="345" ht="40" customHeight="1">
-      <c r="A345" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.polite.shy[2]</t>
-        </is>
-      </c>
-      <c r="B345" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C345" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
-        </is>
-      </c>
-      <c r="D345" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">polite.shy[2]</t>
-        </is>
-      </c>
-      <c r="E345" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
-        </is>
-      </c>
-      <c r="F345" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">み、みんなで戦います…</t>
-        </is>
-      </c>
-    </row>
-    <row r="346" ht="40" customHeight="1">
-      <c r="A346" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.polite.shy[1]</t>
-        </is>
-      </c>
-      <c r="B346" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C346" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
-        </is>
-      </c>
-      <c r="D346" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">polite.shy[1]</t>
-        </is>
-      </c>
-      <c r="E346" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
-        </is>
-      </c>
-      <c r="F346" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">す、すみません…今回は、お断りさせてください…</t>
-        </is>
-      </c>
-    </row>
-    <row r="347" ht="40" customHeight="1">
-      <c r="A347" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.polite.shy[2]</t>
-        </is>
-      </c>
-      <c r="B347" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C347" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
-        </is>
-      </c>
-      <c r="D347" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">polite.shy[2]</t>
-        </is>
-      </c>
-      <c r="E347" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
-        </is>
-      </c>
-      <c r="F347" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">ま、また機会があれば…</t>
-        </is>
-      </c>
-    </row>
-    <row r="348" ht="40" customHeight="1">
-      <c r="A348" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.polite.shy[1]</t>
-        </is>
-      </c>
-      <c r="B348" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C348" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
-        </is>
-      </c>
-      <c r="D348" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">result_lose.polite.shy[1]</t>
-        </is>
-      </c>
-      <c r="E348" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
-        </is>
-      </c>
-      <c r="F348" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">ま、負けてしまいました…ご、ごめんなさい…</t>
-        </is>
-      </c>
-    </row>
-    <row r="349" ht="40" customHeight="1">
-      <c r="A349" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.polite.shy[2]</t>
-        </is>
-      </c>
-      <c r="B349" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C349" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
-        </is>
-      </c>
-      <c r="D349" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">result_lose.polite.shy[2]</t>
-        </is>
-      </c>
-      <c r="E349" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
-        </is>
-      </c>
-      <c r="F349" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">次は…次こそは…</t>
-        </is>
-      </c>
-    </row>
-    <row r="350" ht="40" customHeight="1">
-      <c r="A350" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.polite.shy[1]</t>
-        </is>
-      </c>
-      <c r="B350" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C350" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
-        </is>
-      </c>
-      <c r="D350" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">result_win.polite.shy[1]</t>
-        </is>
-      </c>
-      <c r="E350" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
-        </is>
-      </c>
-      <c r="F350" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">か、勝てました…団体のみなさんのおかげです…</t>
-        </is>
-      </c>
-    </row>
-    <row r="351" ht="40" customHeight="1">
-      <c r="A351" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.polite.shy[2]</t>
-        </is>
-      </c>
-      <c r="B351" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C351" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
-        </is>
-      </c>
-      <c r="D351" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">result_win.polite.shy[2]</t>
-        </is>
-      </c>
-      <c r="E351" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
-        </is>
-      </c>
-      <c r="F351" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">応援、ありがとうございました…</t>
-        </is>
-      </c>
-    </row>
-    <row r="352" ht="40" customHeight="1">
-      <c r="A352" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.polite.shy[1]</t>
-        </is>
-      </c>
-      <c r="B352" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C352" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
-        </is>
-      </c>
-      <c r="D352" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">polite.shy[1]</t>
-        </is>
-      </c>
-      <c r="E352" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
-        </is>
-      </c>
-      <c r="F352" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">か、勝てました…！ 団体のみなさまに恥じない試合が…できたでしょうか…</t>
-        </is>
-      </c>
-    </row>
-    <row r="353" ht="40" customHeight="1">
-      <c r="A353" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.polite.shy[2]</t>
-        </is>
-      </c>
-      <c r="B353" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C353" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
-        </is>
-      </c>
-      <c r="D353" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">polite.shy[2]</t>
-        </is>
-      </c>
-      <c r="E353" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
-        </is>
-      </c>
-      <c r="F353" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">か、勝たせていただきました…。団体のみなさまに…少しは恩返しできたでしょうか…</t>
-        </is>
-      </c>
-    </row>
-    <row r="354" ht="40" customHeight="1">
-      <c r="A354" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.polite.shy[3]</t>
-        </is>
-      </c>
-      <c r="B354" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C354" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
-        </is>
-      </c>
-      <c r="D354" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">polite.shy[3]</t>
-        </is>
-      </c>
-      <c r="E354" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
-        </is>
-      </c>
-      <c r="F354" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">か、勝てました…！ 団体のみなさまに恥じない試合が…できていたら嬉しいです…</t>
-        </is>
-      </c>
-    </row>
-    <row r="355" ht="40" customHeight="1">
-      <c r="A355" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.polite.shy[1]</t>
-        </is>
-      </c>
-      <c r="B355" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C355" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">ENDING_LINES</t>
-        </is>
-      </c>
-      <c r="D355" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">fighter.polite.shy[1]</t>
-        </is>
-      </c>
-      <c r="E355" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">18 経営危機・エンディング</t>
-        </is>
-      </c>
-      <c r="F355" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">こ、これで…リングを降ります…あ、あの、応援してくれた皆さま…本当に、ありがとうございました…</t>
-        </is>
-      </c>
-    </row>
-    <row r="356" ht="40" customHeight="1">
-      <c r="A356" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">FA_GREETING_LINES.polite.shy[1]</t>
-        </is>
-      </c>
-      <c r="B356" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C356" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">FA_GREETING_LINES</t>
-        </is>
-      </c>
-      <c r="D356" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">polite.shy[1]</t>
-        </is>
-      </c>
-      <c r="E356" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">19 ドラフト・スカウト</t>
-        </is>
-      </c>
-      <c r="F356" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">あ、あの…契約してもらえて…感謝しています…！</t>
-        </is>
-      </c>
-    </row>
-    <row r="357" ht="40" customHeight="1">
-      <c r="A357" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">SCOUT_GREETING_LINES.polite.shy[1]</t>
-        </is>
-      </c>
-      <c r="B357" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C357" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">SCOUT_GREETING_LINES</t>
-        </is>
-      </c>
-      <c r="D357" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">polite.shy[1]</t>
-        </is>
-      </c>
-      <c r="E357" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">19 ドラフト・スカウト</t>
-        </is>
-      </c>
-      <c r="F357" t="inlineStr" s="3">
-        <is>
           <t xml:space="preserve">あ、あの…お声がけ、光栄です…！</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H357"/>
+  <autoFilter ref="A1:H339"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/キャラタイプ別/丁寧×内気.xlsx
+++ b/セリフ編集/キャラタイプ別/丁寧×内気.xlsx
@@ -2422,7 +2422,7 @@
       </c>
       <c r="F65" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの……社長。あの方と、やらせていただけませんか。</t>
+          <t xml:space="preserve">あの……社長。三人で、挑ませていただけませんか。</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="F66" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">言いにくいのですが……どうしても、あの方と。</t>
+          <t xml:space="preserve">言いにくいのですが……どうしても、三人であちらへ。</t>
         </is>
       </c>
     </row>
